--- a/2lit_center.xlsx
+++ b/2lit_center.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="281">
   <si>
     <t>ناجح ✓</t>
   </si>
@@ -755,6 +755,18 @@
     <t>Ayten Saleh Mostafa</t>
   </si>
   <si>
+    <t>2026-03-01 19:16</t>
+  </si>
+  <si>
+    <t>01151728245</t>
+  </si>
+  <si>
+    <t>Hshhzhxbheh@gmail.com</t>
+  </si>
+  <si>
+    <t>يوسف شريف عادل</t>
+  </si>
+  <si>
     <t>2026-03-01 19:08</t>
   </si>
   <si>
@@ -767,6 +779,30 @@
     <t>Abdelrhman hossni saad</t>
   </si>
   <si>
+    <t>2026-03-01 19:12</t>
+  </si>
+  <si>
+    <t>01125776411</t>
+  </si>
+  <si>
+    <t>radwanosama414@gmail.com</t>
+  </si>
+  <si>
+    <t>Radwan Osama</t>
+  </si>
+  <si>
+    <t>2026-03-01 19:19</t>
+  </si>
+  <si>
+    <t>01014956583</t>
+  </si>
+  <si>
+    <t>mennaebrahim543@gmail.com</t>
+  </si>
+  <si>
+    <t>Menna Ibrahim</t>
+  </si>
+  <si>
     <t>الحالة</t>
   </si>
   <si>
@@ -821,7 +857,7 @@
     <t>الدرجة الكاملة: 10 | درجة النجاح: 5.00</t>
   </si>
   <si>
-    <t>تاريخ التصدير: 2026-03-01 19:10</t>
+    <t>تاريخ التصدير: 2026-03-01 19:21</t>
   </si>
 </sst>
 </file>
@@ -1209,7 +1245,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:P65"/>
+  <dimension ref="A1:P68"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="true" style="0"/>
@@ -1232,67 +1268,67 @@
   <sheetData>
     <row r="1" spans="1:16">
       <c r="A1" s="3" t="s">
-        <v>266</v>
+        <v>278</v>
       </c>
     </row>
     <row r="2" spans="1:16">
       <c r="A2" s="3" t="s">
-        <v>267</v>
+        <v>279</v>
       </c>
     </row>
     <row r="3" spans="1:16">
       <c r="A3" s="3" t="s">
-        <v>268</v>
+        <v>280</v>
       </c>
     </row>
     <row r="4" spans="1:16">
       <c r="A4" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="M4" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="N4" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="O4" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="P4" s="1" t="s">
         <v>262</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="L4" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="M4" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="N4" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="O4" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="P4" s="1" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1300,13 +1336,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>248</v>
+        <v>260</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>247</v>
+        <v>259</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>3</v>
@@ -1334,10 +1370,10 @@
         <v>5</v>
       </c>
       <c r="N5" s="2">
-        <v>3.2</v>
+        <v>5.8</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="P5" s="2" t="s">
         <v>0</v>
@@ -1348,13 +1384,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>3</v>
@@ -1363,29 +1399,27 @@
         <v>1</v>
       </c>
       <c r="G6" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H6" s="2">
         <v>10.0</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="J6" s="2">
-        <v>4</v>
-      </c>
-      <c r="K6" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K6" s="2"/>
       <c r="L6" s="2"/>
       <c r="M6" s="2">
         <v>5</v>
       </c>
       <c r="N6" s="2">
-        <v>12.48</v>
+        <v>3.17</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="P6" s="2" t="s">
         <v>0</v>
@@ -1396,13 +1430,13 @@
         <v>3</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>240</v>
+        <v>252</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>3</v>
@@ -1430,10 +1464,10 @@
         <v>5</v>
       </c>
       <c r="N7" s="2">
-        <v>4.22</v>
+        <v>3.2</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>238</v>
+        <v>250</v>
       </c>
       <c r="P7" s="2" t="s">
         <v>0</v>
@@ -1444,13 +1478,13 @@
         <v>4</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>237</v>
+        <v>249</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>3</v>
@@ -1459,29 +1493,29 @@
         <v>1</v>
       </c>
       <c r="G8" s="2">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="H8" s="2">
         <v>10.0</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="J8" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K8" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L8" s="2"/>
       <c r="M8" s="2">
         <v>5</v>
       </c>
       <c r="N8" s="2">
-        <v>8.42</v>
+        <v>14.28</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="P8" s="2" t="s">
         <v>0</v>
@@ -1492,13 +1526,13 @@
         <v>5</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>232</v>
+        <v>244</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>231</v>
+        <v>243</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>3</v>
@@ -1526,10 +1560,10 @@
         <v>5</v>
       </c>
       <c r="N9" s="2">
-        <v>7.37</v>
+        <v>12.48</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>192</v>
+        <v>242</v>
       </c>
       <c r="P9" s="2" t="s">
         <v>0</v>
@@ -1540,13 +1574,13 @@
         <v>6</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>230</v>
+        <v>241</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>229</v>
+        <v>240</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>228</v>
+        <v>239</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>3</v>
@@ -1555,27 +1589,29 @@
         <v>1</v>
       </c>
       <c r="G10" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H10" s="2">
         <v>10.0</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="J10" s="2">
-        <v>5</v>
-      </c>
-      <c r="K10" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K10" s="2">
+        <v>1</v>
+      </c>
       <c r="L10" s="2"/>
       <c r="M10" s="2">
         <v>5</v>
       </c>
       <c r="N10" s="2">
-        <v>23.67</v>
+        <v>4.22</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>227</v>
+        <v>238</v>
       </c>
       <c r="P10" s="2" t="s">
         <v>0</v>
@@ -1586,13 +1622,13 @@
         <v>7</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>225</v>
+        <v>236</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>224</v>
+        <v>235</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>3</v>
@@ -1601,29 +1637,29 @@
         <v>1</v>
       </c>
       <c r="G11" s="2">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
       <c r="H11" s="2">
         <v>10.0</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="J11" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K11" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L11" s="2"/>
       <c r="M11" s="2">
         <v>5</v>
       </c>
       <c r="N11" s="2">
-        <v>15.78</v>
+        <v>8.42</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>223</v>
+        <v>234</v>
       </c>
       <c r="P11" s="2" t="s">
         <v>0</v>
@@ -1634,13 +1670,13 @@
         <v>8</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>222</v>
+        <v>233</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>3</v>
@@ -1649,27 +1685,29 @@
         <v>1</v>
       </c>
       <c r="G12" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H12" s="2">
         <v>10.0</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="J12" s="2">
-        <v>5</v>
-      </c>
-      <c r="K12" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K12" s="2">
+        <v>1</v>
+      </c>
       <c r="L12" s="2"/>
       <c r="M12" s="2">
         <v>5</v>
       </c>
       <c r="N12" s="2">
-        <v>7.02</v>
+        <v>7.37</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>219</v>
+        <v>192</v>
       </c>
       <c r="P12" s="2" t="s">
         <v>0</v>
@@ -1680,13 +1718,13 @@
         <v>9</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>218</v>
+        <v>230</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>217</v>
+        <v>229</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>3</v>
@@ -1695,29 +1733,27 @@
         <v>1</v>
       </c>
       <c r="G13" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H13" s="2">
         <v>10.0</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="J13" s="2">
-        <v>4</v>
-      </c>
-      <c r="K13" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K13" s="2"/>
       <c r="L13" s="2"/>
       <c r="M13" s="2">
         <v>5</v>
       </c>
       <c r="N13" s="2">
-        <v>7.05</v>
+        <v>23.67</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>215</v>
+        <v>227</v>
       </c>
       <c r="P13" s="2" t="s">
         <v>0</v>
@@ -1728,13 +1764,13 @@
         <v>10</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>213</v>
+        <v>225</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>212</v>
+        <v>224</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>3</v>
@@ -1743,32 +1779,32 @@
         <v>1</v>
       </c>
       <c r="G14" s="2">
-        <v>2.0</v>
+        <v>8.0</v>
       </c>
       <c r="H14" s="2">
         <v>10.0</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>163</v>
+        <v>2</v>
       </c>
       <c r="J14" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K14" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L14" s="2"/>
       <c r="M14" s="2">
         <v>5</v>
       </c>
       <c r="N14" s="2">
-        <v>5.35</v>
+        <v>15.78</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="P14" s="2" t="s">
-        <v>161</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -1776,44 +1812,42 @@
         <v>11</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>210</v>
+        <v>222</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>209</v>
+        <v>221</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>208</v>
+        <v>220</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F15" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G15" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H15" s="2">
         <v>10.0</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="J15" s="2">
-        <v>4</v>
-      </c>
-      <c r="K15" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K15" s="2"/>
       <c r="L15" s="2"/>
       <c r="M15" s="2">
         <v>5</v>
       </c>
       <c r="N15" s="2">
-        <v>3.77</v>
+        <v>7.02</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>207</v>
+        <v>219</v>
       </c>
       <c r="P15" s="2" t="s">
         <v>0</v>
@@ -1824,13 +1858,13 @@
         <v>12</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>205</v>
+        <v>217</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>204</v>
+        <v>216</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>3</v>
@@ -1858,10 +1892,10 @@
         <v>5</v>
       </c>
       <c r="N16" s="2">
-        <v>11.42</v>
+        <v>7.05</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>203</v>
+        <v>215</v>
       </c>
       <c r="P16" s="2" t="s">
         <v>0</v>
@@ -1872,13 +1906,13 @@
         <v>13</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>202</v>
+        <v>214</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>201</v>
+        <v>213</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>200</v>
+        <v>212</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>3</v>
@@ -1887,32 +1921,32 @@
         <v>1</v>
       </c>
       <c r="G17" s="2">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
       <c r="H17" s="2">
         <v>10.0</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>16</v>
+        <v>163</v>
       </c>
       <c r="J17" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K17" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L17" s="2"/>
       <c r="M17" s="2">
         <v>5</v>
       </c>
       <c r="N17" s="2">
-        <v>3.57</v>
+        <v>5.35</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="P17" s="2" t="s">
-        <v>0</v>
+        <v>161</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -1920,19 +1954,19 @@
         <v>14</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>198</v>
+        <v>210</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>197</v>
+        <v>209</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>196</v>
+        <v>208</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F18" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G18" s="2">
         <v>8.0</v>
@@ -1954,10 +1988,10 @@
         <v>5</v>
       </c>
       <c r="N18" s="2">
-        <v>7.5</v>
+        <v>3.77</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>184</v>
+        <v>207</v>
       </c>
       <c r="P18" s="2" t="s">
         <v>0</v>
@@ -1968,13 +2002,13 @@
         <v>15</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>195</v>
+        <v>206</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>193</v>
+        <v>204</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>3</v>
@@ -2002,10 +2036,10 @@
         <v>5</v>
       </c>
       <c r="N19" s="2">
-        <v>39.38</v>
+        <v>11.42</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>192</v>
+        <v>203</v>
       </c>
       <c r="P19" s="2" t="s">
         <v>0</v>
@@ -2016,13 +2050,13 @@
         <v>16</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>191</v>
+        <v>202</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>190</v>
+        <v>201</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>189</v>
+        <v>200</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>3</v>
@@ -2031,29 +2065,29 @@
         <v>1</v>
       </c>
       <c r="G20" s="2">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
       <c r="H20" s="2">
         <v>10.0</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="J20" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K20" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L20" s="2"/>
       <c r="M20" s="2">
         <v>5</v>
       </c>
       <c r="N20" s="2">
-        <v>11.68</v>
+        <v>3.57</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>188</v>
+        <v>199</v>
       </c>
       <c r="P20" s="2" t="s">
         <v>0</v>
@@ -2064,13 +2098,13 @@
         <v>17</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>187</v>
+        <v>198</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>186</v>
+        <v>197</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>185</v>
+        <v>196</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>3</v>
@@ -2098,7 +2132,7 @@
         <v>5</v>
       </c>
       <c r="N21" s="2">
-        <v>15.92</v>
+        <v>7.5</v>
       </c>
       <c r="O21" s="2" t="s">
         <v>184</v>
@@ -2112,13 +2146,13 @@
         <v>18</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>3</v>
@@ -2146,10 +2180,10 @@
         <v>5</v>
       </c>
       <c r="N22" s="2">
-        <v>6.17</v>
+        <v>39.38</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="P22" s="2" t="s">
         <v>0</v>
@@ -2160,13 +2194,13 @@
         <v>19</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>177</v>
+        <v>189</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>3</v>
@@ -2175,27 +2209,29 @@
         <v>1</v>
       </c>
       <c r="G23" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H23" s="2">
         <v>10.0</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="J23" s="2">
-        <v>5</v>
-      </c>
-      <c r="K23" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K23" s="2">
+        <v>1</v>
+      </c>
       <c r="L23" s="2"/>
       <c r="M23" s="2">
         <v>5</v>
       </c>
       <c r="N23" s="2">
-        <v>5.92</v>
+        <v>11.68</v>
       </c>
       <c r="O23" s="2" t="s">
-        <v>176</v>
+        <v>188</v>
       </c>
       <c r="P23" s="2" t="s">
         <v>0</v>
@@ -2206,13 +2242,13 @@
         <v>20</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>174</v>
+        <v>186</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>3</v>
@@ -2221,32 +2257,32 @@
         <v>1</v>
       </c>
       <c r="G24" s="2">
-        <v>4.0</v>
+        <v>8.0</v>
       </c>
       <c r="H24" s="2">
         <v>10.0</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>172</v>
+        <v>2</v>
       </c>
       <c r="J24" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K24" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L24" s="2"/>
       <c r="M24" s="2">
         <v>5</v>
       </c>
       <c r="N24" s="2">
-        <v>5.95</v>
+        <v>15.92</v>
       </c>
       <c r="O24" s="2" t="s">
-        <v>171</v>
+        <v>184</v>
       </c>
       <c r="P24" s="2" t="s">
-        <v>161</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -2254,13 +2290,13 @@
         <v>21</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>169</v>
+        <v>182</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>3</v>
@@ -2269,27 +2305,29 @@
         <v>1</v>
       </c>
       <c r="G25" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H25" s="2">
         <v>10.0</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="J25" s="2">
-        <v>5</v>
-      </c>
-      <c r="K25" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K25" s="2">
+        <v>1</v>
+      </c>
       <c r="L25" s="2"/>
       <c r="M25" s="2">
         <v>5</v>
       </c>
       <c r="N25" s="2">
-        <v>9.08</v>
+        <v>6.17</v>
       </c>
       <c r="O25" s="2" t="s">
-        <v>167</v>
+        <v>180</v>
       </c>
       <c r="P25" s="2" t="s">
         <v>0</v>
@@ -2300,13 +2338,13 @@
         <v>22</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>166</v>
+        <v>179</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>165</v>
+        <v>178</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>164</v>
+        <v>177</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>3</v>
@@ -2315,32 +2353,30 @@
         <v>1</v>
       </c>
       <c r="G26" s="2">
-        <v>2.0</v>
+        <v>10.0</v>
       </c>
       <c r="H26" s="2">
         <v>10.0</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>163</v>
+        <v>29</v>
       </c>
       <c r="J26" s="2">
-        <v>1</v>
-      </c>
-      <c r="K26" s="2">
-        <v>4</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K26" s="2"/>
       <c r="L26" s="2"/>
       <c r="M26" s="2">
         <v>5</v>
       </c>
       <c r="N26" s="2">
-        <v>10.48</v>
+        <v>5.92</v>
       </c>
       <c r="O26" s="2" t="s">
-        <v>162</v>
+        <v>176</v>
       </c>
       <c r="P26" s="2" t="s">
-        <v>161</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -2348,13 +2384,13 @@
         <v>23</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>3</v>
@@ -2363,32 +2399,32 @@
         <v>1</v>
       </c>
       <c r="G27" s="2">
-        <v>8.0</v>
+        <v>4.0</v>
       </c>
       <c r="H27" s="2">
         <v>10.0</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>2</v>
+        <v>172</v>
       </c>
       <c r="J27" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K27" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L27" s="2"/>
       <c r="M27" s="2">
         <v>5</v>
       </c>
       <c r="N27" s="2">
-        <v>13.42</v>
+        <v>5.95</v>
       </c>
       <c r="O27" s="2" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
       <c r="P27" s="2" t="s">
-        <v>0</v>
+        <v>161</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -2396,13 +2432,13 @@
         <v>24</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>156</v>
+        <v>170</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>155</v>
+        <v>169</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>154</v>
+        <v>168</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>3</v>
@@ -2411,29 +2447,27 @@
         <v>1</v>
       </c>
       <c r="G28" s="2">
-        <v>6.0</v>
+        <v>10.0</v>
       </c>
       <c r="H28" s="2">
         <v>10.0</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="J28" s="2">
-        <v>3</v>
-      </c>
-      <c r="K28" s="2">
-        <v>2</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K28" s="2"/>
       <c r="L28" s="2"/>
       <c r="M28" s="2">
         <v>5</v>
       </c>
       <c r="N28" s="2">
-        <v>2.57</v>
+        <v>9.08</v>
       </c>
       <c r="O28" s="2" t="s">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="P28" s="2" t="s">
         <v>0</v>
@@ -2444,13 +2478,13 @@
         <v>25</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>152</v>
+        <v>166</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>151</v>
+        <v>165</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>150</v>
+        <v>164</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>3</v>
@@ -2459,30 +2493,32 @@
         <v>1</v>
       </c>
       <c r="G29" s="2">
-        <v>10.0</v>
+        <v>2.0</v>
       </c>
       <c r="H29" s="2">
         <v>10.0</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>29</v>
+        <v>163</v>
       </c>
       <c r="J29" s="2">
-        <v>5</v>
-      </c>
-      <c r="K29" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="K29" s="2">
+        <v>4</v>
+      </c>
       <c r="L29" s="2"/>
       <c r="M29" s="2">
         <v>5</v>
       </c>
       <c r="N29" s="2">
-        <v>1.65</v>
+        <v>10.48</v>
       </c>
       <c r="O29" s="2" t="s">
-        <v>149</v>
+        <v>162</v>
       </c>
       <c r="P29" s="2" t="s">
-        <v>0</v>
+        <v>161</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -2490,13 +2526,13 @@
         <v>26</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>148</v>
+        <v>160</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>146</v>
+        <v>158</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>3</v>
@@ -2505,29 +2541,29 @@
         <v>1</v>
       </c>
       <c r="G30" s="2">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="H30" s="2">
         <v>10.0</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="J30" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K30" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L30" s="2"/>
       <c r="M30" s="2">
         <v>5</v>
       </c>
       <c r="N30" s="2">
-        <v>12.1</v>
+        <v>13.42</v>
       </c>
       <c r="O30" s="2" t="s">
-        <v>145</v>
+        <v>157</v>
       </c>
       <c r="P30" s="2" t="s">
         <v>0</v>
@@ -2538,13 +2574,13 @@
         <v>27</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>144</v>
+        <v>156</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>143</v>
+        <v>155</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>142</v>
+        <v>154</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>3</v>
@@ -2572,10 +2608,10 @@
         <v>5</v>
       </c>
       <c r="N31" s="2">
-        <v>18.58</v>
+        <v>2.57</v>
       </c>
       <c r="O31" s="2" t="s">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="P31" s="2" t="s">
         <v>0</v>
@@ -2586,13 +2622,13 @@
         <v>28</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>140</v>
+        <v>152</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>3</v>
@@ -2618,10 +2654,10 @@
         <v>5</v>
       </c>
       <c r="N32" s="2">
-        <v>18.03</v>
+        <v>1.65</v>
       </c>
       <c r="O32" s="2" t="s">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="P32" s="2" t="s">
         <v>0</v>
@@ -2632,13 +2668,13 @@
         <v>29</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>3</v>
@@ -2647,29 +2683,29 @@
         <v>1</v>
       </c>
       <c r="G33" s="2">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
       <c r="H33" s="2">
         <v>10.0</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="J33" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K33" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L33" s="2"/>
       <c r="M33" s="2">
         <v>5</v>
       </c>
       <c r="N33" s="2">
-        <v>9.68</v>
+        <v>12.1</v>
       </c>
       <c r="O33" s="2" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="P33" s="2" t="s">
         <v>0</v>
@@ -2680,13 +2716,13 @@
         <v>30</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>3</v>
@@ -2714,10 +2750,10 @@
         <v>5</v>
       </c>
       <c r="N34" s="2">
-        <v>14.13</v>
+        <v>18.58</v>
       </c>
       <c r="O34" s="2" t="s">
-        <v>129</v>
+        <v>141</v>
       </c>
       <c r="P34" s="2" t="s">
         <v>0</v>
@@ -2728,13 +2764,13 @@
         <v>31</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>127</v>
+        <v>139</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>3</v>
@@ -2743,29 +2779,27 @@
         <v>1</v>
       </c>
       <c r="G35" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H35" s="2">
         <v>10.0</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="J35" s="2">
-        <v>4</v>
-      </c>
-      <c r="K35" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K35" s="2"/>
       <c r="L35" s="2"/>
       <c r="M35" s="2">
         <v>5</v>
       </c>
       <c r="N35" s="2">
-        <v>11.45</v>
+        <v>18.03</v>
       </c>
       <c r="O35" s="2" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="P35" s="2" t="s">
         <v>0</v>
@@ -2776,13 +2810,13 @@
         <v>32</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>3</v>
@@ -2810,10 +2844,10 @@
         <v>5</v>
       </c>
       <c r="N36" s="2">
-        <v>12.55</v>
+        <v>9.68</v>
       </c>
       <c r="O36" s="2" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="P36" s="2" t="s">
         <v>0</v>
@@ -2824,13 +2858,13 @@
         <v>33</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>3</v>
@@ -2839,27 +2873,29 @@
         <v>1</v>
       </c>
       <c r="G37" s="2">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
       <c r="H37" s="2">
         <v>10.0</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="J37" s="2">
-        <v>5</v>
-      </c>
-      <c r="K37" s="2"/>
+        <v>3</v>
+      </c>
+      <c r="K37" s="2">
+        <v>2</v>
+      </c>
       <c r="L37" s="2"/>
       <c r="M37" s="2">
         <v>5</v>
       </c>
       <c r="N37" s="2">
-        <v>6.58</v>
+        <v>14.13</v>
       </c>
       <c r="O37" s="2" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="P37" s="2" t="s">
         <v>0</v>
@@ -2870,13 +2906,13 @@
         <v>34</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>3</v>
@@ -2904,10 +2940,10 @@
         <v>5</v>
       </c>
       <c r="N38" s="2">
-        <v>18.78</v>
+        <v>11.45</v>
       </c>
       <c r="O38" s="2" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="P38" s="2" t="s">
         <v>0</v>
@@ -2918,13 +2954,13 @@
         <v>35</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>3</v>
@@ -2952,10 +2988,10 @@
         <v>5</v>
       </c>
       <c r="N39" s="2">
-        <v>12.03</v>
+        <v>12.55</v>
       </c>
       <c r="O39" s="2" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="P39" s="2" t="s">
         <v>0</v>
@@ -2966,13 +3002,13 @@
         <v>36</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>3</v>
@@ -2981,29 +3017,27 @@
         <v>1</v>
       </c>
       <c r="G40" s="2">
-        <v>6.0</v>
+        <v>10.0</v>
       </c>
       <c r="H40" s="2">
         <v>10.0</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="J40" s="2">
-        <v>3</v>
-      </c>
-      <c r="K40" s="2">
-        <v>2</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K40" s="2"/>
       <c r="L40" s="2"/>
       <c r="M40" s="2">
         <v>5</v>
       </c>
       <c r="N40" s="2">
-        <v>25.12</v>
+        <v>6.58</v>
       </c>
       <c r="O40" s="2" t="s">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="P40" s="2" t="s">
         <v>0</v>
@@ -3014,13 +3048,13 @@
         <v>37</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>3</v>
@@ -3029,29 +3063,29 @@
         <v>1</v>
       </c>
       <c r="G41" s="2">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="H41" s="2">
         <v>10.0</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="J41" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K41" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L41" s="2"/>
       <c r="M41" s="2">
         <v>5</v>
       </c>
       <c r="N41" s="2">
-        <v>16.98</v>
+        <v>18.78</v>
       </c>
       <c r="O41" s="2" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="P41" s="2" t="s">
         <v>0</v>
@@ -3062,13 +3096,13 @@
         <v>38</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>3</v>
@@ -3077,27 +3111,29 @@
         <v>1</v>
       </c>
       <c r="G42" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H42" s="2">
         <v>10.0</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="J42" s="2">
-        <v>5</v>
-      </c>
-      <c r="K42" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K42" s="2">
+        <v>1</v>
+      </c>
       <c r="L42" s="2"/>
       <c r="M42" s="2">
         <v>5</v>
       </c>
       <c r="N42" s="2">
-        <v>1.45</v>
+        <v>12.03</v>
       </c>
       <c r="O42" s="2" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="P42" s="2" t="s">
         <v>0</v>
@@ -3108,42 +3144,44 @@
         <v>39</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F43" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G43" s="2">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
       <c r="H43" s="2">
         <v>10.0</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="J43" s="2">
-        <v>5</v>
-      </c>
-      <c r="K43" s="2"/>
+        <v>3</v>
+      </c>
+      <c r="K43" s="2">
+        <v>2</v>
+      </c>
       <c r="L43" s="2"/>
       <c r="M43" s="2">
         <v>5</v>
       </c>
       <c r="N43" s="2">
-        <v>6.18</v>
+        <v>25.12</v>
       </c>
       <c r="O43" s="2" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="P43" s="2" t="s">
         <v>0</v>
@@ -3154,13 +3192,13 @@
         <v>40</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>3</v>
@@ -3169,27 +3207,29 @@
         <v>1</v>
       </c>
       <c r="G44" s="2">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
       <c r="H44" s="2">
         <v>10.0</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="J44" s="2">
-        <v>5</v>
-      </c>
-      <c r="K44" s="2"/>
+        <v>3</v>
+      </c>
+      <c r="K44" s="2">
+        <v>2</v>
+      </c>
       <c r="L44" s="2"/>
       <c r="M44" s="2">
         <v>5</v>
       </c>
       <c r="N44" s="2">
-        <v>6.13</v>
+        <v>16.98</v>
       </c>
       <c r="O44" s="2" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="P44" s="2" t="s">
         <v>0</v>
@@ -3200,13 +3240,13 @@
         <v>41</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>3</v>
@@ -3215,29 +3255,27 @@
         <v>1</v>
       </c>
       <c r="G45" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H45" s="2">
         <v>10.0</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="J45" s="2">
-        <v>4</v>
-      </c>
-      <c r="K45" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K45" s="2"/>
       <c r="L45" s="2"/>
       <c r="M45" s="2">
         <v>5</v>
       </c>
       <c r="N45" s="2">
-        <v>2.4</v>
+        <v>1.45</v>
       </c>
       <c r="O45" s="2" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="P45" s="2" t="s">
         <v>0</v>
@@ -3248,44 +3286,42 @@
         <v>42</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F46" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G46" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H46" s="2">
         <v>10.0</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="J46" s="2">
-        <v>4</v>
-      </c>
-      <c r="K46" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K46" s="2"/>
       <c r="L46" s="2"/>
       <c r="M46" s="2">
         <v>5</v>
       </c>
       <c r="N46" s="2">
-        <v>15.75</v>
+        <v>6.18</v>
       </c>
       <c r="O46" s="2" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="P46" s="2" t="s">
         <v>0</v>
@@ -3296,13 +3332,13 @@
         <v>43</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>3</v>
@@ -3328,10 +3364,10 @@
         <v>5</v>
       </c>
       <c r="N47" s="2">
-        <v>2.17</v>
+        <v>6.13</v>
       </c>
       <c r="O47" s="2" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="P47" s="2" t="s">
         <v>0</v>
@@ -3342,13 +3378,13 @@
         <v>44</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>3</v>
@@ -3357,29 +3393,29 @@
         <v>1</v>
       </c>
       <c r="G48" s="2">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="H48" s="2">
         <v>10.0</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="J48" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K48" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L48" s="2"/>
       <c r="M48" s="2">
         <v>5</v>
       </c>
       <c r="N48" s="2">
-        <v>9.5</v>
+        <v>2.4</v>
       </c>
       <c r="O48" s="2" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="P48" s="2" t="s">
         <v>0</v>
@@ -3390,13 +3426,13 @@
         <v>45</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>3</v>
@@ -3405,27 +3441,29 @@
         <v>1</v>
       </c>
       <c r="G49" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H49" s="2">
         <v>10.0</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="J49" s="2">
-        <v>5</v>
-      </c>
-      <c r="K49" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K49" s="2">
+        <v>1</v>
+      </c>
       <c r="L49" s="2"/>
       <c r="M49" s="2">
         <v>5</v>
       </c>
       <c r="N49" s="2">
-        <v>10.75</v>
+        <v>15.75</v>
       </c>
       <c r="O49" s="2" t="s">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="P49" s="2" t="s">
         <v>0</v>
@@ -3436,44 +3474,42 @@
         <v>46</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F50" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G50" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H50" s="2">
         <v>10.0</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="J50" s="2">
-        <v>4</v>
-      </c>
-      <c r="K50" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K50" s="2"/>
       <c r="L50" s="2"/>
       <c r="M50" s="2">
         <v>5</v>
       </c>
       <c r="N50" s="2">
-        <v>23.17</v>
+        <v>2.17</v>
       </c>
       <c r="O50" s="2" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="P50" s="2" t="s">
         <v>0</v>
@@ -3484,42 +3520,44 @@
         <v>47</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F51" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G51" s="2">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
       <c r="H51" s="2">
         <v>10.0</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="J51" s="2">
-        <v>5</v>
-      </c>
-      <c r="K51" s="2"/>
+        <v>3</v>
+      </c>
+      <c r="K51" s="2">
+        <v>2</v>
+      </c>
       <c r="L51" s="2"/>
       <c r="M51" s="2">
         <v>5</v>
       </c>
       <c r="N51" s="2">
-        <v>5.47</v>
+        <v>9.5</v>
       </c>
       <c r="O51" s="2" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="P51" s="2" t="s">
         <v>0</v>
@@ -3530,13 +3568,13 @@
         <v>48</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>3</v>
@@ -3545,29 +3583,27 @@
         <v>1</v>
       </c>
       <c r="G52" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H52" s="2">
         <v>10.0</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="J52" s="2">
-        <v>4</v>
-      </c>
-      <c r="K52" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K52" s="2"/>
       <c r="L52" s="2"/>
       <c r="M52" s="2">
         <v>5</v>
       </c>
       <c r="N52" s="2">
-        <v>15.8</v>
+        <v>10.75</v>
       </c>
       <c r="O52" s="2" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="P52" s="2" t="s">
         <v>0</v>
@@ -3578,42 +3614,44 @@
         <v>49</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F53" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G53" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H53" s="2">
         <v>10.0</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="J53" s="2">
-        <v>5</v>
-      </c>
-      <c r="K53" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K53" s="2">
+        <v>1</v>
+      </c>
       <c r="L53" s="2"/>
       <c r="M53" s="2">
         <v>5</v>
       </c>
       <c r="N53" s="2">
-        <v>4.07</v>
+        <v>23.17</v>
       </c>
       <c r="O53" s="2" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="P53" s="2" t="s">
         <v>0</v>
@@ -3624,44 +3662,42 @@
         <v>50</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F54" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G54" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H54" s="2">
         <v>10.0</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="J54" s="2">
-        <v>4</v>
-      </c>
-      <c r="K54" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K54" s="2"/>
       <c r="L54" s="2"/>
       <c r="M54" s="2">
         <v>5</v>
       </c>
       <c r="N54" s="2">
-        <v>21.8</v>
+        <v>5.47</v>
       </c>
       <c r="O54" s="2" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="P54" s="2" t="s">
         <v>0</v>
@@ -3672,13 +3708,13 @@
         <v>51</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>3</v>
@@ -3706,10 +3742,10 @@
         <v>5</v>
       </c>
       <c r="N55" s="2">
-        <v>10.12</v>
+        <v>15.8</v>
       </c>
       <c r="O55" s="2" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="P55" s="2" t="s">
         <v>0</v>
@@ -3720,13 +3756,13 @@
         <v>52</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>3</v>
@@ -3752,10 +3788,10 @@
         <v>5</v>
       </c>
       <c r="N56" s="2">
-        <v>13.48</v>
+        <v>4.07</v>
       </c>
       <c r="O56" s="2" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="P56" s="2" t="s">
         <v>0</v>
@@ -3766,13 +3802,13 @@
         <v>53</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>3</v>
@@ -3800,10 +3836,10 @@
         <v>5</v>
       </c>
       <c r="N57" s="2">
-        <v>10.6</v>
+        <v>21.8</v>
       </c>
       <c r="O57" s="2" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="P57" s="2" t="s">
         <v>0</v>
@@ -3814,13 +3850,13 @@
         <v>54</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>3</v>
@@ -3829,27 +3865,29 @@
         <v>1</v>
       </c>
       <c r="G58" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H58" s="2">
         <v>10.0</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="J58" s="2">
-        <v>5</v>
-      </c>
-      <c r="K58" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K58" s="2">
+        <v>1</v>
+      </c>
       <c r="L58" s="2"/>
       <c r="M58" s="2">
         <v>5</v>
       </c>
       <c r="N58" s="2">
-        <v>12.52</v>
+        <v>10.12</v>
       </c>
       <c r="O58" s="2" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="P58" s="2" t="s">
         <v>0</v>
@@ -3860,13 +3898,13 @@
         <v>55</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>3</v>
@@ -3892,10 +3930,10 @@
         <v>5</v>
       </c>
       <c r="N59" s="2">
-        <v>15.33</v>
+        <v>13.48</v>
       </c>
       <c r="O59" s="2" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="P59" s="2" t="s">
         <v>0</v>
@@ -3906,13 +3944,13 @@
         <v>56</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>3</v>
@@ -3940,10 +3978,10 @@
         <v>5</v>
       </c>
       <c r="N60" s="2">
-        <v>9.45</v>
+        <v>10.6</v>
       </c>
       <c r="O60" s="2" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="P60" s="2" t="s">
         <v>0</v>
@@ -3954,13 +3992,13 @@
         <v>57</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>3</v>
@@ -3969,29 +4007,27 @@
         <v>1</v>
       </c>
       <c r="G61" s="2">
-        <v>6.0</v>
+        <v>10.0</v>
       </c>
       <c r="H61" s="2">
         <v>10.0</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="J61" s="2">
-        <v>3</v>
-      </c>
-      <c r="K61" s="2">
-        <v>2</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K61" s="2"/>
       <c r="L61" s="2"/>
       <c r="M61" s="2">
         <v>5</v>
       </c>
       <c r="N61" s="2">
-        <v>3.6</v>
+        <v>12.52</v>
       </c>
       <c r="O61" s="2" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="P61" s="2" t="s">
         <v>0</v>
@@ -4002,13 +4038,13 @@
         <v>58</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>3</v>
@@ -4017,29 +4053,27 @@
         <v>1</v>
       </c>
       <c r="G62" s="2">
-        <v>6.0</v>
+        <v>10.0</v>
       </c>
       <c r="H62" s="2">
         <v>10.0</v>
       </c>
       <c r="I62" s="2" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="J62" s="2">
-        <v>3</v>
-      </c>
-      <c r="K62" s="2">
-        <v>2</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K62" s="2"/>
       <c r="L62" s="2"/>
       <c r="M62" s="2">
         <v>5</v>
       </c>
       <c r="N62" s="2">
-        <v>10.15</v>
+        <v>15.33</v>
       </c>
       <c r="O62" s="2" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="P62" s="2" t="s">
         <v>0</v>
@@ -4050,13 +4084,13 @@
         <v>59</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>3</v>
@@ -4084,10 +4118,10 @@
         <v>5</v>
       </c>
       <c r="N63" s="2">
-        <v>6.12</v>
+        <v>9.45</v>
       </c>
       <c r="O63" s="2" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="P63" s="2" t="s">
         <v>0</v>
@@ -4098,44 +4132,44 @@
         <v>60</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F64" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G64" s="2">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
       <c r="H64" s="2">
         <v>10.0</v>
       </c>
       <c r="I64" s="2" t="s">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="J64" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K64" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L64" s="2"/>
       <c r="M64" s="2">
         <v>5</v>
       </c>
       <c r="N64" s="2">
-        <v>8.33</v>
+        <v>3.6</v>
       </c>
       <c r="O64" s="2" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="P64" s="2" t="s">
         <v>0</v>
@@ -4146,13 +4180,13 @@
         <v>61</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>3</v>
@@ -4161,31 +4195,175 @@
         <v>1</v>
       </c>
       <c r="G65" s="2">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
       <c r="H65" s="2">
         <v>10.0</v>
       </c>
       <c r="I65" s="2" t="s">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="J65" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K65" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L65" s="2"/>
       <c r="M65" s="2">
         <v>5</v>
       </c>
       <c r="N65" s="2">
+        <v>10.15</v>
+      </c>
+      <c r="O65" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="P65" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:16">
+      <c r="A66" s="2">
+        <v>62</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F66" s="2">
+        <v>1</v>
+      </c>
+      <c r="G66" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="H66" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I66" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J66" s="2">
+        <v>4</v>
+      </c>
+      <c r="K66" s="2">
+        <v>1</v>
+      </c>
+      <c r="L66" s="2"/>
+      <c r="M66" s="2">
+        <v>5</v>
+      </c>
+      <c r="N66" s="2">
+        <v>6.12</v>
+      </c>
+      <c r="O66" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="P66" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:16">
+      <c r="A67" s="2">
+        <v>63</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F67" s="2">
+        <v>2</v>
+      </c>
+      <c r="G67" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="H67" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I67" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J67" s="2">
+        <v>4</v>
+      </c>
+      <c r="K67" s="2">
+        <v>1</v>
+      </c>
+      <c r="L67" s="2"/>
+      <c r="M67" s="2">
+        <v>5</v>
+      </c>
+      <c r="N67" s="2">
+        <v>8.33</v>
+      </c>
+      <c r="O67" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="P67" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:16">
+      <c r="A68" s="2">
+        <v>64</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F68" s="2">
+        <v>1</v>
+      </c>
+      <c r="G68" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="H68" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I68" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J68" s="2">
+        <v>4</v>
+      </c>
+      <c r="K68" s="2">
+        <v>1</v>
+      </c>
+      <c r="L68" s="2"/>
+      <c r="M68" s="2">
+        <v>5</v>
+      </c>
+      <c r="N68" s="2">
         <v>7.77</v>
       </c>
-      <c r="O65" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="P65" s="2" t="s">
+      <c r="O68" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="P68" s="2" t="s">
         <v>0</v>
       </c>
     </row>

--- a/2lit_center.xlsx
+++ b/2lit_center.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="281">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="312">
   <si>
     <t>ناجح ✓</t>
   </si>
@@ -803,6 +803,99 @@
     <t>Menna Ibrahim</t>
   </si>
   <si>
+    <t>2026-03-01 19:22</t>
+  </si>
+  <si>
+    <t>01023876919</t>
+  </si>
+  <si>
+    <t>yassinahmedsaid139@gmail.com</t>
+  </si>
+  <si>
+    <t>ياسين احمد سعيد</t>
+  </si>
+  <si>
+    <t>2026-03-01 19:23</t>
+  </si>
+  <si>
+    <t>01113765691</t>
+  </si>
+  <si>
+    <t>ahmed148mody@gmail.com</t>
+  </si>
+  <si>
+    <t>أحمد محمد أحمد سلمان</t>
+  </si>
+  <si>
+    <t>2026-03-01 19:31</t>
+  </si>
+  <si>
+    <t>01027647278</t>
+  </si>
+  <si>
+    <t>jodymohamad13@gmail.com</t>
+  </si>
+  <si>
+    <t>judy mohamed thabt</t>
+  </si>
+  <si>
+    <t>2026-03-01 19:30</t>
+  </si>
+  <si>
+    <t>karimmowafak@gmail.com</t>
+  </si>
+  <si>
+    <t>Karim Mowafak</t>
+  </si>
+  <si>
+    <t>2026-03-01 19:51</t>
+  </si>
+  <si>
+    <t>01552635868</t>
+  </si>
+  <si>
+    <t>habibaazi@icloud.com</t>
+  </si>
+  <si>
+    <t>habiba mahmoud</t>
+  </si>
+  <si>
+    <t>2026-03-01 19:36</t>
+  </si>
+  <si>
+    <t>01157331074</t>
+  </si>
+  <si>
+    <t>farahgadallh@gmail.com</t>
+  </si>
+  <si>
+    <t>Farah Ahmed mohamed</t>
+  </si>
+  <si>
+    <t>2026-03-01 19:41</t>
+  </si>
+  <si>
+    <t>01501181314</t>
+  </si>
+  <si>
+    <t>bebonasser399@gamil.com</t>
+  </si>
+  <si>
+    <t>Habiba Nasser Ahmed</t>
+  </si>
+  <si>
+    <t>2026-03-01 19:56</t>
+  </si>
+  <si>
+    <t>01017244083</t>
+  </si>
+  <si>
+    <t>albaraam357@gmail.com</t>
+  </si>
+  <si>
+    <t>Albaraamohamed</t>
+  </si>
+  <si>
     <t>الحالة</t>
   </si>
   <si>
@@ -857,7 +950,7 @@
     <t>الدرجة الكاملة: 10 | درجة النجاح: 5.00</t>
   </si>
   <si>
-    <t>تاريخ التصدير: 2026-03-01 19:21</t>
+    <t>تاريخ التصدير: 2026-03-01 20:29</t>
   </si>
 </sst>
 </file>
@@ -1245,7 +1338,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:P68"/>
+  <dimension ref="A1:P76"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="true" style="0"/>
@@ -1268,67 +1361,67 @@
   <sheetData>
     <row r="1" spans="1:16">
       <c r="A1" s="3" t="s">
-        <v>278</v>
+        <v>309</v>
       </c>
     </row>
     <row r="2" spans="1:16">
       <c r="A2" s="3" t="s">
-        <v>279</v>
+        <v>310</v>
       </c>
     </row>
     <row r="3" spans="1:16">
       <c r="A3" s="3" t="s">
-        <v>280</v>
+        <v>311</v>
       </c>
     </row>
     <row r="4" spans="1:16">
       <c r="A4" s="1" t="s">
-        <v>277</v>
+        <v>308</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>276</v>
+        <v>307</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>275</v>
+        <v>306</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>274</v>
+        <v>305</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>273</v>
+        <v>304</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>272</v>
+        <v>303</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>271</v>
+        <v>302</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>270</v>
+        <v>301</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>269</v>
+        <v>300</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>268</v>
+        <v>299</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>267</v>
+        <v>298</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>266</v>
+        <v>297</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>265</v>
+        <v>296</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>264</v>
+        <v>295</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>263</v>
+        <v>294</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>262</v>
+        <v>293</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1336,19 +1429,19 @@
         <v>1</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>261</v>
+        <v>292</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>260</v>
+        <v>291</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>259</v>
+        <v>290</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F5" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G5" s="2">
         <v>8.0</v>
@@ -1370,10 +1463,10 @@
         <v>5</v>
       </c>
       <c r="N5" s="2">
-        <v>5.8</v>
+        <v>3.0</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>258</v>
+        <v>289</v>
       </c>
       <c r="P5" s="2" t="s">
         <v>0</v>
@@ -1384,13 +1477,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>257</v>
+        <v>288</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>256</v>
+        <v>287</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>255</v>
+        <v>286</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>3</v>
@@ -1416,10 +1509,10 @@
         <v>5</v>
       </c>
       <c r="N6" s="2">
-        <v>3.17</v>
+        <v>4.58</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>254</v>
+        <v>285</v>
       </c>
       <c r="P6" s="2" t="s">
         <v>0</v>
@@ -1430,13 +1523,13 @@
         <v>3</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>253</v>
+        <v>284</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>252</v>
+        <v>283</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>251</v>
+        <v>282</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>3</v>
@@ -1445,29 +1538,27 @@
         <v>1</v>
       </c>
       <c r="G7" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H7" s="2">
         <v>10.0</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="J7" s="2">
-        <v>4</v>
-      </c>
-      <c r="K7" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K7" s="2"/>
       <c r="L7" s="2"/>
       <c r="M7" s="2">
         <v>5</v>
       </c>
       <c r="N7" s="2">
-        <v>3.2</v>
+        <v>5.58</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>250</v>
+        <v>281</v>
       </c>
       <c r="P7" s="2" t="s">
         <v>0</v>
@@ -1478,13 +1569,13 @@
         <v>4</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>249</v>
+        <v>280</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>248</v>
+        <v>279</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>247</v>
+        <v>278</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>3</v>
@@ -1493,29 +1584,29 @@
         <v>1</v>
       </c>
       <c r="G8" s="2">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
       <c r="H8" s="2">
         <v>10.0</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="J8" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K8" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L8" s="2"/>
       <c r="M8" s="2">
         <v>5</v>
       </c>
       <c r="N8" s="2">
-        <v>14.28</v>
+        <v>22.25</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>246</v>
+        <v>277</v>
       </c>
       <c r="P8" s="2" t="s">
         <v>0</v>
@@ -1526,13 +1617,13 @@
         <v>5</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>245</v>
+        <v>276</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>243</v>
+        <v>275</v>
+      </c>
+      <c r="D9" s="2">
+        <v>201118200153</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>3</v>
@@ -1541,29 +1632,29 @@
         <v>1</v>
       </c>
       <c r="G9" s="2">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
       <c r="H9" s="2">
         <v>10.0</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="J9" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K9" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L9" s="2"/>
       <c r="M9" s="2">
         <v>5</v>
       </c>
       <c r="N9" s="2">
-        <v>12.48</v>
+        <v>2.13</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>242</v>
+        <v>274</v>
       </c>
       <c r="P9" s="2" t="s">
         <v>0</v>
@@ -1574,13 +1665,13 @@
         <v>6</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>241</v>
+        <v>273</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>240</v>
+        <v>272</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>239</v>
+        <v>271</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>3</v>
@@ -1589,29 +1680,27 @@
         <v>1</v>
       </c>
       <c r="G10" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H10" s="2">
         <v>10.0</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="J10" s="2">
-        <v>4</v>
-      </c>
-      <c r="K10" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K10" s="2"/>
       <c r="L10" s="2"/>
       <c r="M10" s="2">
         <v>5</v>
       </c>
       <c r="N10" s="2">
-        <v>4.22</v>
+        <v>5.0</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>238</v>
+        <v>270</v>
       </c>
       <c r="P10" s="2" t="s">
         <v>0</v>
@@ -1622,13 +1711,13 @@
         <v>7</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>237</v>
+        <v>269</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>236</v>
+        <v>268</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>235</v>
+        <v>267</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>3</v>
@@ -1637,29 +1726,27 @@
         <v>1</v>
       </c>
       <c r="G11" s="2">
-        <v>6.0</v>
+        <v>10.0</v>
       </c>
       <c r="H11" s="2">
         <v>10.0</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="J11" s="2">
-        <v>3</v>
-      </c>
-      <c r="K11" s="2">
-        <v>2</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K11" s="2"/>
       <c r="L11" s="2"/>
       <c r="M11" s="2">
         <v>5</v>
       </c>
       <c r="N11" s="2">
-        <v>8.42</v>
+        <v>5.87</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>234</v>
+        <v>266</v>
       </c>
       <c r="P11" s="2" t="s">
         <v>0</v>
@@ -1670,13 +1757,13 @@
         <v>8</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>233</v>
+        <v>265</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>232</v>
+        <v>264</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>231</v>
+        <v>263</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>3</v>
@@ -1704,10 +1791,10 @@
         <v>5</v>
       </c>
       <c r="N12" s="2">
-        <v>7.37</v>
+        <v>8.92</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>192</v>
+        <v>262</v>
       </c>
       <c r="P12" s="2" t="s">
         <v>0</v>
@@ -1718,13 +1805,13 @@
         <v>9</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>230</v>
+        <v>261</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>229</v>
+        <v>260</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>228</v>
+        <v>259</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>3</v>
@@ -1733,27 +1820,29 @@
         <v>1</v>
       </c>
       <c r="G13" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H13" s="2">
         <v>10.0</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="J13" s="2">
-        <v>5</v>
-      </c>
-      <c r="K13" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K13" s="2">
+        <v>1</v>
+      </c>
       <c r="L13" s="2"/>
       <c r="M13" s="2">
         <v>5</v>
       </c>
       <c r="N13" s="2">
-        <v>23.67</v>
+        <v>5.8</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>227</v>
+        <v>258</v>
       </c>
       <c r="P13" s="2" t="s">
         <v>0</v>
@@ -1764,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>226</v>
+        <v>257</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>225</v>
+        <v>256</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>224</v>
+        <v>255</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>3</v>
@@ -1779,29 +1868,27 @@
         <v>1</v>
       </c>
       <c r="G14" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H14" s="2">
         <v>10.0</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="J14" s="2">
-        <v>4</v>
-      </c>
-      <c r="K14" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K14" s="2"/>
       <c r="L14" s="2"/>
       <c r="M14" s="2">
         <v>5</v>
       </c>
       <c r="N14" s="2">
-        <v>15.78</v>
+        <v>3.17</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>223</v>
+        <v>254</v>
       </c>
       <c r="P14" s="2" t="s">
         <v>0</v>
@@ -1812,13 +1899,13 @@
         <v>11</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>222</v>
+        <v>253</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>221</v>
+        <v>252</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>220</v>
+        <v>251</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>3</v>
@@ -1827,27 +1914,29 @@
         <v>1</v>
       </c>
       <c r="G15" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H15" s="2">
         <v>10.0</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="J15" s="2">
-        <v>5</v>
-      </c>
-      <c r="K15" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K15" s="2">
+        <v>1</v>
+      </c>
       <c r="L15" s="2"/>
       <c r="M15" s="2">
         <v>5</v>
       </c>
       <c r="N15" s="2">
-        <v>7.02</v>
+        <v>3.2</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>219</v>
+        <v>250</v>
       </c>
       <c r="P15" s="2" t="s">
         <v>0</v>
@@ -1858,13 +1947,13 @@
         <v>12</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>218</v>
+        <v>249</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>217</v>
+        <v>248</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>216</v>
+        <v>247</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>3</v>
@@ -1892,10 +1981,10 @@
         <v>5</v>
       </c>
       <c r="N16" s="2">
-        <v>7.05</v>
+        <v>14.28</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>215</v>
+        <v>246</v>
       </c>
       <c r="P16" s="2" t="s">
         <v>0</v>
@@ -1906,13 +1995,13 @@
         <v>13</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>214</v>
+        <v>245</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>213</v>
+        <v>244</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>212</v>
+        <v>243</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>3</v>
@@ -1921,32 +2010,32 @@
         <v>1</v>
       </c>
       <c r="G17" s="2">
-        <v>2.0</v>
+        <v>8.0</v>
       </c>
       <c r="H17" s="2">
         <v>10.0</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>163</v>
+        <v>2</v>
       </c>
       <c r="J17" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K17" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L17" s="2"/>
       <c r="M17" s="2">
         <v>5</v>
       </c>
       <c r="N17" s="2">
-        <v>5.35</v>
+        <v>12.48</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>211</v>
+        <v>242</v>
       </c>
       <c r="P17" s="2" t="s">
-        <v>161</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -1954,19 +2043,19 @@
         <v>14</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>210</v>
+        <v>241</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>209</v>
+        <v>240</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>208</v>
+        <v>239</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F18" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G18" s="2">
         <v>8.0</v>
@@ -1988,10 +2077,10 @@
         <v>5</v>
       </c>
       <c r="N18" s="2">
-        <v>3.77</v>
+        <v>4.22</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>207</v>
+        <v>238</v>
       </c>
       <c r="P18" s="2" t="s">
         <v>0</v>
@@ -2002,13 +2091,13 @@
         <v>15</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>206</v>
+        <v>237</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>205</v>
+        <v>236</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>204</v>
+        <v>235</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>3</v>
@@ -2017,29 +2106,29 @@
         <v>1</v>
       </c>
       <c r="G19" s="2">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
       <c r="H19" s="2">
         <v>10.0</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="J19" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K19" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L19" s="2"/>
       <c r="M19" s="2">
         <v>5</v>
       </c>
       <c r="N19" s="2">
-        <v>11.42</v>
+        <v>8.42</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>203</v>
+        <v>234</v>
       </c>
       <c r="P19" s="2" t="s">
         <v>0</v>
@@ -2050,13 +2139,13 @@
         <v>16</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>202</v>
+        <v>233</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>201</v>
+        <v>232</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>200</v>
+        <v>231</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>3</v>
@@ -2065,29 +2154,29 @@
         <v>1</v>
       </c>
       <c r="G20" s="2">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="H20" s="2">
         <v>10.0</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="J20" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K20" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L20" s="2"/>
       <c r="M20" s="2">
         <v>5</v>
       </c>
       <c r="N20" s="2">
-        <v>3.57</v>
+        <v>7.37</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="P20" s="2" t="s">
         <v>0</v>
@@ -2098,13 +2187,13 @@
         <v>17</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>198</v>
+        <v>230</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>197</v>
+        <v>229</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>196</v>
+        <v>228</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>3</v>
@@ -2113,29 +2202,27 @@
         <v>1</v>
       </c>
       <c r="G21" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H21" s="2">
         <v>10.0</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="J21" s="2">
-        <v>4</v>
-      </c>
-      <c r="K21" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K21" s="2"/>
       <c r="L21" s="2"/>
       <c r="M21" s="2">
         <v>5</v>
       </c>
       <c r="N21" s="2">
-        <v>7.5</v>
+        <v>23.67</v>
       </c>
       <c r="O21" s="2" t="s">
-        <v>184</v>
+        <v>227</v>
       </c>
       <c r="P21" s="2" t="s">
         <v>0</v>
@@ -2146,13 +2233,13 @@
         <v>18</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>195</v>
+        <v>226</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>194</v>
+        <v>225</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>193</v>
+        <v>224</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>3</v>
@@ -2180,10 +2267,10 @@
         <v>5</v>
       </c>
       <c r="N22" s="2">
-        <v>39.38</v>
+        <v>15.78</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>192</v>
+        <v>223</v>
       </c>
       <c r="P22" s="2" t="s">
         <v>0</v>
@@ -2194,13 +2281,13 @@
         <v>19</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>191</v>
+        <v>222</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>190</v>
+        <v>221</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>189</v>
+        <v>220</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>3</v>
@@ -2209,29 +2296,27 @@
         <v>1</v>
       </c>
       <c r="G23" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H23" s="2">
         <v>10.0</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="J23" s="2">
-        <v>4</v>
-      </c>
-      <c r="K23" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K23" s="2"/>
       <c r="L23" s="2"/>
       <c r="M23" s="2">
         <v>5</v>
       </c>
       <c r="N23" s="2">
-        <v>11.68</v>
+        <v>7.02</v>
       </c>
       <c r="O23" s="2" t="s">
-        <v>188</v>
+        <v>219</v>
       </c>
       <c r="P23" s="2" t="s">
         <v>0</v>
@@ -2242,13 +2327,13 @@
         <v>20</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>187</v>
+        <v>218</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>186</v>
+        <v>217</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>185</v>
+        <v>216</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>3</v>
@@ -2276,10 +2361,10 @@
         <v>5</v>
       </c>
       <c r="N24" s="2">
-        <v>15.92</v>
+        <v>7.05</v>
       </c>
       <c r="O24" s="2" t="s">
-        <v>184</v>
+        <v>215</v>
       </c>
       <c r="P24" s="2" t="s">
         <v>0</v>
@@ -2290,13 +2375,13 @@
         <v>21</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>183</v>
+        <v>214</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>182</v>
+        <v>213</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>181</v>
+        <v>212</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>3</v>
@@ -2305,32 +2390,32 @@
         <v>1</v>
       </c>
       <c r="G25" s="2">
-        <v>8.0</v>
+        <v>2.0</v>
       </c>
       <c r="H25" s="2">
         <v>10.0</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>2</v>
+        <v>163</v>
       </c>
       <c r="J25" s="2">
+        <v>1</v>
+      </c>
+      <c r="K25" s="2">
         <v>4</v>
-      </c>
-      <c r="K25" s="2">
-        <v>1</v>
       </c>
       <c r="L25" s="2"/>
       <c r="M25" s="2">
         <v>5</v>
       </c>
       <c r="N25" s="2">
-        <v>6.17</v>
+        <v>5.35</v>
       </c>
       <c r="O25" s="2" t="s">
-        <v>180</v>
+        <v>211</v>
       </c>
       <c r="P25" s="2" t="s">
-        <v>0</v>
+        <v>161</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -2338,42 +2423,44 @@
         <v>22</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>179</v>
+        <v>210</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>178</v>
+        <v>209</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>177</v>
+        <v>208</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F26" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G26" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H26" s="2">
         <v>10.0</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="J26" s="2">
-        <v>5</v>
-      </c>
-      <c r="K26" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K26" s="2">
+        <v>1</v>
+      </c>
       <c r="L26" s="2"/>
       <c r="M26" s="2">
         <v>5</v>
       </c>
       <c r="N26" s="2">
-        <v>5.92</v>
+        <v>3.77</v>
       </c>
       <c r="O26" s="2" t="s">
-        <v>176</v>
+        <v>207</v>
       </c>
       <c r="P26" s="2" t="s">
         <v>0</v>
@@ -2384,13 +2471,13 @@
         <v>23</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>175</v>
+        <v>206</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>174</v>
+        <v>205</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>173</v>
+        <v>204</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>3</v>
@@ -2399,32 +2486,32 @@
         <v>1</v>
       </c>
       <c r="G27" s="2">
-        <v>4.0</v>
+        <v>8.0</v>
       </c>
       <c r="H27" s="2">
         <v>10.0</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>172</v>
+        <v>2</v>
       </c>
       <c r="J27" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K27" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L27" s="2"/>
       <c r="M27" s="2">
         <v>5</v>
       </c>
       <c r="N27" s="2">
-        <v>5.95</v>
+        <v>11.42</v>
       </c>
       <c r="O27" s="2" t="s">
-        <v>171</v>
+        <v>203</v>
       </c>
       <c r="P27" s="2" t="s">
-        <v>161</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -2432,13 +2519,13 @@
         <v>24</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>170</v>
+        <v>202</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>169</v>
+        <v>201</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>168</v>
+        <v>200</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>3</v>
@@ -2447,27 +2534,29 @@
         <v>1</v>
       </c>
       <c r="G28" s="2">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
       <c r="H28" s="2">
         <v>10.0</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="J28" s="2">
-        <v>5</v>
-      </c>
-      <c r="K28" s="2"/>
+        <v>3</v>
+      </c>
+      <c r="K28" s="2">
+        <v>2</v>
+      </c>
       <c r="L28" s="2"/>
       <c r="M28" s="2">
         <v>5</v>
       </c>
       <c r="N28" s="2">
-        <v>9.08</v>
+        <v>3.57</v>
       </c>
       <c r="O28" s="2" t="s">
-        <v>167</v>
+        <v>199</v>
       </c>
       <c r="P28" s="2" t="s">
         <v>0</v>
@@ -2478,13 +2567,13 @@
         <v>25</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>166</v>
+        <v>198</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>165</v>
+        <v>197</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>164</v>
+        <v>196</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>3</v>
@@ -2493,32 +2582,32 @@
         <v>1</v>
       </c>
       <c r="G29" s="2">
-        <v>2.0</v>
+        <v>8.0</v>
       </c>
       <c r="H29" s="2">
         <v>10.0</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>163</v>
+        <v>2</v>
       </c>
       <c r="J29" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K29" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L29" s="2"/>
       <c r="M29" s="2">
         <v>5</v>
       </c>
       <c r="N29" s="2">
-        <v>10.48</v>
+        <v>7.5</v>
       </c>
       <c r="O29" s="2" t="s">
-        <v>162</v>
+        <v>184</v>
       </c>
       <c r="P29" s="2" t="s">
-        <v>161</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -2526,13 +2615,13 @@
         <v>26</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>160</v>
+        <v>195</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>159</v>
+        <v>194</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>158</v>
+        <v>193</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>3</v>
@@ -2560,10 +2649,10 @@
         <v>5</v>
       </c>
       <c r="N30" s="2">
-        <v>13.42</v>
+        <v>39.38</v>
       </c>
       <c r="O30" s="2" t="s">
-        <v>157</v>
+        <v>192</v>
       </c>
       <c r="P30" s="2" t="s">
         <v>0</v>
@@ -2574,13 +2663,13 @@
         <v>27</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>156</v>
+        <v>191</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>155</v>
+        <v>190</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>154</v>
+        <v>189</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>3</v>
@@ -2589,29 +2678,29 @@
         <v>1</v>
       </c>
       <c r="G31" s="2">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="H31" s="2">
         <v>10.0</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="J31" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K31" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L31" s="2"/>
       <c r="M31" s="2">
         <v>5</v>
       </c>
       <c r="N31" s="2">
-        <v>2.57</v>
+        <v>11.68</v>
       </c>
       <c r="O31" s="2" t="s">
-        <v>153</v>
+        <v>188</v>
       </c>
       <c r="P31" s="2" t="s">
         <v>0</v>
@@ -2622,13 +2711,13 @@
         <v>28</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>152</v>
+        <v>187</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>151</v>
+        <v>186</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>150</v>
+        <v>185</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>3</v>
@@ -2637,27 +2726,29 @@
         <v>1</v>
       </c>
       <c r="G32" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H32" s="2">
         <v>10.0</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="J32" s="2">
-        <v>5</v>
-      </c>
-      <c r="K32" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K32" s="2">
+        <v>1</v>
+      </c>
       <c r="L32" s="2"/>
       <c r="M32" s="2">
         <v>5</v>
       </c>
       <c r="N32" s="2">
-        <v>1.65</v>
+        <v>15.92</v>
       </c>
       <c r="O32" s="2" t="s">
-        <v>149</v>
+        <v>184</v>
       </c>
       <c r="P32" s="2" t="s">
         <v>0</v>
@@ -2668,13 +2759,13 @@
         <v>29</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>148</v>
+        <v>183</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>147</v>
+        <v>182</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>146</v>
+        <v>181</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>3</v>
@@ -2683,29 +2774,29 @@
         <v>1</v>
       </c>
       <c r="G33" s="2">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="H33" s="2">
         <v>10.0</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="J33" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K33" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L33" s="2"/>
       <c r="M33" s="2">
         <v>5</v>
       </c>
       <c r="N33" s="2">
-        <v>12.1</v>
+        <v>6.17</v>
       </c>
       <c r="O33" s="2" t="s">
-        <v>145</v>
+        <v>180</v>
       </c>
       <c r="P33" s="2" t="s">
         <v>0</v>
@@ -2716,13 +2807,13 @@
         <v>30</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>144</v>
+        <v>179</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>143</v>
+        <v>178</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>142</v>
+        <v>177</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>3</v>
@@ -2731,29 +2822,27 @@
         <v>1</v>
       </c>
       <c r="G34" s="2">
-        <v>6.0</v>
+        <v>10.0</v>
       </c>
       <c r="H34" s="2">
         <v>10.0</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="J34" s="2">
-        <v>3</v>
-      </c>
-      <c r="K34" s="2">
-        <v>2</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K34" s="2"/>
       <c r="L34" s="2"/>
       <c r="M34" s="2">
         <v>5</v>
       </c>
       <c r="N34" s="2">
-        <v>18.58</v>
+        <v>5.92</v>
       </c>
       <c r="O34" s="2" t="s">
-        <v>141</v>
+        <v>176</v>
       </c>
       <c r="P34" s="2" t="s">
         <v>0</v>
@@ -2764,13 +2853,13 @@
         <v>31</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>140</v>
+        <v>175</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>139</v>
+        <v>174</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>138</v>
+        <v>173</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>3</v>
@@ -2779,30 +2868,32 @@
         <v>1</v>
       </c>
       <c r="G35" s="2">
-        <v>10.0</v>
+        <v>4.0</v>
       </c>
       <c r="H35" s="2">
         <v>10.0</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>29</v>
+        <v>172</v>
       </c>
       <c r="J35" s="2">
-        <v>5</v>
-      </c>
-      <c r="K35" s="2"/>
+        <v>2</v>
+      </c>
+      <c r="K35" s="2">
+        <v>3</v>
+      </c>
       <c r="L35" s="2"/>
       <c r="M35" s="2">
         <v>5</v>
       </c>
       <c r="N35" s="2">
-        <v>18.03</v>
+        <v>5.95</v>
       </c>
       <c r="O35" s="2" t="s">
-        <v>137</v>
+        <v>171</v>
       </c>
       <c r="P35" s="2" t="s">
-        <v>0</v>
+        <v>161</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -2810,13 +2901,13 @@
         <v>32</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>136</v>
+        <v>170</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>135</v>
+        <v>169</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>134</v>
+        <v>168</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>3</v>
@@ -2825,29 +2916,27 @@
         <v>1</v>
       </c>
       <c r="G36" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H36" s="2">
         <v>10.0</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="J36" s="2">
-        <v>4</v>
-      </c>
-      <c r="K36" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K36" s="2"/>
       <c r="L36" s="2"/>
       <c r="M36" s="2">
         <v>5</v>
       </c>
       <c r="N36" s="2">
-        <v>9.68</v>
+        <v>9.08</v>
       </c>
       <c r="O36" s="2" t="s">
-        <v>133</v>
+        <v>167</v>
       </c>
       <c r="P36" s="2" t="s">
         <v>0</v>
@@ -2858,13 +2947,13 @@
         <v>33</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>132</v>
+        <v>166</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>131</v>
+        <v>165</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>130</v>
+        <v>164</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>3</v>
@@ -2873,32 +2962,32 @@
         <v>1</v>
       </c>
       <c r="G37" s="2">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
       <c r="H37" s="2">
         <v>10.0</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>16</v>
+        <v>163</v>
       </c>
       <c r="J37" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K37" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L37" s="2"/>
       <c r="M37" s="2">
         <v>5</v>
       </c>
       <c r="N37" s="2">
-        <v>14.13</v>
+        <v>10.48</v>
       </c>
       <c r="O37" s="2" t="s">
-        <v>129</v>
+        <v>162</v>
       </c>
       <c r="P37" s="2" t="s">
-        <v>0</v>
+        <v>161</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -2906,13 +2995,13 @@
         <v>34</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>128</v>
+        <v>160</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>127</v>
+        <v>159</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>126</v>
+        <v>158</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>3</v>
@@ -2940,10 +3029,10 @@
         <v>5</v>
       </c>
       <c r="N38" s="2">
-        <v>11.45</v>
+        <v>13.42</v>
       </c>
       <c r="O38" s="2" t="s">
-        <v>125</v>
+        <v>157</v>
       </c>
       <c r="P38" s="2" t="s">
         <v>0</v>
@@ -2954,13 +3043,13 @@
         <v>35</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>124</v>
+        <v>156</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>123</v>
+        <v>155</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>122</v>
+        <v>154</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>3</v>
@@ -2969,29 +3058,29 @@
         <v>1</v>
       </c>
       <c r="G39" s="2">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
       <c r="H39" s="2">
         <v>10.0</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="J39" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K39" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L39" s="2"/>
       <c r="M39" s="2">
         <v>5</v>
       </c>
       <c r="N39" s="2">
-        <v>12.55</v>
+        <v>2.57</v>
       </c>
       <c r="O39" s="2" t="s">
-        <v>121</v>
+        <v>153</v>
       </c>
       <c r="P39" s="2" t="s">
         <v>0</v>
@@ -3002,13 +3091,13 @@
         <v>36</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>120</v>
+        <v>152</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>119</v>
+        <v>151</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>118</v>
+        <v>150</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>3</v>
@@ -3034,10 +3123,10 @@
         <v>5</v>
       </c>
       <c r="N40" s="2">
-        <v>6.58</v>
+        <v>1.65</v>
       </c>
       <c r="O40" s="2" t="s">
-        <v>117</v>
+        <v>149</v>
       </c>
       <c r="P40" s="2" t="s">
         <v>0</v>
@@ -3048,13 +3137,13 @@
         <v>37</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>116</v>
+        <v>148</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>115</v>
+        <v>147</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>114</v>
+        <v>146</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>3</v>
@@ -3063,29 +3152,29 @@
         <v>1</v>
       </c>
       <c r="G41" s="2">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
       <c r="H41" s="2">
         <v>10.0</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="J41" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K41" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L41" s="2"/>
       <c r="M41" s="2">
         <v>5</v>
       </c>
       <c r="N41" s="2">
-        <v>18.78</v>
+        <v>12.1</v>
       </c>
       <c r="O41" s="2" t="s">
-        <v>113</v>
+        <v>145</v>
       </c>
       <c r="P41" s="2" t="s">
         <v>0</v>
@@ -3096,13 +3185,13 @@
         <v>38</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>112</v>
+        <v>144</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>111</v>
+        <v>143</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>110</v>
+        <v>142</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>3</v>
@@ -3111,29 +3200,29 @@
         <v>1</v>
       </c>
       <c r="G42" s="2">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
       <c r="H42" s="2">
         <v>10.0</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="J42" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K42" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L42" s="2"/>
       <c r="M42" s="2">
         <v>5</v>
       </c>
       <c r="N42" s="2">
-        <v>12.03</v>
+        <v>18.58</v>
       </c>
       <c r="O42" s="2" t="s">
-        <v>109</v>
+        <v>141</v>
       </c>
       <c r="P42" s="2" t="s">
         <v>0</v>
@@ -3144,13 +3233,13 @@
         <v>39</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>108</v>
+        <v>140</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>107</v>
+        <v>139</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>106</v>
+        <v>138</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>3</v>
@@ -3159,29 +3248,27 @@
         <v>1</v>
       </c>
       <c r="G43" s="2">
-        <v>6.0</v>
+        <v>10.0</v>
       </c>
       <c r="H43" s="2">
         <v>10.0</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="J43" s="2">
-        <v>3</v>
-      </c>
-      <c r="K43" s="2">
-        <v>2</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K43" s="2"/>
       <c r="L43" s="2"/>
       <c r="M43" s="2">
         <v>5</v>
       </c>
       <c r="N43" s="2">
-        <v>25.12</v>
+        <v>18.03</v>
       </c>
       <c r="O43" s="2" t="s">
-        <v>105</v>
+        <v>137</v>
       </c>
       <c r="P43" s="2" t="s">
         <v>0</v>
@@ -3192,13 +3279,13 @@
         <v>40</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>104</v>
+        <v>136</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>103</v>
+        <v>135</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>102</v>
+        <v>134</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>3</v>
@@ -3207,29 +3294,29 @@
         <v>1</v>
       </c>
       <c r="G44" s="2">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="H44" s="2">
         <v>10.0</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="J44" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K44" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L44" s="2"/>
       <c r="M44" s="2">
         <v>5</v>
       </c>
       <c r="N44" s="2">
-        <v>16.98</v>
+        <v>9.68</v>
       </c>
       <c r="O44" s="2" t="s">
-        <v>101</v>
+        <v>133</v>
       </c>
       <c r="P44" s="2" t="s">
         <v>0</v>
@@ -3240,13 +3327,13 @@
         <v>41</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>100</v>
+        <v>132</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>99</v>
+        <v>131</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>98</v>
+        <v>130</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>3</v>
@@ -3255,27 +3342,29 @@
         <v>1</v>
       </c>
       <c r="G45" s="2">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
       <c r="H45" s="2">
         <v>10.0</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="J45" s="2">
-        <v>5</v>
-      </c>
-      <c r="K45" s="2"/>
+        <v>3</v>
+      </c>
+      <c r="K45" s="2">
+        <v>2</v>
+      </c>
       <c r="L45" s="2"/>
       <c r="M45" s="2">
         <v>5</v>
       </c>
       <c r="N45" s="2">
-        <v>1.45</v>
+        <v>14.13</v>
       </c>
       <c r="O45" s="2" t="s">
-        <v>97</v>
+        <v>129</v>
       </c>
       <c r="P45" s="2" t="s">
         <v>0</v>
@@ -3286,42 +3375,44 @@
         <v>42</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>96</v>
+        <v>128</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>95</v>
+        <v>127</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>94</v>
+        <v>126</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F46" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G46" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H46" s="2">
         <v>10.0</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="J46" s="2">
-        <v>5</v>
-      </c>
-      <c r="K46" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K46" s="2">
+        <v>1</v>
+      </c>
       <c r="L46" s="2"/>
       <c r="M46" s="2">
         <v>5</v>
       </c>
       <c r="N46" s="2">
-        <v>6.18</v>
+        <v>11.45</v>
       </c>
       <c r="O46" s="2" t="s">
-        <v>93</v>
+        <v>125</v>
       </c>
       <c r="P46" s="2" t="s">
         <v>0</v>
@@ -3332,13 +3423,13 @@
         <v>43</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>92</v>
+        <v>124</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>91</v>
+        <v>123</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>90</v>
+        <v>122</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>3</v>
@@ -3347,27 +3438,29 @@
         <v>1</v>
       </c>
       <c r="G47" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H47" s="2">
         <v>10.0</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="J47" s="2">
-        <v>5</v>
-      </c>
-      <c r="K47" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K47" s="2">
+        <v>1</v>
+      </c>
       <c r="L47" s="2"/>
       <c r="M47" s="2">
         <v>5</v>
       </c>
       <c r="N47" s="2">
-        <v>6.13</v>
+        <v>12.55</v>
       </c>
       <c r="O47" s="2" t="s">
-        <v>89</v>
+        <v>121</v>
       </c>
       <c r="P47" s="2" t="s">
         <v>0</v>
@@ -3378,13 +3471,13 @@
         <v>44</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>88</v>
+        <v>120</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>87</v>
+        <v>119</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>86</v>
+        <v>118</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>3</v>
@@ -3393,29 +3486,27 @@
         <v>1</v>
       </c>
       <c r="G48" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H48" s="2">
         <v>10.0</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="J48" s="2">
-        <v>4</v>
-      </c>
-      <c r="K48" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K48" s="2"/>
       <c r="L48" s="2"/>
       <c r="M48" s="2">
         <v>5</v>
       </c>
       <c r="N48" s="2">
-        <v>2.4</v>
+        <v>6.58</v>
       </c>
       <c r="O48" s="2" t="s">
-        <v>85</v>
+        <v>117</v>
       </c>
       <c r="P48" s="2" t="s">
         <v>0</v>
@@ -3426,13 +3517,13 @@
         <v>45</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>84</v>
+        <v>116</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>83</v>
+        <v>115</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>82</v>
+        <v>114</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>3</v>
@@ -3460,10 +3551,10 @@
         <v>5</v>
       </c>
       <c r="N49" s="2">
-        <v>15.75</v>
+        <v>18.78</v>
       </c>
       <c r="O49" s="2" t="s">
-        <v>81</v>
+        <v>113</v>
       </c>
       <c r="P49" s="2" t="s">
         <v>0</v>
@@ -3474,13 +3565,13 @@
         <v>46</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>80</v>
+        <v>112</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>79</v>
+        <v>111</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>3</v>
@@ -3489,27 +3580,29 @@
         <v>1</v>
       </c>
       <c r="G50" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H50" s="2">
         <v>10.0</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="J50" s="2">
-        <v>5</v>
-      </c>
-      <c r="K50" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K50" s="2">
+        <v>1</v>
+      </c>
       <c r="L50" s="2"/>
       <c r="M50" s="2">
         <v>5</v>
       </c>
       <c r="N50" s="2">
-        <v>2.17</v>
+        <v>12.03</v>
       </c>
       <c r="O50" s="2" t="s">
-        <v>77</v>
+        <v>109</v>
       </c>
       <c r="P50" s="2" t="s">
         <v>0</v>
@@ -3520,13 +3613,13 @@
         <v>47</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>76</v>
+        <v>108</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>75</v>
+        <v>107</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>74</v>
+        <v>106</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>3</v>
@@ -3554,10 +3647,10 @@
         <v>5</v>
       </c>
       <c r="N51" s="2">
-        <v>9.5</v>
+        <v>25.12</v>
       </c>
       <c r="O51" s="2" t="s">
-        <v>73</v>
+        <v>105</v>
       </c>
       <c r="P51" s="2" t="s">
         <v>0</v>
@@ -3568,13 +3661,13 @@
         <v>48</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>72</v>
+        <v>104</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>71</v>
+        <v>103</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>70</v>
+        <v>102</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>3</v>
@@ -3583,27 +3676,29 @@
         <v>1</v>
       </c>
       <c r="G52" s="2">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
       <c r="H52" s="2">
         <v>10.0</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="J52" s="2">
-        <v>5</v>
-      </c>
-      <c r="K52" s="2"/>
+        <v>3</v>
+      </c>
+      <c r="K52" s="2">
+        <v>2</v>
+      </c>
       <c r="L52" s="2"/>
       <c r="M52" s="2">
         <v>5</v>
       </c>
       <c r="N52" s="2">
-        <v>10.75</v>
+        <v>16.98</v>
       </c>
       <c r="O52" s="2" t="s">
-        <v>69</v>
+        <v>101</v>
       </c>
       <c r="P52" s="2" t="s">
         <v>0</v>
@@ -3614,44 +3709,42 @@
         <v>49</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>68</v>
+        <v>100</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>67</v>
+        <v>99</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>66</v>
+        <v>98</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F53" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G53" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H53" s="2">
         <v>10.0</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="J53" s="2">
-        <v>4</v>
-      </c>
-      <c r="K53" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K53" s="2"/>
       <c r="L53" s="2"/>
       <c r="M53" s="2">
         <v>5</v>
       </c>
       <c r="N53" s="2">
-        <v>23.17</v>
+        <v>1.45</v>
       </c>
       <c r="O53" s="2" t="s">
-        <v>65</v>
+        <v>97</v>
       </c>
       <c r="P53" s="2" t="s">
         <v>0</v>
@@ -3662,13 +3755,13 @@
         <v>50</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>64</v>
+        <v>96</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>63</v>
+        <v>95</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>3</v>
@@ -3694,10 +3787,10 @@
         <v>5</v>
       </c>
       <c r="N54" s="2">
-        <v>5.47</v>
+        <v>6.18</v>
       </c>
       <c r="O54" s="2" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="P54" s="2" t="s">
         <v>0</v>
@@ -3708,13 +3801,13 @@
         <v>51</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>60</v>
+        <v>92</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>59</v>
+        <v>91</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>58</v>
+        <v>90</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>3</v>
@@ -3723,29 +3816,27 @@
         <v>1</v>
       </c>
       <c r="G55" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H55" s="2">
         <v>10.0</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="J55" s="2">
-        <v>4</v>
-      </c>
-      <c r="K55" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K55" s="2"/>
       <c r="L55" s="2"/>
       <c r="M55" s="2">
         <v>5</v>
       </c>
       <c r="N55" s="2">
-        <v>15.8</v>
+        <v>6.13</v>
       </c>
       <c r="O55" s="2" t="s">
-        <v>57</v>
+        <v>89</v>
       </c>
       <c r="P55" s="2" t="s">
         <v>0</v>
@@ -3756,13 +3847,13 @@
         <v>52</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>56</v>
+        <v>88</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>55</v>
+        <v>87</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>54</v>
+        <v>86</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>3</v>
@@ -3771,27 +3862,29 @@
         <v>1</v>
       </c>
       <c r="G56" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H56" s="2">
         <v>10.0</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="J56" s="2">
-        <v>5</v>
-      </c>
-      <c r="K56" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K56" s="2">
+        <v>1</v>
+      </c>
       <c r="L56" s="2"/>
       <c r="M56" s="2">
         <v>5</v>
       </c>
       <c r="N56" s="2">
-        <v>4.07</v>
+        <v>2.4</v>
       </c>
       <c r="O56" s="2" t="s">
-        <v>53</v>
+        <v>85</v>
       </c>
       <c r="P56" s="2" t="s">
         <v>0</v>
@@ -3802,13 +3895,13 @@
         <v>53</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>52</v>
+        <v>84</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>51</v>
+        <v>83</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>50</v>
+        <v>82</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>3</v>
@@ -3836,10 +3929,10 @@
         <v>5</v>
       </c>
       <c r="N57" s="2">
-        <v>21.8</v>
+        <v>15.75</v>
       </c>
       <c r="O57" s="2" t="s">
-        <v>49</v>
+        <v>81</v>
       </c>
       <c r="P57" s="2" t="s">
         <v>0</v>
@@ -3850,13 +3943,13 @@
         <v>54</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>48</v>
+        <v>80</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>47</v>
+        <v>79</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>46</v>
+        <v>78</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>3</v>
@@ -3865,29 +3958,27 @@
         <v>1</v>
       </c>
       <c r="G58" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H58" s="2">
         <v>10.0</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="J58" s="2">
-        <v>4</v>
-      </c>
-      <c r="K58" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K58" s="2"/>
       <c r="L58" s="2"/>
       <c r="M58" s="2">
         <v>5</v>
       </c>
       <c r="N58" s="2">
-        <v>10.12</v>
+        <v>2.17</v>
       </c>
       <c r="O58" s="2" t="s">
-        <v>45</v>
+        <v>77</v>
       </c>
       <c r="P58" s="2" t="s">
         <v>0</v>
@@ -3898,13 +3989,13 @@
         <v>55</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>44</v>
+        <v>76</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>43</v>
+        <v>75</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>3</v>
@@ -3913,27 +4004,29 @@
         <v>1</v>
       </c>
       <c r="G59" s="2">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
       <c r="H59" s="2">
         <v>10.0</v>
       </c>
       <c r="I59" s="2" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="J59" s="2">
-        <v>5</v>
-      </c>
-      <c r="K59" s="2"/>
+        <v>3</v>
+      </c>
+      <c r="K59" s="2">
+        <v>2</v>
+      </c>
       <c r="L59" s="2"/>
       <c r="M59" s="2">
         <v>5</v>
       </c>
       <c r="N59" s="2">
-        <v>13.48</v>
+        <v>9.5</v>
       </c>
       <c r="O59" s="2" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="P59" s="2" t="s">
         <v>0</v>
@@ -3944,13 +4037,13 @@
         <v>56</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>39</v>
+        <v>71</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>3</v>
@@ -3959,29 +4052,27 @@
         <v>1</v>
       </c>
       <c r="G60" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H60" s="2">
         <v>10.0</v>
       </c>
       <c r="I60" s="2" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="J60" s="2">
-        <v>4</v>
-      </c>
-      <c r="K60" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K60" s="2"/>
       <c r="L60" s="2"/>
       <c r="M60" s="2">
         <v>5</v>
       </c>
       <c r="N60" s="2">
-        <v>10.6</v>
+        <v>10.75</v>
       </c>
       <c r="O60" s="2" t="s">
-        <v>37</v>
+        <v>69</v>
       </c>
       <c r="P60" s="2" t="s">
         <v>0</v>
@@ -3992,42 +4083,44 @@
         <v>57</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>36</v>
+        <v>68</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>35</v>
+        <v>67</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>34</v>
+        <v>66</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F61" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G61" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H61" s="2">
         <v>10.0</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="J61" s="2">
-        <v>5</v>
-      </c>
-      <c r="K61" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K61" s="2">
+        <v>1</v>
+      </c>
       <c r="L61" s="2"/>
       <c r="M61" s="2">
         <v>5</v>
       </c>
       <c r="N61" s="2">
-        <v>12.52</v>
+        <v>23.17</v>
       </c>
       <c r="O61" s="2" t="s">
-        <v>33</v>
+        <v>65</v>
       </c>
       <c r="P61" s="2" t="s">
         <v>0</v>
@@ -4038,19 +4131,19 @@
         <v>58</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>31</v>
+        <v>63</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>30</v>
+        <v>62</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F62" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G62" s="2">
         <v>10.0</v>
@@ -4070,10 +4163,10 @@
         <v>5</v>
       </c>
       <c r="N62" s="2">
-        <v>15.33</v>
+        <v>5.47</v>
       </c>
       <c r="O62" s="2" t="s">
-        <v>28</v>
+        <v>61</v>
       </c>
       <c r="P62" s="2" t="s">
         <v>0</v>
@@ -4084,13 +4177,13 @@
         <v>59</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>26</v>
+        <v>59</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>3</v>
@@ -4118,10 +4211,10 @@
         <v>5</v>
       </c>
       <c r="N63" s="2">
-        <v>9.45</v>
+        <v>15.8</v>
       </c>
       <c r="O63" s="2" t="s">
-        <v>24</v>
+        <v>57</v>
       </c>
       <c r="P63" s="2" t="s">
         <v>0</v>
@@ -4132,13 +4225,13 @@
         <v>60</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>23</v>
+        <v>56</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>3</v>
@@ -4147,29 +4240,27 @@
         <v>1</v>
       </c>
       <c r="G64" s="2">
-        <v>6.0</v>
+        <v>10.0</v>
       </c>
       <c r="H64" s="2">
         <v>10.0</v>
       </c>
       <c r="I64" s="2" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="J64" s="2">
-        <v>3</v>
-      </c>
-      <c r="K64" s="2">
-        <v>2</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K64" s="2"/>
       <c r="L64" s="2"/>
       <c r="M64" s="2">
         <v>5</v>
       </c>
       <c r="N64" s="2">
-        <v>3.6</v>
+        <v>4.07</v>
       </c>
       <c r="O64" s="2" t="s">
-        <v>20</v>
+        <v>53</v>
       </c>
       <c r="P64" s="2" t="s">
         <v>0</v>
@@ -4180,13 +4271,13 @@
         <v>61</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>19</v>
+        <v>52</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>3</v>
@@ -4195,29 +4286,29 @@
         <v>1</v>
       </c>
       <c r="G65" s="2">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="H65" s="2">
         <v>10.0</v>
       </c>
       <c r="I65" s="2" t="s">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="J65" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K65" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L65" s="2"/>
       <c r="M65" s="2">
         <v>5</v>
       </c>
       <c r="N65" s="2">
-        <v>10.15</v>
+        <v>21.8</v>
       </c>
       <c r="O65" s="2" t="s">
-        <v>15</v>
+        <v>49</v>
       </c>
       <c r="P65" s="2" t="s">
         <v>0</v>
@@ -4228,13 +4319,13 @@
         <v>62</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>14</v>
+        <v>48</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>13</v>
+        <v>47</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>12</v>
+        <v>46</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>3</v>
@@ -4262,10 +4353,10 @@
         <v>5</v>
       </c>
       <c r="N66" s="2">
-        <v>6.12</v>
+        <v>10.12</v>
       </c>
       <c r="O66" s="2" t="s">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="P66" s="2" t="s">
         <v>0</v>
@@ -4276,44 +4367,42 @@
         <v>63</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>9</v>
+        <v>43</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F67" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G67" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H67" s="2">
         <v>10.0</v>
       </c>
       <c r="I67" s="2" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="J67" s="2">
-        <v>4</v>
-      </c>
-      <c r="K67" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K67" s="2"/>
       <c r="L67" s="2"/>
       <c r="M67" s="2">
         <v>5</v>
       </c>
       <c r="N67" s="2">
-        <v>8.33</v>
+        <v>13.48</v>
       </c>
       <c r="O67" s="2" t="s">
-        <v>7</v>
+        <v>41</v>
       </c>
       <c r="P67" s="2" t="s">
         <v>0</v>
@@ -4324,13 +4413,13 @@
         <v>64</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>5</v>
+        <v>39</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="E68" s="2" t="s">
         <v>3</v>
@@ -4358,12 +4447,392 @@
         <v>5</v>
       </c>
       <c r="N68" s="2">
+        <v>10.6</v>
+      </c>
+      <c r="O68" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="P68" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:16">
+      <c r="A69" s="2">
+        <v>65</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F69" s="2">
+        <v>1</v>
+      </c>
+      <c r="G69" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="H69" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I69" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="J69" s="2">
+        <v>5</v>
+      </c>
+      <c r="K69" s="2"/>
+      <c r="L69" s="2"/>
+      <c r="M69" s="2">
+        <v>5</v>
+      </c>
+      <c r="N69" s="2">
+        <v>12.52</v>
+      </c>
+      <c r="O69" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P69" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:16">
+      <c r="A70" s="2">
+        <v>66</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F70" s="2">
+        <v>1</v>
+      </c>
+      <c r="G70" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="H70" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I70" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="J70" s="2">
+        <v>5</v>
+      </c>
+      <c r="K70" s="2"/>
+      <c r="L70" s="2"/>
+      <c r="M70" s="2">
+        <v>5</v>
+      </c>
+      <c r="N70" s="2">
+        <v>15.33</v>
+      </c>
+      <c r="O70" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P70" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:16">
+      <c r="A71" s="2">
+        <v>67</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F71" s="2">
+        <v>1</v>
+      </c>
+      <c r="G71" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="H71" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I71" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J71" s="2">
+        <v>4</v>
+      </c>
+      <c r="K71" s="2">
+        <v>1</v>
+      </c>
+      <c r="L71" s="2"/>
+      <c r="M71" s="2">
+        <v>5</v>
+      </c>
+      <c r="N71" s="2">
+        <v>9.45</v>
+      </c>
+      <c r="O71" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="P71" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:16">
+      <c r="A72" s="2">
+        <v>68</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F72" s="2">
+        <v>1</v>
+      </c>
+      <c r="G72" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="H72" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I72" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J72" s="2">
+        <v>3</v>
+      </c>
+      <c r="K72" s="2">
+        <v>2</v>
+      </c>
+      <c r="L72" s="2"/>
+      <c r="M72" s="2">
+        <v>5</v>
+      </c>
+      <c r="N72" s="2">
+        <v>3.6</v>
+      </c>
+      <c r="O72" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="P72" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:16">
+      <c r="A73" s="2">
+        <v>69</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F73" s="2">
+        <v>1</v>
+      </c>
+      <c r="G73" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="H73" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I73" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J73" s="2">
+        <v>3</v>
+      </c>
+      <c r="K73" s="2">
+        <v>2</v>
+      </c>
+      <c r="L73" s="2"/>
+      <c r="M73" s="2">
+        <v>5</v>
+      </c>
+      <c r="N73" s="2">
+        <v>10.15</v>
+      </c>
+      <c r="O73" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="P73" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:16">
+      <c r="A74" s="2">
+        <v>70</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F74" s="2">
+        <v>1</v>
+      </c>
+      <c r="G74" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="H74" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I74" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J74" s="2">
+        <v>4</v>
+      </c>
+      <c r="K74" s="2">
+        <v>1</v>
+      </c>
+      <c r="L74" s="2"/>
+      <c r="M74" s="2">
+        <v>5</v>
+      </c>
+      <c r="N74" s="2">
+        <v>6.12</v>
+      </c>
+      <c r="O74" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="P74" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:16">
+      <c r="A75" s="2">
+        <v>71</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F75" s="2">
+        <v>2</v>
+      </c>
+      <c r="G75" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="H75" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I75" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J75" s="2">
+        <v>4</v>
+      </c>
+      <c r="K75" s="2">
+        <v>1</v>
+      </c>
+      <c r="L75" s="2"/>
+      <c r="M75" s="2">
+        <v>5</v>
+      </c>
+      <c r="N75" s="2">
+        <v>8.33</v>
+      </c>
+      <c r="O75" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="P75" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:16">
+      <c r="A76" s="2">
+        <v>72</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F76" s="2">
+        <v>1</v>
+      </c>
+      <c r="G76" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="H76" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I76" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J76" s="2">
+        <v>4</v>
+      </c>
+      <c r="K76" s="2">
+        <v>1</v>
+      </c>
+      <c r="L76" s="2"/>
+      <c r="M76" s="2">
+        <v>5</v>
+      </c>
+      <c r="N76" s="2">
         <v>7.77</v>
       </c>
-      <c r="O68" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="P68" s="2" t="s">
+      <c r="O76" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="P76" s="2" t="s">
         <v>0</v>
       </c>
     </row>

--- a/2lit_center.xlsx
+++ b/2lit_center.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="312">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="392">
   <si>
     <t>ناجح ✓</t>
   </si>
@@ -896,6 +896,246 @@
     <t>Albaraamohamed</t>
   </si>
   <si>
+    <t>2026-03-01 20:44</t>
+  </si>
+  <si>
+    <t>01069408851</t>
+  </si>
+  <si>
+    <t>diaah700@gmail.com</t>
+  </si>
+  <si>
+    <t>ضياء هيثم ضياء السيد</t>
+  </si>
+  <si>
+    <t>2026-03-01 21:18</t>
+  </si>
+  <si>
+    <t>01011744851</t>
+  </si>
+  <si>
+    <t>abdelrahmanbedo@gmail.com</t>
+  </si>
+  <si>
+    <t>عبدالرحمن محمد محمد</t>
+  </si>
+  <si>
+    <t>2026-03-02 11:11</t>
+  </si>
+  <si>
+    <t>01555066805</t>
+  </si>
+  <si>
+    <t>mohammed.el.shazly2009@gmail.com</t>
+  </si>
+  <si>
+    <t>محمد أسامة محمد الشاذلي</t>
+  </si>
+  <si>
+    <t>2026-03-02 12:53</t>
+  </si>
+  <si>
+    <t>01001084045</t>
+  </si>
+  <si>
+    <t>engmohamedsaad62@gmail.com</t>
+  </si>
+  <si>
+    <t>محمد عبد الفتاح</t>
+  </si>
+  <si>
+    <t>2026-03-02 13:32</t>
+  </si>
+  <si>
+    <t>01150619596</t>
+  </si>
+  <si>
+    <t>ruokff593@gmail.com</t>
+  </si>
+  <si>
+    <t>ياسين حسين عبد الحميد عبد الله</t>
+  </si>
+  <si>
+    <t>2026-03-02 13:30</t>
+  </si>
+  <si>
+    <t>01125509128</t>
+  </si>
+  <si>
+    <t>marwanayman72009@gmail.com</t>
+  </si>
+  <si>
+    <t>مروان ايمن عاطف</t>
+  </si>
+  <si>
+    <t>2026-03-02 13:55</t>
+  </si>
+  <si>
+    <t>01062623490</t>
+  </si>
+  <si>
+    <t>omarzakaa1@gmail.com</t>
+  </si>
+  <si>
+    <t>omar zakaa</t>
+  </si>
+  <si>
+    <t>2026-03-02 16:35</t>
+  </si>
+  <si>
+    <t>01227631797</t>
+  </si>
+  <si>
+    <t>Sherifelkady199@gmail.com</t>
+  </si>
+  <si>
+    <t>SHERIF MOHAMED</t>
+  </si>
+  <si>
+    <t>2026-03-02 17:02</t>
+  </si>
+  <si>
+    <t>01222221223</t>
+  </si>
+  <si>
+    <t>elbadryjojo@gmail.com</t>
+  </si>
+  <si>
+    <t>لوجين</t>
+  </si>
+  <si>
+    <t>2026-03-02 17:20</t>
+  </si>
+  <si>
+    <t>01017803931</t>
+  </si>
+  <si>
+    <t>kokymzykm2007@gmail.com</t>
+  </si>
+  <si>
+    <t>Kenzy Mohamed</t>
+  </si>
+  <si>
+    <t>2026-03-02 17:27</t>
+  </si>
+  <si>
+    <t>01103622316</t>
+  </si>
+  <si>
+    <t>esraassaaddd30@gmail.com</t>
+  </si>
+  <si>
+    <t>Esraa saad</t>
+  </si>
+  <si>
+    <t>2026-03-02 17:29</t>
+  </si>
+  <si>
+    <t>01017099170</t>
+  </si>
+  <si>
+    <t>joudhanynabil@gmail.com</t>
+  </si>
+  <si>
+    <t>joudy</t>
+  </si>
+  <si>
+    <t>2026-03-02 18:00</t>
+  </si>
+  <si>
+    <t>01099284562</t>
+  </si>
+  <si>
+    <t>samehsami9@gmail.com</t>
+  </si>
+  <si>
+    <t>Mariam sameh sami</t>
+  </si>
+  <si>
+    <t>2026-03-02 18:21</t>
+  </si>
+  <si>
+    <t>01221970126</t>
+  </si>
+  <si>
+    <t>mareiaramez1@gmail.com</t>
+  </si>
+  <si>
+    <t>Maria ramez</t>
+  </si>
+  <si>
+    <t>2026-03-02 18:22</t>
+  </si>
+  <si>
+    <t>01123268908</t>
+  </si>
+  <si>
+    <t>habibaamrmm@icloud.com</t>
+  </si>
+  <si>
+    <t>Habiba amr eladwy</t>
+  </si>
+  <si>
+    <t>2026-03-02 18:35</t>
+  </si>
+  <si>
+    <t>+01122773746</t>
+  </si>
+  <si>
+    <t>begomego66@gmail.com</t>
+  </si>
+  <si>
+    <t>Begad Magdy Ali</t>
+  </si>
+  <si>
+    <t>2026-03-02 18:53</t>
+  </si>
+  <si>
+    <t>01204129971</t>
+  </si>
+  <si>
+    <t>paula.anis2712@gmail.com</t>
+  </si>
+  <si>
+    <t>Paula anis</t>
+  </si>
+  <si>
+    <t>2026-03-02 19:04</t>
+  </si>
+  <si>
+    <t>01016345481</t>
+  </si>
+  <si>
+    <t>ao5617814@gmail.com</t>
+  </si>
+  <si>
+    <t>Abdelrahman Ibrahim Hegazy</t>
+  </si>
+  <si>
+    <t>2026-03-02 19:09</t>
+  </si>
+  <si>
+    <t>01067922612</t>
+  </si>
+  <si>
+    <t>mayanmokhtar7@gmail.com</t>
+  </si>
+  <si>
+    <t>Mayan moktar Mohamed</t>
+  </si>
+  <si>
+    <t>2026-03-02 19:19</t>
+  </si>
+  <si>
+    <t>01012462274</t>
+  </si>
+  <si>
+    <t>Loujain1356@gmail.com</t>
+  </si>
+  <si>
+    <t>Loujain Osama elsayed</t>
+  </si>
+  <si>
     <t>الحالة</t>
   </si>
   <si>
@@ -950,7 +1190,7 @@
     <t>الدرجة الكاملة: 10 | درجة النجاح: 5.00</t>
   </si>
   <si>
-    <t>تاريخ التصدير: 2026-03-01 20:29</t>
+    <t>تاريخ التصدير: 2026-03-02 19:21</t>
   </si>
 </sst>
 </file>
@@ -1338,7 +1578,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:P76"/>
+  <dimension ref="A1:P96"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="true" style="0"/>
@@ -1361,67 +1601,67 @@
   <sheetData>
     <row r="1" spans="1:16">
       <c r="A1" s="3" t="s">
-        <v>309</v>
+        <v>389</v>
       </c>
     </row>
     <row r="2" spans="1:16">
       <c r="A2" s="3" t="s">
-        <v>310</v>
+        <v>390</v>
       </c>
     </row>
     <row r="3" spans="1:16">
       <c r="A3" s="3" t="s">
-        <v>311</v>
+        <v>391</v>
       </c>
     </row>
     <row r="4" spans="1:16">
       <c r="A4" s="1" t="s">
-        <v>308</v>
+        <v>388</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>307</v>
+        <v>387</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>306</v>
+        <v>386</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>305</v>
+        <v>385</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>304</v>
+        <v>384</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>303</v>
+        <v>383</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>302</v>
+        <v>382</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>301</v>
+        <v>381</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>300</v>
+        <v>380</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>299</v>
+        <v>379</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>298</v>
+        <v>378</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>297</v>
+        <v>377</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>296</v>
+        <v>376</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>295</v>
+        <v>375</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>294</v>
+        <v>374</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>293</v>
+        <v>373</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1429,44 +1669,42 @@
         <v>1</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>292</v>
+        <v>372</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>291</v>
+        <v>371</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>290</v>
+        <v>370</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F5" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G5" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H5" s="2">
         <v>10.0</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="J5" s="2">
-        <v>4</v>
-      </c>
-      <c r="K5" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K5" s="2"/>
       <c r="L5" s="2"/>
       <c r="M5" s="2">
         <v>5</v>
       </c>
       <c r="N5" s="2">
-        <v>3.0</v>
+        <v>6.55</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>289</v>
+        <v>369</v>
       </c>
       <c r="P5" s="2" t="s">
         <v>0</v>
@@ -1477,13 +1715,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>288</v>
+        <v>368</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>287</v>
+        <v>367</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>286</v>
+        <v>366</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>3</v>
@@ -1492,27 +1730,29 @@
         <v>1</v>
       </c>
       <c r="G6" s="2">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
       <c r="H6" s="2">
         <v>10.0</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="J6" s="2">
-        <v>5</v>
-      </c>
-      <c r="K6" s="2"/>
+        <v>3</v>
+      </c>
+      <c r="K6" s="2">
+        <v>2</v>
+      </c>
       <c r="L6" s="2"/>
       <c r="M6" s="2">
         <v>5</v>
       </c>
       <c r="N6" s="2">
-        <v>4.58</v>
+        <v>12.5</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>285</v>
+        <v>365</v>
       </c>
       <c r="P6" s="2" t="s">
         <v>0</v>
@@ -1523,13 +1763,13 @@
         <v>3</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>284</v>
+        <v>364</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>283</v>
+        <v>363</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>282</v>
+        <v>362</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>3</v>
@@ -1538,27 +1778,29 @@
         <v>1</v>
       </c>
       <c r="G7" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H7" s="2">
         <v>10.0</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="J7" s="2">
-        <v>5</v>
-      </c>
-      <c r="K7" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K7" s="2">
+        <v>1</v>
+      </c>
       <c r="L7" s="2"/>
       <c r="M7" s="2">
         <v>5</v>
       </c>
       <c r="N7" s="2">
-        <v>5.58</v>
+        <v>11.57</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>281</v>
+        <v>361</v>
       </c>
       <c r="P7" s="2" t="s">
         <v>0</v>
@@ -1569,13 +1811,13 @@
         <v>4</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>280</v>
+        <v>360</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>279</v>
+        <v>359</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>278</v>
+        <v>358</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>3</v>
@@ -1584,29 +1826,29 @@
         <v>1</v>
       </c>
       <c r="G8" s="2">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="H8" s="2">
         <v>10.0</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="J8" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K8" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L8" s="2"/>
       <c r="M8" s="2">
         <v>5</v>
       </c>
       <c r="N8" s="2">
-        <v>22.25</v>
+        <v>17.75</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>277</v>
+        <v>357</v>
       </c>
       <c r="P8" s="2" t="s">
         <v>0</v>
@@ -1617,13 +1859,13 @@
         <v>5</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>276</v>
+        <v>356</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="D9" s="2">
-        <v>201118200153</v>
+        <v>355</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>354</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>3</v>
@@ -1632,29 +1874,29 @@
         <v>1</v>
       </c>
       <c r="G9" s="2">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="H9" s="2">
         <v>10.0</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="J9" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K9" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L9" s="2"/>
       <c r="M9" s="2">
         <v>5</v>
       </c>
       <c r="N9" s="2">
-        <v>2.13</v>
+        <v>3.12</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>274</v>
+        <v>353</v>
       </c>
       <c r="P9" s="2" t="s">
         <v>0</v>
@@ -1665,13 +1907,13 @@
         <v>6</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>273</v>
+        <v>352</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>272</v>
+        <v>351</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>271</v>
+        <v>350</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>3</v>
@@ -1680,27 +1922,29 @@
         <v>1</v>
       </c>
       <c r="G10" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H10" s="2">
         <v>10.0</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="J10" s="2">
-        <v>5</v>
-      </c>
-      <c r="K10" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K10" s="2">
+        <v>1</v>
+      </c>
       <c r="L10" s="2"/>
       <c r="M10" s="2">
         <v>5</v>
       </c>
       <c r="N10" s="2">
-        <v>5.0</v>
+        <v>9.75</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>270</v>
+        <v>349</v>
       </c>
       <c r="P10" s="2" t="s">
         <v>0</v>
@@ -1711,13 +1955,13 @@
         <v>7</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>269</v>
+        <v>348</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>268</v>
+        <v>347</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>267</v>
+        <v>346</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>3</v>
@@ -1726,27 +1970,29 @@
         <v>1</v>
       </c>
       <c r="G11" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H11" s="2">
         <v>10.0</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="J11" s="2">
-        <v>5</v>
-      </c>
-      <c r="K11" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K11" s="2">
+        <v>1</v>
+      </c>
       <c r="L11" s="2"/>
       <c r="M11" s="2">
         <v>5</v>
       </c>
       <c r="N11" s="2">
-        <v>5.87</v>
+        <v>9.92</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>266</v>
+        <v>345</v>
       </c>
       <c r="P11" s="2" t="s">
         <v>0</v>
@@ -1757,13 +2003,13 @@
         <v>8</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>265</v>
+        <v>344</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>264</v>
+        <v>343</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>263</v>
+        <v>342</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>3</v>
@@ -1791,10 +2037,10 @@
         <v>5</v>
       </c>
       <c r="N12" s="2">
-        <v>8.92</v>
+        <v>15.08</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>262</v>
+        <v>341</v>
       </c>
       <c r="P12" s="2" t="s">
         <v>0</v>
@@ -1805,13 +2051,13 @@
         <v>9</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>261</v>
+        <v>340</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>260</v>
+        <v>339</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>259</v>
+        <v>338</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>3</v>
@@ -1820,29 +2066,27 @@
         <v>1</v>
       </c>
       <c r="G13" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H13" s="2">
         <v>10.0</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="J13" s="2">
-        <v>4</v>
-      </c>
-      <c r="K13" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K13" s="2"/>
       <c r="L13" s="2"/>
       <c r="M13" s="2">
         <v>5</v>
       </c>
       <c r="N13" s="2">
-        <v>5.8</v>
+        <v>12.9</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>258</v>
+        <v>337</v>
       </c>
       <c r="P13" s="2" t="s">
         <v>0</v>
@@ -1853,13 +2097,13 @@
         <v>10</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>257</v>
+        <v>336</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>256</v>
+        <v>335</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>255</v>
+        <v>334</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>3</v>
@@ -1885,10 +2129,10 @@
         <v>5</v>
       </c>
       <c r="N14" s="2">
-        <v>3.17</v>
+        <v>12.02</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>254</v>
+        <v>333</v>
       </c>
       <c r="P14" s="2" t="s">
         <v>0</v>
@@ -1899,13 +2143,13 @@
         <v>11</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>253</v>
+        <v>332</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>252</v>
+        <v>331</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>251</v>
+        <v>330</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>3</v>
@@ -1914,29 +2158,27 @@
         <v>1</v>
       </c>
       <c r="G15" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H15" s="2">
         <v>10.0</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="J15" s="2">
-        <v>4</v>
-      </c>
-      <c r="K15" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K15" s="2"/>
       <c r="L15" s="2"/>
       <c r="M15" s="2">
         <v>5</v>
       </c>
       <c r="N15" s="2">
-        <v>3.2</v>
+        <v>9.12</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>250</v>
+        <v>329</v>
       </c>
       <c r="P15" s="2" t="s">
         <v>0</v>
@@ -1947,13 +2189,13 @@
         <v>12</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>249</v>
+        <v>328</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>248</v>
+        <v>327</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>247</v>
+        <v>326</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>3</v>
@@ -1962,29 +2204,29 @@
         <v>1</v>
       </c>
       <c r="G16" s="2">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
       <c r="H16" s="2">
         <v>10.0</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="J16" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K16" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L16" s="2"/>
       <c r="M16" s="2">
         <v>5</v>
       </c>
       <c r="N16" s="2">
-        <v>14.28</v>
+        <v>19.67</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>246</v>
+        <v>325</v>
       </c>
       <c r="P16" s="2" t="s">
         <v>0</v>
@@ -1995,13 +2237,13 @@
         <v>13</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>245</v>
+        <v>324</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>244</v>
+        <v>323</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>243</v>
+        <v>322</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>3</v>
@@ -2010,29 +2252,29 @@
         <v>1</v>
       </c>
       <c r="G17" s="2">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
       <c r="H17" s="2">
         <v>10.0</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="J17" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K17" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L17" s="2"/>
       <c r="M17" s="2">
         <v>5</v>
       </c>
       <c r="N17" s="2">
-        <v>12.48</v>
+        <v>9.32</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>242</v>
+        <v>321</v>
       </c>
       <c r="P17" s="2" t="s">
         <v>0</v>
@@ -2043,13 +2285,13 @@
         <v>14</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>241</v>
+        <v>320</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>240</v>
+        <v>319</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>239</v>
+        <v>318</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>3</v>
@@ -2058,29 +2300,27 @@
         <v>1</v>
       </c>
       <c r="G18" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H18" s="2">
         <v>10.0</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="J18" s="2">
-        <v>4</v>
-      </c>
-      <c r="K18" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K18" s="2"/>
       <c r="L18" s="2"/>
       <c r="M18" s="2">
         <v>5</v>
       </c>
       <c r="N18" s="2">
-        <v>4.22</v>
+        <v>24.92</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>238</v>
+        <v>317</v>
       </c>
       <c r="P18" s="2" t="s">
         <v>0</v>
@@ -2091,19 +2331,19 @@
         <v>15</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>237</v>
+        <v>316</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>236</v>
+        <v>315</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>235</v>
+        <v>314</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F19" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G19" s="2">
         <v>6.0</v>
@@ -2125,10 +2365,10 @@
         <v>5</v>
       </c>
       <c r="N19" s="2">
-        <v>8.42</v>
+        <v>5.23</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>234</v>
+        <v>313</v>
       </c>
       <c r="P19" s="2" t="s">
         <v>0</v>
@@ -2139,13 +2379,13 @@
         <v>16</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>233</v>
+        <v>312</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>232</v>
+        <v>311</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>231</v>
+        <v>310</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>3</v>
@@ -2154,29 +2394,29 @@
         <v>1</v>
       </c>
       <c r="G20" s="2">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
       <c r="H20" s="2">
         <v>10.0</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="J20" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K20" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L20" s="2"/>
       <c r="M20" s="2">
         <v>5</v>
       </c>
       <c r="N20" s="2">
-        <v>7.37</v>
+        <v>22.08</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>192</v>
+        <v>309</v>
       </c>
       <c r="P20" s="2" t="s">
         <v>0</v>
@@ -2187,13 +2427,13 @@
         <v>17</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>230</v>
+        <v>308</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>229</v>
+        <v>307</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>228</v>
+        <v>306</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>3</v>
@@ -2202,27 +2442,29 @@
         <v>1</v>
       </c>
       <c r="G21" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H21" s="2">
         <v>10.0</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="J21" s="2">
-        <v>5</v>
-      </c>
-      <c r="K21" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K21" s="2">
+        <v>1</v>
+      </c>
       <c r="L21" s="2"/>
       <c r="M21" s="2">
         <v>5</v>
       </c>
       <c r="N21" s="2">
-        <v>23.67</v>
+        <v>10.18</v>
       </c>
       <c r="O21" s="2" t="s">
-        <v>227</v>
+        <v>305</v>
       </c>
       <c r="P21" s="2" t="s">
         <v>0</v>
@@ -2233,13 +2475,13 @@
         <v>18</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>226</v>
+        <v>304</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>225</v>
+        <v>303</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>224</v>
+        <v>302</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>3</v>
@@ -2248,29 +2490,27 @@
         <v>1</v>
       </c>
       <c r="G22" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H22" s="2">
         <v>10.0</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="J22" s="2">
-        <v>4</v>
-      </c>
-      <c r="K22" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K22" s="2"/>
       <c r="L22" s="2"/>
       <c r="M22" s="2">
         <v>5</v>
       </c>
       <c r="N22" s="2">
-        <v>15.78</v>
+        <v>25.72</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>223</v>
+        <v>301</v>
       </c>
       <c r="P22" s="2" t="s">
         <v>0</v>
@@ -2281,13 +2521,13 @@
         <v>19</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>222</v>
+        <v>300</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>221</v>
+        <v>299</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>220</v>
+        <v>298</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>3</v>
@@ -2296,27 +2536,29 @@
         <v>1</v>
       </c>
       <c r="G23" s="2">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
       <c r="H23" s="2">
         <v>10.0</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="J23" s="2">
-        <v>5</v>
-      </c>
-      <c r="K23" s="2"/>
+        <v>3</v>
+      </c>
+      <c r="K23" s="2">
+        <v>2</v>
+      </c>
       <c r="L23" s="2"/>
       <c r="M23" s="2">
         <v>5</v>
       </c>
       <c r="N23" s="2">
-        <v>7.02</v>
+        <v>13.57</v>
       </c>
       <c r="O23" s="2" t="s">
-        <v>219</v>
+        <v>297</v>
       </c>
       <c r="P23" s="2" t="s">
         <v>0</v>
@@ -2327,13 +2569,13 @@
         <v>20</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>218</v>
+        <v>296</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>217</v>
+        <v>295</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>216</v>
+        <v>294</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>3</v>
@@ -2342,29 +2584,27 @@
         <v>1</v>
       </c>
       <c r="G24" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H24" s="2">
         <v>10.0</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="J24" s="2">
-        <v>4</v>
-      </c>
-      <c r="K24" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K24" s="2"/>
       <c r="L24" s="2"/>
       <c r="M24" s="2">
         <v>5</v>
       </c>
       <c r="N24" s="2">
-        <v>7.05</v>
+        <v>27.03</v>
       </c>
       <c r="O24" s="2" t="s">
-        <v>215</v>
+        <v>293</v>
       </c>
       <c r="P24" s="2" t="s">
         <v>0</v>
@@ -2375,47 +2615,47 @@
         <v>21</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>214</v>
+        <v>292</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>213</v>
+        <v>291</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>212</v>
+        <v>290</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F25" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G25" s="2">
-        <v>2.0</v>
+        <v>8.0</v>
       </c>
       <c r="H25" s="2">
         <v>10.0</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>163</v>
+        <v>2</v>
       </c>
       <c r="J25" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K25" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L25" s="2"/>
       <c r="M25" s="2">
         <v>5</v>
       </c>
       <c r="N25" s="2">
-        <v>5.35</v>
+        <v>3.0</v>
       </c>
       <c r="O25" s="2" t="s">
-        <v>211</v>
+        <v>289</v>
       </c>
       <c r="P25" s="2" t="s">
-        <v>161</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -2423,44 +2663,42 @@
         <v>22</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>210</v>
+        <v>288</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>209</v>
+        <v>287</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>208</v>
+        <v>286</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F26" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G26" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H26" s="2">
         <v>10.0</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="J26" s="2">
-        <v>4</v>
-      </c>
-      <c r="K26" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K26" s="2"/>
       <c r="L26" s="2"/>
       <c r="M26" s="2">
         <v>5</v>
       </c>
       <c r="N26" s="2">
-        <v>3.77</v>
+        <v>4.58</v>
       </c>
       <c r="O26" s="2" t="s">
-        <v>207</v>
+        <v>285</v>
       </c>
       <c r="P26" s="2" t="s">
         <v>0</v>
@@ -2471,13 +2709,13 @@
         <v>23</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>206</v>
+        <v>284</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>205</v>
+        <v>283</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>204</v>
+        <v>282</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>3</v>
@@ -2486,29 +2724,27 @@
         <v>1</v>
       </c>
       <c r="G27" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H27" s="2">
         <v>10.0</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="J27" s="2">
-        <v>4</v>
-      </c>
-      <c r="K27" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K27" s="2"/>
       <c r="L27" s="2"/>
       <c r="M27" s="2">
         <v>5</v>
       </c>
       <c r="N27" s="2">
-        <v>11.42</v>
+        <v>5.58</v>
       </c>
       <c r="O27" s="2" t="s">
-        <v>203</v>
+        <v>281</v>
       </c>
       <c r="P27" s="2" t="s">
         <v>0</v>
@@ -2519,13 +2755,13 @@
         <v>24</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>202</v>
+        <v>280</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>201</v>
+        <v>279</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>200</v>
+        <v>278</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>3</v>
@@ -2553,10 +2789,10 @@
         <v>5</v>
       </c>
       <c r="N28" s="2">
-        <v>3.57</v>
+        <v>22.25</v>
       </c>
       <c r="O28" s="2" t="s">
-        <v>199</v>
+        <v>277</v>
       </c>
       <c r="P28" s="2" t="s">
         <v>0</v>
@@ -2567,13 +2803,13 @@
         <v>25</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>198</v>
+        <v>276</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>196</v>
+        <v>275</v>
+      </c>
+      <c r="D29" s="2">
+        <v>201118200153</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>3</v>
@@ -2582,29 +2818,29 @@
         <v>1</v>
       </c>
       <c r="G29" s="2">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
       <c r="H29" s="2">
         <v>10.0</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="J29" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K29" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L29" s="2"/>
       <c r="M29" s="2">
         <v>5</v>
       </c>
       <c r="N29" s="2">
-        <v>7.5</v>
+        <v>2.13</v>
       </c>
       <c r="O29" s="2" t="s">
-        <v>184</v>
+        <v>274</v>
       </c>
       <c r="P29" s="2" t="s">
         <v>0</v>
@@ -2615,13 +2851,13 @@
         <v>26</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>195</v>
+        <v>273</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>194</v>
+        <v>272</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>193</v>
+        <v>271</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>3</v>
@@ -2630,29 +2866,27 @@
         <v>1</v>
       </c>
       <c r="G30" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H30" s="2">
         <v>10.0</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="J30" s="2">
-        <v>4</v>
-      </c>
-      <c r="K30" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K30" s="2"/>
       <c r="L30" s="2"/>
       <c r="M30" s="2">
         <v>5</v>
       </c>
       <c r="N30" s="2">
-        <v>39.38</v>
+        <v>5.0</v>
       </c>
       <c r="O30" s="2" t="s">
-        <v>192</v>
+        <v>270</v>
       </c>
       <c r="P30" s="2" t="s">
         <v>0</v>
@@ -2663,13 +2897,13 @@
         <v>27</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>191</v>
+        <v>269</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>189</v>
+        <v>267</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>3</v>
@@ -2678,29 +2912,27 @@
         <v>1</v>
       </c>
       <c r="G31" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H31" s="2">
         <v>10.0</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="J31" s="2">
-        <v>4</v>
-      </c>
-      <c r="K31" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K31" s="2"/>
       <c r="L31" s="2"/>
       <c r="M31" s="2">
         <v>5</v>
       </c>
       <c r="N31" s="2">
-        <v>11.68</v>
+        <v>5.87</v>
       </c>
       <c r="O31" s="2" t="s">
-        <v>188</v>
+        <v>266</v>
       </c>
       <c r="P31" s="2" t="s">
         <v>0</v>
@@ -2711,13 +2943,13 @@
         <v>28</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>187</v>
+        <v>265</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>186</v>
+        <v>264</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>185</v>
+        <v>263</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>3</v>
@@ -2745,10 +2977,10 @@
         <v>5</v>
       </c>
       <c r="N32" s="2">
-        <v>15.92</v>
+        <v>8.92</v>
       </c>
       <c r="O32" s="2" t="s">
-        <v>184</v>
+        <v>262</v>
       </c>
       <c r="P32" s="2" t="s">
         <v>0</v>
@@ -2759,13 +2991,13 @@
         <v>29</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>183</v>
+        <v>261</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>182</v>
+        <v>260</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>181</v>
+        <v>259</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>3</v>
@@ -2793,10 +3025,10 @@
         <v>5</v>
       </c>
       <c r="N33" s="2">
-        <v>6.17</v>
+        <v>5.8</v>
       </c>
       <c r="O33" s="2" t="s">
-        <v>180</v>
+        <v>258</v>
       </c>
       <c r="P33" s="2" t="s">
         <v>0</v>
@@ -2807,13 +3039,13 @@
         <v>30</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>179</v>
+        <v>257</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>178</v>
+        <v>256</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>177</v>
+        <v>255</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>3</v>
@@ -2839,10 +3071,10 @@
         <v>5</v>
       </c>
       <c r="N34" s="2">
-        <v>5.92</v>
+        <v>3.17</v>
       </c>
       <c r="O34" s="2" t="s">
-        <v>176</v>
+        <v>254</v>
       </c>
       <c r="P34" s="2" t="s">
         <v>0</v>
@@ -2853,13 +3085,13 @@
         <v>31</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>175</v>
+        <v>253</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>174</v>
+        <v>252</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>173</v>
+        <v>251</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>3</v>
@@ -2868,32 +3100,32 @@
         <v>1</v>
       </c>
       <c r="G35" s="2">
-        <v>4.0</v>
+        <v>8.0</v>
       </c>
       <c r="H35" s="2">
         <v>10.0</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>172</v>
+        <v>2</v>
       </c>
       <c r="J35" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K35" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L35" s="2"/>
       <c r="M35" s="2">
         <v>5</v>
       </c>
       <c r="N35" s="2">
-        <v>5.95</v>
+        <v>3.2</v>
       </c>
       <c r="O35" s="2" t="s">
-        <v>171</v>
+        <v>250</v>
       </c>
       <c r="P35" s="2" t="s">
-        <v>161</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -2901,13 +3133,13 @@
         <v>32</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>170</v>
+        <v>249</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>169</v>
+        <v>248</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>168</v>
+        <v>247</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>3</v>
@@ -2916,27 +3148,29 @@
         <v>1</v>
       </c>
       <c r="G36" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H36" s="2">
         <v>10.0</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="J36" s="2">
-        <v>5</v>
-      </c>
-      <c r="K36" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K36" s="2">
+        <v>1</v>
+      </c>
       <c r="L36" s="2"/>
       <c r="M36" s="2">
         <v>5</v>
       </c>
       <c r="N36" s="2">
-        <v>9.08</v>
+        <v>14.28</v>
       </c>
       <c r="O36" s="2" t="s">
-        <v>167</v>
+        <v>246</v>
       </c>
       <c r="P36" s="2" t="s">
         <v>0</v>
@@ -2947,13 +3181,13 @@
         <v>33</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>166</v>
+        <v>245</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>165</v>
+        <v>244</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>164</v>
+        <v>243</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>3</v>
@@ -2962,32 +3196,32 @@
         <v>1</v>
       </c>
       <c r="G37" s="2">
-        <v>2.0</v>
+        <v>8.0</v>
       </c>
       <c r="H37" s="2">
         <v>10.0</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>163</v>
+        <v>2</v>
       </c>
       <c r="J37" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K37" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L37" s="2"/>
       <c r="M37" s="2">
         <v>5</v>
       </c>
       <c r="N37" s="2">
-        <v>10.48</v>
+        <v>12.48</v>
       </c>
       <c r="O37" s="2" t="s">
-        <v>162</v>
+        <v>242</v>
       </c>
       <c r="P37" s="2" t="s">
-        <v>161</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -2995,13 +3229,13 @@
         <v>34</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>160</v>
+        <v>241</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>159</v>
+        <v>240</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>158</v>
+        <v>239</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>3</v>
@@ -3029,10 +3263,10 @@
         <v>5</v>
       </c>
       <c r="N38" s="2">
-        <v>13.42</v>
+        <v>4.22</v>
       </c>
       <c r="O38" s="2" t="s">
-        <v>157</v>
+        <v>238</v>
       </c>
       <c r="P38" s="2" t="s">
         <v>0</v>
@@ -3043,13 +3277,13 @@
         <v>35</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>156</v>
+        <v>237</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>155</v>
+        <v>236</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>154</v>
+        <v>235</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>3</v>
@@ -3077,10 +3311,10 @@
         <v>5</v>
       </c>
       <c r="N39" s="2">
-        <v>2.57</v>
+        <v>8.42</v>
       </c>
       <c r="O39" s="2" t="s">
-        <v>153</v>
+        <v>234</v>
       </c>
       <c r="P39" s="2" t="s">
         <v>0</v>
@@ -3091,13 +3325,13 @@
         <v>36</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>152</v>
+        <v>233</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>151</v>
+        <v>232</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>150</v>
+        <v>231</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>3</v>
@@ -3106,27 +3340,29 @@
         <v>1</v>
       </c>
       <c r="G40" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H40" s="2">
         <v>10.0</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="J40" s="2">
-        <v>5</v>
-      </c>
-      <c r="K40" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K40" s="2">
+        <v>1</v>
+      </c>
       <c r="L40" s="2"/>
       <c r="M40" s="2">
         <v>5</v>
       </c>
       <c r="N40" s="2">
-        <v>1.65</v>
+        <v>7.37</v>
       </c>
       <c r="O40" s="2" t="s">
-        <v>149</v>
+        <v>192</v>
       </c>
       <c r="P40" s="2" t="s">
         <v>0</v>
@@ -3137,13 +3373,13 @@
         <v>37</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>148</v>
+        <v>230</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>147</v>
+        <v>229</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>146</v>
+        <v>228</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>3</v>
@@ -3152,29 +3388,27 @@
         <v>1</v>
       </c>
       <c r="G41" s="2">
-        <v>6.0</v>
+        <v>10.0</v>
       </c>
       <c r="H41" s="2">
         <v>10.0</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="J41" s="2">
-        <v>3</v>
-      </c>
-      <c r="K41" s="2">
-        <v>2</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K41" s="2"/>
       <c r="L41" s="2"/>
       <c r="M41" s="2">
         <v>5</v>
       </c>
       <c r="N41" s="2">
-        <v>12.1</v>
+        <v>23.67</v>
       </c>
       <c r="O41" s="2" t="s">
-        <v>145</v>
+        <v>227</v>
       </c>
       <c r="P41" s="2" t="s">
         <v>0</v>
@@ -3185,13 +3419,13 @@
         <v>38</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>144</v>
+        <v>226</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>143</v>
+        <v>225</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>142</v>
+        <v>224</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>3</v>
@@ -3200,29 +3434,29 @@
         <v>1</v>
       </c>
       <c r="G42" s="2">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="H42" s="2">
         <v>10.0</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="J42" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K42" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L42" s="2"/>
       <c r="M42" s="2">
         <v>5</v>
       </c>
       <c r="N42" s="2">
-        <v>18.58</v>
+        <v>15.78</v>
       </c>
       <c r="O42" s="2" t="s">
-        <v>141</v>
+        <v>223</v>
       </c>
       <c r="P42" s="2" t="s">
         <v>0</v>
@@ -3233,13 +3467,13 @@
         <v>39</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>140</v>
+        <v>222</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>139</v>
+        <v>221</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>138</v>
+        <v>220</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>3</v>
@@ -3265,10 +3499,10 @@
         <v>5</v>
       </c>
       <c r="N43" s="2">
-        <v>18.03</v>
+        <v>7.02</v>
       </c>
       <c r="O43" s="2" t="s">
-        <v>137</v>
+        <v>219</v>
       </c>
       <c r="P43" s="2" t="s">
         <v>0</v>
@@ -3279,13 +3513,13 @@
         <v>40</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>136</v>
+        <v>218</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>135</v>
+        <v>217</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>134</v>
+        <v>216</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>3</v>
@@ -3313,10 +3547,10 @@
         <v>5</v>
       </c>
       <c r="N44" s="2">
-        <v>9.68</v>
+        <v>7.05</v>
       </c>
       <c r="O44" s="2" t="s">
-        <v>133</v>
+        <v>215</v>
       </c>
       <c r="P44" s="2" t="s">
         <v>0</v>
@@ -3327,13 +3561,13 @@
         <v>41</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>132</v>
+        <v>214</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>131</v>
+        <v>213</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>130</v>
+        <v>212</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>3</v>
@@ -3342,32 +3576,32 @@
         <v>1</v>
       </c>
       <c r="G45" s="2">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
       <c r="H45" s="2">
         <v>10.0</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>16</v>
+        <v>163</v>
       </c>
       <c r="J45" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K45" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L45" s="2"/>
       <c r="M45" s="2">
         <v>5</v>
       </c>
       <c r="N45" s="2">
-        <v>14.13</v>
+        <v>5.35</v>
       </c>
       <c r="O45" s="2" t="s">
-        <v>129</v>
+        <v>211</v>
       </c>
       <c r="P45" s="2" t="s">
-        <v>0</v>
+        <v>161</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -3375,19 +3609,19 @@
         <v>42</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>128</v>
+        <v>210</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>127</v>
+        <v>209</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>126</v>
+        <v>208</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F46" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G46" s="2">
         <v>8.0</v>
@@ -3409,10 +3643,10 @@
         <v>5</v>
       </c>
       <c r="N46" s="2">
-        <v>11.45</v>
+        <v>3.77</v>
       </c>
       <c r="O46" s="2" t="s">
-        <v>125</v>
+        <v>207</v>
       </c>
       <c r="P46" s="2" t="s">
         <v>0</v>
@@ -3423,13 +3657,13 @@
         <v>43</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>124</v>
+        <v>206</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>123</v>
+        <v>205</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>122</v>
+        <v>204</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>3</v>
@@ -3457,10 +3691,10 @@
         <v>5</v>
       </c>
       <c r="N47" s="2">
-        <v>12.55</v>
+        <v>11.42</v>
       </c>
       <c r="O47" s="2" t="s">
-        <v>121</v>
+        <v>203</v>
       </c>
       <c r="P47" s="2" t="s">
         <v>0</v>
@@ -3471,13 +3705,13 @@
         <v>44</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>120</v>
+        <v>202</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>119</v>
+        <v>201</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>118</v>
+        <v>200</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>3</v>
@@ -3486,27 +3720,29 @@
         <v>1</v>
       </c>
       <c r="G48" s="2">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
       <c r="H48" s="2">
         <v>10.0</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="J48" s="2">
-        <v>5</v>
-      </c>
-      <c r="K48" s="2"/>
+        <v>3</v>
+      </c>
+      <c r="K48" s="2">
+        <v>2</v>
+      </c>
       <c r="L48" s="2"/>
       <c r="M48" s="2">
         <v>5</v>
       </c>
       <c r="N48" s="2">
-        <v>6.58</v>
+        <v>3.57</v>
       </c>
       <c r="O48" s="2" t="s">
-        <v>117</v>
+        <v>199</v>
       </c>
       <c r="P48" s="2" t="s">
         <v>0</v>
@@ -3517,13 +3753,13 @@
         <v>45</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>116</v>
+        <v>198</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>115</v>
+        <v>197</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>114</v>
+        <v>196</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>3</v>
@@ -3551,10 +3787,10 @@
         <v>5</v>
       </c>
       <c r="N49" s="2">
-        <v>18.78</v>
+        <v>7.5</v>
       </c>
       <c r="O49" s="2" t="s">
-        <v>113</v>
+        <v>184</v>
       </c>
       <c r="P49" s="2" t="s">
         <v>0</v>
@@ -3565,13 +3801,13 @@
         <v>46</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>112</v>
+        <v>195</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>111</v>
+        <v>194</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>110</v>
+        <v>193</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>3</v>
@@ -3599,10 +3835,10 @@
         <v>5</v>
       </c>
       <c r="N50" s="2">
-        <v>12.03</v>
+        <v>39.38</v>
       </c>
       <c r="O50" s="2" t="s">
-        <v>109</v>
+        <v>192</v>
       </c>
       <c r="P50" s="2" t="s">
         <v>0</v>
@@ -3613,13 +3849,13 @@
         <v>47</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>108</v>
+        <v>191</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>107</v>
+        <v>190</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>106</v>
+        <v>189</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>3</v>
@@ -3628,29 +3864,29 @@
         <v>1</v>
       </c>
       <c r="G51" s="2">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="H51" s="2">
         <v>10.0</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="J51" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K51" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L51" s="2"/>
       <c r="M51" s="2">
         <v>5</v>
       </c>
       <c r="N51" s="2">
-        <v>25.12</v>
+        <v>11.68</v>
       </c>
       <c r="O51" s="2" t="s">
-        <v>105</v>
+        <v>188</v>
       </c>
       <c r="P51" s="2" t="s">
         <v>0</v>
@@ -3661,13 +3897,13 @@
         <v>48</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>104</v>
+        <v>187</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>103</v>
+        <v>186</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>102</v>
+        <v>185</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>3</v>
@@ -3676,29 +3912,29 @@
         <v>1</v>
       </c>
       <c r="G52" s="2">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="H52" s="2">
         <v>10.0</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="J52" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K52" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L52" s="2"/>
       <c r="M52" s="2">
         <v>5</v>
       </c>
       <c r="N52" s="2">
-        <v>16.98</v>
+        <v>15.92</v>
       </c>
       <c r="O52" s="2" t="s">
-        <v>101</v>
+        <v>184</v>
       </c>
       <c r="P52" s="2" t="s">
         <v>0</v>
@@ -3709,13 +3945,13 @@
         <v>49</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>100</v>
+        <v>183</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>99</v>
+        <v>182</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>98</v>
+        <v>181</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>3</v>
@@ -3724,27 +3960,29 @@
         <v>1</v>
       </c>
       <c r="G53" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H53" s="2">
         <v>10.0</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="J53" s="2">
-        <v>5</v>
-      </c>
-      <c r="K53" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K53" s="2">
+        <v>1</v>
+      </c>
       <c r="L53" s="2"/>
       <c r="M53" s="2">
         <v>5</v>
       </c>
       <c r="N53" s="2">
-        <v>1.45</v>
+        <v>6.17</v>
       </c>
       <c r="O53" s="2" t="s">
-        <v>97</v>
+        <v>180</v>
       </c>
       <c r="P53" s="2" t="s">
         <v>0</v>
@@ -3755,19 +3993,19 @@
         <v>50</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>96</v>
+        <v>179</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>95</v>
+        <v>178</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>94</v>
+        <v>177</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F54" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G54" s="2">
         <v>10.0</v>
@@ -3787,10 +4025,10 @@
         <v>5</v>
       </c>
       <c r="N54" s="2">
-        <v>6.18</v>
+        <v>5.92</v>
       </c>
       <c r="O54" s="2" t="s">
-        <v>93</v>
+        <v>176</v>
       </c>
       <c r="P54" s="2" t="s">
         <v>0</v>
@@ -3801,13 +4039,13 @@
         <v>51</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>92</v>
+        <v>175</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>91</v>
+        <v>174</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>90</v>
+        <v>173</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>3</v>
@@ -3816,30 +4054,32 @@
         <v>1</v>
       </c>
       <c r="G55" s="2">
-        <v>10.0</v>
+        <v>4.0</v>
       </c>
       <c r="H55" s="2">
         <v>10.0</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>29</v>
+        <v>172</v>
       </c>
       <c r="J55" s="2">
-        <v>5</v>
-      </c>
-      <c r="K55" s="2"/>
+        <v>2</v>
+      </c>
+      <c r="K55" s="2">
+        <v>3</v>
+      </c>
       <c r="L55" s="2"/>
       <c r="M55" s="2">
         <v>5</v>
       </c>
       <c r="N55" s="2">
-        <v>6.13</v>
+        <v>5.95</v>
       </c>
       <c r="O55" s="2" t="s">
-        <v>89</v>
+        <v>171</v>
       </c>
       <c r="P55" s="2" t="s">
-        <v>0</v>
+        <v>161</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -3847,13 +4087,13 @@
         <v>52</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>88</v>
+        <v>170</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>87</v>
+        <v>169</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>86</v>
+        <v>168</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>3</v>
@@ -3862,29 +4102,27 @@
         <v>1</v>
       </c>
       <c r="G56" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H56" s="2">
         <v>10.0</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="J56" s="2">
-        <v>4</v>
-      </c>
-      <c r="K56" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K56" s="2"/>
       <c r="L56" s="2"/>
       <c r="M56" s="2">
         <v>5</v>
       </c>
       <c r="N56" s="2">
-        <v>2.4</v>
+        <v>9.08</v>
       </c>
       <c r="O56" s="2" t="s">
-        <v>85</v>
+        <v>167</v>
       </c>
       <c r="P56" s="2" t="s">
         <v>0</v>
@@ -3895,13 +4133,13 @@
         <v>53</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>84</v>
+        <v>166</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>83</v>
+        <v>165</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>82</v>
+        <v>164</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>3</v>
@@ -3910,32 +4148,32 @@
         <v>1</v>
       </c>
       <c r="G57" s="2">
-        <v>8.0</v>
+        <v>2.0</v>
       </c>
       <c r="H57" s="2">
         <v>10.0</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>2</v>
+        <v>163</v>
       </c>
       <c r="J57" s="2">
+        <v>1</v>
+      </c>
+      <c r="K57" s="2">
         <v>4</v>
-      </c>
-      <c r="K57" s="2">
-        <v>1</v>
       </c>
       <c r="L57" s="2"/>
       <c r="M57" s="2">
         <v>5</v>
       </c>
       <c r="N57" s="2">
-        <v>15.75</v>
+        <v>10.48</v>
       </c>
       <c r="O57" s="2" t="s">
-        <v>81</v>
+        <v>162</v>
       </c>
       <c r="P57" s="2" t="s">
-        <v>0</v>
+        <v>161</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -3943,13 +4181,13 @@
         <v>54</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>80</v>
+        <v>160</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>79</v>
+        <v>159</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>78</v>
+        <v>158</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>3</v>
@@ -3958,27 +4196,29 @@
         <v>1</v>
       </c>
       <c r="G58" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H58" s="2">
         <v>10.0</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="J58" s="2">
-        <v>5</v>
-      </c>
-      <c r="K58" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K58" s="2">
+        <v>1</v>
+      </c>
       <c r="L58" s="2"/>
       <c r="M58" s="2">
         <v>5</v>
       </c>
       <c r="N58" s="2">
-        <v>2.17</v>
+        <v>13.42</v>
       </c>
       <c r="O58" s="2" t="s">
-        <v>77</v>
+        <v>157</v>
       </c>
       <c r="P58" s="2" t="s">
         <v>0</v>
@@ -3989,13 +4229,13 @@
         <v>55</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>76</v>
+        <v>156</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>75</v>
+        <v>155</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>74</v>
+        <v>154</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>3</v>
@@ -4023,10 +4263,10 @@
         <v>5</v>
       </c>
       <c r="N59" s="2">
-        <v>9.5</v>
+        <v>2.57</v>
       </c>
       <c r="O59" s="2" t="s">
-        <v>73</v>
+        <v>153</v>
       </c>
       <c r="P59" s="2" t="s">
         <v>0</v>
@@ -4037,13 +4277,13 @@
         <v>56</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>72</v>
+        <v>152</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>71</v>
+        <v>151</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>70</v>
+        <v>150</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>3</v>
@@ -4069,10 +4309,10 @@
         <v>5</v>
       </c>
       <c r="N60" s="2">
-        <v>10.75</v>
+        <v>1.65</v>
       </c>
       <c r="O60" s="2" t="s">
-        <v>69</v>
+        <v>149</v>
       </c>
       <c r="P60" s="2" t="s">
         <v>0</v>
@@ -4083,44 +4323,44 @@
         <v>57</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>68</v>
+        <v>148</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>67</v>
+        <v>147</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>66</v>
+        <v>146</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F61" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G61" s="2">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
       <c r="H61" s="2">
         <v>10.0</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="J61" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K61" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L61" s="2"/>
       <c r="M61" s="2">
         <v>5</v>
       </c>
       <c r="N61" s="2">
-        <v>23.17</v>
+        <v>12.1</v>
       </c>
       <c r="O61" s="2" t="s">
-        <v>65</v>
+        <v>145</v>
       </c>
       <c r="P61" s="2" t="s">
         <v>0</v>
@@ -4131,42 +4371,44 @@
         <v>58</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>64</v>
+        <v>144</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>63</v>
+        <v>143</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>62</v>
+        <v>142</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F62" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G62" s="2">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
       <c r="H62" s="2">
         <v>10.0</v>
       </c>
       <c r="I62" s="2" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="J62" s="2">
-        <v>5</v>
-      </c>
-      <c r="K62" s="2"/>
+        <v>3</v>
+      </c>
+      <c r="K62" s="2">
+        <v>2</v>
+      </c>
       <c r="L62" s="2"/>
       <c r="M62" s="2">
         <v>5</v>
       </c>
       <c r="N62" s="2">
-        <v>5.47</v>
+        <v>18.58</v>
       </c>
       <c r="O62" s="2" t="s">
-        <v>61</v>
+        <v>141</v>
       </c>
       <c r="P62" s="2" t="s">
         <v>0</v>
@@ -4177,13 +4419,13 @@
         <v>59</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>60</v>
+        <v>140</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>59</v>
+        <v>139</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>58</v>
+        <v>138</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>3</v>
@@ -4192,29 +4434,27 @@
         <v>1</v>
       </c>
       <c r="G63" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H63" s="2">
         <v>10.0</v>
       </c>
       <c r="I63" s="2" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="J63" s="2">
-        <v>4</v>
-      </c>
-      <c r="K63" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K63" s="2"/>
       <c r="L63" s="2"/>
       <c r="M63" s="2">
         <v>5</v>
       </c>
       <c r="N63" s="2">
-        <v>15.8</v>
+        <v>18.03</v>
       </c>
       <c r="O63" s="2" t="s">
-        <v>57</v>
+        <v>137</v>
       </c>
       <c r="P63" s="2" t="s">
         <v>0</v>
@@ -4225,13 +4465,13 @@
         <v>60</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>56</v>
+        <v>136</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>55</v>
+        <v>135</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>54</v>
+        <v>134</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>3</v>
@@ -4240,27 +4480,29 @@
         <v>1</v>
       </c>
       <c r="G64" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H64" s="2">
         <v>10.0</v>
       </c>
       <c r="I64" s="2" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="J64" s="2">
-        <v>5</v>
-      </c>
-      <c r="K64" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K64" s="2">
+        <v>1</v>
+      </c>
       <c r="L64" s="2"/>
       <c r="M64" s="2">
         <v>5</v>
       </c>
       <c r="N64" s="2">
-        <v>4.07</v>
+        <v>9.68</v>
       </c>
       <c r="O64" s="2" t="s">
-        <v>53</v>
+        <v>133</v>
       </c>
       <c r="P64" s="2" t="s">
         <v>0</v>
@@ -4271,13 +4513,13 @@
         <v>61</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>52</v>
+        <v>132</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>51</v>
+        <v>131</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>50</v>
+        <v>130</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>3</v>
@@ -4286,29 +4528,29 @@
         <v>1</v>
       </c>
       <c r="G65" s="2">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
       <c r="H65" s="2">
         <v>10.0</v>
       </c>
       <c r="I65" s="2" t="s">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="J65" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K65" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L65" s="2"/>
       <c r="M65" s="2">
         <v>5</v>
       </c>
       <c r="N65" s="2">
-        <v>21.8</v>
+        <v>14.13</v>
       </c>
       <c r="O65" s="2" t="s">
-        <v>49</v>
+        <v>129</v>
       </c>
       <c r="P65" s="2" t="s">
         <v>0</v>
@@ -4319,13 +4561,13 @@
         <v>62</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>48</v>
+        <v>128</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>47</v>
+        <v>127</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>46</v>
+        <v>126</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>3</v>
@@ -4353,10 +4595,10 @@
         <v>5</v>
       </c>
       <c r="N66" s="2">
-        <v>10.12</v>
+        <v>11.45</v>
       </c>
       <c r="O66" s="2" t="s">
-        <v>45</v>
+        <v>125</v>
       </c>
       <c r="P66" s="2" t="s">
         <v>0</v>
@@ -4367,13 +4609,13 @@
         <v>63</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>44</v>
+        <v>124</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>43</v>
+        <v>123</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>42</v>
+        <v>122</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>3</v>
@@ -4382,27 +4624,29 @@
         <v>1</v>
       </c>
       <c r="G67" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H67" s="2">
         <v>10.0</v>
       </c>
       <c r="I67" s="2" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="J67" s="2">
-        <v>5</v>
-      </c>
-      <c r="K67" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K67" s="2">
+        <v>1</v>
+      </c>
       <c r="L67" s="2"/>
       <c r="M67" s="2">
         <v>5</v>
       </c>
       <c r="N67" s="2">
-        <v>13.48</v>
+        <v>12.55</v>
       </c>
       <c r="O67" s="2" t="s">
-        <v>41</v>
+        <v>121</v>
       </c>
       <c r="P67" s="2" t="s">
         <v>0</v>
@@ -4413,13 +4657,13 @@
         <v>64</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>40</v>
+        <v>120</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>39</v>
+        <v>119</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>38</v>
+        <v>118</v>
       </c>
       <c r="E68" s="2" t="s">
         <v>3</v>
@@ -4428,29 +4672,27 @@
         <v>1</v>
       </c>
       <c r="G68" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H68" s="2">
         <v>10.0</v>
       </c>
       <c r="I68" s="2" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="J68" s="2">
-        <v>4</v>
-      </c>
-      <c r="K68" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K68" s="2"/>
       <c r="L68" s="2"/>
       <c r="M68" s="2">
         <v>5</v>
       </c>
       <c r="N68" s="2">
-        <v>10.6</v>
+        <v>6.58</v>
       </c>
       <c r="O68" s="2" t="s">
-        <v>37</v>
+        <v>117</v>
       </c>
       <c r="P68" s="2" t="s">
         <v>0</v>
@@ -4461,13 +4703,13 @@
         <v>65</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>36</v>
+        <v>116</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>35</v>
+        <v>115</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>34</v>
+        <v>114</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>3</v>
@@ -4476,27 +4718,29 @@
         <v>1</v>
       </c>
       <c r="G69" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H69" s="2">
         <v>10.0</v>
       </c>
       <c r="I69" s="2" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="J69" s="2">
-        <v>5</v>
-      </c>
-      <c r="K69" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K69" s="2">
+        <v>1</v>
+      </c>
       <c r="L69" s="2"/>
       <c r="M69" s="2">
         <v>5</v>
       </c>
       <c r="N69" s="2">
-        <v>12.52</v>
+        <v>18.78</v>
       </c>
       <c r="O69" s="2" t="s">
-        <v>33</v>
+        <v>113</v>
       </c>
       <c r="P69" s="2" t="s">
         <v>0</v>
@@ -4507,13 +4751,13 @@
         <v>66</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>31</v>
+        <v>111</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>30</v>
+        <v>110</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>3</v>
@@ -4522,27 +4766,29 @@
         <v>1</v>
       </c>
       <c r="G70" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H70" s="2">
         <v>10.0</v>
       </c>
       <c r="I70" s="2" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="J70" s="2">
-        <v>5</v>
-      </c>
-      <c r="K70" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K70" s="2">
+        <v>1</v>
+      </c>
       <c r="L70" s="2"/>
       <c r="M70" s="2">
         <v>5</v>
       </c>
       <c r="N70" s="2">
-        <v>15.33</v>
+        <v>12.03</v>
       </c>
       <c r="O70" s="2" t="s">
-        <v>28</v>
+        <v>109</v>
       </c>
       <c r="P70" s="2" t="s">
         <v>0</v>
@@ -4553,13 +4799,13 @@
         <v>67</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>27</v>
+        <v>108</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>26</v>
+        <v>107</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>25</v>
+        <v>106</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>3</v>
@@ -4568,29 +4814,29 @@
         <v>1</v>
       </c>
       <c r="G71" s="2">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
       <c r="H71" s="2">
         <v>10.0</v>
       </c>
       <c r="I71" s="2" t="s">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="J71" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K71" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L71" s="2"/>
       <c r="M71" s="2">
         <v>5</v>
       </c>
       <c r="N71" s="2">
-        <v>9.45</v>
+        <v>25.12</v>
       </c>
       <c r="O71" s="2" t="s">
-        <v>24</v>
+        <v>105</v>
       </c>
       <c r="P71" s="2" t="s">
         <v>0</v>
@@ -4601,13 +4847,13 @@
         <v>68</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>23</v>
+        <v>104</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>22</v>
+        <v>103</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>3</v>
@@ -4635,10 +4881,10 @@
         <v>5</v>
       </c>
       <c r="N72" s="2">
-        <v>3.6</v>
+        <v>16.98</v>
       </c>
       <c r="O72" s="2" t="s">
-        <v>20</v>
+        <v>101</v>
       </c>
       <c r="P72" s="2" t="s">
         <v>0</v>
@@ -4649,13 +4895,13 @@
         <v>69</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>19</v>
+        <v>100</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>18</v>
+        <v>99</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>17</v>
+        <v>98</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>3</v>
@@ -4664,29 +4910,27 @@
         <v>1</v>
       </c>
       <c r="G73" s="2">
-        <v>6.0</v>
+        <v>10.0</v>
       </c>
       <c r="H73" s="2">
         <v>10.0</v>
       </c>
       <c r="I73" s="2" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="J73" s="2">
-        <v>3</v>
-      </c>
-      <c r="K73" s="2">
-        <v>2</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K73" s="2"/>
       <c r="L73" s="2"/>
       <c r="M73" s="2">
         <v>5</v>
       </c>
       <c r="N73" s="2">
-        <v>10.15</v>
+        <v>1.45</v>
       </c>
       <c r="O73" s="2" t="s">
-        <v>15</v>
+        <v>97</v>
       </c>
       <c r="P73" s="2" t="s">
         <v>0</v>
@@ -4697,44 +4941,42 @@
         <v>70</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>14</v>
+        <v>96</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>13</v>
+        <v>95</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>12</v>
+        <v>94</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F74" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G74" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H74" s="2">
         <v>10.0</v>
       </c>
       <c r="I74" s="2" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="J74" s="2">
-        <v>4</v>
-      </c>
-      <c r="K74" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K74" s="2"/>
       <c r="L74" s="2"/>
       <c r="M74" s="2">
         <v>5</v>
       </c>
       <c r="N74" s="2">
-        <v>6.12</v>
+        <v>6.18</v>
       </c>
       <c r="O74" s="2" t="s">
-        <v>11</v>
+        <v>93</v>
       </c>
       <c r="P74" s="2" t="s">
         <v>0</v>
@@ -4745,44 +4987,42 @@
         <v>71</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>10</v>
+        <v>92</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>9</v>
+        <v>91</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>8</v>
+        <v>90</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F75" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G75" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H75" s="2">
         <v>10.0</v>
       </c>
       <c r="I75" s="2" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="J75" s="2">
-        <v>4</v>
-      </c>
-      <c r="K75" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K75" s="2"/>
       <c r="L75" s="2"/>
       <c r="M75" s="2">
         <v>5</v>
       </c>
       <c r="N75" s="2">
-        <v>8.33</v>
+        <v>6.13</v>
       </c>
       <c r="O75" s="2" t="s">
-        <v>7</v>
+        <v>89</v>
       </c>
       <c r="P75" s="2" t="s">
         <v>0</v>
@@ -4793,13 +5033,13 @@
         <v>72</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>6</v>
+        <v>88</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>5</v>
+        <v>87</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>4</v>
+        <v>86</v>
       </c>
       <c r="E76" s="2" t="s">
         <v>3</v>
@@ -4827,12 +5067,958 @@
         <v>5</v>
       </c>
       <c r="N76" s="2">
+        <v>2.4</v>
+      </c>
+      <c r="O76" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="P76" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:16">
+      <c r="A77" s="2">
+        <v>73</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F77" s="2">
+        <v>1</v>
+      </c>
+      <c r="G77" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="H77" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I77" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J77" s="2">
+        <v>4</v>
+      </c>
+      <c r="K77" s="2">
+        <v>1</v>
+      </c>
+      <c r="L77" s="2"/>
+      <c r="M77" s="2">
+        <v>5</v>
+      </c>
+      <c r="N77" s="2">
+        <v>15.75</v>
+      </c>
+      <c r="O77" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="P77" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:16">
+      <c r="A78" s="2">
+        <v>74</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E78" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F78" s="2">
+        <v>1</v>
+      </c>
+      <c r="G78" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="H78" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I78" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="J78" s="2">
+        <v>5</v>
+      </c>
+      <c r="K78" s="2"/>
+      <c r="L78" s="2"/>
+      <c r="M78" s="2">
+        <v>5</v>
+      </c>
+      <c r="N78" s="2">
+        <v>2.17</v>
+      </c>
+      <c r="O78" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="P78" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:16">
+      <c r="A79" s="2">
+        <v>75</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E79" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F79" s="2">
+        <v>1</v>
+      </c>
+      <c r="G79" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="H79" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I79" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J79" s="2">
+        <v>3</v>
+      </c>
+      <c r="K79" s="2">
+        <v>2</v>
+      </c>
+      <c r="L79" s="2"/>
+      <c r="M79" s="2">
+        <v>5</v>
+      </c>
+      <c r="N79" s="2">
+        <v>9.5</v>
+      </c>
+      <c r="O79" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="P79" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:16">
+      <c r="A80" s="2">
+        <v>76</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="E80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F80" s="2">
+        <v>1</v>
+      </c>
+      <c r="G80" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="H80" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I80" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="J80" s="2">
+        <v>5</v>
+      </c>
+      <c r="K80" s="2"/>
+      <c r="L80" s="2"/>
+      <c r="M80" s="2">
+        <v>5</v>
+      </c>
+      <c r="N80" s="2">
+        <v>10.75</v>
+      </c>
+      <c r="O80" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="P80" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:16">
+      <c r="A81" s="2">
+        <v>77</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E81" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F81" s="2">
+        <v>2</v>
+      </c>
+      <c r="G81" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="H81" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I81" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J81" s="2">
+        <v>4</v>
+      </c>
+      <c r="K81" s="2">
+        <v>1</v>
+      </c>
+      <c r="L81" s="2"/>
+      <c r="M81" s="2">
+        <v>5</v>
+      </c>
+      <c r="N81" s="2">
+        <v>23.17</v>
+      </c>
+      <c r="O81" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="P81" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:16">
+      <c r="A82" s="2">
+        <v>78</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F82" s="2">
+        <v>2</v>
+      </c>
+      <c r="G82" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="H82" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I82" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="J82" s="2">
+        <v>5</v>
+      </c>
+      <c r="K82" s="2"/>
+      <c r="L82" s="2"/>
+      <c r="M82" s="2">
+        <v>5</v>
+      </c>
+      <c r="N82" s="2">
+        <v>5.47</v>
+      </c>
+      <c r="O82" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="P82" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:16">
+      <c r="A83" s="2">
+        <v>79</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F83" s="2">
+        <v>1</v>
+      </c>
+      <c r="G83" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="H83" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I83" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J83" s="2">
+        <v>4</v>
+      </c>
+      <c r="K83" s="2">
+        <v>1</v>
+      </c>
+      <c r="L83" s="2"/>
+      <c r="M83" s="2">
+        <v>5</v>
+      </c>
+      <c r="N83" s="2">
+        <v>15.8</v>
+      </c>
+      <c r="O83" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="P83" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:16">
+      <c r="A84" s="2">
+        <v>80</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F84" s="2">
+        <v>1</v>
+      </c>
+      <c r="G84" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="H84" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I84" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="J84" s="2">
+        <v>5</v>
+      </c>
+      <c r="K84" s="2"/>
+      <c r="L84" s="2"/>
+      <c r="M84" s="2">
+        <v>5</v>
+      </c>
+      <c r="N84" s="2">
+        <v>4.07</v>
+      </c>
+      <c r="O84" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="P84" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:16">
+      <c r="A85" s="2">
+        <v>81</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F85" s="2">
+        <v>1</v>
+      </c>
+      <c r="G85" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="H85" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I85" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J85" s="2">
+        <v>4</v>
+      </c>
+      <c r="K85" s="2">
+        <v>1</v>
+      </c>
+      <c r="L85" s="2"/>
+      <c r="M85" s="2">
+        <v>5</v>
+      </c>
+      <c r="N85" s="2">
+        <v>21.8</v>
+      </c>
+      <c r="O85" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="P85" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:16">
+      <c r="A86" s="2">
+        <v>82</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E86" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F86" s="2">
+        <v>1</v>
+      </c>
+      <c r="G86" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="H86" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I86" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J86" s="2">
+        <v>4</v>
+      </c>
+      <c r="K86" s="2">
+        <v>1</v>
+      </c>
+      <c r="L86" s="2"/>
+      <c r="M86" s="2">
+        <v>5</v>
+      </c>
+      <c r="N86" s="2">
+        <v>10.12</v>
+      </c>
+      <c r="O86" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="P86" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:16">
+      <c r="A87" s="2">
+        <v>83</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E87" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F87" s="2">
+        <v>1</v>
+      </c>
+      <c r="G87" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="H87" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I87" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="J87" s="2">
+        <v>5</v>
+      </c>
+      <c r="K87" s="2"/>
+      <c r="L87" s="2"/>
+      <c r="M87" s="2">
+        <v>5</v>
+      </c>
+      <c r="N87" s="2">
+        <v>13.48</v>
+      </c>
+      <c r="O87" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="P87" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:16">
+      <c r="A88" s="2">
+        <v>84</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E88" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F88" s="2">
+        <v>1</v>
+      </c>
+      <c r="G88" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="H88" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I88" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J88" s="2">
+        <v>4</v>
+      </c>
+      <c r="K88" s="2">
+        <v>1</v>
+      </c>
+      <c r="L88" s="2"/>
+      <c r="M88" s="2">
+        <v>5</v>
+      </c>
+      <c r="N88" s="2">
+        <v>10.6</v>
+      </c>
+      <c r="O88" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="P88" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:16">
+      <c r="A89" s="2">
+        <v>85</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E89" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F89" s="2">
+        <v>1</v>
+      </c>
+      <c r="G89" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="H89" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I89" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="J89" s="2">
+        <v>5</v>
+      </c>
+      <c r="K89" s="2"/>
+      <c r="L89" s="2"/>
+      <c r="M89" s="2">
+        <v>5</v>
+      </c>
+      <c r="N89" s="2">
+        <v>12.52</v>
+      </c>
+      <c r="O89" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P89" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:16">
+      <c r="A90" s="2">
+        <v>86</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E90" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F90" s="2">
+        <v>1</v>
+      </c>
+      <c r="G90" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="H90" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I90" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="J90" s="2">
+        <v>5</v>
+      </c>
+      <c r="K90" s="2"/>
+      <c r="L90" s="2"/>
+      <c r="M90" s="2">
+        <v>5</v>
+      </c>
+      <c r="N90" s="2">
+        <v>15.33</v>
+      </c>
+      <c r="O90" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P90" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:16">
+      <c r="A91" s="2">
+        <v>87</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E91" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F91" s="2">
+        <v>1</v>
+      </c>
+      <c r="G91" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="H91" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I91" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J91" s="2">
+        <v>4</v>
+      </c>
+      <c r="K91" s="2">
+        <v>1</v>
+      </c>
+      <c r="L91" s="2"/>
+      <c r="M91" s="2">
+        <v>5</v>
+      </c>
+      <c r="N91" s="2">
+        <v>9.45</v>
+      </c>
+      <c r="O91" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="P91" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:16">
+      <c r="A92" s="2">
+        <v>88</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E92" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F92" s="2">
+        <v>1</v>
+      </c>
+      <c r="G92" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="H92" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I92" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J92" s="2">
+        <v>3</v>
+      </c>
+      <c r="K92" s="2">
+        <v>2</v>
+      </c>
+      <c r="L92" s="2"/>
+      <c r="M92" s="2">
+        <v>5</v>
+      </c>
+      <c r="N92" s="2">
+        <v>3.6</v>
+      </c>
+      <c r="O92" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="P92" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:16">
+      <c r="A93" s="2">
+        <v>89</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E93" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F93" s="2">
+        <v>1</v>
+      </c>
+      <c r="G93" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="H93" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I93" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J93" s="2">
+        <v>3</v>
+      </c>
+      <c r="K93" s="2">
+        <v>2</v>
+      </c>
+      <c r="L93" s="2"/>
+      <c r="M93" s="2">
+        <v>5</v>
+      </c>
+      <c r="N93" s="2">
+        <v>10.15</v>
+      </c>
+      <c r="O93" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="P93" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:16">
+      <c r="A94" s="2">
+        <v>90</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E94" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F94" s="2">
+        <v>1</v>
+      </c>
+      <c r="G94" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="H94" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I94" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J94" s="2">
+        <v>4</v>
+      </c>
+      <c r="K94" s="2">
+        <v>1</v>
+      </c>
+      <c r="L94" s="2"/>
+      <c r="M94" s="2">
+        <v>5</v>
+      </c>
+      <c r="N94" s="2">
+        <v>6.12</v>
+      </c>
+      <c r="O94" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="P94" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:16">
+      <c r="A95" s="2">
+        <v>91</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E95" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F95" s="2">
+        <v>2</v>
+      </c>
+      <c r="G95" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="H95" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I95" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J95" s="2">
+        <v>4</v>
+      </c>
+      <c r="K95" s="2">
+        <v>1</v>
+      </c>
+      <c r="L95" s="2"/>
+      <c r="M95" s="2">
+        <v>5</v>
+      </c>
+      <c r="N95" s="2">
+        <v>8.33</v>
+      </c>
+      <c r="O95" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="P95" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:16">
+      <c r="A96" s="2">
+        <v>92</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E96" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" s="2">
+        <v>1</v>
+      </c>
+      <c r="G96" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="H96" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I96" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J96" s="2">
+        <v>4</v>
+      </c>
+      <c r="K96" s="2">
+        <v>1</v>
+      </c>
+      <c r="L96" s="2"/>
+      <c r="M96" s="2">
+        <v>5</v>
+      </c>
+      <c r="N96" s="2">
         <v>7.77</v>
       </c>
-      <c r="O76" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="P76" s="2" t="s">
+      <c r="O96" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="P96" s="2" t="s">
         <v>0</v>
       </c>
     </row>

--- a/2lit_center.xlsx
+++ b/2lit_center.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="392">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="420">
   <si>
     <t>ناجح ✓</t>
   </si>
@@ -1124,6 +1124,18 @@
     <t>Mayan moktar Mohamed</t>
   </si>
   <si>
+    <t>2026-03-02 19:27</t>
+  </si>
+  <si>
+    <t>01032808309</t>
+  </si>
+  <si>
+    <t>ahmedav200@gmail.com</t>
+  </si>
+  <si>
+    <t>احمد سامح حسين</t>
+  </si>
+  <si>
     <t>2026-03-02 19:19</t>
   </si>
   <si>
@@ -1136,6 +1148,78 @@
     <t>Loujain Osama elsayed</t>
   </si>
   <si>
+    <t>2026-03-02 19:23</t>
+  </si>
+  <si>
+    <t>01154109786</t>
+  </si>
+  <si>
+    <t>nadaaseleem@gmail.com</t>
+  </si>
+  <si>
+    <t>Nada Ahmed Seleem</t>
+  </si>
+  <si>
+    <t>2026-03-02 19:25</t>
+  </si>
+  <si>
+    <t>01507680145</t>
+  </si>
+  <si>
+    <t>100demonking001@gmail.com</t>
+  </si>
+  <si>
+    <t>يوسف وائل كمال</t>
+  </si>
+  <si>
+    <t>2026-03-02 19:31</t>
+  </si>
+  <si>
+    <t>01555931663</t>
+  </si>
+  <si>
+    <t>Hagarmokhtar138@gmail.com</t>
+  </si>
+  <si>
+    <t>هاجر مختار عبدالمنعم احمد</t>
+  </si>
+  <si>
+    <t>2026-03-02 19:30</t>
+  </si>
+  <si>
+    <t>01001269403</t>
+  </si>
+  <si>
+    <t>ahmed.tarek3729@gmail.com</t>
+  </si>
+  <si>
+    <t>احمد طارق فتحي</t>
+  </si>
+  <si>
+    <t>2026-03-02 19:44</t>
+  </si>
+  <si>
+    <t>01064753790</t>
+  </si>
+  <si>
+    <t>Abdullazizosama18@gmail.com</t>
+  </si>
+  <si>
+    <t>Abdullaziz</t>
+  </si>
+  <si>
+    <t>2026-03-03 16:36</t>
+  </si>
+  <si>
+    <t>01020745750</t>
+  </si>
+  <si>
+    <t>farragyassin4@gmail.com</t>
+  </si>
+  <si>
+    <t>Yassin Farrag</t>
+  </si>
+  <si>
     <t>الحالة</t>
   </si>
   <si>
@@ -1190,7 +1274,7 @@
     <t>الدرجة الكاملة: 10 | درجة النجاح: 5.00</t>
   </si>
   <si>
-    <t>تاريخ التصدير: 2026-03-02 19:21</t>
+    <t>تاريخ التصدير: 2026-03-04 21:37</t>
   </si>
 </sst>
 </file>
@@ -1578,7 +1662,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:P96"/>
+  <dimension ref="A1:P103"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="true" style="0"/>
@@ -1601,67 +1685,67 @@
   <sheetData>
     <row r="1" spans="1:16">
       <c r="A1" s="3" t="s">
-        <v>389</v>
+        <v>417</v>
       </c>
     </row>
     <row r="2" spans="1:16">
       <c r="A2" s="3" t="s">
-        <v>390</v>
+        <v>418</v>
       </c>
     </row>
     <row r="3" spans="1:16">
       <c r="A3" s="3" t="s">
-        <v>391</v>
+        <v>419</v>
       </c>
     </row>
     <row r="4" spans="1:16">
       <c r="A4" s="1" t="s">
-        <v>388</v>
+        <v>416</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>387</v>
+        <v>415</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>386</v>
+        <v>414</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>385</v>
+        <v>413</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>384</v>
+        <v>412</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>383</v>
+        <v>411</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>382</v>
+        <v>410</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>381</v>
+        <v>409</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>380</v>
+        <v>408</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>379</v>
+        <v>407</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>378</v>
+        <v>406</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>377</v>
+        <v>405</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>376</v>
+        <v>404</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>375</v>
+        <v>403</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>374</v>
+        <v>402</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>373</v>
+        <v>401</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1669,13 +1753,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>372</v>
+        <v>400</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>371</v>
+        <v>399</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>370</v>
+        <v>398</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>3</v>
@@ -1701,10 +1785,10 @@
         <v>5</v>
       </c>
       <c r="N5" s="2">
-        <v>6.55</v>
+        <v>19.5</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>369</v>
+        <v>397</v>
       </c>
       <c r="P5" s="2" t="s">
         <v>0</v>
@@ -1715,13 +1799,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>368</v>
+        <v>396</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>367</v>
+        <v>395</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>366</v>
+        <v>394</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>3</v>
@@ -1749,10 +1833,10 @@
         <v>5</v>
       </c>
       <c r="N6" s="2">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>365</v>
+        <v>393</v>
       </c>
       <c r="P6" s="2" t="s">
         <v>0</v>
@@ -1763,44 +1847,44 @@
         <v>3</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>364</v>
+        <v>392</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>363</v>
+        <v>391</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>362</v>
+        <v>390</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F7" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G7" s="2">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
       <c r="H7" s="2">
         <v>10.0</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="J7" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K7" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L7" s="2"/>
       <c r="M7" s="2">
         <v>5</v>
       </c>
       <c r="N7" s="2">
-        <v>11.57</v>
+        <v>0.8</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>361</v>
+        <v>389</v>
       </c>
       <c r="P7" s="2" t="s">
         <v>0</v>
@@ -1811,13 +1895,13 @@
         <v>4</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>360</v>
+        <v>388</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>359</v>
+        <v>387</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>358</v>
+        <v>386</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>3</v>
@@ -1845,10 +1929,10 @@
         <v>5</v>
       </c>
       <c r="N8" s="2">
-        <v>17.75</v>
+        <v>6.42</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>357</v>
+        <v>385</v>
       </c>
       <c r="P8" s="2" t="s">
         <v>0</v>
@@ -1859,13 +1943,13 @@
         <v>5</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>356</v>
+        <v>384</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>355</v>
+        <v>383</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>354</v>
+        <v>382</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>3</v>
@@ -1874,29 +1958,29 @@
         <v>1</v>
       </c>
       <c r="G9" s="2">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
       <c r="H9" s="2">
         <v>10.0</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="J9" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K9" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L9" s="2"/>
       <c r="M9" s="2">
         <v>5</v>
       </c>
       <c r="N9" s="2">
-        <v>3.12</v>
+        <v>3.05</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>353</v>
+        <v>381</v>
       </c>
       <c r="P9" s="2" t="s">
         <v>0</v>
@@ -1907,13 +1991,13 @@
         <v>6</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>352</v>
+        <v>380</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>351</v>
+        <v>379</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>350</v>
+        <v>378</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>3</v>
@@ -1941,10 +2025,10 @@
         <v>5</v>
       </c>
       <c r="N10" s="2">
-        <v>9.75</v>
+        <v>8.8</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>349</v>
+        <v>377</v>
       </c>
       <c r="P10" s="2" t="s">
         <v>0</v>
@@ -1955,13 +2039,13 @@
         <v>7</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>348</v>
+        <v>376</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>347</v>
+        <v>375</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>346</v>
+        <v>374</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>3</v>
@@ -1970,29 +2054,27 @@
         <v>1</v>
       </c>
       <c r="G11" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H11" s="2">
         <v>10.0</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="J11" s="2">
-        <v>4</v>
-      </c>
-      <c r="K11" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K11" s="2"/>
       <c r="L11" s="2"/>
       <c r="M11" s="2">
         <v>5</v>
       </c>
       <c r="N11" s="2">
-        <v>9.92</v>
+        <v>6.55</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>345</v>
+        <v>373</v>
       </c>
       <c r="P11" s="2" t="s">
         <v>0</v>
@@ -2003,13 +2085,13 @@
         <v>8</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>344</v>
+        <v>372</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>343</v>
+        <v>371</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>342</v>
+        <v>370</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>3</v>
@@ -2037,10 +2119,10 @@
         <v>5</v>
       </c>
       <c r="N12" s="2">
-        <v>15.08</v>
+        <v>16.72</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>341</v>
+        <v>369</v>
       </c>
       <c r="P12" s="2" t="s">
         <v>0</v>
@@ -2051,13 +2133,13 @@
         <v>9</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>340</v>
+        <v>368</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>339</v>
+        <v>367</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>338</v>
+        <v>366</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>3</v>
@@ -2066,27 +2148,29 @@
         <v>1</v>
       </c>
       <c r="G13" s="2">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
       <c r="H13" s="2">
         <v>10.0</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="J13" s="2">
-        <v>5</v>
-      </c>
-      <c r="K13" s="2"/>
+        <v>3</v>
+      </c>
+      <c r="K13" s="2">
+        <v>2</v>
+      </c>
       <c r="L13" s="2"/>
       <c r="M13" s="2">
         <v>5</v>
       </c>
       <c r="N13" s="2">
-        <v>12.9</v>
+        <v>12.5</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>337</v>
+        <v>365</v>
       </c>
       <c r="P13" s="2" t="s">
         <v>0</v>
@@ -2097,13 +2181,13 @@
         <v>10</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>336</v>
+        <v>364</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>335</v>
+        <v>363</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>334</v>
+        <v>362</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>3</v>
@@ -2112,27 +2196,29 @@
         <v>1</v>
       </c>
       <c r="G14" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H14" s="2">
         <v>10.0</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="J14" s="2">
-        <v>5</v>
-      </c>
-      <c r="K14" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K14" s="2">
+        <v>1</v>
+      </c>
       <c r="L14" s="2"/>
       <c r="M14" s="2">
         <v>5</v>
       </c>
       <c r="N14" s="2">
-        <v>12.02</v>
+        <v>11.57</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>333</v>
+        <v>361</v>
       </c>
       <c r="P14" s="2" t="s">
         <v>0</v>
@@ -2143,13 +2229,13 @@
         <v>11</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>332</v>
+        <v>360</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>331</v>
+        <v>359</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>330</v>
+        <v>358</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>3</v>
@@ -2158,27 +2244,29 @@
         <v>1</v>
       </c>
       <c r="G15" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H15" s="2">
         <v>10.0</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="J15" s="2">
-        <v>5</v>
-      </c>
-      <c r="K15" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K15" s="2">
+        <v>1</v>
+      </c>
       <c r="L15" s="2"/>
       <c r="M15" s="2">
         <v>5</v>
       </c>
       <c r="N15" s="2">
-        <v>9.12</v>
+        <v>17.75</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>329</v>
+        <v>357</v>
       </c>
       <c r="P15" s="2" t="s">
         <v>0</v>
@@ -2189,13 +2277,13 @@
         <v>12</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>328</v>
+        <v>356</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>327</v>
+        <v>355</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>326</v>
+        <v>354</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>3</v>
@@ -2204,29 +2292,29 @@
         <v>1</v>
       </c>
       <c r="G16" s="2">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="H16" s="2">
         <v>10.0</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="J16" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K16" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L16" s="2"/>
       <c r="M16" s="2">
         <v>5</v>
       </c>
       <c r="N16" s="2">
-        <v>19.67</v>
+        <v>3.12</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>325</v>
+        <v>353</v>
       </c>
       <c r="P16" s="2" t="s">
         <v>0</v>
@@ -2237,13 +2325,13 @@
         <v>13</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>324</v>
+        <v>352</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>323</v>
+        <v>351</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>322</v>
+        <v>350</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>3</v>
@@ -2252,29 +2340,29 @@
         <v>1</v>
       </c>
       <c r="G17" s="2">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="H17" s="2">
         <v>10.0</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="J17" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K17" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L17" s="2"/>
       <c r="M17" s="2">
         <v>5</v>
       </c>
       <c r="N17" s="2">
-        <v>9.32</v>
+        <v>9.75</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>321</v>
+        <v>349</v>
       </c>
       <c r="P17" s="2" t="s">
         <v>0</v>
@@ -2285,13 +2373,13 @@
         <v>14</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>320</v>
+        <v>348</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>319</v>
+        <v>347</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>318</v>
+        <v>346</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>3</v>
@@ -2300,27 +2388,29 @@
         <v>1</v>
       </c>
       <c r="G18" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H18" s="2">
         <v>10.0</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="J18" s="2">
-        <v>5</v>
-      </c>
-      <c r="K18" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K18" s="2">
+        <v>1</v>
+      </c>
       <c r="L18" s="2"/>
       <c r="M18" s="2">
         <v>5</v>
       </c>
       <c r="N18" s="2">
-        <v>24.92</v>
+        <v>9.92</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>317</v>
+        <v>345</v>
       </c>
       <c r="P18" s="2" t="s">
         <v>0</v>
@@ -2331,44 +2421,44 @@
         <v>15</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>316</v>
+        <v>344</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>315</v>
+        <v>343</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>314</v>
+        <v>342</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F19" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G19" s="2">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="H19" s="2">
         <v>10.0</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="J19" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K19" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L19" s="2"/>
       <c r="M19" s="2">
         <v>5</v>
       </c>
       <c r="N19" s="2">
-        <v>5.23</v>
+        <v>15.08</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>313</v>
+        <v>341</v>
       </c>
       <c r="P19" s="2" t="s">
         <v>0</v>
@@ -2379,13 +2469,13 @@
         <v>16</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>312</v>
+        <v>340</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>311</v>
+        <v>339</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>310</v>
+        <v>338</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>3</v>
@@ -2394,29 +2484,27 @@
         <v>1</v>
       </c>
       <c r="G20" s="2">
-        <v>6.0</v>
+        <v>10.0</v>
       </c>
       <c r="H20" s="2">
         <v>10.0</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="J20" s="2">
-        <v>3</v>
-      </c>
-      <c r="K20" s="2">
-        <v>2</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K20" s="2"/>
       <c r="L20" s="2"/>
       <c r="M20" s="2">
         <v>5</v>
       </c>
       <c r="N20" s="2">
-        <v>22.08</v>
+        <v>12.9</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>309</v>
+        <v>337</v>
       </c>
       <c r="P20" s="2" t="s">
         <v>0</v>
@@ -2427,13 +2515,13 @@
         <v>17</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>308</v>
+        <v>336</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>307</v>
+        <v>335</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>306</v>
+        <v>334</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>3</v>
@@ -2442,29 +2530,27 @@
         <v>1</v>
       </c>
       <c r="G21" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H21" s="2">
         <v>10.0</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="J21" s="2">
-        <v>4</v>
-      </c>
-      <c r="K21" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K21" s="2"/>
       <c r="L21" s="2"/>
       <c r="M21" s="2">
         <v>5</v>
       </c>
       <c r="N21" s="2">
-        <v>10.18</v>
+        <v>12.02</v>
       </c>
       <c r="O21" s="2" t="s">
-        <v>305</v>
+        <v>333</v>
       </c>
       <c r="P21" s="2" t="s">
         <v>0</v>
@@ -2475,13 +2561,13 @@
         <v>18</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>304</v>
+        <v>332</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>303</v>
+        <v>331</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>302</v>
+        <v>330</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>3</v>
@@ -2507,10 +2593,10 @@
         <v>5</v>
       </c>
       <c r="N22" s="2">
-        <v>25.72</v>
+        <v>9.12</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>301</v>
+        <v>329</v>
       </c>
       <c r="P22" s="2" t="s">
         <v>0</v>
@@ -2521,13 +2607,13 @@
         <v>19</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>300</v>
+        <v>328</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>299</v>
+        <v>327</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>298</v>
+        <v>326</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>3</v>
@@ -2555,10 +2641,10 @@
         <v>5</v>
       </c>
       <c r="N23" s="2">
-        <v>13.57</v>
+        <v>19.67</v>
       </c>
       <c r="O23" s="2" t="s">
-        <v>297</v>
+        <v>325</v>
       </c>
       <c r="P23" s="2" t="s">
         <v>0</v>
@@ -2569,13 +2655,13 @@
         <v>20</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>296</v>
+        <v>324</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>295</v>
+        <v>323</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>294</v>
+        <v>322</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>3</v>
@@ -2584,27 +2670,29 @@
         <v>1</v>
       </c>
       <c r="G24" s="2">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
       <c r="H24" s="2">
         <v>10.0</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="J24" s="2">
-        <v>5</v>
-      </c>
-      <c r="K24" s="2"/>
+        <v>3</v>
+      </c>
+      <c r="K24" s="2">
+        <v>2</v>
+      </c>
       <c r="L24" s="2"/>
       <c r="M24" s="2">
         <v>5</v>
       </c>
       <c r="N24" s="2">
-        <v>27.03</v>
+        <v>9.32</v>
       </c>
       <c r="O24" s="2" t="s">
-        <v>293</v>
+        <v>321</v>
       </c>
       <c r="P24" s="2" t="s">
         <v>0</v>
@@ -2615,44 +2703,42 @@
         <v>21</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>292</v>
+        <v>320</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>291</v>
+        <v>319</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>290</v>
+        <v>318</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F25" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G25" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H25" s="2">
         <v>10.0</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="J25" s="2">
-        <v>4</v>
-      </c>
-      <c r="K25" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K25" s="2"/>
       <c r="L25" s="2"/>
       <c r="M25" s="2">
         <v>5</v>
       </c>
       <c r="N25" s="2">
-        <v>3.0</v>
+        <v>24.92</v>
       </c>
       <c r="O25" s="2" t="s">
-        <v>289</v>
+        <v>317</v>
       </c>
       <c r="P25" s="2" t="s">
         <v>0</v>
@@ -2663,42 +2749,44 @@
         <v>22</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>288</v>
+        <v>316</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>287</v>
+        <v>315</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>286</v>
+        <v>314</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F26" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G26" s="2">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
       <c r="H26" s="2">
         <v>10.0</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="J26" s="2">
-        <v>5</v>
-      </c>
-      <c r="K26" s="2"/>
+        <v>3</v>
+      </c>
+      <c r="K26" s="2">
+        <v>2</v>
+      </c>
       <c r="L26" s="2"/>
       <c r="M26" s="2">
         <v>5</v>
       </c>
       <c r="N26" s="2">
-        <v>4.58</v>
+        <v>5.23</v>
       </c>
       <c r="O26" s="2" t="s">
-        <v>285</v>
+        <v>313</v>
       </c>
       <c r="P26" s="2" t="s">
         <v>0</v>
@@ -2709,13 +2797,13 @@
         <v>23</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>284</v>
+        <v>312</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>283</v>
+        <v>311</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>282</v>
+        <v>310</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>3</v>
@@ -2724,27 +2812,29 @@
         <v>1</v>
       </c>
       <c r="G27" s="2">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
       <c r="H27" s="2">
         <v>10.0</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="J27" s="2">
-        <v>5</v>
-      </c>
-      <c r="K27" s="2"/>
+        <v>3</v>
+      </c>
+      <c r="K27" s="2">
+        <v>2</v>
+      </c>
       <c r="L27" s="2"/>
       <c r="M27" s="2">
         <v>5</v>
       </c>
       <c r="N27" s="2">
-        <v>5.58</v>
+        <v>22.08</v>
       </c>
       <c r="O27" s="2" t="s">
-        <v>281</v>
+        <v>309</v>
       </c>
       <c r="P27" s="2" t="s">
         <v>0</v>
@@ -2755,13 +2845,13 @@
         <v>24</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>280</v>
+        <v>308</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>279</v>
+        <v>307</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>278</v>
+        <v>306</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>3</v>
@@ -2770,29 +2860,29 @@
         <v>1</v>
       </c>
       <c r="G28" s="2">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="H28" s="2">
         <v>10.0</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="J28" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K28" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L28" s="2"/>
       <c r="M28" s="2">
         <v>5</v>
       </c>
       <c r="N28" s="2">
-        <v>22.25</v>
+        <v>10.18</v>
       </c>
       <c r="O28" s="2" t="s">
-        <v>277</v>
+        <v>305</v>
       </c>
       <c r="P28" s="2" t="s">
         <v>0</v>
@@ -2803,13 +2893,13 @@
         <v>25</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>276</v>
+        <v>304</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="D29" s="2">
-        <v>201118200153</v>
+        <v>303</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>302</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>3</v>
@@ -2818,29 +2908,27 @@
         <v>1</v>
       </c>
       <c r="G29" s="2">
-        <v>6.0</v>
+        <v>10.0</v>
       </c>
       <c r="H29" s="2">
         <v>10.0</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="J29" s="2">
-        <v>3</v>
-      </c>
-      <c r="K29" s="2">
-        <v>2</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K29" s="2"/>
       <c r="L29" s="2"/>
       <c r="M29" s="2">
         <v>5</v>
       </c>
       <c r="N29" s="2">
-        <v>2.13</v>
+        <v>25.72</v>
       </c>
       <c r="O29" s="2" t="s">
-        <v>274</v>
+        <v>301</v>
       </c>
       <c r="P29" s="2" t="s">
         <v>0</v>
@@ -2851,13 +2939,13 @@
         <v>26</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>273</v>
+        <v>300</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>272</v>
+        <v>299</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>271</v>
+        <v>298</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>3</v>
@@ -2866,27 +2954,29 @@
         <v>1</v>
       </c>
       <c r="G30" s="2">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
       <c r="H30" s="2">
         <v>10.0</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="J30" s="2">
-        <v>5</v>
-      </c>
-      <c r="K30" s="2"/>
+        <v>3</v>
+      </c>
+      <c r="K30" s="2">
+        <v>2</v>
+      </c>
       <c r="L30" s="2"/>
       <c r="M30" s="2">
         <v>5</v>
       </c>
       <c r="N30" s="2">
-        <v>5.0</v>
+        <v>13.57</v>
       </c>
       <c r="O30" s="2" t="s">
-        <v>270</v>
+        <v>297</v>
       </c>
       <c r="P30" s="2" t="s">
         <v>0</v>
@@ -2897,13 +2987,13 @@
         <v>27</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>269</v>
+        <v>296</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>268</v>
+        <v>295</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>267</v>
+        <v>294</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>3</v>
@@ -2929,10 +3019,10 @@
         <v>5</v>
       </c>
       <c r="N31" s="2">
-        <v>5.87</v>
+        <v>27.03</v>
       </c>
       <c r="O31" s="2" t="s">
-        <v>266</v>
+        <v>293</v>
       </c>
       <c r="P31" s="2" t="s">
         <v>0</v>
@@ -2943,19 +3033,19 @@
         <v>28</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>265</v>
+        <v>292</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>264</v>
+        <v>291</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>263</v>
+        <v>290</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F32" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G32" s="2">
         <v>8.0</v>
@@ -2977,10 +3067,10 @@
         <v>5</v>
       </c>
       <c r="N32" s="2">
-        <v>8.92</v>
+        <v>3.0</v>
       </c>
       <c r="O32" s="2" t="s">
-        <v>262</v>
+        <v>289</v>
       </c>
       <c r="P32" s="2" t="s">
         <v>0</v>
@@ -2991,13 +3081,13 @@
         <v>29</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>261</v>
+        <v>288</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>260</v>
+        <v>287</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>259</v>
+        <v>286</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>3</v>
@@ -3006,29 +3096,27 @@
         <v>1</v>
       </c>
       <c r="G33" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H33" s="2">
         <v>10.0</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="J33" s="2">
-        <v>4</v>
-      </c>
-      <c r="K33" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K33" s="2"/>
       <c r="L33" s="2"/>
       <c r="M33" s="2">
         <v>5</v>
       </c>
       <c r="N33" s="2">
-        <v>5.8</v>
+        <v>4.58</v>
       </c>
       <c r="O33" s="2" t="s">
-        <v>258</v>
+        <v>285</v>
       </c>
       <c r="P33" s="2" t="s">
         <v>0</v>
@@ -3039,13 +3127,13 @@
         <v>30</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>257</v>
+        <v>284</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>256</v>
+        <v>283</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>255</v>
+        <v>282</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>3</v>
@@ -3071,10 +3159,10 @@
         <v>5</v>
       </c>
       <c r="N34" s="2">
-        <v>3.17</v>
+        <v>5.58</v>
       </c>
       <c r="O34" s="2" t="s">
-        <v>254</v>
+        <v>281</v>
       </c>
       <c r="P34" s="2" t="s">
         <v>0</v>
@@ -3085,13 +3173,13 @@
         <v>31</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>253</v>
+        <v>280</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>252</v>
+        <v>279</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>251</v>
+        <v>278</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>3</v>
@@ -3100,29 +3188,29 @@
         <v>1</v>
       </c>
       <c r="G35" s="2">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
       <c r="H35" s="2">
         <v>10.0</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="J35" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K35" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L35" s="2"/>
       <c r="M35" s="2">
         <v>5</v>
       </c>
       <c r="N35" s="2">
-        <v>3.2</v>
+        <v>22.25</v>
       </c>
       <c r="O35" s="2" t="s">
-        <v>250</v>
+        <v>277</v>
       </c>
       <c r="P35" s="2" t="s">
         <v>0</v>
@@ -3133,13 +3221,13 @@
         <v>32</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>249</v>
+        <v>276</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>247</v>
+        <v>275</v>
+      </c>
+      <c r="D36" s="2">
+        <v>201118200153</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>3</v>
@@ -3148,29 +3236,29 @@
         <v>1</v>
       </c>
       <c r="G36" s="2">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
       <c r="H36" s="2">
         <v>10.0</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="J36" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K36" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L36" s="2"/>
       <c r="M36" s="2">
         <v>5</v>
       </c>
       <c r="N36" s="2">
-        <v>14.28</v>
+        <v>2.13</v>
       </c>
       <c r="O36" s="2" t="s">
-        <v>246</v>
+        <v>274</v>
       </c>
       <c r="P36" s="2" t="s">
         <v>0</v>
@@ -3181,13 +3269,13 @@
         <v>33</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>245</v>
+        <v>273</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>244</v>
+        <v>272</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>243</v>
+        <v>271</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>3</v>
@@ -3196,29 +3284,27 @@
         <v>1</v>
       </c>
       <c r="G37" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H37" s="2">
         <v>10.0</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="J37" s="2">
-        <v>4</v>
-      </c>
-      <c r="K37" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K37" s="2"/>
       <c r="L37" s="2"/>
       <c r="M37" s="2">
         <v>5</v>
       </c>
       <c r="N37" s="2">
-        <v>12.48</v>
+        <v>5.0</v>
       </c>
       <c r="O37" s="2" t="s">
-        <v>242</v>
+        <v>270</v>
       </c>
       <c r="P37" s="2" t="s">
         <v>0</v>
@@ -3229,13 +3315,13 @@
         <v>34</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>241</v>
+        <v>269</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>240</v>
+        <v>268</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>239</v>
+        <v>267</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>3</v>
@@ -3244,29 +3330,27 @@
         <v>1</v>
       </c>
       <c r="G38" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H38" s="2">
         <v>10.0</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="J38" s="2">
-        <v>4</v>
-      </c>
-      <c r="K38" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K38" s="2"/>
       <c r="L38" s="2"/>
       <c r="M38" s="2">
         <v>5</v>
       </c>
       <c r="N38" s="2">
-        <v>4.22</v>
+        <v>5.87</v>
       </c>
       <c r="O38" s="2" t="s">
-        <v>238</v>
+        <v>266</v>
       </c>
       <c r="P38" s="2" t="s">
         <v>0</v>
@@ -3277,13 +3361,13 @@
         <v>35</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>237</v>
+        <v>265</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>236</v>
+        <v>264</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>235</v>
+        <v>263</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>3</v>
@@ -3292,29 +3376,29 @@
         <v>1</v>
       </c>
       <c r="G39" s="2">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="H39" s="2">
         <v>10.0</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="J39" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K39" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L39" s="2"/>
       <c r="M39" s="2">
         <v>5</v>
       </c>
       <c r="N39" s="2">
-        <v>8.42</v>
+        <v>8.92</v>
       </c>
       <c r="O39" s="2" t="s">
-        <v>234</v>
+        <v>262</v>
       </c>
       <c r="P39" s="2" t="s">
         <v>0</v>
@@ -3325,13 +3409,13 @@
         <v>36</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>233</v>
+        <v>261</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>232</v>
+        <v>260</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>231</v>
+        <v>259</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>3</v>
@@ -3359,10 +3443,10 @@
         <v>5</v>
       </c>
       <c r="N40" s="2">
-        <v>7.37</v>
+        <v>5.8</v>
       </c>
       <c r="O40" s="2" t="s">
-        <v>192</v>
+        <v>258</v>
       </c>
       <c r="P40" s="2" t="s">
         <v>0</v>
@@ -3373,13 +3457,13 @@
         <v>37</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>230</v>
+        <v>257</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>229</v>
+        <v>256</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>228</v>
+        <v>255</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>3</v>
@@ -3405,10 +3489,10 @@
         <v>5</v>
       </c>
       <c r="N41" s="2">
-        <v>23.67</v>
+        <v>3.17</v>
       </c>
       <c r="O41" s="2" t="s">
-        <v>227</v>
+        <v>254</v>
       </c>
       <c r="P41" s="2" t="s">
         <v>0</v>
@@ -3419,13 +3503,13 @@
         <v>38</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>226</v>
+        <v>253</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>225</v>
+        <v>252</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>224</v>
+        <v>251</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>3</v>
@@ -3453,10 +3537,10 @@
         <v>5</v>
       </c>
       <c r="N42" s="2">
-        <v>15.78</v>
+        <v>3.2</v>
       </c>
       <c r="O42" s="2" t="s">
-        <v>223</v>
+        <v>250</v>
       </c>
       <c r="P42" s="2" t="s">
         <v>0</v>
@@ -3467,13 +3551,13 @@
         <v>39</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>222</v>
+        <v>249</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>221</v>
+        <v>248</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>220</v>
+        <v>247</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>3</v>
@@ -3482,27 +3566,29 @@
         <v>1</v>
       </c>
       <c r="G43" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H43" s="2">
         <v>10.0</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="J43" s="2">
-        <v>5</v>
-      </c>
-      <c r="K43" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K43" s="2">
+        <v>1</v>
+      </c>
       <c r="L43" s="2"/>
       <c r="M43" s="2">
         <v>5</v>
       </c>
       <c r="N43" s="2">
-        <v>7.02</v>
+        <v>14.28</v>
       </c>
       <c r="O43" s="2" t="s">
-        <v>219</v>
+        <v>246</v>
       </c>
       <c r="P43" s="2" t="s">
         <v>0</v>
@@ -3513,13 +3599,13 @@
         <v>40</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>218</v>
+        <v>245</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>217</v>
+        <v>244</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>216</v>
+        <v>243</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>3</v>
@@ -3547,10 +3633,10 @@
         <v>5</v>
       </c>
       <c r="N44" s="2">
-        <v>7.05</v>
+        <v>12.48</v>
       </c>
       <c r="O44" s="2" t="s">
-        <v>215</v>
+        <v>242</v>
       </c>
       <c r="P44" s="2" t="s">
         <v>0</v>
@@ -3561,13 +3647,13 @@
         <v>41</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>214</v>
+        <v>241</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>213</v>
+        <v>240</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>212</v>
+        <v>239</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>3</v>
@@ -3576,32 +3662,32 @@
         <v>1</v>
       </c>
       <c r="G45" s="2">
-        <v>2.0</v>
+        <v>8.0</v>
       </c>
       <c r="H45" s="2">
         <v>10.0</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>163</v>
+        <v>2</v>
       </c>
       <c r="J45" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K45" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L45" s="2"/>
       <c r="M45" s="2">
         <v>5</v>
       </c>
       <c r="N45" s="2">
-        <v>5.35</v>
+        <v>4.22</v>
       </c>
       <c r="O45" s="2" t="s">
-        <v>211</v>
+        <v>238</v>
       </c>
       <c r="P45" s="2" t="s">
-        <v>161</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -3609,44 +3695,44 @@
         <v>42</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>210</v>
+        <v>237</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>209</v>
+        <v>236</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>208</v>
+        <v>235</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F46" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G46" s="2">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
       <c r="H46" s="2">
         <v>10.0</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="J46" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K46" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L46" s="2"/>
       <c r="M46" s="2">
         <v>5</v>
       </c>
       <c r="N46" s="2">
-        <v>3.77</v>
+        <v>8.42</v>
       </c>
       <c r="O46" s="2" t="s">
-        <v>207</v>
+        <v>234</v>
       </c>
       <c r="P46" s="2" t="s">
         <v>0</v>
@@ -3657,13 +3743,13 @@
         <v>43</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>206</v>
+        <v>233</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>205</v>
+        <v>232</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>204</v>
+        <v>231</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>3</v>
@@ -3691,10 +3777,10 @@
         <v>5</v>
       </c>
       <c r="N47" s="2">
-        <v>11.42</v>
+        <v>7.37</v>
       </c>
       <c r="O47" s="2" t="s">
-        <v>203</v>
+        <v>192</v>
       </c>
       <c r="P47" s="2" t="s">
         <v>0</v>
@@ -3705,13 +3791,13 @@
         <v>44</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>202</v>
+        <v>230</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>201</v>
+        <v>229</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>200</v>
+        <v>228</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>3</v>
@@ -3720,29 +3806,27 @@
         <v>1</v>
       </c>
       <c r="G48" s="2">
-        <v>6.0</v>
+        <v>10.0</v>
       </c>
       <c r="H48" s="2">
         <v>10.0</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="J48" s="2">
-        <v>3</v>
-      </c>
-      <c r="K48" s="2">
-        <v>2</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K48" s="2"/>
       <c r="L48" s="2"/>
       <c r="M48" s="2">
         <v>5</v>
       </c>
       <c r="N48" s="2">
-        <v>3.57</v>
+        <v>23.67</v>
       </c>
       <c r="O48" s="2" t="s">
-        <v>199</v>
+        <v>227</v>
       </c>
       <c r="P48" s="2" t="s">
         <v>0</v>
@@ -3753,13 +3837,13 @@
         <v>45</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>198</v>
+        <v>226</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>197</v>
+        <v>225</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>196</v>
+        <v>224</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>3</v>
@@ -3787,10 +3871,10 @@
         <v>5</v>
       </c>
       <c r="N49" s="2">
-        <v>7.5</v>
+        <v>15.78</v>
       </c>
       <c r="O49" s="2" t="s">
-        <v>184</v>
+        <v>223</v>
       </c>
       <c r="P49" s="2" t="s">
         <v>0</v>
@@ -3801,13 +3885,13 @@
         <v>46</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>195</v>
+        <v>222</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>194</v>
+        <v>221</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>193</v>
+        <v>220</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>3</v>
@@ -3816,29 +3900,27 @@
         <v>1</v>
       </c>
       <c r="G50" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H50" s="2">
         <v>10.0</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="J50" s="2">
-        <v>4</v>
-      </c>
-      <c r="K50" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K50" s="2"/>
       <c r="L50" s="2"/>
       <c r="M50" s="2">
         <v>5</v>
       </c>
       <c r="N50" s="2">
-        <v>39.38</v>
+        <v>7.02</v>
       </c>
       <c r="O50" s="2" t="s">
-        <v>192</v>
+        <v>219</v>
       </c>
       <c r="P50" s="2" t="s">
         <v>0</v>
@@ -3849,13 +3931,13 @@
         <v>47</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>191</v>
+        <v>218</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>190</v>
+        <v>217</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>189</v>
+        <v>216</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>3</v>
@@ -3883,10 +3965,10 @@
         <v>5</v>
       </c>
       <c r="N51" s="2">
-        <v>11.68</v>
+        <v>7.05</v>
       </c>
       <c r="O51" s="2" t="s">
-        <v>188</v>
+        <v>215</v>
       </c>
       <c r="P51" s="2" t="s">
         <v>0</v>
@@ -3897,13 +3979,13 @@
         <v>48</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>187</v>
+        <v>214</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>186</v>
+        <v>213</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>185</v>
+        <v>212</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>3</v>
@@ -3912,32 +3994,32 @@
         <v>1</v>
       </c>
       <c r="G52" s="2">
-        <v>8.0</v>
+        <v>2.0</v>
       </c>
       <c r="H52" s="2">
         <v>10.0</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>2</v>
+        <v>163</v>
       </c>
       <c r="J52" s="2">
+        <v>1</v>
+      </c>
+      <c r="K52" s="2">
         <v>4</v>
-      </c>
-      <c r="K52" s="2">
-        <v>1</v>
       </c>
       <c r="L52" s="2"/>
       <c r="M52" s="2">
         <v>5</v>
       </c>
       <c r="N52" s="2">
-        <v>15.92</v>
+        <v>5.35</v>
       </c>
       <c r="O52" s="2" t="s">
-        <v>184</v>
+        <v>211</v>
       </c>
       <c r="P52" s="2" t="s">
-        <v>0</v>
+        <v>161</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -3945,19 +4027,19 @@
         <v>49</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>183</v>
+        <v>210</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>182</v>
+        <v>209</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>181</v>
+        <v>208</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F53" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G53" s="2">
         <v>8.0</v>
@@ -3979,10 +4061,10 @@
         <v>5</v>
       </c>
       <c r="N53" s="2">
-        <v>6.17</v>
+        <v>3.77</v>
       </c>
       <c r="O53" s="2" t="s">
-        <v>180</v>
+        <v>207</v>
       </c>
       <c r="P53" s="2" t="s">
         <v>0</v>
@@ -3993,13 +4075,13 @@
         <v>50</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>179</v>
+        <v>206</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>178</v>
+        <v>205</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>177</v>
+        <v>204</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>3</v>
@@ -4008,27 +4090,29 @@
         <v>1</v>
       </c>
       <c r="G54" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H54" s="2">
         <v>10.0</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="J54" s="2">
-        <v>5</v>
-      </c>
-      <c r="K54" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K54" s="2">
+        <v>1</v>
+      </c>
       <c r="L54" s="2"/>
       <c r="M54" s="2">
         <v>5</v>
       </c>
       <c r="N54" s="2">
-        <v>5.92</v>
+        <v>11.42</v>
       </c>
       <c r="O54" s="2" t="s">
-        <v>176</v>
+        <v>203</v>
       </c>
       <c r="P54" s="2" t="s">
         <v>0</v>
@@ -4039,13 +4123,13 @@
         <v>51</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>175</v>
+        <v>202</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>174</v>
+        <v>201</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>173</v>
+        <v>200</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>3</v>
@@ -4054,32 +4138,32 @@
         <v>1</v>
       </c>
       <c r="G55" s="2">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
       <c r="H55" s="2">
         <v>10.0</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>172</v>
+        <v>16</v>
       </c>
       <c r="J55" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K55" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L55" s="2"/>
       <c r="M55" s="2">
         <v>5</v>
       </c>
       <c r="N55" s="2">
-        <v>5.95</v>
+        <v>3.57</v>
       </c>
       <c r="O55" s="2" t="s">
-        <v>171</v>
+        <v>199</v>
       </c>
       <c r="P55" s="2" t="s">
-        <v>161</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -4087,13 +4171,13 @@
         <v>52</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>170</v>
+        <v>198</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>169</v>
+        <v>197</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>168</v>
+        <v>196</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>3</v>
@@ -4102,27 +4186,29 @@
         <v>1</v>
       </c>
       <c r="G56" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H56" s="2">
         <v>10.0</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="J56" s="2">
-        <v>5</v>
-      </c>
-      <c r="K56" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K56" s="2">
+        <v>1</v>
+      </c>
       <c r="L56" s="2"/>
       <c r="M56" s="2">
         <v>5</v>
       </c>
       <c r="N56" s="2">
-        <v>9.08</v>
+        <v>7.5</v>
       </c>
       <c r="O56" s="2" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
       <c r="P56" s="2" t="s">
         <v>0</v>
@@ -4133,13 +4219,13 @@
         <v>53</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>166</v>
+        <v>195</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>165</v>
+        <v>194</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>164</v>
+        <v>193</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>3</v>
@@ -4148,32 +4234,32 @@
         <v>1</v>
       </c>
       <c r="G57" s="2">
-        <v>2.0</v>
+        <v>8.0</v>
       </c>
       <c r="H57" s="2">
         <v>10.0</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>163</v>
+        <v>2</v>
       </c>
       <c r="J57" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K57" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L57" s="2"/>
       <c r="M57" s="2">
         <v>5</v>
       </c>
       <c r="N57" s="2">
-        <v>10.48</v>
+        <v>39.38</v>
       </c>
       <c r="O57" s="2" t="s">
-        <v>162</v>
+        <v>192</v>
       </c>
       <c r="P57" s="2" t="s">
-        <v>161</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -4181,13 +4267,13 @@
         <v>54</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>160</v>
+        <v>191</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>159</v>
+        <v>190</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>158</v>
+        <v>189</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>3</v>
@@ -4215,10 +4301,10 @@
         <v>5</v>
       </c>
       <c r="N58" s="2">
-        <v>13.42</v>
+        <v>11.68</v>
       </c>
       <c r="O58" s="2" t="s">
-        <v>157</v>
+        <v>188</v>
       </c>
       <c r="P58" s="2" t="s">
         <v>0</v>
@@ -4229,13 +4315,13 @@
         <v>55</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>156</v>
+        <v>187</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>155</v>
+        <v>186</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>154</v>
+        <v>185</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>3</v>
@@ -4244,29 +4330,29 @@
         <v>1</v>
       </c>
       <c r="G59" s="2">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="H59" s="2">
         <v>10.0</v>
       </c>
       <c r="I59" s="2" t="s">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="J59" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K59" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L59" s="2"/>
       <c r="M59" s="2">
         <v>5</v>
       </c>
       <c r="N59" s="2">
-        <v>2.57</v>
+        <v>15.92</v>
       </c>
       <c r="O59" s="2" t="s">
-        <v>153</v>
+        <v>184</v>
       </c>
       <c r="P59" s="2" t="s">
         <v>0</v>
@@ -4277,13 +4363,13 @@
         <v>56</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>152</v>
+        <v>183</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>151</v>
+        <v>182</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>150</v>
+        <v>181</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>3</v>
@@ -4292,27 +4378,29 @@
         <v>1</v>
       </c>
       <c r="G60" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H60" s="2">
         <v>10.0</v>
       </c>
       <c r="I60" s="2" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="J60" s="2">
-        <v>5</v>
-      </c>
-      <c r="K60" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K60" s="2">
+        <v>1</v>
+      </c>
       <c r="L60" s="2"/>
       <c r="M60" s="2">
         <v>5</v>
       </c>
       <c r="N60" s="2">
-        <v>1.65</v>
+        <v>6.17</v>
       </c>
       <c r="O60" s="2" t="s">
-        <v>149</v>
+        <v>180</v>
       </c>
       <c r="P60" s="2" t="s">
         <v>0</v>
@@ -4323,13 +4411,13 @@
         <v>57</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>148</v>
+        <v>179</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>147</v>
+        <v>178</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>146</v>
+        <v>177</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>3</v>
@@ -4338,29 +4426,27 @@
         <v>1</v>
       </c>
       <c r="G61" s="2">
-        <v>6.0</v>
+        <v>10.0</v>
       </c>
       <c r="H61" s="2">
         <v>10.0</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="J61" s="2">
-        <v>3</v>
-      </c>
-      <c r="K61" s="2">
-        <v>2</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K61" s="2"/>
       <c r="L61" s="2"/>
       <c r="M61" s="2">
         <v>5</v>
       </c>
       <c r="N61" s="2">
-        <v>12.1</v>
+        <v>5.92</v>
       </c>
       <c r="O61" s="2" t="s">
-        <v>145</v>
+        <v>176</v>
       </c>
       <c r="P61" s="2" t="s">
         <v>0</v>
@@ -4371,13 +4457,13 @@
         <v>58</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>144</v>
+        <v>175</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>143</v>
+        <v>174</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>142</v>
+        <v>173</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>3</v>
@@ -4386,32 +4472,32 @@
         <v>1</v>
       </c>
       <c r="G62" s="2">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
       <c r="H62" s="2">
         <v>10.0</v>
       </c>
       <c r="I62" s="2" t="s">
-        <v>16</v>
+        <v>172</v>
       </c>
       <c r="J62" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K62" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L62" s="2"/>
       <c r="M62" s="2">
         <v>5</v>
       </c>
       <c r="N62" s="2">
-        <v>18.58</v>
+        <v>5.95</v>
       </c>
       <c r="O62" s="2" t="s">
-        <v>141</v>
+        <v>171</v>
       </c>
       <c r="P62" s="2" t="s">
-        <v>0</v>
+        <v>161</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -4419,13 +4505,13 @@
         <v>59</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>140</v>
+        <v>170</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>139</v>
+        <v>169</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>138</v>
+        <v>168</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>3</v>
@@ -4451,10 +4537,10 @@
         <v>5</v>
       </c>
       <c r="N63" s="2">
-        <v>18.03</v>
+        <v>9.08</v>
       </c>
       <c r="O63" s="2" t="s">
-        <v>137</v>
+        <v>167</v>
       </c>
       <c r="P63" s="2" t="s">
         <v>0</v>
@@ -4465,13 +4551,13 @@
         <v>60</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>136</v>
+        <v>166</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>135</v>
+        <v>165</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>134</v>
+        <v>164</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>3</v>
@@ -4480,32 +4566,32 @@
         <v>1</v>
       </c>
       <c r="G64" s="2">
-        <v>8.0</v>
+        <v>2.0</v>
       </c>
       <c r="H64" s="2">
         <v>10.0</v>
       </c>
       <c r="I64" s="2" t="s">
-        <v>2</v>
+        <v>163</v>
       </c>
       <c r="J64" s="2">
+        <v>1</v>
+      </c>
+      <c r="K64" s="2">
         <v>4</v>
-      </c>
-      <c r="K64" s="2">
-        <v>1</v>
       </c>
       <c r="L64" s="2"/>
       <c r="M64" s="2">
         <v>5</v>
       </c>
       <c r="N64" s="2">
-        <v>9.68</v>
+        <v>10.48</v>
       </c>
       <c r="O64" s="2" t="s">
-        <v>133</v>
+        <v>162</v>
       </c>
       <c r="P64" s="2" t="s">
-        <v>0</v>
+        <v>161</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -4513,13 +4599,13 @@
         <v>61</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>132</v>
+        <v>160</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>131</v>
+        <v>159</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>130</v>
+        <v>158</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>3</v>
@@ -4528,29 +4614,29 @@
         <v>1</v>
       </c>
       <c r="G65" s="2">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="H65" s="2">
         <v>10.0</v>
       </c>
       <c r="I65" s="2" t="s">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="J65" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K65" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L65" s="2"/>
       <c r="M65" s="2">
         <v>5</v>
       </c>
       <c r="N65" s="2">
-        <v>14.13</v>
+        <v>13.42</v>
       </c>
       <c r="O65" s="2" t="s">
-        <v>129</v>
+        <v>157</v>
       </c>
       <c r="P65" s="2" t="s">
         <v>0</v>
@@ -4561,13 +4647,13 @@
         <v>62</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>128</v>
+        <v>156</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>127</v>
+        <v>155</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>126</v>
+        <v>154</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>3</v>
@@ -4576,29 +4662,29 @@
         <v>1</v>
       </c>
       <c r="G66" s="2">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
       <c r="H66" s="2">
         <v>10.0</v>
       </c>
       <c r="I66" s="2" t="s">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="J66" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K66" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L66" s="2"/>
       <c r="M66" s="2">
         <v>5</v>
       </c>
       <c r="N66" s="2">
-        <v>11.45</v>
+        <v>2.57</v>
       </c>
       <c r="O66" s="2" t="s">
-        <v>125</v>
+        <v>153</v>
       </c>
       <c r="P66" s="2" t="s">
         <v>0</v>
@@ -4609,13 +4695,13 @@
         <v>63</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>124</v>
+        <v>152</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>123</v>
+        <v>151</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>122</v>
+        <v>150</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>3</v>
@@ -4624,29 +4710,27 @@
         <v>1</v>
       </c>
       <c r="G67" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H67" s="2">
         <v>10.0</v>
       </c>
       <c r="I67" s="2" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="J67" s="2">
-        <v>4</v>
-      </c>
-      <c r="K67" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K67" s="2"/>
       <c r="L67" s="2"/>
       <c r="M67" s="2">
         <v>5</v>
       </c>
       <c r="N67" s="2">
-        <v>12.55</v>
+        <v>1.65</v>
       </c>
       <c r="O67" s="2" t="s">
-        <v>121</v>
+        <v>149</v>
       </c>
       <c r="P67" s="2" t="s">
         <v>0</v>
@@ -4657,13 +4741,13 @@
         <v>64</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>120</v>
+        <v>148</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>119</v>
+        <v>147</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>118</v>
+        <v>146</v>
       </c>
       <c r="E68" s="2" t="s">
         <v>3</v>
@@ -4672,27 +4756,29 @@
         <v>1</v>
       </c>
       <c r="G68" s="2">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
       <c r="H68" s="2">
         <v>10.0</v>
       </c>
       <c r="I68" s="2" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="J68" s="2">
-        <v>5</v>
-      </c>
-      <c r="K68" s="2"/>
+        <v>3</v>
+      </c>
+      <c r="K68" s="2">
+        <v>2</v>
+      </c>
       <c r="L68" s="2"/>
       <c r="M68" s="2">
         <v>5</v>
       </c>
       <c r="N68" s="2">
-        <v>6.58</v>
+        <v>12.1</v>
       </c>
       <c r="O68" s="2" t="s">
-        <v>117</v>
+        <v>145</v>
       </c>
       <c r="P68" s="2" t="s">
         <v>0</v>
@@ -4703,13 +4789,13 @@
         <v>65</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>116</v>
+        <v>144</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>115</v>
+        <v>143</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>114</v>
+        <v>142</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>3</v>
@@ -4718,29 +4804,29 @@
         <v>1</v>
       </c>
       <c r="G69" s="2">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
       <c r="H69" s="2">
         <v>10.0</v>
       </c>
       <c r="I69" s="2" t="s">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="J69" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K69" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L69" s="2"/>
       <c r="M69" s="2">
         <v>5</v>
       </c>
       <c r="N69" s="2">
-        <v>18.78</v>
+        <v>18.58</v>
       </c>
       <c r="O69" s="2" t="s">
-        <v>113</v>
+        <v>141</v>
       </c>
       <c r="P69" s="2" t="s">
         <v>0</v>
@@ -4751,13 +4837,13 @@
         <v>66</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>112</v>
+        <v>140</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>111</v>
+        <v>139</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>110</v>
+        <v>138</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>3</v>
@@ -4766,29 +4852,27 @@
         <v>1</v>
       </c>
       <c r="G70" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H70" s="2">
         <v>10.0</v>
       </c>
       <c r="I70" s="2" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="J70" s="2">
-        <v>4</v>
-      </c>
-      <c r="K70" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K70" s="2"/>
       <c r="L70" s="2"/>
       <c r="M70" s="2">
         <v>5</v>
       </c>
       <c r="N70" s="2">
-        <v>12.03</v>
+        <v>18.03</v>
       </c>
       <c r="O70" s="2" t="s">
-        <v>109</v>
+        <v>137</v>
       </c>
       <c r="P70" s="2" t="s">
         <v>0</v>
@@ -4799,13 +4883,13 @@
         <v>67</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>108</v>
+        <v>136</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>107</v>
+        <v>135</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>106</v>
+        <v>134</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>3</v>
@@ -4814,29 +4898,29 @@
         <v>1</v>
       </c>
       <c r="G71" s="2">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="H71" s="2">
         <v>10.0</v>
       </c>
       <c r="I71" s="2" t="s">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="J71" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K71" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L71" s="2"/>
       <c r="M71" s="2">
         <v>5</v>
       </c>
       <c r="N71" s="2">
-        <v>25.12</v>
+        <v>9.68</v>
       </c>
       <c r="O71" s="2" t="s">
-        <v>105</v>
+        <v>133</v>
       </c>
       <c r="P71" s="2" t="s">
         <v>0</v>
@@ -4847,13 +4931,13 @@
         <v>68</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>104</v>
+        <v>132</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>103</v>
+        <v>131</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>102</v>
+        <v>130</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>3</v>
@@ -4881,10 +4965,10 @@
         <v>5</v>
       </c>
       <c r="N72" s="2">
-        <v>16.98</v>
+        <v>14.13</v>
       </c>
       <c r="O72" s="2" t="s">
-        <v>101</v>
+        <v>129</v>
       </c>
       <c r="P72" s="2" t="s">
         <v>0</v>
@@ -4895,13 +4979,13 @@
         <v>69</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>100</v>
+        <v>128</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>99</v>
+        <v>127</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>98</v>
+        <v>126</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>3</v>
@@ -4910,27 +4994,29 @@
         <v>1</v>
       </c>
       <c r="G73" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H73" s="2">
         <v>10.0</v>
       </c>
       <c r="I73" s="2" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="J73" s="2">
-        <v>5</v>
-      </c>
-      <c r="K73" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K73" s="2">
+        <v>1</v>
+      </c>
       <c r="L73" s="2"/>
       <c r="M73" s="2">
         <v>5</v>
       </c>
       <c r="N73" s="2">
-        <v>1.45</v>
+        <v>11.45</v>
       </c>
       <c r="O73" s="2" t="s">
-        <v>97</v>
+        <v>125</v>
       </c>
       <c r="P73" s="2" t="s">
         <v>0</v>
@@ -4941,42 +5027,44 @@
         <v>70</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>96</v>
+        <v>124</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>95</v>
+        <v>123</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>94</v>
+        <v>122</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F74" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G74" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H74" s="2">
         <v>10.0</v>
       </c>
       <c r="I74" s="2" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="J74" s="2">
-        <v>5</v>
-      </c>
-      <c r="K74" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K74" s="2">
+        <v>1</v>
+      </c>
       <c r="L74" s="2"/>
       <c r="M74" s="2">
         <v>5</v>
       </c>
       <c r="N74" s="2">
-        <v>6.18</v>
+        <v>12.55</v>
       </c>
       <c r="O74" s="2" t="s">
-        <v>93</v>
+        <v>121</v>
       </c>
       <c r="P74" s="2" t="s">
         <v>0</v>
@@ -4987,13 +5075,13 @@
         <v>71</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>92</v>
+        <v>120</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>91</v>
+        <v>119</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>90</v>
+        <v>118</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>3</v>
@@ -5019,10 +5107,10 @@
         <v>5</v>
       </c>
       <c r="N75" s="2">
-        <v>6.13</v>
+        <v>6.58</v>
       </c>
       <c r="O75" s="2" t="s">
-        <v>89</v>
+        <v>117</v>
       </c>
       <c r="P75" s="2" t="s">
         <v>0</v>
@@ -5033,13 +5121,13 @@
         <v>72</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>88</v>
+        <v>116</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>87</v>
+        <v>115</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>86</v>
+        <v>114</v>
       </c>
       <c r="E76" s="2" t="s">
         <v>3</v>
@@ -5067,10 +5155,10 @@
         <v>5</v>
       </c>
       <c r="N76" s="2">
-        <v>2.4</v>
+        <v>18.78</v>
       </c>
       <c r="O76" s="2" t="s">
-        <v>85</v>
+        <v>113</v>
       </c>
       <c r="P76" s="2" t="s">
         <v>0</v>
@@ -5081,13 +5169,13 @@
         <v>73</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>84</v>
+        <v>112</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>83</v>
+        <v>111</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>82</v>
+        <v>110</v>
       </c>
       <c r="E77" s="2" t="s">
         <v>3</v>
@@ -5115,10 +5203,10 @@
         <v>5</v>
       </c>
       <c r="N77" s="2">
-        <v>15.75</v>
+        <v>12.03</v>
       </c>
       <c r="O77" s="2" t="s">
-        <v>81</v>
+        <v>109</v>
       </c>
       <c r="P77" s="2" t="s">
         <v>0</v>
@@ -5129,13 +5217,13 @@
         <v>74</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>80</v>
+        <v>108</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>79</v>
+        <v>107</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>78</v>
+        <v>106</v>
       </c>
       <c r="E78" s="2" t="s">
         <v>3</v>
@@ -5144,27 +5232,29 @@
         <v>1</v>
       </c>
       <c r="G78" s="2">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
       <c r="H78" s="2">
         <v>10.0</v>
       </c>
       <c r="I78" s="2" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="J78" s="2">
-        <v>5</v>
-      </c>
-      <c r="K78" s="2"/>
+        <v>3</v>
+      </c>
+      <c r="K78" s="2">
+        <v>2</v>
+      </c>
       <c r="L78" s="2"/>
       <c r="M78" s="2">
         <v>5</v>
       </c>
       <c r="N78" s="2">
-        <v>2.17</v>
+        <v>25.12</v>
       </c>
       <c r="O78" s="2" t="s">
-        <v>77</v>
+        <v>105</v>
       </c>
       <c r="P78" s="2" t="s">
         <v>0</v>
@@ -5175,13 +5265,13 @@
         <v>75</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>76</v>
+        <v>104</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>75</v>
+        <v>103</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>74</v>
+        <v>102</v>
       </c>
       <c r="E79" s="2" t="s">
         <v>3</v>
@@ -5209,10 +5299,10 @@
         <v>5</v>
       </c>
       <c r="N79" s="2">
-        <v>9.5</v>
+        <v>16.98</v>
       </c>
       <c r="O79" s="2" t="s">
-        <v>73</v>
+        <v>101</v>
       </c>
       <c r="P79" s="2" t="s">
         <v>0</v>
@@ -5223,13 +5313,13 @@
         <v>76</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>72</v>
+        <v>100</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>71</v>
+        <v>99</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>70</v>
+        <v>98</v>
       </c>
       <c r="E80" s="2" t="s">
         <v>3</v>
@@ -5255,10 +5345,10 @@
         <v>5</v>
       </c>
       <c r="N80" s="2">
-        <v>10.75</v>
+        <v>1.45</v>
       </c>
       <c r="O80" s="2" t="s">
-        <v>69</v>
+        <v>97</v>
       </c>
       <c r="P80" s="2" t="s">
         <v>0</v>
@@ -5269,13 +5359,13 @@
         <v>77</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>68</v>
+        <v>96</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>67</v>
+        <v>95</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>66</v>
+        <v>94</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>3</v>
@@ -5284,29 +5374,27 @@
         <v>2</v>
       </c>
       <c r="G81" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H81" s="2">
         <v>10.0</v>
       </c>
       <c r="I81" s="2" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="J81" s="2">
-        <v>4</v>
-      </c>
-      <c r="K81" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K81" s="2"/>
       <c r="L81" s="2"/>
       <c r="M81" s="2">
         <v>5</v>
       </c>
       <c r="N81" s="2">
-        <v>23.17</v>
+        <v>6.18</v>
       </c>
       <c r="O81" s="2" t="s">
-        <v>65</v>
+        <v>93</v>
       </c>
       <c r="P81" s="2" t="s">
         <v>0</v>
@@ -5317,19 +5405,19 @@
         <v>78</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>64</v>
+        <v>92</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>63</v>
+        <v>91</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>62</v>
+        <v>90</v>
       </c>
       <c r="E82" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F82" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G82" s="2">
         <v>10.0</v>
@@ -5349,10 +5437,10 @@
         <v>5</v>
       </c>
       <c r="N82" s="2">
-        <v>5.47</v>
+        <v>6.13</v>
       </c>
       <c r="O82" s="2" t="s">
-        <v>61</v>
+        <v>89</v>
       </c>
       <c r="P82" s="2" t="s">
         <v>0</v>
@@ -5363,13 +5451,13 @@
         <v>79</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>60</v>
+        <v>88</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>59</v>
+        <v>87</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>58</v>
+        <v>86</v>
       </c>
       <c r="E83" s="2" t="s">
         <v>3</v>
@@ -5397,10 +5485,10 @@
         <v>5</v>
       </c>
       <c r="N83" s="2">
-        <v>15.8</v>
+        <v>2.4</v>
       </c>
       <c r="O83" s="2" t="s">
-        <v>57</v>
+        <v>85</v>
       </c>
       <c r="P83" s="2" t="s">
         <v>0</v>
@@ -5411,13 +5499,13 @@
         <v>80</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>56</v>
+        <v>84</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>55</v>
+        <v>83</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>54</v>
+        <v>82</v>
       </c>
       <c r="E84" s="2" t="s">
         <v>3</v>
@@ -5426,27 +5514,29 @@
         <v>1</v>
       </c>
       <c r="G84" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H84" s="2">
         <v>10.0</v>
       </c>
       <c r="I84" s="2" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="J84" s="2">
-        <v>5</v>
-      </c>
-      <c r="K84" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K84" s="2">
+        <v>1</v>
+      </c>
       <c r="L84" s="2"/>
       <c r="M84" s="2">
         <v>5</v>
       </c>
       <c r="N84" s="2">
-        <v>4.07</v>
+        <v>15.75</v>
       </c>
       <c r="O84" s="2" t="s">
-        <v>53</v>
+        <v>81</v>
       </c>
       <c r="P84" s="2" t="s">
         <v>0</v>
@@ -5457,13 +5547,13 @@
         <v>81</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>52</v>
+        <v>80</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>51</v>
+        <v>79</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="E85" s="2" t="s">
         <v>3</v>
@@ -5472,29 +5562,27 @@
         <v>1</v>
       </c>
       <c r="G85" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H85" s="2">
         <v>10.0</v>
       </c>
       <c r="I85" s="2" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="J85" s="2">
-        <v>4</v>
-      </c>
-      <c r="K85" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K85" s="2"/>
       <c r="L85" s="2"/>
       <c r="M85" s="2">
         <v>5</v>
       </c>
       <c r="N85" s="2">
-        <v>21.8</v>
+        <v>2.17</v>
       </c>
       <c r="O85" s="2" t="s">
-        <v>49</v>
+        <v>77</v>
       </c>
       <c r="P85" s="2" t="s">
         <v>0</v>
@@ -5505,13 +5593,13 @@
         <v>82</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>48</v>
+        <v>76</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>46</v>
+        <v>74</v>
       </c>
       <c r="E86" s="2" t="s">
         <v>3</v>
@@ -5520,29 +5608,29 @@
         <v>1</v>
       </c>
       <c r="G86" s="2">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
       <c r="H86" s="2">
         <v>10.0</v>
       </c>
       <c r="I86" s="2" t="s">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="J86" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K86" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L86" s="2"/>
       <c r="M86" s="2">
         <v>5</v>
       </c>
       <c r="N86" s="2">
-        <v>10.12</v>
+        <v>9.5</v>
       </c>
       <c r="O86" s="2" t="s">
-        <v>45</v>
+        <v>73</v>
       </c>
       <c r="P86" s="2" t="s">
         <v>0</v>
@@ -5553,13 +5641,13 @@
         <v>83</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>44</v>
+        <v>72</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>43</v>
+        <v>71</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="E87" s="2" t="s">
         <v>3</v>
@@ -5585,10 +5673,10 @@
         <v>5</v>
       </c>
       <c r="N87" s="2">
-        <v>13.48</v>
+        <v>10.75</v>
       </c>
       <c r="O87" s="2" t="s">
-        <v>41</v>
+        <v>69</v>
       </c>
       <c r="P87" s="2" t="s">
         <v>0</v>
@@ -5599,19 +5687,19 @@
         <v>84</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>39</v>
+        <v>67</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="E88" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F88" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G88" s="2">
         <v>8.0</v>
@@ -5633,10 +5721,10 @@
         <v>5</v>
       </c>
       <c r="N88" s="2">
-        <v>10.6</v>
+        <v>23.17</v>
       </c>
       <c r="O88" s="2" t="s">
-        <v>37</v>
+        <v>65</v>
       </c>
       <c r="P88" s="2" t="s">
         <v>0</v>
@@ -5647,19 +5735,19 @@
         <v>85</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>36</v>
+        <v>64</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>34</v>
+        <v>62</v>
       </c>
       <c r="E89" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F89" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G89" s="2">
         <v>10.0</v>
@@ -5679,10 +5767,10 @@
         <v>5</v>
       </c>
       <c r="N89" s="2">
-        <v>12.52</v>
+        <v>5.47</v>
       </c>
       <c r="O89" s="2" t="s">
-        <v>33</v>
+        <v>61</v>
       </c>
       <c r="P89" s="2" t="s">
         <v>0</v>
@@ -5693,13 +5781,13 @@
         <v>86</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>31</v>
+        <v>59</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>30</v>
+        <v>58</v>
       </c>
       <c r="E90" s="2" t="s">
         <v>3</v>
@@ -5708,27 +5796,29 @@
         <v>1</v>
       </c>
       <c r="G90" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H90" s="2">
         <v>10.0</v>
       </c>
       <c r="I90" s="2" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="J90" s="2">
-        <v>5</v>
-      </c>
-      <c r="K90" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K90" s="2">
+        <v>1</v>
+      </c>
       <c r="L90" s="2"/>
       <c r="M90" s="2">
         <v>5</v>
       </c>
       <c r="N90" s="2">
-        <v>15.33</v>
+        <v>15.8</v>
       </c>
       <c r="O90" s="2" t="s">
-        <v>28</v>
+        <v>57</v>
       </c>
       <c r="P90" s="2" t="s">
         <v>0</v>
@@ -5739,13 +5829,13 @@
         <v>87</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>27</v>
+        <v>56</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>26</v>
+        <v>55</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>25</v>
+        <v>54</v>
       </c>
       <c r="E91" s="2" t="s">
         <v>3</v>
@@ -5754,29 +5844,27 @@
         <v>1</v>
       </c>
       <c r="G91" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H91" s="2">
         <v>10.0</v>
       </c>
       <c r="I91" s="2" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="J91" s="2">
-        <v>4</v>
-      </c>
-      <c r="K91" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K91" s="2"/>
       <c r="L91" s="2"/>
       <c r="M91" s="2">
         <v>5</v>
       </c>
       <c r="N91" s="2">
-        <v>9.45</v>
+        <v>4.07</v>
       </c>
       <c r="O91" s="2" t="s">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="P91" s="2" t="s">
         <v>0</v>
@@ -5787,13 +5875,13 @@
         <v>88</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>22</v>
+        <v>51</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>21</v>
+        <v>50</v>
       </c>
       <c r="E92" s="2" t="s">
         <v>3</v>
@@ -5802,29 +5890,29 @@
         <v>1</v>
       </c>
       <c r="G92" s="2">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="H92" s="2">
         <v>10.0</v>
       </c>
       <c r="I92" s="2" t="s">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="J92" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K92" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L92" s="2"/>
       <c r="M92" s="2">
         <v>5</v>
       </c>
       <c r="N92" s="2">
-        <v>3.6</v>
+        <v>21.8</v>
       </c>
       <c r="O92" s="2" t="s">
-        <v>20</v>
+        <v>49</v>
       </c>
       <c r="P92" s="2" t="s">
         <v>0</v>
@@ -5835,13 +5923,13 @@
         <v>89</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>18</v>
+        <v>47</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="E93" s="2" t="s">
         <v>3</v>
@@ -5850,29 +5938,29 @@
         <v>1</v>
       </c>
       <c r="G93" s="2">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="H93" s="2">
         <v>10.0</v>
       </c>
       <c r="I93" s="2" t="s">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="J93" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K93" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L93" s="2"/>
       <c r="M93" s="2">
         <v>5</v>
       </c>
       <c r="N93" s="2">
-        <v>10.15</v>
+        <v>10.12</v>
       </c>
       <c r="O93" s="2" t="s">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="P93" s="2" t="s">
         <v>0</v>
@@ -5883,13 +5971,13 @@
         <v>90</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="E94" s="2" t="s">
         <v>3</v>
@@ -5898,29 +5986,27 @@
         <v>1</v>
       </c>
       <c r="G94" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H94" s="2">
         <v>10.0</v>
       </c>
       <c r="I94" s="2" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="J94" s="2">
-        <v>4</v>
-      </c>
-      <c r="K94" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K94" s="2"/>
       <c r="L94" s="2"/>
       <c r="M94" s="2">
         <v>5</v>
       </c>
       <c r="N94" s="2">
-        <v>6.12</v>
+        <v>13.48</v>
       </c>
       <c r="O94" s="2" t="s">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="P94" s="2" t="s">
         <v>0</v>
@@ -5931,19 +6017,19 @@
         <v>91</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="E95" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F95" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G95" s="2">
         <v>8.0</v>
@@ -5965,10 +6051,10 @@
         <v>5</v>
       </c>
       <c r="N95" s="2">
-        <v>8.33</v>
+        <v>10.6</v>
       </c>
       <c r="O95" s="2" t="s">
-        <v>7</v>
+        <v>37</v>
       </c>
       <c r="P95" s="2" t="s">
         <v>0</v>
@@ -5979,13 +6065,13 @@
         <v>92</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="E96" s="2" t="s">
         <v>3</v>
@@ -5994,31 +6080,363 @@
         <v>1</v>
       </c>
       <c r="G96" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H96" s="2">
         <v>10.0</v>
       </c>
       <c r="I96" s="2" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="J96" s="2">
-        <v>4</v>
-      </c>
-      <c r="K96" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K96" s="2"/>
       <c r="L96" s="2"/>
       <c r="M96" s="2">
         <v>5</v>
       </c>
       <c r="N96" s="2">
+        <v>12.52</v>
+      </c>
+      <c r="O96" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P96" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:16">
+      <c r="A97" s="2">
+        <v>93</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D97" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E97" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F97" s="2">
+        <v>1</v>
+      </c>
+      <c r="G97" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="H97" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I97" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="J97" s="2">
+        <v>5</v>
+      </c>
+      <c r="K97" s="2"/>
+      <c r="L97" s="2"/>
+      <c r="M97" s="2">
+        <v>5</v>
+      </c>
+      <c r="N97" s="2">
+        <v>15.33</v>
+      </c>
+      <c r="O97" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P97" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:16">
+      <c r="A98" s="2">
+        <v>94</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D98" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E98" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F98" s="2">
+        <v>1</v>
+      </c>
+      <c r="G98" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="H98" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I98" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J98" s="2">
+        <v>4</v>
+      </c>
+      <c r="K98" s="2">
+        <v>1</v>
+      </c>
+      <c r="L98" s="2"/>
+      <c r="M98" s="2">
+        <v>5</v>
+      </c>
+      <c r="N98" s="2">
+        <v>9.45</v>
+      </c>
+      <c r="O98" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="P98" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:16">
+      <c r="A99" s="2">
+        <v>95</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D99" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E99" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F99" s="2">
+        <v>1</v>
+      </c>
+      <c r="G99" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="H99" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I99" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J99" s="2">
+        <v>3</v>
+      </c>
+      <c r="K99" s="2">
+        <v>2</v>
+      </c>
+      <c r="L99" s="2"/>
+      <c r="M99" s="2">
+        <v>5</v>
+      </c>
+      <c r="N99" s="2">
+        <v>3.6</v>
+      </c>
+      <c r="O99" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="P99" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:16">
+      <c r="A100" s="2">
+        <v>96</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D100" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E100" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F100" s="2">
+        <v>1</v>
+      </c>
+      <c r="G100" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="H100" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I100" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J100" s="2">
+        <v>3</v>
+      </c>
+      <c r="K100" s="2">
+        <v>2</v>
+      </c>
+      <c r="L100" s="2"/>
+      <c r="M100" s="2">
+        <v>5</v>
+      </c>
+      <c r="N100" s="2">
+        <v>10.15</v>
+      </c>
+      <c r="O100" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="P100" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:16">
+      <c r="A101" s="2">
+        <v>97</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D101" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E101" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F101" s="2">
+        <v>1</v>
+      </c>
+      <c r="G101" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="H101" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I101" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J101" s="2">
+        <v>4</v>
+      </c>
+      <c r="K101" s="2">
+        <v>1</v>
+      </c>
+      <c r="L101" s="2"/>
+      <c r="M101" s="2">
+        <v>5</v>
+      </c>
+      <c r="N101" s="2">
+        <v>6.12</v>
+      </c>
+      <c r="O101" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="P101" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:16">
+      <c r="A102" s="2">
+        <v>98</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D102" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E102" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F102" s="2">
+        <v>2</v>
+      </c>
+      <c r="G102" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="H102" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I102" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J102" s="2">
+        <v>4</v>
+      </c>
+      <c r="K102" s="2">
+        <v>1</v>
+      </c>
+      <c r="L102" s="2"/>
+      <c r="M102" s="2">
+        <v>5</v>
+      </c>
+      <c r="N102" s="2">
+        <v>8.33</v>
+      </c>
+      <c r="O102" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="P102" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:16">
+      <c r="A103" s="2">
+        <v>99</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D103" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E103" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F103" s="2">
+        <v>1</v>
+      </c>
+      <c r="G103" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="H103" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I103" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J103" s="2">
+        <v>4</v>
+      </c>
+      <c r="K103" s="2">
+        <v>1</v>
+      </c>
+      <c r="L103" s="2"/>
+      <c r="M103" s="2">
+        <v>5</v>
+      </c>
+      <c r="N103" s="2">
         <v>7.77</v>
       </c>
-      <c r="O96" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="P96" s="2" t="s">
+      <c r="O103" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="P103" s="2" t="s">
         <v>0</v>
       </c>
     </row>

--- a/2lit_center.xlsx
+++ b/2lit_center.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="420">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="469">
   <si>
     <t>ناجح ✓</t>
   </si>
@@ -344,7 +344,13 @@
     <t>habiba tamer tamer</t>
   </si>
   <si>
-    <t>2026-03-01 15:37</t>
+    <t>راسب ✗</t>
+  </si>
+  <si>
+    <t>2026-03-08 17:18</t>
+  </si>
+  <si>
+    <t>40.0%</t>
   </si>
   <si>
     <t>01552477901</t>
@@ -500,13 +506,277 @@
     <t>Farah mohamed</t>
   </si>
   <si>
-    <t>راسب ✗</t>
-  </si>
-  <si>
-    <t>2026-03-01 17:36</t>
-  </si>
-  <si>
-    <t>20.0%</t>
+    <t>2026-03-01 17:41</t>
+  </si>
+  <si>
+    <t>01008577439</t>
+  </si>
+  <si>
+    <t>malak5tamerbadr@gmail.com</t>
+  </si>
+  <si>
+    <t>ملك تامر بدر الدين</t>
+  </si>
+  <si>
+    <t>2026-03-01 17:50</t>
+  </si>
+  <si>
+    <t>01069612668</t>
+  </si>
+  <si>
+    <t>meskayman999@gmail.com</t>
+  </si>
+  <si>
+    <t>مسك ايمن محمد حسن</t>
+  </si>
+  <si>
+    <t>2026-03-01 17:54</t>
+  </si>
+  <si>
+    <t>01020099526</t>
+  </si>
+  <si>
+    <t>mariem@gmail.com</t>
+  </si>
+  <si>
+    <t>Mariem Sameh Farouk</t>
+  </si>
+  <si>
+    <t>2026-03-01 18:08</t>
+  </si>
+  <si>
+    <t>01508312623</t>
+  </si>
+  <si>
+    <t>nooratef1232009@gmail.com</t>
+  </si>
+  <si>
+    <t>Nour</t>
+  </si>
+  <si>
+    <t>2026-03-01 18:25</t>
+  </si>
+  <si>
+    <t>01283830831</t>
+  </si>
+  <si>
+    <t>4000ahmedwael@gmail.com</t>
+  </si>
+  <si>
+    <t>أحمد وائل صلاح</t>
+  </si>
+  <si>
+    <t>2026-03-01 18:26</t>
+  </si>
+  <si>
+    <t>01012082687</t>
+  </si>
+  <si>
+    <t>Mennasalem98765432@gmail.con</t>
+  </si>
+  <si>
+    <t>Menna salem</t>
+  </si>
+  <si>
+    <t>2026-03-01 18:54</t>
+  </si>
+  <si>
+    <t>01551501457</t>
+  </si>
+  <si>
+    <t>roaaahmed21080001@gmail.com</t>
+  </si>
+  <si>
+    <t>رؤى احمد حسين</t>
+  </si>
+  <si>
+    <t>01010003985</t>
+  </si>
+  <si>
+    <t>mahmoudxhj@GMAIL.cOM</t>
+  </si>
+  <si>
+    <t>محمود محمد ضياء الدين محمود</t>
+  </si>
+  <si>
+    <t>2026-03-01 18:24</t>
+  </si>
+  <si>
+    <t>01061920915</t>
+  </si>
+  <si>
+    <t>goudysherif@gmail.com</t>
+  </si>
+  <si>
+    <t>محمد شريف</t>
+  </si>
+  <si>
+    <t>2026-03-01 18:34</t>
+  </si>
+  <si>
+    <t>01100682703</t>
+  </si>
+  <si>
+    <t>Lara.eldiasti@gmail.com</t>
+  </si>
+  <si>
+    <t>لارا الحسن الديسطي</t>
+  </si>
+  <si>
+    <t>2026-03-01 18:30</t>
+  </si>
+  <si>
+    <t>01018376379</t>
+  </si>
+  <si>
+    <t>mohamed.waleed.barakat.2008@gmail.com</t>
+  </si>
+  <si>
+    <t>Mohamed Barakat</t>
+  </si>
+  <si>
+    <t>2026-03-01 18:35</t>
+  </si>
+  <si>
+    <t>01148353989</t>
+  </si>
+  <si>
+    <t>janaamrmohamed2472009@gmail.com</t>
+  </si>
+  <si>
+    <t>Jana Amr</t>
+  </si>
+  <si>
+    <t>2026-03-01 18:41</t>
+  </si>
+  <si>
+    <t>01124926013</t>
+  </si>
+  <si>
+    <t>marwanelnakeeb2009@gmail.com</t>
+  </si>
+  <si>
+    <t>Marwan omar</t>
+  </si>
+  <si>
+    <t>2026-03-01 18:55</t>
+  </si>
+  <si>
+    <t>01091828377</t>
+  </si>
+  <si>
+    <t>yossefshref2009@gmail.com</t>
+  </si>
+  <si>
+    <t>Youssef sherif youssef</t>
+  </si>
+  <si>
+    <t>2026-03-01 19:07</t>
+  </si>
+  <si>
+    <t>01026933947</t>
+  </si>
+  <si>
+    <t>malaksamykamel2008@gmail.com</t>
+  </si>
+  <si>
+    <t>Malak Samy</t>
+  </si>
+  <si>
+    <t>01007217521</t>
+  </si>
+  <si>
+    <t>abdelrhmanmohamed2938@gmail.com</t>
+  </si>
+  <si>
+    <t>عبدالرحمن محمد حمدته</t>
+  </si>
+  <si>
+    <t>2026-03-01 18:57</t>
+  </si>
+  <si>
+    <t>01065596920</t>
+  </si>
+  <si>
+    <t>caramella3750@gmail.com</t>
+  </si>
+  <si>
+    <t>Carma Ehab</t>
+  </si>
+  <si>
+    <t>2026-03-01 19:01</t>
+  </si>
+  <si>
+    <t>01012424377</t>
+  </si>
+  <si>
+    <t>janayousry@2008gmail.com</t>
+  </si>
+  <si>
+    <t>jana ahmed mohmed yousry</t>
+  </si>
+  <si>
+    <t>2026-03-01 19:09</t>
+  </si>
+  <si>
+    <t>01097794201</t>
+  </si>
+  <si>
+    <t>aytensaleh6@gmail.com</t>
+  </si>
+  <si>
+    <t>Ayten Saleh Mostafa</t>
+  </si>
+  <si>
+    <t>2026-03-01 19:16</t>
+  </si>
+  <si>
+    <t>01151728245</t>
+  </si>
+  <si>
+    <t>Hshhzhxbheh@gmail.com</t>
+  </si>
+  <si>
+    <t>يوسف شريف عادل</t>
+  </si>
+  <si>
+    <t>2026-03-01 19:08</t>
+  </si>
+  <si>
+    <t>01063000688</t>
+  </si>
+  <si>
+    <t>bodihossni@gmail.com</t>
+  </si>
+  <si>
+    <t>Abdelrhman hossni saad</t>
+  </si>
+  <si>
+    <t>2026-03-01 19:12</t>
+  </si>
+  <si>
+    <t>01125776411</t>
+  </si>
+  <si>
+    <t>radwanosama414@gmail.com</t>
+  </si>
+  <si>
+    <t>Radwan Osama</t>
+  </si>
+  <si>
+    <t>2026-03-08 18:03</t>
+  </si>
+  <si>
+    <t>01156486570</t>
+  </si>
+  <si>
+    <t>ahmed1404mostafa@gmail.com</t>
+  </si>
+  <si>
+    <t>احمد مصطفي احمد يوسف</t>
+  </si>
+  <si>
+    <t>2026-03-08 16:23</t>
   </si>
   <si>
     <t>01225460949</t>
@@ -518,279 +788,6 @@
     <t>Rahma mohamed mostafa</t>
   </si>
   <si>
-    <t>2026-03-01 17:41</t>
-  </si>
-  <si>
-    <t>01008577439</t>
-  </si>
-  <si>
-    <t>malak5tamerbadr@gmail.com</t>
-  </si>
-  <si>
-    <t>ملك تامر بدر الدين</t>
-  </si>
-  <si>
-    <t>2026-03-01 17:50</t>
-  </si>
-  <si>
-    <t>40.0%</t>
-  </si>
-  <si>
-    <t>01069612668</t>
-  </si>
-  <si>
-    <t>meskayman999@gmail.com</t>
-  </si>
-  <si>
-    <t>مسك ايمن محمد حسن</t>
-  </si>
-  <si>
-    <t>2026-03-01 17:54</t>
-  </si>
-  <si>
-    <t>01020099526</t>
-  </si>
-  <si>
-    <t>mariem@gmail.com</t>
-  </si>
-  <si>
-    <t>Mariem Sameh Farouk</t>
-  </si>
-  <si>
-    <t>2026-03-01 18:08</t>
-  </si>
-  <si>
-    <t>01508312623</t>
-  </si>
-  <si>
-    <t>nooratef1232009@gmail.com</t>
-  </si>
-  <si>
-    <t>Nour</t>
-  </si>
-  <si>
-    <t>2026-03-01 18:25</t>
-  </si>
-  <si>
-    <t>01283830831</t>
-  </si>
-  <si>
-    <t>4000ahmedwael@gmail.com</t>
-  </si>
-  <si>
-    <t>أحمد وائل صلاح</t>
-  </si>
-  <si>
-    <t>2026-03-01 18:26</t>
-  </si>
-  <si>
-    <t>01012082687</t>
-  </si>
-  <si>
-    <t>Mennasalem98765432@gmail.con</t>
-  </si>
-  <si>
-    <t>Menna salem</t>
-  </si>
-  <si>
-    <t>2026-03-01 18:54</t>
-  </si>
-  <si>
-    <t>01551501457</t>
-  </si>
-  <si>
-    <t>roaaahmed21080001@gmail.com</t>
-  </si>
-  <si>
-    <t>رؤى احمد حسين</t>
-  </si>
-  <si>
-    <t>01010003985</t>
-  </si>
-  <si>
-    <t>mahmoudxhj@GMAIL.cOM</t>
-  </si>
-  <si>
-    <t>محمود محمد ضياء الدين محمود</t>
-  </si>
-  <si>
-    <t>2026-03-01 18:24</t>
-  </si>
-  <si>
-    <t>01061920915</t>
-  </si>
-  <si>
-    <t>goudysherif@gmail.com</t>
-  </si>
-  <si>
-    <t>محمد شريف</t>
-  </si>
-  <si>
-    <t>2026-03-01 18:34</t>
-  </si>
-  <si>
-    <t>01100682703</t>
-  </si>
-  <si>
-    <t>Lara.eldiasti@gmail.com</t>
-  </si>
-  <si>
-    <t>لارا الحسن الديسطي</t>
-  </si>
-  <si>
-    <t>2026-03-01 18:30</t>
-  </si>
-  <si>
-    <t>01018376379</t>
-  </si>
-  <si>
-    <t>mohamed.waleed.barakat.2008@gmail.com</t>
-  </si>
-  <si>
-    <t>Mohamed Barakat</t>
-  </si>
-  <si>
-    <t>2026-03-01 18:32</t>
-  </si>
-  <si>
-    <t>01156486570</t>
-  </si>
-  <si>
-    <t>ahmed1404mostafa@gmail.com</t>
-  </si>
-  <si>
-    <t>احمد مصطفي احمد يوسف</t>
-  </si>
-  <si>
-    <t>2026-03-01 18:35</t>
-  </si>
-  <si>
-    <t>01148353989</t>
-  </si>
-  <si>
-    <t>janaamrmohamed2472009@gmail.com</t>
-  </si>
-  <si>
-    <t>Jana Amr</t>
-  </si>
-  <si>
-    <t>2026-03-01 18:41</t>
-  </si>
-  <si>
-    <t>01124926013</t>
-  </si>
-  <si>
-    <t>marwanelnakeeb2009@gmail.com</t>
-  </si>
-  <si>
-    <t>Marwan omar</t>
-  </si>
-  <si>
-    <t>2026-03-01 18:55</t>
-  </si>
-  <si>
-    <t>01091828377</t>
-  </si>
-  <si>
-    <t>yossefshref2009@gmail.com</t>
-  </si>
-  <si>
-    <t>Youssef sherif youssef</t>
-  </si>
-  <si>
-    <t>2026-03-01 19:07</t>
-  </si>
-  <si>
-    <t>01026933947</t>
-  </si>
-  <si>
-    <t>malaksamykamel2008@gmail.com</t>
-  </si>
-  <si>
-    <t>Malak Samy</t>
-  </si>
-  <si>
-    <t>01007217521</t>
-  </si>
-  <si>
-    <t>abdelrhmanmohamed2938@gmail.com</t>
-  </si>
-  <si>
-    <t>عبدالرحمن محمد حمدته</t>
-  </si>
-  <si>
-    <t>2026-03-01 18:57</t>
-  </si>
-  <si>
-    <t>01065596920</t>
-  </si>
-  <si>
-    <t>caramella3750@gmail.com</t>
-  </si>
-  <si>
-    <t>Carma Ehab</t>
-  </si>
-  <si>
-    <t>2026-03-01 19:01</t>
-  </si>
-  <si>
-    <t>01012424377</t>
-  </si>
-  <si>
-    <t>janayousry@2008gmail.com</t>
-  </si>
-  <si>
-    <t>jana ahmed mohmed yousry</t>
-  </si>
-  <si>
-    <t>2026-03-01 19:09</t>
-  </si>
-  <si>
-    <t>01097794201</t>
-  </si>
-  <si>
-    <t>aytensaleh6@gmail.com</t>
-  </si>
-  <si>
-    <t>Ayten Saleh Mostafa</t>
-  </si>
-  <si>
-    <t>2026-03-01 19:16</t>
-  </si>
-  <si>
-    <t>01151728245</t>
-  </si>
-  <si>
-    <t>Hshhzhxbheh@gmail.com</t>
-  </si>
-  <si>
-    <t>يوسف شريف عادل</t>
-  </si>
-  <si>
-    <t>2026-03-01 19:08</t>
-  </si>
-  <si>
-    <t>01063000688</t>
-  </si>
-  <si>
-    <t>bodihossni@gmail.com</t>
-  </si>
-  <si>
-    <t>Abdelrhman hossni saad</t>
-  </si>
-  <si>
-    <t>2026-03-01 19:12</t>
-  </si>
-  <si>
-    <t>01125776411</t>
-  </si>
-  <si>
-    <t>radwanosama414@gmail.com</t>
-  </si>
-  <si>
-    <t>Radwan Osama</t>
-  </si>
-  <si>
     <t>2026-03-01 19:19</t>
   </si>
   <si>
@@ -992,7 +989,7 @@
     <t>SHERIF MOHAMED</t>
   </si>
   <si>
-    <t>2026-03-02 17:02</t>
+    <t>2026-03-06 18:12</t>
   </si>
   <si>
     <t>01222221223</t>
@@ -1220,6 +1217,156 @@
     <t>Yassin Farrag</t>
   </si>
   <si>
+    <t>2026-03-06 13:57</t>
+  </si>
+  <si>
+    <t>01030350614</t>
+  </si>
+  <si>
+    <t>mahstorlive@gmail.com</t>
+  </si>
+  <si>
+    <t>محمود محمد محمود</t>
+  </si>
+  <si>
+    <t>2026-03-07 00:30</t>
+  </si>
+  <si>
+    <t>01019713904</t>
+  </si>
+  <si>
+    <t>mayar.mohamed.200813@gmail.com</t>
+  </si>
+  <si>
+    <t>ميار محمد رفعت</t>
+  </si>
+  <si>
+    <t>2026-03-08 00:55</t>
+  </si>
+  <si>
+    <t>01040794109</t>
+  </si>
+  <si>
+    <t>oa2743370@gmail.com</t>
+  </si>
+  <si>
+    <t>Omar Ibrahim Hegazy</t>
+  </si>
+  <si>
+    <t>2026-03-08 05:42</t>
+  </si>
+  <si>
+    <t>01013764074</t>
+  </si>
+  <si>
+    <t>nadayusuf2010@gmail.com</t>
+  </si>
+  <si>
+    <t>ندى يوسف عبدالله</t>
+  </si>
+  <si>
+    <t>2026-03-08 10:52</t>
+  </si>
+  <si>
+    <t>01129793194</t>
+  </si>
+  <si>
+    <t>mrxyt881@gmail.com</t>
+  </si>
+  <si>
+    <t>Mahmoud ahmed salah</t>
+  </si>
+  <si>
+    <t>2026-03-08 11:04</t>
+  </si>
+  <si>
+    <t>01553495959</t>
+  </si>
+  <si>
+    <t>elmaghlopm@gmail.com</t>
+  </si>
+  <si>
+    <t>Mariam elmaghlop</t>
+  </si>
+  <si>
+    <t>2026-03-08 13:47</t>
+  </si>
+  <si>
+    <t>01092255761</t>
+  </si>
+  <si>
+    <t>habibagalal552004@gmail.com</t>
+  </si>
+  <si>
+    <t>moustafa galal</t>
+  </si>
+  <si>
+    <t>2026-03-08 16:26</t>
+  </si>
+  <si>
+    <t>janafrahat@icloud.com</t>
+  </si>
+  <si>
+    <t>Jana Ahmed frahat</t>
+  </si>
+  <si>
+    <t>2026-03-08 17:37</t>
+  </si>
+  <si>
+    <t>01062019265</t>
+  </si>
+  <si>
+    <t>Ffdragonoo75@gmail.com</t>
+  </si>
+  <si>
+    <t>Ali waleed</t>
+  </si>
+  <si>
+    <t>2026-03-08 17:28</t>
+  </si>
+  <si>
+    <t>01101097272</t>
+  </si>
+  <si>
+    <t>mohamed.almalt2009@gmail.com</t>
+  </si>
+  <si>
+    <t>محمد السيد  بهيج</t>
+  </si>
+  <si>
+    <t>2026-03-08 19:02</t>
+  </si>
+  <si>
+    <t>01028891956</t>
+  </si>
+  <si>
+    <t>jhesham652@gmail.com</t>
+  </si>
+  <si>
+    <t>جني هشام محمد</t>
+  </si>
+  <si>
+    <t>2026-03-08 19:00</t>
+  </si>
+  <si>
+    <t>01093571345</t>
+  </si>
+  <si>
+    <t>Mallakfathyazzam@gmail.com</t>
+  </si>
+  <si>
+    <t>Malak  fathy azzam</t>
+  </si>
+  <si>
+    <t>01226990421</t>
+  </si>
+  <si>
+    <t>Hussienahmedmounir@gmail.com</t>
+  </si>
+  <si>
+    <t>حسين احمد منير</t>
+  </si>
+  <si>
     <t>الحالة</t>
   </si>
   <si>
@@ -1274,7 +1421,7 @@
     <t>الدرجة الكاملة: 10 | درجة النجاح: 5.00</t>
   </si>
   <si>
-    <t>تاريخ التصدير: 2026-03-04 21:37</t>
+    <t>تاريخ التصدير: 2026-03-08 19:44</t>
   </si>
 </sst>
 </file>
@@ -1662,7 +1809,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:P103"/>
+  <dimension ref="A1:P116"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="true" style="0"/>
@@ -1685,67 +1832,67 @@
   <sheetData>
     <row r="1" spans="1:16">
       <c r="A1" s="3" t="s">
-        <v>417</v>
+        <v>466</v>
       </c>
     </row>
     <row r="2" spans="1:16">
       <c r="A2" s="3" t="s">
-        <v>418</v>
+        <v>467</v>
       </c>
     </row>
     <row r="3" spans="1:16">
       <c r="A3" s="3" t="s">
-        <v>419</v>
+        <v>468</v>
       </c>
     </row>
     <row r="4" spans="1:16">
       <c r="A4" s="1" t="s">
-        <v>416</v>
+        <v>465</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>415</v>
+        <v>464</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>414</v>
+        <v>463</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>413</v>
+        <v>462</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>412</v>
+        <v>461</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>411</v>
+        <v>460</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>410</v>
+        <v>459</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>409</v>
+        <v>458</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>408</v>
+        <v>457</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>407</v>
+        <v>456</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>406</v>
+        <v>455</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>405</v>
+        <v>454</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>404</v>
+        <v>453</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>403</v>
+        <v>452</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>402</v>
+        <v>451</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>401</v>
+        <v>450</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1753,13 +1900,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>400</v>
+        <v>449</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>399</v>
+        <v>448</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>398</v>
+        <v>447</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>3</v>
@@ -1785,10 +1932,10 @@
         <v>5</v>
       </c>
       <c r="N5" s="2">
-        <v>19.5</v>
+        <v>2.63</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>397</v>
+        <v>443</v>
       </c>
       <c r="P5" s="2" t="s">
         <v>0</v>
@@ -1799,13 +1946,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>396</v>
+        <v>446</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>395</v>
+        <v>445</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>394</v>
+        <v>444</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>3</v>
@@ -1814,29 +1961,29 @@
         <v>1</v>
       </c>
       <c r="G6" s="2">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="H6" s="2">
         <v>10.0</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="J6" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K6" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L6" s="2"/>
       <c r="M6" s="2">
         <v>5</v>
       </c>
       <c r="N6" s="2">
-        <v>14.5</v>
+        <v>4.5</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>393</v>
+        <v>443</v>
       </c>
       <c r="P6" s="2" t="s">
         <v>0</v>
@@ -1847,19 +1994,19 @@
         <v>3</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>392</v>
+        <v>442</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>391</v>
+        <v>441</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>390</v>
+        <v>440</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F7" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G7" s="2">
         <v>6.0</v>
@@ -1881,10 +2028,10 @@
         <v>5</v>
       </c>
       <c r="N7" s="2">
-        <v>0.8</v>
+        <v>9.08</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>389</v>
+        <v>439</v>
       </c>
       <c r="P7" s="2" t="s">
         <v>0</v>
@@ -1895,44 +2042,44 @@
         <v>4</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>388</v>
+        <v>438</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>387</v>
+        <v>437</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>386</v>
+        <v>436</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F8" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G8" s="2">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
       <c r="H8" s="2">
         <v>10.0</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="J8" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K8" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L8" s="2"/>
       <c r="M8" s="2">
         <v>5</v>
       </c>
       <c r="N8" s="2">
-        <v>6.42</v>
+        <v>5.43</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>385</v>
+        <v>435</v>
       </c>
       <c r="P8" s="2" t="s">
         <v>0</v>
@@ -1943,13 +2090,13 @@
         <v>5</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>384</v>
+        <v>434</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>383</v>
+        <v>433</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>382</v>
+        <v>432</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>3</v>
@@ -1958,29 +2105,27 @@
         <v>1</v>
       </c>
       <c r="G9" s="2">
-        <v>6.0</v>
+        <v>10.0</v>
       </c>
       <c r="H9" s="2">
         <v>10.0</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="J9" s="2">
-        <v>3</v>
-      </c>
-      <c r="K9" s="2">
-        <v>2</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K9" s="2"/>
       <c r="L9" s="2"/>
       <c r="M9" s="2">
         <v>5</v>
       </c>
       <c r="N9" s="2">
-        <v>3.05</v>
+        <v>20.33</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>381</v>
+        <v>431</v>
       </c>
       <c r="P9" s="2" t="s">
         <v>0</v>
@@ -1991,13 +2136,13 @@
         <v>6</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>380</v>
+        <v>430</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>378</v>
+        <v>429</v>
+      </c>
+      <c r="D10" s="2">
+        <v>1159792350</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>3</v>
@@ -2006,29 +2151,27 @@
         <v>1</v>
       </c>
       <c r="G10" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H10" s="2">
         <v>10.0</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="J10" s="2">
-        <v>4</v>
-      </c>
-      <c r="K10" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K10" s="2"/>
       <c r="L10" s="2"/>
       <c r="M10" s="2">
         <v>5</v>
       </c>
       <c r="N10" s="2">
-        <v>8.8</v>
+        <v>11.83</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>377</v>
+        <v>428</v>
       </c>
       <c r="P10" s="2" t="s">
         <v>0</v>
@@ -2039,13 +2182,13 @@
         <v>7</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>376</v>
+        <v>427</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>375</v>
+        <v>426</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>374</v>
+        <v>425</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>3</v>
@@ -2054,27 +2197,29 @@
         <v>1</v>
       </c>
       <c r="G11" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H11" s="2">
         <v>10.0</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="J11" s="2">
-        <v>5</v>
-      </c>
-      <c r="K11" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K11" s="2">
+        <v>1</v>
+      </c>
       <c r="L11" s="2"/>
       <c r="M11" s="2">
         <v>5</v>
       </c>
       <c r="N11" s="2">
-        <v>6.55</v>
+        <v>4.88</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>373</v>
+        <v>424</v>
       </c>
       <c r="P11" s="2" t="s">
         <v>0</v>
@@ -2085,13 +2230,13 @@
         <v>8</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>372</v>
+        <v>423</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>371</v>
+        <v>422</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>370</v>
+        <v>421</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>3</v>
@@ -2119,10 +2264,10 @@
         <v>5</v>
       </c>
       <c r="N12" s="2">
-        <v>16.72</v>
+        <v>6.03</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>369</v>
+        <v>420</v>
       </c>
       <c r="P12" s="2" t="s">
         <v>0</v>
@@ -2133,13 +2278,13 @@
         <v>9</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>368</v>
+        <v>419</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>367</v>
+        <v>418</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>366</v>
+        <v>417</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>3</v>
@@ -2148,29 +2293,29 @@
         <v>1</v>
       </c>
       <c r="G13" s="2">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="H13" s="2">
         <v>10.0</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="J13" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K13" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L13" s="2"/>
       <c r="M13" s="2">
         <v>5</v>
       </c>
       <c r="N13" s="2">
-        <v>12.5</v>
+        <v>4.48</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>365</v>
+        <v>416</v>
       </c>
       <c r="P13" s="2" t="s">
         <v>0</v>
@@ -2181,13 +2326,13 @@
         <v>10</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>364</v>
+        <v>415</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>363</v>
+        <v>414</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>362</v>
+        <v>413</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>3</v>
@@ -2196,29 +2341,29 @@
         <v>1</v>
       </c>
       <c r="G14" s="2">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
       <c r="H14" s="2">
         <v>10.0</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="J14" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K14" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L14" s="2"/>
       <c r="M14" s="2">
         <v>5</v>
       </c>
       <c r="N14" s="2">
-        <v>11.57</v>
+        <v>49.1</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>361</v>
+        <v>412</v>
       </c>
       <c r="P14" s="2" t="s">
         <v>0</v>
@@ -2229,13 +2374,13 @@
         <v>11</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>360</v>
+        <v>411</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>359</v>
+        <v>410</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>358</v>
+        <v>409</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>3</v>
@@ -2244,29 +2389,27 @@
         <v>1</v>
       </c>
       <c r="G15" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H15" s="2">
         <v>10.0</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="J15" s="2">
-        <v>4</v>
-      </c>
-      <c r="K15" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K15" s="2"/>
       <c r="L15" s="2"/>
       <c r="M15" s="2">
         <v>5</v>
       </c>
       <c r="N15" s="2">
-        <v>17.75</v>
+        <v>17.32</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>357</v>
+        <v>408</v>
       </c>
       <c r="P15" s="2" t="s">
         <v>0</v>
@@ -2277,13 +2420,13 @@
         <v>12</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>356</v>
+        <v>407</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>355</v>
+        <v>406</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>354</v>
+        <v>405</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>3</v>
@@ -2311,10 +2454,10 @@
         <v>5</v>
       </c>
       <c r="N16" s="2">
-        <v>3.12</v>
+        <v>5.93</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>353</v>
+        <v>404</v>
       </c>
       <c r="P16" s="2" t="s">
         <v>0</v>
@@ -2325,44 +2468,44 @@
         <v>13</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>352</v>
+        <v>403</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>351</v>
+        <v>402</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>350</v>
+        <v>401</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F17" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G17" s="2">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
       <c r="H17" s="2">
         <v>10.0</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="J17" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K17" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L17" s="2"/>
       <c r="M17" s="2">
         <v>5</v>
       </c>
       <c r="N17" s="2">
-        <v>9.75</v>
+        <v>13.98</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>349</v>
+        <v>400</v>
       </c>
       <c r="P17" s="2" t="s">
         <v>0</v>
@@ -2373,13 +2516,13 @@
         <v>14</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>348</v>
+        <v>399</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>347</v>
+        <v>398</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>346</v>
+        <v>397</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>3</v>
@@ -2388,29 +2531,27 @@
         <v>1</v>
       </c>
       <c r="G18" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H18" s="2">
         <v>10.0</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="J18" s="2">
-        <v>4</v>
-      </c>
-      <c r="K18" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K18" s="2"/>
       <c r="L18" s="2"/>
       <c r="M18" s="2">
         <v>5</v>
       </c>
       <c r="N18" s="2">
-        <v>9.92</v>
+        <v>19.5</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>345</v>
+        <v>396</v>
       </c>
       <c r="P18" s="2" t="s">
         <v>0</v>
@@ -2421,13 +2562,13 @@
         <v>15</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>344</v>
+        <v>395</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>343</v>
+        <v>394</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>342</v>
+        <v>393</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>3</v>
@@ -2436,29 +2577,29 @@
         <v>1</v>
       </c>
       <c r="G19" s="2">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
       <c r="H19" s="2">
         <v>10.0</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="J19" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K19" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L19" s="2"/>
       <c r="M19" s="2">
         <v>5</v>
       </c>
       <c r="N19" s="2">
-        <v>15.08</v>
+        <v>14.5</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>341</v>
+        <v>392</v>
       </c>
       <c r="P19" s="2" t="s">
         <v>0</v>
@@ -2469,42 +2610,44 @@
         <v>16</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>340</v>
+        <v>391</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>339</v>
+        <v>390</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>338</v>
+        <v>389</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F20" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G20" s="2">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
       <c r="H20" s="2">
         <v>10.0</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="J20" s="2">
-        <v>5</v>
-      </c>
-      <c r="K20" s="2"/>
+        <v>3</v>
+      </c>
+      <c r="K20" s="2">
+        <v>2</v>
+      </c>
       <c r="L20" s="2"/>
       <c r="M20" s="2">
         <v>5</v>
       </c>
       <c r="N20" s="2">
-        <v>12.9</v>
+        <v>0.8</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>337</v>
+        <v>388</v>
       </c>
       <c r="P20" s="2" t="s">
         <v>0</v>
@@ -2515,13 +2658,13 @@
         <v>17</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>336</v>
+        <v>387</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>335</v>
+        <v>386</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>334</v>
+        <v>385</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>3</v>
@@ -2530,27 +2673,29 @@
         <v>1</v>
       </c>
       <c r="G21" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H21" s="2">
         <v>10.0</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="J21" s="2">
-        <v>5</v>
-      </c>
-      <c r="K21" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K21" s="2">
+        <v>1</v>
+      </c>
       <c r="L21" s="2"/>
       <c r="M21" s="2">
         <v>5</v>
       </c>
       <c r="N21" s="2">
-        <v>12.02</v>
+        <v>6.42</v>
       </c>
       <c r="O21" s="2" t="s">
-        <v>333</v>
+        <v>384</v>
       </c>
       <c r="P21" s="2" t="s">
         <v>0</v>
@@ -2561,13 +2706,13 @@
         <v>18</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>332</v>
+        <v>383</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>331</v>
+        <v>382</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>330</v>
+        <v>381</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>3</v>
@@ -2576,27 +2721,29 @@
         <v>1</v>
       </c>
       <c r="G22" s="2">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
       <c r="H22" s="2">
         <v>10.0</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="J22" s="2">
-        <v>5</v>
-      </c>
-      <c r="K22" s="2"/>
+        <v>3</v>
+      </c>
+      <c r="K22" s="2">
+        <v>2</v>
+      </c>
       <c r="L22" s="2"/>
       <c r="M22" s="2">
         <v>5</v>
       </c>
       <c r="N22" s="2">
-        <v>9.12</v>
+        <v>3.05</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>329</v>
+        <v>380</v>
       </c>
       <c r="P22" s="2" t="s">
         <v>0</v>
@@ -2607,13 +2754,13 @@
         <v>19</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>328</v>
+        <v>379</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>327</v>
+        <v>378</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>326</v>
+        <v>377</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>3</v>
@@ -2622,29 +2769,29 @@
         <v>1</v>
       </c>
       <c r="G23" s="2">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="H23" s="2">
         <v>10.0</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="J23" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K23" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L23" s="2"/>
       <c r="M23" s="2">
         <v>5</v>
       </c>
       <c r="N23" s="2">
-        <v>19.67</v>
+        <v>8.8</v>
       </c>
       <c r="O23" s="2" t="s">
-        <v>325</v>
+        <v>376</v>
       </c>
       <c r="P23" s="2" t="s">
         <v>0</v>
@@ -2655,13 +2802,13 @@
         <v>20</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>324</v>
+        <v>375</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>323</v>
+        <v>374</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>322</v>
+        <v>373</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>3</v>
@@ -2670,29 +2817,27 @@
         <v>1</v>
       </c>
       <c r="G24" s="2">
-        <v>6.0</v>
+        <v>10.0</v>
       </c>
       <c r="H24" s="2">
         <v>10.0</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="J24" s="2">
-        <v>3</v>
-      </c>
-      <c r="K24" s="2">
-        <v>2</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K24" s="2"/>
       <c r="L24" s="2"/>
       <c r="M24" s="2">
         <v>5</v>
       </c>
       <c r="N24" s="2">
-        <v>9.32</v>
+        <v>6.55</v>
       </c>
       <c r="O24" s="2" t="s">
-        <v>321</v>
+        <v>372</v>
       </c>
       <c r="P24" s="2" t="s">
         <v>0</v>
@@ -2703,13 +2848,13 @@
         <v>21</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>320</v>
+        <v>371</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>319</v>
+        <v>370</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>318</v>
+        <v>369</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>3</v>
@@ -2718,27 +2863,29 @@
         <v>1</v>
       </c>
       <c r="G25" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H25" s="2">
         <v>10.0</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="J25" s="2">
-        <v>5</v>
-      </c>
-      <c r="K25" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K25" s="2">
+        <v>1</v>
+      </c>
       <c r="L25" s="2"/>
       <c r="M25" s="2">
         <v>5</v>
       </c>
       <c r="N25" s="2">
-        <v>24.92</v>
+        <v>16.72</v>
       </c>
       <c r="O25" s="2" t="s">
-        <v>317</v>
+        <v>368</v>
       </c>
       <c r="P25" s="2" t="s">
         <v>0</v>
@@ -2749,19 +2896,19 @@
         <v>22</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>316</v>
+        <v>367</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>315</v>
+        <v>366</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>314</v>
+        <v>365</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F26" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G26" s="2">
         <v>6.0</v>
@@ -2783,10 +2930,10 @@
         <v>5</v>
       </c>
       <c r="N26" s="2">
-        <v>5.23</v>
+        <v>12.5</v>
       </c>
       <c r="O26" s="2" t="s">
-        <v>313</v>
+        <v>364</v>
       </c>
       <c r="P26" s="2" t="s">
         <v>0</v>
@@ -2797,13 +2944,13 @@
         <v>23</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>312</v>
+        <v>363</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>311</v>
+        <v>362</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>310</v>
+        <v>361</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>3</v>
@@ -2812,29 +2959,29 @@
         <v>1</v>
       </c>
       <c r="G27" s="2">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="H27" s="2">
         <v>10.0</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="J27" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K27" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L27" s="2"/>
       <c r="M27" s="2">
         <v>5</v>
       </c>
       <c r="N27" s="2">
-        <v>22.08</v>
+        <v>11.57</v>
       </c>
       <c r="O27" s="2" t="s">
-        <v>309</v>
+        <v>360</v>
       </c>
       <c r="P27" s="2" t="s">
         <v>0</v>
@@ -2845,13 +2992,13 @@
         <v>24</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>308</v>
+        <v>359</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>307</v>
+        <v>358</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>306</v>
+        <v>357</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>3</v>
@@ -2879,10 +3026,10 @@
         <v>5</v>
       </c>
       <c r="N28" s="2">
-        <v>10.18</v>
+        <v>17.75</v>
       </c>
       <c r="O28" s="2" t="s">
-        <v>305</v>
+        <v>356</v>
       </c>
       <c r="P28" s="2" t="s">
         <v>0</v>
@@ -2893,13 +3040,13 @@
         <v>25</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>304</v>
+        <v>355</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>303</v>
+        <v>354</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>302</v>
+        <v>353</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>3</v>
@@ -2908,27 +3055,29 @@
         <v>1</v>
       </c>
       <c r="G29" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H29" s="2">
         <v>10.0</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="J29" s="2">
-        <v>5</v>
-      </c>
-      <c r="K29" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K29" s="2">
+        <v>1</v>
+      </c>
       <c r="L29" s="2"/>
       <c r="M29" s="2">
         <v>5</v>
       </c>
       <c r="N29" s="2">
-        <v>25.72</v>
+        <v>3.12</v>
       </c>
       <c r="O29" s="2" t="s">
-        <v>301</v>
+        <v>352</v>
       </c>
       <c r="P29" s="2" t="s">
         <v>0</v>
@@ -2939,13 +3088,13 @@
         <v>26</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>300</v>
+        <v>351</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>299</v>
+        <v>350</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>298</v>
+        <v>349</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>3</v>
@@ -2954,29 +3103,29 @@
         <v>1</v>
       </c>
       <c r="G30" s="2">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="H30" s="2">
         <v>10.0</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="J30" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K30" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L30" s="2"/>
       <c r="M30" s="2">
         <v>5</v>
       </c>
       <c r="N30" s="2">
-        <v>13.57</v>
+        <v>9.75</v>
       </c>
       <c r="O30" s="2" t="s">
-        <v>297</v>
+        <v>348</v>
       </c>
       <c r="P30" s="2" t="s">
         <v>0</v>
@@ -2987,13 +3136,13 @@
         <v>27</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>296</v>
+        <v>347</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>295</v>
+        <v>346</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>294</v>
+        <v>345</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>3</v>
@@ -3002,27 +3151,29 @@
         <v>1</v>
       </c>
       <c r="G31" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H31" s="2">
         <v>10.0</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="J31" s="2">
-        <v>5</v>
-      </c>
-      <c r="K31" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K31" s="2">
+        <v>1</v>
+      </c>
       <c r="L31" s="2"/>
       <c r="M31" s="2">
         <v>5</v>
       </c>
       <c r="N31" s="2">
-        <v>27.03</v>
+        <v>9.92</v>
       </c>
       <c r="O31" s="2" t="s">
-        <v>293</v>
+        <v>344</v>
       </c>
       <c r="P31" s="2" t="s">
         <v>0</v>
@@ -3033,19 +3184,19 @@
         <v>28</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>292</v>
+        <v>343</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>291</v>
+        <v>342</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>290</v>
+        <v>341</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F32" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G32" s="2">
         <v>8.0</v>
@@ -3067,10 +3218,10 @@
         <v>5</v>
       </c>
       <c r="N32" s="2">
-        <v>3.0</v>
+        <v>15.08</v>
       </c>
       <c r="O32" s="2" t="s">
-        <v>289</v>
+        <v>340</v>
       </c>
       <c r="P32" s="2" t="s">
         <v>0</v>
@@ -3081,13 +3232,13 @@
         <v>29</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>288</v>
+        <v>339</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>287</v>
+        <v>338</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>286</v>
+        <v>337</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>3</v>
@@ -3113,10 +3264,10 @@
         <v>5</v>
       </c>
       <c r="N33" s="2">
-        <v>4.58</v>
+        <v>12.9</v>
       </c>
       <c r="O33" s="2" t="s">
-        <v>285</v>
+        <v>336</v>
       </c>
       <c r="P33" s="2" t="s">
         <v>0</v>
@@ -3127,13 +3278,13 @@
         <v>30</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>284</v>
+        <v>335</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>283</v>
+        <v>334</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>282</v>
+        <v>333</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>3</v>
@@ -3159,10 +3310,10 @@
         <v>5</v>
       </c>
       <c r="N34" s="2">
-        <v>5.58</v>
+        <v>12.02</v>
       </c>
       <c r="O34" s="2" t="s">
-        <v>281</v>
+        <v>332</v>
       </c>
       <c r="P34" s="2" t="s">
         <v>0</v>
@@ -3173,13 +3324,13 @@
         <v>31</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>280</v>
+        <v>331</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>279</v>
+        <v>330</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>278</v>
+        <v>329</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>3</v>
@@ -3188,29 +3339,27 @@
         <v>1</v>
       </c>
       <c r="G35" s="2">
-        <v>6.0</v>
+        <v>10.0</v>
       </c>
       <c r="H35" s="2">
         <v>10.0</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="J35" s="2">
-        <v>3</v>
-      </c>
-      <c r="K35" s="2">
-        <v>2</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K35" s="2"/>
       <c r="L35" s="2"/>
       <c r="M35" s="2">
         <v>5</v>
       </c>
       <c r="N35" s="2">
-        <v>22.25</v>
+        <v>9.12</v>
       </c>
       <c r="O35" s="2" t="s">
-        <v>277</v>
+        <v>328</v>
       </c>
       <c r="P35" s="2" t="s">
         <v>0</v>
@@ -3221,44 +3370,44 @@
         <v>32</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>276</v>
+        <v>327</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="D36" s="2">
-        <v>201118200153</v>
+        <v>326</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>325</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F36" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G36" s="2">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="H36" s="2">
         <v>10.0</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="J36" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K36" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L36" s="2"/>
       <c r="M36" s="2">
         <v>5</v>
       </c>
       <c r="N36" s="2">
-        <v>2.13</v>
+        <v>5829.68</v>
       </c>
       <c r="O36" s="2" t="s">
-        <v>274</v>
+        <v>324</v>
       </c>
       <c r="P36" s="2" t="s">
         <v>0</v>
@@ -3269,13 +3418,13 @@
         <v>33</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>273</v>
+        <v>323</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>272</v>
+        <v>322</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>271</v>
+        <v>321</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>3</v>
@@ -3284,27 +3433,29 @@
         <v>1</v>
       </c>
       <c r="G37" s="2">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
       <c r="H37" s="2">
         <v>10.0</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="J37" s="2">
-        <v>5</v>
-      </c>
-      <c r="K37" s="2"/>
+        <v>3</v>
+      </c>
+      <c r="K37" s="2">
+        <v>2</v>
+      </c>
       <c r="L37" s="2"/>
       <c r="M37" s="2">
         <v>5</v>
       </c>
       <c r="N37" s="2">
-        <v>5.0</v>
+        <v>9.32</v>
       </c>
       <c r="O37" s="2" t="s">
-        <v>270</v>
+        <v>320</v>
       </c>
       <c r="P37" s="2" t="s">
         <v>0</v>
@@ -3315,13 +3466,13 @@
         <v>34</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>269</v>
+        <v>319</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>268</v>
+        <v>318</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>267</v>
+        <v>317</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>3</v>
@@ -3347,10 +3498,10 @@
         <v>5</v>
       </c>
       <c r="N38" s="2">
-        <v>5.87</v>
+        <v>24.92</v>
       </c>
       <c r="O38" s="2" t="s">
-        <v>266</v>
+        <v>316</v>
       </c>
       <c r="P38" s="2" t="s">
         <v>0</v>
@@ -3361,44 +3512,44 @@
         <v>35</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>265</v>
+        <v>315</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>264</v>
+        <v>314</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>263</v>
+        <v>313</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F39" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G39" s="2">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
       <c r="H39" s="2">
         <v>10.0</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="J39" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K39" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L39" s="2"/>
       <c r="M39" s="2">
         <v>5</v>
       </c>
       <c r="N39" s="2">
-        <v>8.92</v>
+        <v>5.23</v>
       </c>
       <c r="O39" s="2" t="s">
-        <v>262</v>
+        <v>312</v>
       </c>
       <c r="P39" s="2" t="s">
         <v>0</v>
@@ -3409,13 +3560,13 @@
         <v>36</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>261</v>
+        <v>311</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>260</v>
+        <v>310</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>259</v>
+        <v>309</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>3</v>
@@ -3424,29 +3575,29 @@
         <v>1</v>
       </c>
       <c r="G40" s="2">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
       <c r="H40" s="2">
         <v>10.0</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="J40" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K40" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L40" s="2"/>
       <c r="M40" s="2">
         <v>5</v>
       </c>
       <c r="N40" s="2">
-        <v>5.8</v>
+        <v>22.08</v>
       </c>
       <c r="O40" s="2" t="s">
-        <v>258</v>
+        <v>308</v>
       </c>
       <c r="P40" s="2" t="s">
         <v>0</v>
@@ -3457,13 +3608,13 @@
         <v>37</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>257</v>
+        <v>307</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>256</v>
+        <v>306</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>255</v>
+        <v>305</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>3</v>
@@ -3472,27 +3623,29 @@
         <v>1</v>
       </c>
       <c r="G41" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H41" s="2">
         <v>10.0</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="J41" s="2">
-        <v>5</v>
-      </c>
-      <c r="K41" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K41" s="2">
+        <v>1</v>
+      </c>
       <c r="L41" s="2"/>
       <c r="M41" s="2">
         <v>5</v>
       </c>
       <c r="N41" s="2">
-        <v>3.17</v>
+        <v>10.18</v>
       </c>
       <c r="O41" s="2" t="s">
-        <v>254</v>
+        <v>304</v>
       </c>
       <c r="P41" s="2" t="s">
         <v>0</v>
@@ -3503,13 +3656,13 @@
         <v>38</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>253</v>
+        <v>303</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>252</v>
+        <v>302</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>251</v>
+        <v>301</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>3</v>
@@ -3518,29 +3671,27 @@
         <v>1</v>
       </c>
       <c r="G42" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H42" s="2">
         <v>10.0</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="J42" s="2">
-        <v>4</v>
-      </c>
-      <c r="K42" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K42" s="2"/>
       <c r="L42" s="2"/>
       <c r="M42" s="2">
         <v>5</v>
       </c>
       <c r="N42" s="2">
-        <v>3.2</v>
+        <v>25.72</v>
       </c>
       <c r="O42" s="2" t="s">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="P42" s="2" t="s">
         <v>0</v>
@@ -3551,13 +3702,13 @@
         <v>39</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>249</v>
+        <v>299</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>248</v>
+        <v>298</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>247</v>
+        <v>297</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>3</v>
@@ -3566,29 +3717,29 @@
         <v>1</v>
       </c>
       <c r="G43" s="2">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
       <c r="H43" s="2">
         <v>10.0</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="J43" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K43" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L43" s="2"/>
       <c r="M43" s="2">
         <v>5</v>
       </c>
       <c r="N43" s="2">
-        <v>14.28</v>
+        <v>13.57</v>
       </c>
       <c r="O43" s="2" t="s">
-        <v>246</v>
+        <v>296</v>
       </c>
       <c r="P43" s="2" t="s">
         <v>0</v>
@@ -3599,13 +3750,13 @@
         <v>40</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>245</v>
+        <v>295</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>244</v>
+        <v>294</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>243</v>
+        <v>293</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>3</v>
@@ -3614,29 +3765,27 @@
         <v>1</v>
       </c>
       <c r="G44" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H44" s="2">
         <v>10.0</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="J44" s="2">
-        <v>4</v>
-      </c>
-      <c r="K44" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K44" s="2"/>
       <c r="L44" s="2"/>
       <c r="M44" s="2">
         <v>5</v>
       </c>
       <c r="N44" s="2">
-        <v>12.48</v>
+        <v>27.03</v>
       </c>
       <c r="O44" s="2" t="s">
-        <v>242</v>
+        <v>292</v>
       </c>
       <c r="P44" s="2" t="s">
         <v>0</v>
@@ -3647,19 +3796,19 @@
         <v>41</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>241</v>
+        <v>291</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>240</v>
+        <v>290</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>239</v>
+        <v>289</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F45" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G45" s="2">
         <v>8.0</v>
@@ -3681,10 +3830,10 @@
         <v>5</v>
       </c>
       <c r="N45" s="2">
-        <v>4.22</v>
+        <v>3.0</v>
       </c>
       <c r="O45" s="2" t="s">
-        <v>238</v>
+        <v>288</v>
       </c>
       <c r="P45" s="2" t="s">
         <v>0</v>
@@ -3695,13 +3844,13 @@
         <v>42</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>237</v>
+        <v>287</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>236</v>
+        <v>286</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>235</v>
+        <v>285</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>3</v>
@@ -3710,29 +3859,27 @@
         <v>1</v>
       </c>
       <c r="G46" s="2">
-        <v>6.0</v>
+        <v>10.0</v>
       </c>
       <c r="H46" s="2">
         <v>10.0</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="J46" s="2">
-        <v>3</v>
-      </c>
-      <c r="K46" s="2">
-        <v>2</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K46" s="2"/>
       <c r="L46" s="2"/>
       <c r="M46" s="2">
         <v>5</v>
       </c>
       <c r="N46" s="2">
-        <v>8.42</v>
+        <v>4.58</v>
       </c>
       <c r="O46" s="2" t="s">
-        <v>234</v>
+        <v>284</v>
       </c>
       <c r="P46" s="2" t="s">
         <v>0</v>
@@ -3743,13 +3890,13 @@
         <v>43</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>233</v>
+        <v>283</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>232</v>
+        <v>282</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>231</v>
+        <v>281</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>3</v>
@@ -3758,29 +3905,27 @@
         <v>1</v>
       </c>
       <c r="G47" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H47" s="2">
         <v>10.0</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="J47" s="2">
-        <v>4</v>
-      </c>
-      <c r="K47" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K47" s="2"/>
       <c r="L47" s="2"/>
       <c r="M47" s="2">
         <v>5</v>
       </c>
       <c r="N47" s="2">
-        <v>7.37</v>
+        <v>5.58</v>
       </c>
       <c r="O47" s="2" t="s">
-        <v>192</v>
+        <v>280</v>
       </c>
       <c r="P47" s="2" t="s">
         <v>0</v>
@@ -3791,13 +3936,13 @@
         <v>44</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>230</v>
+        <v>279</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>229</v>
+        <v>278</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>228</v>
+        <v>277</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>3</v>
@@ -3806,27 +3951,29 @@
         <v>1</v>
       </c>
       <c r="G48" s="2">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
       <c r="H48" s="2">
         <v>10.0</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="J48" s="2">
-        <v>5</v>
-      </c>
-      <c r="K48" s="2"/>
+        <v>3</v>
+      </c>
+      <c r="K48" s="2">
+        <v>2</v>
+      </c>
       <c r="L48" s="2"/>
       <c r="M48" s="2">
         <v>5</v>
       </c>
       <c r="N48" s="2">
-        <v>23.67</v>
+        <v>22.25</v>
       </c>
       <c r="O48" s="2" t="s">
-        <v>227</v>
+        <v>276</v>
       </c>
       <c r="P48" s="2" t="s">
         <v>0</v>
@@ -3837,13 +3984,13 @@
         <v>45</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>226</v>
+        <v>275</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>224</v>
+        <v>274</v>
+      </c>
+      <c r="D49" s="2">
+        <v>201118200153</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>3</v>
@@ -3852,29 +3999,29 @@
         <v>1</v>
       </c>
       <c r="G49" s="2">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
       <c r="H49" s="2">
         <v>10.0</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="J49" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K49" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L49" s="2"/>
       <c r="M49" s="2">
         <v>5</v>
       </c>
       <c r="N49" s="2">
-        <v>15.78</v>
+        <v>2.13</v>
       </c>
       <c r="O49" s="2" t="s">
-        <v>223</v>
+        <v>273</v>
       </c>
       <c r="P49" s="2" t="s">
         <v>0</v>
@@ -3885,13 +4032,13 @@
         <v>46</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>222</v>
+        <v>272</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>221</v>
+        <v>271</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>220</v>
+        <v>270</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>3</v>
@@ -3917,10 +4064,10 @@
         <v>5</v>
       </c>
       <c r="N50" s="2">
-        <v>7.02</v>
+        <v>5.0</v>
       </c>
       <c r="O50" s="2" t="s">
-        <v>219</v>
+        <v>269</v>
       </c>
       <c r="P50" s="2" t="s">
         <v>0</v>
@@ -3931,13 +4078,13 @@
         <v>47</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>218</v>
+        <v>268</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>217</v>
+        <v>267</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>216</v>
+        <v>266</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>3</v>
@@ -3946,29 +4093,27 @@
         <v>1</v>
       </c>
       <c r="G51" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H51" s="2">
         <v>10.0</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="J51" s="2">
-        <v>4</v>
-      </c>
-      <c r="K51" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K51" s="2"/>
       <c r="L51" s="2"/>
       <c r="M51" s="2">
         <v>5</v>
       </c>
       <c r="N51" s="2">
-        <v>7.05</v>
+        <v>5.87</v>
       </c>
       <c r="O51" s="2" t="s">
-        <v>215</v>
+        <v>265</v>
       </c>
       <c r="P51" s="2" t="s">
         <v>0</v>
@@ -3979,13 +4124,13 @@
         <v>48</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>214</v>
+        <v>264</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>213</v>
+        <v>263</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>212</v>
+        <v>262</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>3</v>
@@ -3994,32 +4139,32 @@
         <v>1</v>
       </c>
       <c r="G52" s="2">
-        <v>2.0</v>
+        <v>8.0</v>
       </c>
       <c r="H52" s="2">
         <v>10.0</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>163</v>
+        <v>2</v>
       </c>
       <c r="J52" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K52" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L52" s="2"/>
       <c r="M52" s="2">
         <v>5</v>
       </c>
       <c r="N52" s="2">
-        <v>5.35</v>
+        <v>8.92</v>
       </c>
       <c r="O52" s="2" t="s">
-        <v>211</v>
+        <v>261</v>
       </c>
       <c r="P52" s="2" t="s">
-        <v>161</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -4027,19 +4172,19 @@
         <v>49</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>210</v>
+        <v>260</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>209</v>
+        <v>259</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>208</v>
+        <v>258</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F53" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G53" s="2">
         <v>8.0</v>
@@ -4061,10 +4206,10 @@
         <v>5</v>
       </c>
       <c r="N53" s="2">
-        <v>3.77</v>
+        <v>5.8</v>
       </c>
       <c r="O53" s="2" t="s">
-        <v>207</v>
+        <v>257</v>
       </c>
       <c r="P53" s="2" t="s">
         <v>0</v>
@@ -4075,19 +4220,19 @@
         <v>50</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>206</v>
+        <v>256</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>205</v>
+        <v>255</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>204</v>
+        <v>254</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F54" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G54" s="2">
         <v>8.0</v>
@@ -4109,10 +4254,10 @@
         <v>5</v>
       </c>
       <c r="N54" s="2">
-        <v>11.42</v>
+        <v>9911.38</v>
       </c>
       <c r="O54" s="2" t="s">
-        <v>203</v>
+        <v>253</v>
       </c>
       <c r="P54" s="2" t="s">
         <v>0</v>
@@ -4123,19 +4268,19 @@
         <v>51</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>202</v>
+        <v>252</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>201</v>
+        <v>251</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F55" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G55" s="2">
         <v>6.0</v>
@@ -4157,10 +4302,10 @@
         <v>5</v>
       </c>
       <c r="N55" s="2">
-        <v>3.57</v>
+        <v>10012.08</v>
       </c>
       <c r="O55" s="2" t="s">
-        <v>199</v>
+        <v>249</v>
       </c>
       <c r="P55" s="2" t="s">
         <v>0</v>
@@ -4171,13 +4316,13 @@
         <v>52</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>198</v>
+        <v>248</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>197</v>
+        <v>247</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>196</v>
+        <v>246</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>3</v>
@@ -4186,29 +4331,27 @@
         <v>1</v>
       </c>
       <c r="G56" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H56" s="2">
         <v>10.0</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="J56" s="2">
-        <v>4</v>
-      </c>
-      <c r="K56" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K56" s="2"/>
       <c r="L56" s="2"/>
       <c r="M56" s="2">
         <v>5</v>
       </c>
       <c r="N56" s="2">
-        <v>7.5</v>
+        <v>3.17</v>
       </c>
       <c r="O56" s="2" t="s">
-        <v>184</v>
+        <v>245</v>
       </c>
       <c r="P56" s="2" t="s">
         <v>0</v>
@@ -4219,13 +4362,13 @@
         <v>53</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>195</v>
+        <v>244</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>194</v>
+        <v>243</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>193</v>
+        <v>242</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>3</v>
@@ -4253,10 +4396,10 @@
         <v>5</v>
       </c>
       <c r="N57" s="2">
-        <v>39.38</v>
+        <v>3.2</v>
       </c>
       <c r="O57" s="2" t="s">
-        <v>192</v>
+        <v>241</v>
       </c>
       <c r="P57" s="2" t="s">
         <v>0</v>
@@ -4267,13 +4410,13 @@
         <v>54</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>191</v>
+        <v>240</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>190</v>
+        <v>239</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>189</v>
+        <v>238</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>3</v>
@@ -4301,10 +4444,10 @@
         <v>5</v>
       </c>
       <c r="N58" s="2">
-        <v>11.68</v>
+        <v>14.28</v>
       </c>
       <c r="O58" s="2" t="s">
-        <v>188</v>
+        <v>237</v>
       </c>
       <c r="P58" s="2" t="s">
         <v>0</v>
@@ -4315,13 +4458,13 @@
         <v>55</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>187</v>
+        <v>236</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>186</v>
+        <v>235</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>185</v>
+        <v>234</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>3</v>
@@ -4349,10 +4492,10 @@
         <v>5</v>
       </c>
       <c r="N59" s="2">
-        <v>15.92</v>
+        <v>12.48</v>
       </c>
       <c r="O59" s="2" t="s">
-        <v>184</v>
+        <v>233</v>
       </c>
       <c r="P59" s="2" t="s">
         <v>0</v>
@@ -4363,13 +4506,13 @@
         <v>56</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>183</v>
+        <v>232</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>182</v>
+        <v>231</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>181</v>
+        <v>230</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>3</v>
@@ -4397,10 +4540,10 @@
         <v>5</v>
       </c>
       <c r="N60" s="2">
-        <v>6.17</v>
+        <v>4.22</v>
       </c>
       <c r="O60" s="2" t="s">
-        <v>180</v>
+        <v>229</v>
       </c>
       <c r="P60" s="2" t="s">
         <v>0</v>
@@ -4411,13 +4554,13 @@
         <v>57</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>179</v>
+        <v>228</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>178</v>
+        <v>227</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>177</v>
+        <v>226</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>3</v>
@@ -4426,27 +4569,29 @@
         <v>1</v>
       </c>
       <c r="G61" s="2">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
       <c r="H61" s="2">
         <v>10.0</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="J61" s="2">
-        <v>5</v>
-      </c>
-      <c r="K61" s="2"/>
+        <v>3</v>
+      </c>
+      <c r="K61" s="2">
+        <v>2</v>
+      </c>
       <c r="L61" s="2"/>
       <c r="M61" s="2">
         <v>5</v>
       </c>
       <c r="N61" s="2">
-        <v>5.92</v>
+        <v>8.42</v>
       </c>
       <c r="O61" s="2" t="s">
-        <v>176</v>
+        <v>225</v>
       </c>
       <c r="P61" s="2" t="s">
         <v>0</v>
@@ -4457,13 +4602,13 @@
         <v>58</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>175</v>
+        <v>224</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>174</v>
+        <v>223</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>173</v>
+        <v>222</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>3</v>
@@ -4472,32 +4617,32 @@
         <v>1</v>
       </c>
       <c r="G62" s="2">
-        <v>4.0</v>
+        <v>8.0</v>
       </c>
       <c r="H62" s="2">
         <v>10.0</v>
       </c>
       <c r="I62" s="2" t="s">
-        <v>172</v>
+        <v>2</v>
       </c>
       <c r="J62" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K62" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L62" s="2"/>
       <c r="M62" s="2">
         <v>5</v>
       </c>
       <c r="N62" s="2">
-        <v>5.95</v>
+        <v>7.37</v>
       </c>
       <c r="O62" s="2" t="s">
-        <v>171</v>
+        <v>187</v>
       </c>
       <c r="P62" s="2" t="s">
-        <v>161</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -4505,13 +4650,13 @@
         <v>59</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>170</v>
+        <v>221</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>169</v>
+        <v>220</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>168</v>
+        <v>219</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>3</v>
@@ -4537,10 +4682,10 @@
         <v>5</v>
       </c>
       <c r="N63" s="2">
-        <v>9.08</v>
+        <v>23.67</v>
       </c>
       <c r="O63" s="2" t="s">
-        <v>167</v>
+        <v>218</v>
       </c>
       <c r="P63" s="2" t="s">
         <v>0</v>
@@ -4551,13 +4696,13 @@
         <v>60</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>166</v>
+        <v>217</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>165</v>
+        <v>216</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>164</v>
+        <v>215</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>3</v>
@@ -4566,32 +4711,32 @@
         <v>1</v>
       </c>
       <c r="G64" s="2">
-        <v>2.0</v>
+        <v>8.0</v>
       </c>
       <c r="H64" s="2">
         <v>10.0</v>
       </c>
       <c r="I64" s="2" t="s">
-        <v>163</v>
+        <v>2</v>
       </c>
       <c r="J64" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K64" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L64" s="2"/>
       <c r="M64" s="2">
         <v>5</v>
       </c>
       <c r="N64" s="2">
-        <v>10.48</v>
+        <v>15.78</v>
       </c>
       <c r="O64" s="2" t="s">
-        <v>162</v>
+        <v>214</v>
       </c>
       <c r="P64" s="2" t="s">
-        <v>161</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -4599,13 +4744,13 @@
         <v>61</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>160</v>
+        <v>213</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>159</v>
+        <v>212</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>158</v>
+        <v>211</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>3</v>
@@ -4614,29 +4759,27 @@
         <v>1</v>
       </c>
       <c r="G65" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H65" s="2">
         <v>10.0</v>
       </c>
       <c r="I65" s="2" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="J65" s="2">
-        <v>4</v>
-      </c>
-      <c r="K65" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K65" s="2"/>
       <c r="L65" s="2"/>
       <c r="M65" s="2">
         <v>5</v>
       </c>
       <c r="N65" s="2">
-        <v>13.42</v>
+        <v>7.02</v>
       </c>
       <c r="O65" s="2" t="s">
-        <v>157</v>
+        <v>210</v>
       </c>
       <c r="P65" s="2" t="s">
         <v>0</v>
@@ -4647,13 +4790,13 @@
         <v>62</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>156</v>
+        <v>209</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>155</v>
+        <v>208</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>154</v>
+        <v>207</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>3</v>
@@ -4662,29 +4805,29 @@
         <v>1</v>
       </c>
       <c r="G66" s="2">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="H66" s="2">
         <v>10.0</v>
       </c>
       <c r="I66" s="2" t="s">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="J66" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K66" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L66" s="2"/>
       <c r="M66" s="2">
         <v>5</v>
       </c>
       <c r="N66" s="2">
-        <v>2.57</v>
+        <v>7.05</v>
       </c>
       <c r="O66" s="2" t="s">
-        <v>153</v>
+        <v>206</v>
       </c>
       <c r="P66" s="2" t="s">
         <v>0</v>
@@ -4695,42 +4838,44 @@
         <v>63</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>152</v>
+        <v>205</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>151</v>
+        <v>204</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>150</v>
+        <v>203</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F67" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G67" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H67" s="2">
         <v>10.0</v>
       </c>
       <c r="I67" s="2" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="J67" s="2">
-        <v>5</v>
-      </c>
-      <c r="K67" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K67" s="2">
+        <v>1</v>
+      </c>
       <c r="L67" s="2"/>
       <c r="M67" s="2">
         <v>5</v>
       </c>
       <c r="N67" s="2">
-        <v>1.65</v>
+        <v>3.77</v>
       </c>
       <c r="O67" s="2" t="s">
-        <v>149</v>
+        <v>202</v>
       </c>
       <c r="P67" s="2" t="s">
         <v>0</v>
@@ -4741,13 +4886,13 @@
         <v>64</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>148</v>
+        <v>201</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>147</v>
+        <v>200</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>146</v>
+        <v>199</v>
       </c>
       <c r="E68" s="2" t="s">
         <v>3</v>
@@ -4756,29 +4901,29 @@
         <v>1</v>
       </c>
       <c r="G68" s="2">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="H68" s="2">
         <v>10.0</v>
       </c>
       <c r="I68" s="2" t="s">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="J68" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K68" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L68" s="2"/>
       <c r="M68" s="2">
         <v>5</v>
       </c>
       <c r="N68" s="2">
-        <v>12.1</v>
+        <v>11.42</v>
       </c>
       <c r="O68" s="2" t="s">
-        <v>145</v>
+        <v>198</v>
       </c>
       <c r="P68" s="2" t="s">
         <v>0</v>
@@ -4789,13 +4934,13 @@
         <v>65</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>144</v>
+        <v>197</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>143</v>
+        <v>196</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>142</v>
+        <v>195</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>3</v>
@@ -4823,10 +4968,10 @@
         <v>5</v>
       </c>
       <c r="N69" s="2">
-        <v>18.58</v>
+        <v>3.57</v>
       </c>
       <c r="O69" s="2" t="s">
-        <v>141</v>
+        <v>194</v>
       </c>
       <c r="P69" s="2" t="s">
         <v>0</v>
@@ -4837,13 +4982,13 @@
         <v>66</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>140</v>
+        <v>193</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>139</v>
+        <v>192</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>138</v>
+        <v>191</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>3</v>
@@ -4852,27 +4997,29 @@
         <v>1</v>
       </c>
       <c r="G70" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H70" s="2">
         <v>10.0</v>
       </c>
       <c r="I70" s="2" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="J70" s="2">
-        <v>5</v>
-      </c>
-      <c r="K70" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K70" s="2">
+        <v>1</v>
+      </c>
       <c r="L70" s="2"/>
       <c r="M70" s="2">
         <v>5</v>
       </c>
       <c r="N70" s="2">
-        <v>18.03</v>
+        <v>7.5</v>
       </c>
       <c r="O70" s="2" t="s">
-        <v>137</v>
+        <v>179</v>
       </c>
       <c r="P70" s="2" t="s">
         <v>0</v>
@@ -4883,13 +5030,13 @@
         <v>67</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>136</v>
+        <v>190</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>135</v>
+        <v>189</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>134</v>
+        <v>188</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>3</v>
@@ -4917,10 +5064,10 @@
         <v>5</v>
       </c>
       <c r="N71" s="2">
-        <v>9.68</v>
+        <v>39.38</v>
       </c>
       <c r="O71" s="2" t="s">
-        <v>133</v>
+        <v>187</v>
       </c>
       <c r="P71" s="2" t="s">
         <v>0</v>
@@ -4931,13 +5078,13 @@
         <v>68</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>132</v>
+        <v>186</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>131</v>
+        <v>185</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>130</v>
+        <v>184</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>3</v>
@@ -4946,29 +5093,29 @@
         <v>1</v>
       </c>
       <c r="G72" s="2">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="H72" s="2">
         <v>10.0</v>
       </c>
       <c r="I72" s="2" t="s">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="J72" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K72" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L72" s="2"/>
       <c r="M72" s="2">
         <v>5</v>
       </c>
       <c r="N72" s="2">
-        <v>14.13</v>
+        <v>11.68</v>
       </c>
       <c r="O72" s="2" t="s">
-        <v>129</v>
+        <v>183</v>
       </c>
       <c r="P72" s="2" t="s">
         <v>0</v>
@@ -4979,13 +5126,13 @@
         <v>69</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>128</v>
+        <v>182</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>127</v>
+        <v>181</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>126</v>
+        <v>180</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>3</v>
@@ -5013,10 +5160,10 @@
         <v>5</v>
       </c>
       <c r="N73" s="2">
-        <v>11.45</v>
+        <v>15.92</v>
       </c>
       <c r="O73" s="2" t="s">
-        <v>125</v>
+        <v>179</v>
       </c>
       <c r="P73" s="2" t="s">
         <v>0</v>
@@ -5027,13 +5174,13 @@
         <v>70</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>124</v>
+        <v>178</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>123</v>
+        <v>177</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>122</v>
+        <v>176</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>3</v>
@@ -5061,10 +5208,10 @@
         <v>5</v>
       </c>
       <c r="N74" s="2">
-        <v>12.55</v>
+        <v>6.17</v>
       </c>
       <c r="O74" s="2" t="s">
-        <v>121</v>
+        <v>175</v>
       </c>
       <c r="P74" s="2" t="s">
         <v>0</v>
@@ -5075,13 +5222,13 @@
         <v>71</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>120</v>
+        <v>174</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>119</v>
+        <v>173</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>118</v>
+        <v>172</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>3</v>
@@ -5107,10 +5254,10 @@
         <v>5</v>
       </c>
       <c r="N75" s="2">
-        <v>6.58</v>
+        <v>5.92</v>
       </c>
       <c r="O75" s="2" t="s">
-        <v>117</v>
+        <v>171</v>
       </c>
       <c r="P75" s="2" t="s">
         <v>0</v>
@@ -5121,13 +5268,13 @@
         <v>72</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>116</v>
+        <v>170</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>115</v>
+        <v>169</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>114</v>
+        <v>168</v>
       </c>
       <c r="E76" s="2" t="s">
         <v>3</v>
@@ -5136,32 +5283,32 @@
         <v>1</v>
       </c>
       <c r="G76" s="2">
-        <v>8.0</v>
+        <v>4.0</v>
       </c>
       <c r="H76" s="2">
         <v>10.0</v>
       </c>
       <c r="I76" s="2" t="s">
-        <v>2</v>
+        <v>111</v>
       </c>
       <c r="J76" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K76" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L76" s="2"/>
       <c r="M76" s="2">
         <v>5</v>
       </c>
       <c r="N76" s="2">
-        <v>18.78</v>
+        <v>5.95</v>
       </c>
       <c r="O76" s="2" t="s">
-        <v>113</v>
+        <v>167</v>
       </c>
       <c r="P76" s="2" t="s">
-        <v>0</v>
+        <v>109</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -5169,13 +5316,13 @@
         <v>73</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>112</v>
+        <v>166</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>111</v>
+        <v>165</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>110</v>
+        <v>164</v>
       </c>
       <c r="E77" s="2" t="s">
         <v>3</v>
@@ -5184,29 +5331,27 @@
         <v>1</v>
       </c>
       <c r="G77" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H77" s="2">
         <v>10.0</v>
       </c>
       <c r="I77" s="2" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="J77" s="2">
-        <v>4</v>
-      </c>
-      <c r="K77" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K77" s="2"/>
       <c r="L77" s="2"/>
       <c r="M77" s="2">
         <v>5</v>
       </c>
       <c r="N77" s="2">
-        <v>12.03</v>
+        <v>9.08</v>
       </c>
       <c r="O77" s="2" t="s">
-        <v>109</v>
+        <v>163</v>
       </c>
       <c r="P77" s="2" t="s">
         <v>0</v>
@@ -5217,13 +5362,13 @@
         <v>74</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>108</v>
+        <v>162</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>107</v>
+        <v>161</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>106</v>
+        <v>160</v>
       </c>
       <c r="E78" s="2" t="s">
         <v>3</v>
@@ -5232,29 +5377,29 @@
         <v>1</v>
       </c>
       <c r="G78" s="2">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="H78" s="2">
         <v>10.0</v>
       </c>
       <c r="I78" s="2" t="s">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="J78" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K78" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L78" s="2"/>
       <c r="M78" s="2">
         <v>5</v>
       </c>
       <c r="N78" s="2">
-        <v>25.12</v>
+        <v>13.42</v>
       </c>
       <c r="O78" s="2" t="s">
-        <v>105</v>
+        <v>159</v>
       </c>
       <c r="P78" s="2" t="s">
         <v>0</v>
@@ -5265,13 +5410,13 @@
         <v>75</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>104</v>
+        <v>158</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>103</v>
+        <v>157</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>102</v>
+        <v>156</v>
       </c>
       <c r="E79" s="2" t="s">
         <v>3</v>
@@ -5299,10 +5444,10 @@
         <v>5</v>
       </c>
       <c r="N79" s="2">
-        <v>16.98</v>
+        <v>2.57</v>
       </c>
       <c r="O79" s="2" t="s">
-        <v>101</v>
+        <v>155</v>
       </c>
       <c r="P79" s="2" t="s">
         <v>0</v>
@@ -5313,13 +5458,13 @@
         <v>76</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>100</v>
+        <v>154</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>99</v>
+        <v>153</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>98</v>
+        <v>152</v>
       </c>
       <c r="E80" s="2" t="s">
         <v>3</v>
@@ -5345,10 +5490,10 @@
         <v>5</v>
       </c>
       <c r="N80" s="2">
-        <v>1.45</v>
+        <v>1.65</v>
       </c>
       <c r="O80" s="2" t="s">
-        <v>97</v>
+        <v>151</v>
       </c>
       <c r="P80" s="2" t="s">
         <v>0</v>
@@ -5359,42 +5504,44 @@
         <v>77</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>96</v>
+        <v>150</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>95</v>
+        <v>149</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>94</v>
+        <v>148</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F81" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G81" s="2">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
       <c r="H81" s="2">
         <v>10.0</v>
       </c>
       <c r="I81" s="2" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="J81" s="2">
-        <v>5</v>
-      </c>
-      <c r="K81" s="2"/>
+        <v>3</v>
+      </c>
+      <c r="K81" s="2">
+        <v>2</v>
+      </c>
       <c r="L81" s="2"/>
       <c r="M81" s="2">
         <v>5</v>
       </c>
       <c r="N81" s="2">
-        <v>6.18</v>
+        <v>12.1</v>
       </c>
       <c r="O81" s="2" t="s">
-        <v>93</v>
+        <v>147</v>
       </c>
       <c r="P81" s="2" t="s">
         <v>0</v>
@@ -5405,13 +5552,13 @@
         <v>78</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>92</v>
+        <v>146</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>91</v>
+        <v>145</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>90</v>
+        <v>144</v>
       </c>
       <c r="E82" s="2" t="s">
         <v>3</v>
@@ -5420,27 +5567,29 @@
         <v>1</v>
       </c>
       <c r="G82" s="2">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
       <c r="H82" s="2">
         <v>10.0</v>
       </c>
       <c r="I82" s="2" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="J82" s="2">
-        <v>5</v>
-      </c>
-      <c r="K82" s="2"/>
+        <v>3</v>
+      </c>
+      <c r="K82" s="2">
+        <v>2</v>
+      </c>
       <c r="L82" s="2"/>
       <c r="M82" s="2">
         <v>5</v>
       </c>
       <c r="N82" s="2">
-        <v>6.13</v>
+        <v>18.58</v>
       </c>
       <c r="O82" s="2" t="s">
-        <v>89</v>
+        <v>143</v>
       </c>
       <c r="P82" s="2" t="s">
         <v>0</v>
@@ -5451,13 +5600,13 @@
         <v>79</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>88</v>
+        <v>142</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>87</v>
+        <v>141</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>86</v>
+        <v>140</v>
       </c>
       <c r="E83" s="2" t="s">
         <v>3</v>
@@ -5466,29 +5615,27 @@
         <v>1</v>
       </c>
       <c r="G83" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H83" s="2">
         <v>10.0</v>
       </c>
       <c r="I83" s="2" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="J83" s="2">
-        <v>4</v>
-      </c>
-      <c r="K83" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K83" s="2"/>
       <c r="L83" s="2"/>
       <c r="M83" s="2">
         <v>5</v>
       </c>
       <c r="N83" s="2">
-        <v>2.4</v>
+        <v>18.03</v>
       </c>
       <c r="O83" s="2" t="s">
-        <v>85</v>
+        <v>139</v>
       </c>
       <c r="P83" s="2" t="s">
         <v>0</v>
@@ -5499,13 +5646,13 @@
         <v>80</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>84</v>
+        <v>138</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>83</v>
+        <v>137</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>82</v>
+        <v>136</v>
       </c>
       <c r="E84" s="2" t="s">
         <v>3</v>
@@ -5533,10 +5680,10 @@
         <v>5</v>
       </c>
       <c r="N84" s="2">
-        <v>15.75</v>
+        <v>9.68</v>
       </c>
       <c r="O84" s="2" t="s">
-        <v>81</v>
+        <v>135</v>
       </c>
       <c r="P84" s="2" t="s">
         <v>0</v>
@@ -5547,13 +5694,13 @@
         <v>81</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>80</v>
+        <v>134</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>79</v>
+        <v>133</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>78</v>
+        <v>132</v>
       </c>
       <c r="E85" s="2" t="s">
         <v>3</v>
@@ -5562,27 +5709,29 @@
         <v>1</v>
       </c>
       <c r="G85" s="2">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
       <c r="H85" s="2">
         <v>10.0</v>
       </c>
       <c r="I85" s="2" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="J85" s="2">
-        <v>5</v>
-      </c>
-      <c r="K85" s="2"/>
+        <v>3</v>
+      </c>
+      <c r="K85" s="2">
+        <v>2</v>
+      </c>
       <c r="L85" s="2"/>
       <c r="M85" s="2">
         <v>5</v>
       </c>
       <c r="N85" s="2">
-        <v>2.17</v>
+        <v>14.13</v>
       </c>
       <c r="O85" s="2" t="s">
-        <v>77</v>
+        <v>131</v>
       </c>
       <c r="P85" s="2" t="s">
         <v>0</v>
@@ -5593,13 +5742,13 @@
         <v>82</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>76</v>
+        <v>130</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>75</v>
+        <v>129</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>74</v>
+        <v>128</v>
       </c>
       <c r="E86" s="2" t="s">
         <v>3</v>
@@ -5608,29 +5757,29 @@
         <v>1</v>
       </c>
       <c r="G86" s="2">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="H86" s="2">
         <v>10.0</v>
       </c>
       <c r="I86" s="2" t="s">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="J86" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K86" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L86" s="2"/>
       <c r="M86" s="2">
         <v>5</v>
       </c>
       <c r="N86" s="2">
-        <v>9.5</v>
+        <v>11.45</v>
       </c>
       <c r="O86" s="2" t="s">
-        <v>73</v>
+        <v>127</v>
       </c>
       <c r="P86" s="2" t="s">
         <v>0</v>
@@ -5641,13 +5790,13 @@
         <v>83</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>72</v>
+        <v>126</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>71</v>
+        <v>125</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>70</v>
+        <v>124</v>
       </c>
       <c r="E87" s="2" t="s">
         <v>3</v>
@@ -5656,27 +5805,29 @@
         <v>1</v>
       </c>
       <c r="G87" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H87" s="2">
         <v>10.0</v>
       </c>
       <c r="I87" s="2" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="J87" s="2">
-        <v>5</v>
-      </c>
-      <c r="K87" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K87" s="2">
+        <v>1</v>
+      </c>
       <c r="L87" s="2"/>
       <c r="M87" s="2">
         <v>5</v>
       </c>
       <c r="N87" s="2">
-        <v>10.75</v>
+        <v>12.55</v>
       </c>
       <c r="O87" s="2" t="s">
-        <v>69</v>
+        <v>123</v>
       </c>
       <c r="P87" s="2" t="s">
         <v>0</v>
@@ -5687,44 +5838,42 @@
         <v>84</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>68</v>
+        <v>122</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>67</v>
+        <v>121</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>66</v>
+        <v>120</v>
       </c>
       <c r="E88" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F88" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G88" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H88" s="2">
         <v>10.0</v>
       </c>
       <c r="I88" s="2" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="J88" s="2">
-        <v>4</v>
-      </c>
-      <c r="K88" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K88" s="2"/>
       <c r="L88" s="2"/>
       <c r="M88" s="2">
         <v>5</v>
       </c>
       <c r="N88" s="2">
-        <v>23.17</v>
+        <v>6.58</v>
       </c>
       <c r="O88" s="2" t="s">
-        <v>65</v>
+        <v>119</v>
       </c>
       <c r="P88" s="2" t="s">
         <v>0</v>
@@ -5735,42 +5884,44 @@
         <v>85</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>64</v>
+        <v>118</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>63</v>
+        <v>117</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>62</v>
+        <v>116</v>
       </c>
       <c r="E89" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F89" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G89" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H89" s="2">
         <v>10.0</v>
       </c>
       <c r="I89" s="2" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="J89" s="2">
-        <v>5</v>
-      </c>
-      <c r="K89" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K89" s="2">
+        <v>1</v>
+      </c>
       <c r="L89" s="2"/>
       <c r="M89" s="2">
         <v>5</v>
       </c>
       <c r="N89" s="2">
-        <v>5.47</v>
+        <v>18.78</v>
       </c>
       <c r="O89" s="2" t="s">
-        <v>61</v>
+        <v>115</v>
       </c>
       <c r="P89" s="2" t="s">
         <v>0</v>
@@ -5781,47 +5932,47 @@
         <v>86</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>60</v>
+        <v>114</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>59</v>
+        <v>113</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>58</v>
+        <v>112</v>
       </c>
       <c r="E90" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F90" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G90" s="2">
-        <v>8.0</v>
+        <v>4.0</v>
       </c>
       <c r="H90" s="2">
         <v>10.0</v>
       </c>
       <c r="I90" s="2" t="s">
-        <v>2</v>
+        <v>111</v>
       </c>
       <c r="J90" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K90" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L90" s="2"/>
       <c r="M90" s="2">
         <v>5</v>
       </c>
       <c r="N90" s="2">
-        <v>15.8</v>
+        <v>10181.77</v>
       </c>
       <c r="O90" s="2" t="s">
-        <v>57</v>
+        <v>110</v>
       </c>
       <c r="P90" s="2" t="s">
-        <v>0</v>
+        <v>109</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -5829,13 +5980,13 @@
         <v>87</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>56</v>
+        <v>108</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>55</v>
+        <v>107</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>54</v>
+        <v>106</v>
       </c>
       <c r="E91" s="2" t="s">
         <v>3</v>
@@ -5844,27 +5995,29 @@
         <v>1</v>
       </c>
       <c r="G91" s="2">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
       <c r="H91" s="2">
         <v>10.0</v>
       </c>
       <c r="I91" s="2" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="J91" s="2">
-        <v>5</v>
-      </c>
-      <c r="K91" s="2"/>
+        <v>3</v>
+      </c>
+      <c r="K91" s="2">
+        <v>2</v>
+      </c>
       <c r="L91" s="2"/>
       <c r="M91" s="2">
         <v>5</v>
       </c>
       <c r="N91" s="2">
-        <v>4.07</v>
+        <v>25.12</v>
       </c>
       <c r="O91" s="2" t="s">
-        <v>53</v>
+        <v>105</v>
       </c>
       <c r="P91" s="2" t="s">
         <v>0</v>
@@ -5875,13 +6028,13 @@
         <v>88</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>52</v>
+        <v>104</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>51</v>
+        <v>103</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>50</v>
+        <v>102</v>
       </c>
       <c r="E92" s="2" t="s">
         <v>3</v>
@@ -5890,29 +6043,29 @@
         <v>1</v>
       </c>
       <c r="G92" s="2">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
       <c r="H92" s="2">
         <v>10.0</v>
       </c>
       <c r="I92" s="2" t="s">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="J92" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K92" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L92" s="2"/>
       <c r="M92" s="2">
         <v>5</v>
       </c>
       <c r="N92" s="2">
-        <v>21.8</v>
+        <v>16.98</v>
       </c>
       <c r="O92" s="2" t="s">
-        <v>49</v>
+        <v>101</v>
       </c>
       <c r="P92" s="2" t="s">
         <v>0</v>
@@ -5923,13 +6076,13 @@
         <v>89</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>48</v>
+        <v>100</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>47</v>
+        <v>99</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>46</v>
+        <v>98</v>
       </c>
       <c r="E93" s="2" t="s">
         <v>3</v>
@@ -5938,29 +6091,27 @@
         <v>1</v>
       </c>
       <c r="G93" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H93" s="2">
         <v>10.0</v>
       </c>
       <c r="I93" s="2" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="J93" s="2">
-        <v>4</v>
-      </c>
-      <c r="K93" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K93" s="2"/>
       <c r="L93" s="2"/>
       <c r="M93" s="2">
         <v>5</v>
       </c>
       <c r="N93" s="2">
-        <v>10.12</v>
+        <v>1.45</v>
       </c>
       <c r="O93" s="2" t="s">
-        <v>45</v>
+        <v>97</v>
       </c>
       <c r="P93" s="2" t="s">
         <v>0</v>
@@ -5971,19 +6122,19 @@
         <v>90</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>44</v>
+        <v>96</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>43</v>
+        <v>95</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>42</v>
+        <v>94</v>
       </c>
       <c r="E94" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F94" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G94" s="2">
         <v>10.0</v>
@@ -6003,10 +6154,10 @@
         <v>5</v>
       </c>
       <c r="N94" s="2">
-        <v>13.48</v>
+        <v>6.18</v>
       </c>
       <c r="O94" s="2" t="s">
-        <v>41</v>
+        <v>93</v>
       </c>
       <c r="P94" s="2" t="s">
         <v>0</v>
@@ -6017,13 +6168,13 @@
         <v>91</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>40</v>
+        <v>92</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>39</v>
+        <v>91</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>38</v>
+        <v>90</v>
       </c>
       <c r="E95" s="2" t="s">
         <v>3</v>
@@ -6032,29 +6183,27 @@
         <v>1</v>
       </c>
       <c r="G95" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H95" s="2">
         <v>10.0</v>
       </c>
       <c r="I95" s="2" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="J95" s="2">
-        <v>4</v>
-      </c>
-      <c r="K95" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K95" s="2"/>
       <c r="L95" s="2"/>
       <c r="M95" s="2">
         <v>5</v>
       </c>
       <c r="N95" s="2">
-        <v>10.6</v>
+        <v>6.13</v>
       </c>
       <c r="O95" s="2" t="s">
-        <v>37</v>
+        <v>89</v>
       </c>
       <c r="P95" s="2" t="s">
         <v>0</v>
@@ -6065,13 +6214,13 @@
         <v>92</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>36</v>
+        <v>88</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>35</v>
+        <v>87</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>34</v>
+        <v>86</v>
       </c>
       <c r="E96" s="2" t="s">
         <v>3</v>
@@ -6080,27 +6229,29 @@
         <v>1</v>
       </c>
       <c r="G96" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H96" s="2">
         <v>10.0</v>
       </c>
       <c r="I96" s="2" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="J96" s="2">
-        <v>5</v>
-      </c>
-      <c r="K96" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K96" s="2">
+        <v>1</v>
+      </c>
       <c r="L96" s="2"/>
       <c r="M96" s="2">
         <v>5</v>
       </c>
       <c r="N96" s="2">
-        <v>12.52</v>
+        <v>2.4</v>
       </c>
       <c r="O96" s="2" t="s">
-        <v>33</v>
+        <v>85</v>
       </c>
       <c r="P96" s="2" t="s">
         <v>0</v>
@@ -6111,13 +6262,13 @@
         <v>93</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>32</v>
+        <v>84</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>31</v>
+        <v>83</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>30</v>
+        <v>82</v>
       </c>
       <c r="E97" s="2" t="s">
         <v>3</v>
@@ -6126,27 +6277,29 @@
         <v>1</v>
       </c>
       <c r="G97" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H97" s="2">
         <v>10.0</v>
       </c>
       <c r="I97" s="2" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="J97" s="2">
-        <v>5</v>
-      </c>
-      <c r="K97" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K97" s="2">
+        <v>1</v>
+      </c>
       <c r="L97" s="2"/>
       <c r="M97" s="2">
         <v>5</v>
       </c>
       <c r="N97" s="2">
-        <v>15.33</v>
+        <v>15.75</v>
       </c>
       <c r="O97" s="2" t="s">
-        <v>28</v>
+        <v>81</v>
       </c>
       <c r="P97" s="2" t="s">
         <v>0</v>
@@ -6157,13 +6310,13 @@
         <v>94</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>27</v>
+        <v>80</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>26</v>
+        <v>79</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>25</v>
+        <v>78</v>
       </c>
       <c r="E98" s="2" t="s">
         <v>3</v>
@@ -6172,29 +6325,27 @@
         <v>1</v>
       </c>
       <c r="G98" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H98" s="2">
         <v>10.0</v>
       </c>
       <c r="I98" s="2" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="J98" s="2">
-        <v>4</v>
-      </c>
-      <c r="K98" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K98" s="2"/>
       <c r="L98" s="2"/>
       <c r="M98" s="2">
         <v>5</v>
       </c>
       <c r="N98" s="2">
-        <v>9.45</v>
+        <v>2.17</v>
       </c>
       <c r="O98" s="2" t="s">
-        <v>24</v>
+        <v>77</v>
       </c>
       <c r="P98" s="2" t="s">
         <v>0</v>
@@ -6205,13 +6356,13 @@
         <v>95</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>23</v>
+        <v>76</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>22</v>
+        <v>75</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>21</v>
+        <v>74</v>
       </c>
       <c r="E99" s="2" t="s">
         <v>3</v>
@@ -6239,10 +6390,10 @@
         <v>5</v>
       </c>
       <c r="N99" s="2">
-        <v>3.6</v>
+        <v>9.5</v>
       </c>
       <c r="O99" s="2" t="s">
-        <v>20</v>
+        <v>73</v>
       </c>
       <c r="P99" s="2" t="s">
         <v>0</v>
@@ -6253,13 +6404,13 @@
         <v>96</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>19</v>
+        <v>72</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>18</v>
+        <v>71</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>17</v>
+        <v>70</v>
       </c>
       <c r="E100" s="2" t="s">
         <v>3</v>
@@ -6268,29 +6419,27 @@
         <v>1</v>
       </c>
       <c r="G100" s="2">
-        <v>6.0</v>
+        <v>10.0</v>
       </c>
       <c r="H100" s="2">
         <v>10.0</v>
       </c>
       <c r="I100" s="2" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="J100" s="2">
-        <v>3</v>
-      </c>
-      <c r="K100" s="2">
-        <v>2</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K100" s="2"/>
       <c r="L100" s="2"/>
       <c r="M100" s="2">
         <v>5</v>
       </c>
       <c r="N100" s="2">
-        <v>10.15</v>
+        <v>10.75</v>
       </c>
       <c r="O100" s="2" t="s">
-        <v>15</v>
+        <v>69</v>
       </c>
       <c r="P100" s="2" t="s">
         <v>0</v>
@@ -6301,19 +6450,19 @@
         <v>97</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>14</v>
+        <v>68</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>13</v>
+        <v>67</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>12</v>
+        <v>66</v>
       </c>
       <c r="E101" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F101" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G101" s="2">
         <v>8.0</v>
@@ -6335,10 +6484,10 @@
         <v>5</v>
       </c>
       <c r="N101" s="2">
-        <v>6.12</v>
+        <v>23.17</v>
       </c>
       <c r="O101" s="2" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="P101" s="2" t="s">
         <v>0</v>
@@ -6349,13 +6498,13 @@
         <v>98</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>10</v>
+        <v>64</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>9</v>
+        <v>63</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="E102" s="2" t="s">
         <v>3</v>
@@ -6364,29 +6513,27 @@
         <v>2</v>
       </c>
       <c r="G102" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H102" s="2">
         <v>10.0</v>
       </c>
       <c r="I102" s="2" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="J102" s="2">
-        <v>4</v>
-      </c>
-      <c r="K102" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K102" s="2"/>
       <c r="L102" s="2"/>
       <c r="M102" s="2">
         <v>5</v>
       </c>
       <c r="N102" s="2">
-        <v>8.33</v>
+        <v>5.47</v>
       </c>
       <c r="O102" s="2" t="s">
-        <v>7</v>
+        <v>61</v>
       </c>
       <c r="P102" s="2" t="s">
         <v>0</v>
@@ -6397,13 +6544,13 @@
         <v>99</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>6</v>
+        <v>60</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>5</v>
+        <v>59</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>4</v>
+        <v>58</v>
       </c>
       <c r="E103" s="2" t="s">
         <v>3</v>
@@ -6431,12 +6578,628 @@
         <v>5</v>
       </c>
       <c r="N103" s="2">
+        <v>15.8</v>
+      </c>
+      <c r="O103" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="P103" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:16">
+      <c r="A104" s="2">
+        <v>100</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D104" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E104" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F104" s="2">
+        <v>1</v>
+      </c>
+      <c r="G104" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="H104" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I104" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="J104" s="2">
+        <v>5</v>
+      </c>
+      <c r="K104" s="2"/>
+      <c r="L104" s="2"/>
+      <c r="M104" s="2">
+        <v>5</v>
+      </c>
+      <c r="N104" s="2">
+        <v>4.07</v>
+      </c>
+      <c r="O104" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="P104" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:16">
+      <c r="A105" s="2">
+        <v>101</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D105" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E105" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F105" s="2">
+        <v>1</v>
+      </c>
+      <c r="G105" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="H105" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I105" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J105" s="2">
+        <v>4</v>
+      </c>
+      <c r="K105" s="2">
+        <v>1</v>
+      </c>
+      <c r="L105" s="2"/>
+      <c r="M105" s="2">
+        <v>5</v>
+      </c>
+      <c r="N105" s="2">
+        <v>21.8</v>
+      </c>
+      <c r="O105" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="P105" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:16">
+      <c r="A106" s="2">
+        <v>102</v>
+      </c>
+      <c r="B106" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C106" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D106" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E106" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F106" s="2">
+        <v>1</v>
+      </c>
+      <c r="G106" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="H106" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I106" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J106" s="2">
+        <v>4</v>
+      </c>
+      <c r="K106" s="2">
+        <v>1</v>
+      </c>
+      <c r="L106" s="2"/>
+      <c r="M106" s="2">
+        <v>5</v>
+      </c>
+      <c r="N106" s="2">
+        <v>10.12</v>
+      </c>
+      <c r="O106" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="P106" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:16">
+      <c r="A107" s="2">
+        <v>103</v>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C107" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D107" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E107" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F107" s="2">
+        <v>1</v>
+      </c>
+      <c r="G107" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="H107" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I107" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="J107" s="2">
+        <v>5</v>
+      </c>
+      <c r="K107" s="2"/>
+      <c r="L107" s="2"/>
+      <c r="M107" s="2">
+        <v>5</v>
+      </c>
+      <c r="N107" s="2">
+        <v>13.48</v>
+      </c>
+      <c r="O107" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="P107" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:16">
+      <c r="A108" s="2">
+        <v>104</v>
+      </c>
+      <c r="B108" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C108" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D108" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E108" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F108" s="2">
+        <v>1</v>
+      </c>
+      <c r="G108" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="H108" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I108" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J108" s="2">
+        <v>4</v>
+      </c>
+      <c r="K108" s="2">
+        <v>1</v>
+      </c>
+      <c r="L108" s="2"/>
+      <c r="M108" s="2">
+        <v>5</v>
+      </c>
+      <c r="N108" s="2">
+        <v>10.6</v>
+      </c>
+      <c r="O108" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="P108" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:16">
+      <c r="A109" s="2">
+        <v>105</v>
+      </c>
+      <c r="B109" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C109" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D109" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E109" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F109" s="2">
+        <v>1</v>
+      </c>
+      <c r="G109" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="H109" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I109" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="J109" s="2">
+        <v>5</v>
+      </c>
+      <c r="K109" s="2"/>
+      <c r="L109" s="2"/>
+      <c r="M109" s="2">
+        <v>5</v>
+      </c>
+      <c r="N109" s="2">
+        <v>12.52</v>
+      </c>
+      <c r="O109" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P109" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:16">
+      <c r="A110" s="2">
+        <v>106</v>
+      </c>
+      <c r="B110" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C110" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D110" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E110" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F110" s="2">
+        <v>1</v>
+      </c>
+      <c r="G110" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="H110" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I110" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="J110" s="2">
+        <v>5</v>
+      </c>
+      <c r="K110" s="2"/>
+      <c r="L110" s="2"/>
+      <c r="M110" s="2">
+        <v>5</v>
+      </c>
+      <c r="N110" s="2">
+        <v>15.33</v>
+      </c>
+      <c r="O110" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P110" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:16">
+      <c r="A111" s="2">
+        <v>107</v>
+      </c>
+      <c r="B111" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C111" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D111" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E111" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F111" s="2">
+        <v>1</v>
+      </c>
+      <c r="G111" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="H111" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I111" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J111" s="2">
+        <v>4</v>
+      </c>
+      <c r="K111" s="2">
+        <v>1</v>
+      </c>
+      <c r="L111" s="2"/>
+      <c r="M111" s="2">
+        <v>5</v>
+      </c>
+      <c r="N111" s="2">
+        <v>9.45</v>
+      </c>
+      <c r="O111" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="P111" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:16">
+      <c r="A112" s="2">
+        <v>108</v>
+      </c>
+      <c r="B112" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C112" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D112" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E112" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F112" s="2">
+        <v>1</v>
+      </c>
+      <c r="G112" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="H112" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I112" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J112" s="2">
+        <v>3</v>
+      </c>
+      <c r="K112" s="2">
+        <v>2</v>
+      </c>
+      <c r="L112" s="2"/>
+      <c r="M112" s="2">
+        <v>5</v>
+      </c>
+      <c r="N112" s="2">
+        <v>3.6</v>
+      </c>
+      <c r="O112" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="P112" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:16">
+      <c r="A113" s="2">
+        <v>109</v>
+      </c>
+      <c r="B113" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C113" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D113" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E113" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F113" s="2">
+        <v>1</v>
+      </c>
+      <c r="G113" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="H113" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I113" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J113" s="2">
+        <v>3</v>
+      </c>
+      <c r="K113" s="2">
+        <v>2</v>
+      </c>
+      <c r="L113" s="2"/>
+      <c r="M113" s="2">
+        <v>5</v>
+      </c>
+      <c r="N113" s="2">
+        <v>10.15</v>
+      </c>
+      <c r="O113" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="P113" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:16">
+      <c r="A114" s="2">
+        <v>110</v>
+      </c>
+      <c r="B114" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C114" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D114" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E114" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F114" s="2">
+        <v>1</v>
+      </c>
+      <c r="G114" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="H114" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I114" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J114" s="2">
+        <v>4</v>
+      </c>
+      <c r="K114" s="2">
+        <v>1</v>
+      </c>
+      <c r="L114" s="2"/>
+      <c r="M114" s="2">
+        <v>5</v>
+      </c>
+      <c r="N114" s="2">
+        <v>6.12</v>
+      </c>
+      <c r="O114" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="P114" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="1:16">
+      <c r="A115" s="2">
+        <v>111</v>
+      </c>
+      <c r="B115" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C115" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D115" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E115" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F115" s="2">
+        <v>2</v>
+      </c>
+      <c r="G115" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="H115" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I115" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J115" s="2">
+        <v>4</v>
+      </c>
+      <c r="K115" s="2">
+        <v>1</v>
+      </c>
+      <c r="L115" s="2"/>
+      <c r="M115" s="2">
+        <v>5</v>
+      </c>
+      <c r="N115" s="2">
+        <v>8.33</v>
+      </c>
+      <c r="O115" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="P115" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="1:16">
+      <c r="A116" s="2">
+        <v>112</v>
+      </c>
+      <c r="B116" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C116" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D116" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E116" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F116" s="2">
+        <v>1</v>
+      </c>
+      <c r="G116" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="H116" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I116" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J116" s="2">
+        <v>4</v>
+      </c>
+      <c r="K116" s="2">
+        <v>1</v>
+      </c>
+      <c r="L116" s="2"/>
+      <c r="M116" s="2">
+        <v>5</v>
+      </c>
+      <c r="N116" s="2">
         <v>7.77</v>
       </c>
-      <c r="O103" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="P103" s="2" t="s">
+      <c r="O116" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="P116" s="2" t="s">
         <v>0</v>
       </c>
     </row>

--- a/2lit_center.xlsx
+++ b/2lit_center.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="469">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="481">
   <si>
     <t>ناجح ✓</t>
   </si>
@@ -1367,6 +1367,42 @@
     <t>حسين احمد منير</t>
   </si>
   <si>
+    <t>2026-03-09 18:38</t>
+  </si>
+  <si>
+    <t>01121973130</t>
+  </si>
+  <si>
+    <t>seifzarad50@gmail.com</t>
+  </si>
+  <si>
+    <t>سيف ابراهيم ابوالعنين</t>
+  </si>
+  <si>
+    <t>2026-03-09 19:01</t>
+  </si>
+  <si>
+    <t>01030133382</t>
+  </si>
+  <si>
+    <t>hamza2210mg@gmail.com</t>
+  </si>
+  <si>
+    <t>Hamza</t>
+  </si>
+  <si>
+    <t>2026-03-09 19:05</t>
+  </si>
+  <si>
+    <t>01121431168</t>
+  </si>
+  <si>
+    <t>ahmeddaoomy2@gmail.com</t>
+  </si>
+  <si>
+    <t>Ahmed shawky</t>
+  </si>
+  <si>
     <t>الحالة</t>
   </si>
   <si>
@@ -1421,7 +1457,7 @@
     <t>الدرجة الكاملة: 10 | درجة النجاح: 5.00</t>
   </si>
   <si>
-    <t>تاريخ التصدير: 2026-03-08 19:44</t>
+    <t>تاريخ التصدير: 2026-03-09 19:29</t>
   </si>
 </sst>
 </file>
@@ -1809,7 +1845,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:P116"/>
+  <dimension ref="A1:P119"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="true" style="0"/>
@@ -1832,67 +1868,67 @@
   <sheetData>
     <row r="1" spans="1:16">
       <c r="A1" s="3" t="s">
-        <v>466</v>
+        <v>478</v>
       </c>
     </row>
     <row r="2" spans="1:16">
       <c r="A2" s="3" t="s">
-        <v>467</v>
+        <v>479</v>
       </c>
     </row>
     <row r="3" spans="1:16">
       <c r="A3" s="3" t="s">
-        <v>468</v>
+        <v>480</v>
       </c>
     </row>
     <row r="4" spans="1:16">
       <c r="A4" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="M4" s="1" t="s">
         <v>465</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="N4" s="1" t="s">
         <v>464</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="O4" s="1" t="s">
         <v>463</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="P4" s="1" t="s">
         <v>462</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>461</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>460</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>459</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>458</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>457</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>456</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>455</v>
-      </c>
-      <c r="L4" s="1" t="s">
-        <v>454</v>
-      </c>
-      <c r="M4" s="1" t="s">
-        <v>453</v>
-      </c>
-      <c r="N4" s="1" t="s">
-        <v>452</v>
-      </c>
-      <c r="O4" s="1" t="s">
-        <v>451</v>
-      </c>
-      <c r="P4" s="1" t="s">
-        <v>450</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1900,13 +1936,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>449</v>
+        <v>461</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>448</v>
+        <v>460</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>447</v>
+        <v>459</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>3</v>
@@ -1932,10 +1968,10 @@
         <v>5</v>
       </c>
       <c r="N5" s="2">
-        <v>2.63</v>
+        <v>9.03</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>443</v>
+        <v>458</v>
       </c>
       <c r="P5" s="2" t="s">
         <v>0</v>
@@ -1946,13 +1982,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>446</v>
+        <v>457</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>445</v>
+        <v>456</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>444</v>
+        <v>455</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>3</v>
@@ -1961,29 +1997,27 @@
         <v>1</v>
       </c>
       <c r="G6" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H6" s="2">
         <v>10.0</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="J6" s="2">
-        <v>4</v>
-      </c>
-      <c r="K6" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K6" s="2"/>
       <c r="L6" s="2"/>
       <c r="M6" s="2">
         <v>5</v>
       </c>
       <c r="N6" s="2">
-        <v>4.5</v>
+        <v>7.95</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>443</v>
+        <v>454</v>
       </c>
       <c r="P6" s="2" t="s">
         <v>0</v>
@@ -1994,13 +2028,13 @@
         <v>3</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>442</v>
+        <v>453</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>441</v>
+        <v>452</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>440</v>
+        <v>451</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>3</v>
@@ -2009,29 +2043,27 @@
         <v>1</v>
       </c>
       <c r="G7" s="2">
-        <v>6.0</v>
+        <v>10.0</v>
       </c>
       <c r="H7" s="2">
         <v>10.0</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="J7" s="2">
-        <v>3</v>
-      </c>
-      <c r="K7" s="2">
-        <v>2</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K7" s="2"/>
       <c r="L7" s="2"/>
       <c r="M7" s="2">
         <v>5</v>
       </c>
       <c r="N7" s="2">
-        <v>9.08</v>
+        <v>4.62</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>439</v>
+        <v>450</v>
       </c>
       <c r="P7" s="2" t="s">
         <v>0</v>
@@ -2042,44 +2074,42 @@
         <v>4</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>438</v>
+        <v>449</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>437</v>
+        <v>448</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>436</v>
+        <v>447</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F8" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G8" s="2">
-        <v>6.0</v>
+        <v>10.0</v>
       </c>
       <c r="H8" s="2">
         <v>10.0</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="J8" s="2">
-        <v>3</v>
-      </c>
-      <c r="K8" s="2">
-        <v>2</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K8" s="2"/>
       <c r="L8" s="2"/>
       <c r="M8" s="2">
         <v>5</v>
       </c>
       <c r="N8" s="2">
-        <v>5.43</v>
+        <v>2.63</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>435</v>
+        <v>443</v>
       </c>
       <c r="P8" s="2" t="s">
         <v>0</v>
@@ -2090,13 +2120,13 @@
         <v>5</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>434</v>
+        <v>446</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>433</v>
+        <v>445</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>432</v>
+        <v>444</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>3</v>
@@ -2105,27 +2135,29 @@
         <v>1</v>
       </c>
       <c r="G9" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H9" s="2">
         <v>10.0</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="J9" s="2">
-        <v>5</v>
-      </c>
-      <c r="K9" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K9" s="2">
+        <v>1</v>
+      </c>
       <c r="L9" s="2"/>
       <c r="M9" s="2">
         <v>5</v>
       </c>
       <c r="N9" s="2">
-        <v>20.33</v>
+        <v>4.5</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>431</v>
+        <v>443</v>
       </c>
       <c r="P9" s="2" t="s">
         <v>0</v>
@@ -2136,13 +2168,13 @@
         <v>6</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>430</v>
+        <v>442</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>429</v>
-      </c>
-      <c r="D10" s="2">
-        <v>1159792350</v>
+        <v>441</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>440</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>3</v>
@@ -2151,27 +2183,29 @@
         <v>1</v>
       </c>
       <c r="G10" s="2">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
       <c r="H10" s="2">
         <v>10.0</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="J10" s="2">
-        <v>5</v>
-      </c>
-      <c r="K10" s="2"/>
+        <v>3</v>
+      </c>
+      <c r="K10" s="2">
+        <v>2</v>
+      </c>
       <c r="L10" s="2"/>
       <c r="M10" s="2">
         <v>5</v>
       </c>
       <c r="N10" s="2">
-        <v>11.83</v>
+        <v>9.08</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>428</v>
+        <v>439</v>
       </c>
       <c r="P10" s="2" t="s">
         <v>0</v>
@@ -2182,44 +2216,44 @@
         <v>7</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>427</v>
+        <v>438</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>426</v>
+        <v>437</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>425</v>
+        <v>436</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F11" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G11" s="2">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
       <c r="H11" s="2">
         <v>10.0</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="J11" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K11" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L11" s="2"/>
       <c r="M11" s="2">
         <v>5</v>
       </c>
       <c r="N11" s="2">
-        <v>4.88</v>
+        <v>5.43</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>424</v>
+        <v>435</v>
       </c>
       <c r="P11" s="2" t="s">
         <v>0</v>
@@ -2230,13 +2264,13 @@
         <v>8</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>423</v>
+        <v>434</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>422</v>
+        <v>433</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>421</v>
+        <v>432</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>3</v>
@@ -2245,29 +2279,27 @@
         <v>1</v>
       </c>
       <c r="G12" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H12" s="2">
         <v>10.0</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="J12" s="2">
-        <v>4</v>
-      </c>
-      <c r="K12" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K12" s="2"/>
       <c r="L12" s="2"/>
       <c r="M12" s="2">
         <v>5</v>
       </c>
       <c r="N12" s="2">
-        <v>6.03</v>
+        <v>20.33</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>420</v>
+        <v>431</v>
       </c>
       <c r="P12" s="2" t="s">
         <v>0</v>
@@ -2278,13 +2310,13 @@
         <v>9</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>419</v>
+        <v>430</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>418</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>417</v>
+        <v>429</v>
+      </c>
+      <c r="D13" s="2">
+        <v>1159792350</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>3</v>
@@ -2293,29 +2325,27 @@
         <v>1</v>
       </c>
       <c r="G13" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H13" s="2">
         <v>10.0</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="J13" s="2">
-        <v>4</v>
-      </c>
-      <c r="K13" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K13" s="2"/>
       <c r="L13" s="2"/>
       <c r="M13" s="2">
         <v>5</v>
       </c>
       <c r="N13" s="2">
-        <v>4.48</v>
+        <v>11.83</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>416</v>
+        <v>428</v>
       </c>
       <c r="P13" s="2" t="s">
         <v>0</v>
@@ -2326,13 +2356,13 @@
         <v>10</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>415</v>
+        <v>427</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>414</v>
+        <v>426</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>413</v>
+        <v>425</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>3</v>
@@ -2341,29 +2371,29 @@
         <v>1</v>
       </c>
       <c r="G14" s="2">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="H14" s="2">
         <v>10.0</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="J14" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K14" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L14" s="2"/>
       <c r="M14" s="2">
         <v>5</v>
       </c>
       <c r="N14" s="2">
-        <v>49.1</v>
+        <v>4.88</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>412</v>
+        <v>424</v>
       </c>
       <c r="P14" s="2" t="s">
         <v>0</v>
@@ -2374,13 +2404,13 @@
         <v>11</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>411</v>
+        <v>423</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>410</v>
+        <v>422</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>409</v>
+        <v>421</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>3</v>
@@ -2389,27 +2419,29 @@
         <v>1</v>
       </c>
       <c r="G15" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H15" s="2">
         <v>10.0</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="J15" s="2">
-        <v>5</v>
-      </c>
-      <c r="K15" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K15" s="2">
+        <v>1</v>
+      </c>
       <c r="L15" s="2"/>
       <c r="M15" s="2">
         <v>5</v>
       </c>
       <c r="N15" s="2">
-        <v>17.32</v>
+        <v>6.03</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>408</v>
+        <v>420</v>
       </c>
       <c r="P15" s="2" t="s">
         <v>0</v>
@@ -2420,13 +2452,13 @@
         <v>12</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>407</v>
+        <v>419</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>406</v>
+        <v>418</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>405</v>
+        <v>417</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>3</v>
@@ -2454,10 +2486,10 @@
         <v>5</v>
       </c>
       <c r="N16" s="2">
-        <v>5.93</v>
+        <v>4.48</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>404</v>
+        <v>416</v>
       </c>
       <c r="P16" s="2" t="s">
         <v>0</v>
@@ -2468,19 +2500,19 @@
         <v>13</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>403</v>
+        <v>415</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>402</v>
+        <v>414</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>401</v>
+        <v>413</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F17" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G17" s="2">
         <v>6.0</v>
@@ -2502,10 +2534,10 @@
         <v>5</v>
       </c>
       <c r="N17" s="2">
-        <v>13.98</v>
+        <v>49.1</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="P17" s="2" t="s">
         <v>0</v>
@@ -2516,13 +2548,13 @@
         <v>14</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>399</v>
+        <v>411</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>398</v>
+        <v>410</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>397</v>
+        <v>409</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>3</v>
@@ -2548,10 +2580,10 @@
         <v>5</v>
       </c>
       <c r="N18" s="2">
-        <v>19.5</v>
+        <v>17.32</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>396</v>
+        <v>408</v>
       </c>
       <c r="P18" s="2" t="s">
         <v>0</v>
@@ -2562,13 +2594,13 @@
         <v>15</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>395</v>
+        <v>407</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>394</v>
+        <v>406</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>393</v>
+        <v>405</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>3</v>
@@ -2577,29 +2609,29 @@
         <v>1</v>
       </c>
       <c r="G19" s="2">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="H19" s="2">
         <v>10.0</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="J19" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K19" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L19" s="2"/>
       <c r="M19" s="2">
         <v>5</v>
       </c>
       <c r="N19" s="2">
-        <v>14.5</v>
+        <v>5.93</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>392</v>
+        <v>404</v>
       </c>
       <c r="P19" s="2" t="s">
         <v>0</v>
@@ -2610,13 +2642,13 @@
         <v>16</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>391</v>
+        <v>403</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>390</v>
+        <v>402</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>389</v>
+        <v>401</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>3</v>
@@ -2644,10 +2676,10 @@
         <v>5</v>
       </c>
       <c r="N20" s="2">
-        <v>0.8</v>
+        <v>13.98</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>388</v>
+        <v>400</v>
       </c>
       <c r="P20" s="2" t="s">
         <v>0</v>
@@ -2658,13 +2690,13 @@
         <v>17</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>387</v>
+        <v>399</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>386</v>
+        <v>398</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>385</v>
+        <v>397</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>3</v>
@@ -2673,29 +2705,27 @@
         <v>1</v>
       </c>
       <c r="G21" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H21" s="2">
         <v>10.0</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="J21" s="2">
-        <v>4</v>
-      </c>
-      <c r="K21" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K21" s="2"/>
       <c r="L21" s="2"/>
       <c r="M21" s="2">
         <v>5</v>
       </c>
       <c r="N21" s="2">
-        <v>6.42</v>
+        <v>19.5</v>
       </c>
       <c r="O21" s="2" t="s">
-        <v>384</v>
+        <v>396</v>
       </c>
       <c r="P21" s="2" t="s">
         <v>0</v>
@@ -2706,13 +2736,13 @@
         <v>18</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>383</v>
+        <v>395</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>382</v>
+        <v>394</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>381</v>
+        <v>393</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>3</v>
@@ -2740,10 +2770,10 @@
         <v>5</v>
       </c>
       <c r="N22" s="2">
-        <v>3.05</v>
+        <v>14.5</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>380</v>
+        <v>392</v>
       </c>
       <c r="P22" s="2" t="s">
         <v>0</v>
@@ -2754,44 +2784,44 @@
         <v>19</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>379</v>
+        <v>391</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>378</v>
+        <v>390</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>377</v>
+        <v>389</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F23" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G23" s="2">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
       <c r="H23" s="2">
         <v>10.0</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="J23" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K23" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L23" s="2"/>
       <c r="M23" s="2">
         <v>5</v>
       </c>
       <c r="N23" s="2">
-        <v>8.8</v>
+        <v>0.8</v>
       </c>
       <c r="O23" s="2" t="s">
-        <v>376</v>
+        <v>388</v>
       </c>
       <c r="P23" s="2" t="s">
         <v>0</v>
@@ -2802,13 +2832,13 @@
         <v>20</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>375</v>
+        <v>387</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>374</v>
+        <v>386</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>373</v>
+        <v>385</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>3</v>
@@ -2817,27 +2847,29 @@
         <v>1</v>
       </c>
       <c r="G24" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H24" s="2">
         <v>10.0</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="J24" s="2">
-        <v>5</v>
-      </c>
-      <c r="K24" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K24" s="2">
+        <v>1</v>
+      </c>
       <c r="L24" s="2"/>
       <c r="M24" s="2">
         <v>5</v>
       </c>
       <c r="N24" s="2">
-        <v>6.55</v>
+        <v>6.42</v>
       </c>
       <c r="O24" s="2" t="s">
-        <v>372</v>
+        <v>384</v>
       </c>
       <c r="P24" s="2" t="s">
         <v>0</v>
@@ -2848,13 +2880,13 @@
         <v>21</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>371</v>
+        <v>383</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>370</v>
+        <v>382</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>369</v>
+        <v>381</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>3</v>
@@ -2863,29 +2895,29 @@
         <v>1</v>
       </c>
       <c r="G25" s="2">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
       <c r="H25" s="2">
         <v>10.0</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="J25" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K25" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L25" s="2"/>
       <c r="M25" s="2">
         <v>5</v>
       </c>
       <c r="N25" s="2">
-        <v>16.72</v>
+        <v>3.05</v>
       </c>
       <c r="O25" s="2" t="s">
-        <v>368</v>
+        <v>380</v>
       </c>
       <c r="P25" s="2" t="s">
         <v>0</v>
@@ -2896,13 +2928,13 @@
         <v>22</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>367</v>
+        <v>379</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>366</v>
+        <v>378</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>365</v>
+        <v>377</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>3</v>
@@ -2911,29 +2943,29 @@
         <v>1</v>
       </c>
       <c r="G26" s="2">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="H26" s="2">
         <v>10.0</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="J26" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K26" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L26" s="2"/>
       <c r="M26" s="2">
         <v>5</v>
       </c>
       <c r="N26" s="2">
-        <v>12.5</v>
+        <v>8.8</v>
       </c>
       <c r="O26" s="2" t="s">
-        <v>364</v>
+        <v>376</v>
       </c>
       <c r="P26" s="2" t="s">
         <v>0</v>
@@ -2944,13 +2976,13 @@
         <v>23</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>363</v>
+        <v>375</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>362</v>
+        <v>374</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>361</v>
+        <v>373</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>3</v>
@@ -2959,29 +2991,27 @@
         <v>1</v>
       </c>
       <c r="G27" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H27" s="2">
         <v>10.0</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="J27" s="2">
-        <v>4</v>
-      </c>
-      <c r="K27" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K27" s="2"/>
       <c r="L27" s="2"/>
       <c r="M27" s="2">
         <v>5</v>
       </c>
       <c r="N27" s="2">
-        <v>11.57</v>
+        <v>6.55</v>
       </c>
       <c r="O27" s="2" t="s">
-        <v>360</v>
+        <v>372</v>
       </c>
       <c r="P27" s="2" t="s">
         <v>0</v>
@@ -2992,13 +3022,13 @@
         <v>24</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>359</v>
+        <v>371</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>358</v>
+        <v>370</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>357</v>
+        <v>369</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>3</v>
@@ -3026,10 +3056,10 @@
         <v>5</v>
       </c>
       <c r="N28" s="2">
-        <v>17.75</v>
+        <v>16.72</v>
       </c>
       <c r="O28" s="2" t="s">
-        <v>356</v>
+        <v>368</v>
       </c>
       <c r="P28" s="2" t="s">
         <v>0</v>
@@ -3040,13 +3070,13 @@
         <v>25</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>355</v>
+        <v>367</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>354</v>
+        <v>366</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>353</v>
+        <v>365</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>3</v>
@@ -3055,29 +3085,29 @@
         <v>1</v>
       </c>
       <c r="G29" s="2">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
       <c r="H29" s="2">
         <v>10.0</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="J29" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K29" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L29" s="2"/>
       <c r="M29" s="2">
         <v>5</v>
       </c>
       <c r="N29" s="2">
-        <v>3.12</v>
+        <v>12.5</v>
       </c>
       <c r="O29" s="2" t="s">
-        <v>352</v>
+        <v>364</v>
       </c>
       <c r="P29" s="2" t="s">
         <v>0</v>
@@ -3088,13 +3118,13 @@
         <v>26</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>351</v>
+        <v>363</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>350</v>
+        <v>362</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>349</v>
+        <v>361</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>3</v>
@@ -3122,10 +3152,10 @@
         <v>5</v>
       </c>
       <c r="N30" s="2">
-        <v>9.75</v>
+        <v>11.57</v>
       </c>
       <c r="O30" s="2" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="P30" s="2" t="s">
         <v>0</v>
@@ -3136,13 +3166,13 @@
         <v>27</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>347</v>
+        <v>359</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>346</v>
+        <v>358</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>345</v>
+        <v>357</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>3</v>
@@ -3170,10 +3200,10 @@
         <v>5</v>
       </c>
       <c r="N31" s="2">
-        <v>9.92</v>
+        <v>17.75</v>
       </c>
       <c r="O31" s="2" t="s">
-        <v>344</v>
+        <v>356</v>
       </c>
       <c r="P31" s="2" t="s">
         <v>0</v>
@@ -3184,13 +3214,13 @@
         <v>28</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>343</v>
+        <v>355</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>342</v>
+        <v>354</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>341</v>
+        <v>353</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>3</v>
@@ -3218,10 +3248,10 @@
         <v>5</v>
       </c>
       <c r="N32" s="2">
-        <v>15.08</v>
+        <v>3.12</v>
       </c>
       <c r="O32" s="2" t="s">
-        <v>340</v>
+        <v>352</v>
       </c>
       <c r="P32" s="2" t="s">
         <v>0</v>
@@ -3232,13 +3262,13 @@
         <v>29</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>339</v>
+        <v>351</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>338</v>
+        <v>350</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>337</v>
+        <v>349</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>3</v>
@@ -3247,27 +3277,29 @@
         <v>1</v>
       </c>
       <c r="G33" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H33" s="2">
         <v>10.0</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="J33" s="2">
-        <v>5</v>
-      </c>
-      <c r="K33" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K33" s="2">
+        <v>1</v>
+      </c>
       <c r="L33" s="2"/>
       <c r="M33" s="2">
         <v>5</v>
       </c>
       <c r="N33" s="2">
-        <v>12.9</v>
+        <v>9.75</v>
       </c>
       <c r="O33" s="2" t="s">
-        <v>336</v>
+        <v>348</v>
       </c>
       <c r="P33" s="2" t="s">
         <v>0</v>
@@ -3278,13 +3310,13 @@
         <v>30</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>335</v>
+        <v>347</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>334</v>
+        <v>346</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>333</v>
+        <v>345</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>3</v>
@@ -3293,27 +3325,29 @@
         <v>1</v>
       </c>
       <c r="G34" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H34" s="2">
         <v>10.0</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="J34" s="2">
-        <v>5</v>
-      </c>
-      <c r="K34" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K34" s="2">
+        <v>1</v>
+      </c>
       <c r="L34" s="2"/>
       <c r="M34" s="2">
         <v>5</v>
       </c>
       <c r="N34" s="2">
-        <v>12.02</v>
+        <v>9.92</v>
       </c>
       <c r="O34" s="2" t="s">
-        <v>332</v>
+        <v>344</v>
       </c>
       <c r="P34" s="2" t="s">
         <v>0</v>
@@ -3324,13 +3358,13 @@
         <v>31</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>331</v>
+        <v>343</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>330</v>
+        <v>342</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>329</v>
+        <v>341</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>3</v>
@@ -3339,27 +3373,29 @@
         <v>1</v>
       </c>
       <c r="G35" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H35" s="2">
         <v>10.0</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="J35" s="2">
-        <v>5</v>
-      </c>
-      <c r="K35" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K35" s="2">
+        <v>1</v>
+      </c>
       <c r="L35" s="2"/>
       <c r="M35" s="2">
         <v>5</v>
       </c>
       <c r="N35" s="2">
-        <v>9.12</v>
+        <v>15.08</v>
       </c>
       <c r="O35" s="2" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="P35" s="2" t="s">
         <v>0</v>
@@ -3370,44 +3406,42 @@
         <v>32</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>327</v>
+        <v>339</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>326</v>
+        <v>338</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>325</v>
+        <v>337</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F36" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G36" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H36" s="2">
         <v>10.0</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="J36" s="2">
-        <v>4</v>
-      </c>
-      <c r="K36" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K36" s="2"/>
       <c r="L36" s="2"/>
       <c r="M36" s="2">
         <v>5</v>
       </c>
       <c r="N36" s="2">
-        <v>5829.68</v>
+        <v>12.9</v>
       </c>
       <c r="O36" s="2" t="s">
-        <v>324</v>
+        <v>336</v>
       </c>
       <c r="P36" s="2" t="s">
         <v>0</v>
@@ -3418,13 +3452,13 @@
         <v>33</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>322</v>
+        <v>334</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>3</v>
@@ -3433,29 +3467,27 @@
         <v>1</v>
       </c>
       <c r="G37" s="2">
-        <v>6.0</v>
+        <v>10.0</v>
       </c>
       <c r="H37" s="2">
         <v>10.0</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="J37" s="2">
-        <v>3</v>
-      </c>
-      <c r="K37" s="2">
-        <v>2</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K37" s="2"/>
       <c r="L37" s="2"/>
       <c r="M37" s="2">
         <v>5</v>
       </c>
       <c r="N37" s="2">
-        <v>9.32</v>
+        <v>12.02</v>
       </c>
       <c r="O37" s="2" t="s">
-        <v>320</v>
+        <v>332</v>
       </c>
       <c r="P37" s="2" t="s">
         <v>0</v>
@@ -3466,13 +3498,13 @@
         <v>34</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>319</v>
+        <v>331</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>318</v>
+        <v>330</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>317</v>
+        <v>329</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>3</v>
@@ -3498,10 +3530,10 @@
         <v>5</v>
       </c>
       <c r="N38" s="2">
-        <v>24.92</v>
+        <v>9.12</v>
       </c>
       <c r="O38" s="2" t="s">
-        <v>316</v>
+        <v>328</v>
       </c>
       <c r="P38" s="2" t="s">
         <v>0</v>
@@ -3512,13 +3544,13 @@
         <v>35</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>315</v>
+        <v>327</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>314</v>
+        <v>326</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>313</v>
+        <v>325</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>3</v>
@@ -3527,29 +3559,29 @@
         <v>2</v>
       </c>
       <c r="G39" s="2">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="H39" s="2">
         <v>10.0</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="J39" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K39" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L39" s="2"/>
       <c r="M39" s="2">
         <v>5</v>
       </c>
       <c r="N39" s="2">
-        <v>5.23</v>
+        <v>5829.68</v>
       </c>
       <c r="O39" s="2" t="s">
-        <v>312</v>
+        <v>324</v>
       </c>
       <c r="P39" s="2" t="s">
         <v>0</v>
@@ -3560,13 +3592,13 @@
         <v>36</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>311</v>
+        <v>323</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>310</v>
+        <v>322</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>3</v>
@@ -3594,10 +3626,10 @@
         <v>5</v>
       </c>
       <c r="N40" s="2">
-        <v>22.08</v>
+        <v>9.32</v>
       </c>
       <c r="O40" s="2" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
       <c r="P40" s="2" t="s">
         <v>0</v>
@@ -3608,13 +3640,13 @@
         <v>37</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>306</v>
+        <v>318</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>3</v>
@@ -3623,29 +3655,27 @@
         <v>1</v>
       </c>
       <c r="G41" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H41" s="2">
         <v>10.0</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="J41" s="2">
-        <v>4</v>
-      </c>
-      <c r="K41" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K41" s="2"/>
       <c r="L41" s="2"/>
       <c r="M41" s="2">
         <v>5</v>
       </c>
       <c r="N41" s="2">
-        <v>10.18</v>
+        <v>24.92</v>
       </c>
       <c r="O41" s="2" t="s">
-        <v>304</v>
+        <v>316</v>
       </c>
       <c r="P41" s="2" t="s">
         <v>0</v>
@@ -3656,42 +3686,44 @@
         <v>38</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>303</v>
+        <v>315</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>302</v>
+        <v>314</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>301</v>
+        <v>313</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F42" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G42" s="2">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
       <c r="H42" s="2">
         <v>10.0</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="J42" s="2">
-        <v>5</v>
-      </c>
-      <c r="K42" s="2"/>
+        <v>3</v>
+      </c>
+      <c r="K42" s="2">
+        <v>2</v>
+      </c>
       <c r="L42" s="2"/>
       <c r="M42" s="2">
         <v>5</v>
       </c>
       <c r="N42" s="2">
-        <v>25.72</v>
+        <v>5.23</v>
       </c>
       <c r="O42" s="2" t="s">
-        <v>300</v>
+        <v>312</v>
       </c>
       <c r="P42" s="2" t="s">
         <v>0</v>
@@ -3702,13 +3734,13 @@
         <v>39</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>299</v>
+        <v>311</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>298</v>
+        <v>310</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>297</v>
+        <v>309</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>3</v>
@@ -3736,10 +3768,10 @@
         <v>5</v>
       </c>
       <c r="N43" s="2">
-        <v>13.57</v>
+        <v>22.08</v>
       </c>
       <c r="O43" s="2" t="s">
-        <v>296</v>
+        <v>308</v>
       </c>
       <c r="P43" s="2" t="s">
         <v>0</v>
@@ -3750,13 +3782,13 @@
         <v>40</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>295</v>
+        <v>307</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>294</v>
+        <v>306</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>293</v>
+        <v>305</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>3</v>
@@ -3765,27 +3797,29 @@
         <v>1</v>
       </c>
       <c r="G44" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H44" s="2">
         <v>10.0</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="J44" s="2">
-        <v>5</v>
-      </c>
-      <c r="K44" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K44" s="2">
+        <v>1</v>
+      </c>
       <c r="L44" s="2"/>
       <c r="M44" s="2">
         <v>5</v>
       </c>
       <c r="N44" s="2">
-        <v>27.03</v>
+        <v>10.18</v>
       </c>
       <c r="O44" s="2" t="s">
-        <v>292</v>
+        <v>304</v>
       </c>
       <c r="P44" s="2" t="s">
         <v>0</v>
@@ -3796,44 +3830,42 @@
         <v>41</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>291</v>
+        <v>303</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>290</v>
+        <v>302</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>289</v>
+        <v>301</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F45" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G45" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H45" s="2">
         <v>10.0</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="J45" s="2">
-        <v>4</v>
-      </c>
-      <c r="K45" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K45" s="2"/>
       <c r="L45" s="2"/>
       <c r="M45" s="2">
         <v>5</v>
       </c>
       <c r="N45" s="2">
-        <v>3.0</v>
+        <v>25.72</v>
       </c>
       <c r="O45" s="2" t="s">
-        <v>288</v>
+        <v>300</v>
       </c>
       <c r="P45" s="2" t="s">
         <v>0</v>
@@ -3844,13 +3876,13 @@
         <v>42</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>287</v>
+        <v>299</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>286</v>
+        <v>298</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>285</v>
+        <v>297</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>3</v>
@@ -3859,27 +3891,29 @@
         <v>1</v>
       </c>
       <c r="G46" s="2">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
       <c r="H46" s="2">
         <v>10.0</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="J46" s="2">
-        <v>5</v>
-      </c>
-      <c r="K46" s="2"/>
+        <v>3</v>
+      </c>
+      <c r="K46" s="2">
+        <v>2</v>
+      </c>
       <c r="L46" s="2"/>
       <c r="M46" s="2">
         <v>5</v>
       </c>
       <c r="N46" s="2">
-        <v>4.58</v>
+        <v>13.57</v>
       </c>
       <c r="O46" s="2" t="s">
-        <v>284</v>
+        <v>296</v>
       </c>
       <c r="P46" s="2" t="s">
         <v>0</v>
@@ -3890,13 +3924,13 @@
         <v>43</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>283</v>
+        <v>295</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>282</v>
+        <v>294</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>281</v>
+        <v>293</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>3</v>
@@ -3922,10 +3956,10 @@
         <v>5</v>
       </c>
       <c r="N47" s="2">
-        <v>5.58</v>
+        <v>27.03</v>
       </c>
       <c r="O47" s="2" t="s">
-        <v>280</v>
+        <v>292</v>
       </c>
       <c r="P47" s="2" t="s">
         <v>0</v>
@@ -3936,44 +3970,44 @@
         <v>44</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>278</v>
+        <v>290</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>277</v>
+        <v>289</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F48" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G48" s="2">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="H48" s="2">
         <v>10.0</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="J48" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K48" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L48" s="2"/>
       <c r="M48" s="2">
         <v>5</v>
       </c>
       <c r="N48" s="2">
-        <v>22.25</v>
+        <v>3.0</v>
       </c>
       <c r="O48" s="2" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="P48" s="2" t="s">
         <v>0</v>
@@ -3984,13 +4018,13 @@
         <v>45</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>275</v>
+        <v>287</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="D49" s="2">
-        <v>201118200153</v>
+        <v>286</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>285</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>3</v>
@@ -3999,29 +4033,27 @@
         <v>1</v>
       </c>
       <c r="G49" s="2">
-        <v>6.0</v>
+        <v>10.0</v>
       </c>
       <c r="H49" s="2">
         <v>10.0</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="J49" s="2">
-        <v>3</v>
-      </c>
-      <c r="K49" s="2">
-        <v>2</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K49" s="2"/>
       <c r="L49" s="2"/>
       <c r="M49" s="2">
         <v>5</v>
       </c>
       <c r="N49" s="2">
-        <v>2.13</v>
+        <v>4.58</v>
       </c>
       <c r="O49" s="2" t="s">
-        <v>273</v>
+        <v>284</v>
       </c>
       <c r="P49" s="2" t="s">
         <v>0</v>
@@ -4032,13 +4064,13 @@
         <v>46</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>272</v>
+        <v>283</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>271</v>
+        <v>282</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>270</v>
+        <v>281</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>3</v>
@@ -4064,10 +4096,10 @@
         <v>5</v>
       </c>
       <c r="N50" s="2">
-        <v>5.0</v>
+        <v>5.58</v>
       </c>
       <c r="O50" s="2" t="s">
-        <v>269</v>
+        <v>280</v>
       </c>
       <c r="P50" s="2" t="s">
         <v>0</v>
@@ -4078,13 +4110,13 @@
         <v>47</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>268</v>
+        <v>279</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>267</v>
+        <v>278</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>266</v>
+        <v>277</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>3</v>
@@ -4093,27 +4125,29 @@
         <v>1</v>
       </c>
       <c r="G51" s="2">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
       <c r="H51" s="2">
         <v>10.0</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="J51" s="2">
-        <v>5</v>
-      </c>
-      <c r="K51" s="2"/>
+        <v>3</v>
+      </c>
+      <c r="K51" s="2">
+        <v>2</v>
+      </c>
       <c r="L51" s="2"/>
       <c r="M51" s="2">
         <v>5</v>
       </c>
       <c r="N51" s="2">
-        <v>5.87</v>
+        <v>22.25</v>
       </c>
       <c r="O51" s="2" t="s">
-        <v>265</v>
+        <v>276</v>
       </c>
       <c r="P51" s="2" t="s">
         <v>0</v>
@@ -4124,13 +4158,13 @@
         <v>48</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>264</v>
+        <v>275</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>262</v>
+        <v>274</v>
+      </c>
+      <c r="D52" s="2">
+        <v>201118200153</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>3</v>
@@ -4139,29 +4173,29 @@
         <v>1</v>
       </c>
       <c r="G52" s="2">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
       <c r="H52" s="2">
         <v>10.0</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="J52" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K52" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L52" s="2"/>
       <c r="M52" s="2">
         <v>5</v>
       </c>
       <c r="N52" s="2">
-        <v>8.92</v>
+        <v>2.13</v>
       </c>
       <c r="O52" s="2" t="s">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="P52" s="2" t="s">
         <v>0</v>
@@ -4172,13 +4206,13 @@
         <v>49</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>260</v>
+        <v>272</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>258</v>
+        <v>270</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>3</v>
@@ -4187,29 +4221,27 @@
         <v>1</v>
       </c>
       <c r="G53" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H53" s="2">
         <v>10.0</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="J53" s="2">
-        <v>4</v>
-      </c>
-      <c r="K53" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K53" s="2"/>
       <c r="L53" s="2"/>
       <c r="M53" s="2">
         <v>5</v>
       </c>
       <c r="N53" s="2">
-        <v>5.8</v>
+        <v>5.0</v>
       </c>
       <c r="O53" s="2" t="s">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="P53" s="2" t="s">
         <v>0</v>
@@ -4220,44 +4252,42 @@
         <v>50</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>256</v>
+        <v>268</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>255</v>
+        <v>267</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>254</v>
+        <v>266</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F54" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G54" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H54" s="2">
         <v>10.0</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="J54" s="2">
-        <v>4</v>
-      </c>
-      <c r="K54" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K54" s="2"/>
       <c r="L54" s="2"/>
       <c r="M54" s="2">
         <v>5</v>
       </c>
       <c r="N54" s="2">
-        <v>9911.38</v>
+        <v>5.87</v>
       </c>
       <c r="O54" s="2" t="s">
-        <v>253</v>
+        <v>265</v>
       </c>
       <c r="P54" s="2" t="s">
         <v>0</v>
@@ -4268,44 +4298,44 @@
         <v>51</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F55" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G55" s="2">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="H55" s="2">
         <v>10.0</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="J55" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K55" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L55" s="2"/>
       <c r="M55" s="2">
         <v>5</v>
       </c>
       <c r="N55" s="2">
-        <v>10012.08</v>
+        <v>8.92</v>
       </c>
       <c r="O55" s="2" t="s">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="P55" s="2" t="s">
         <v>0</v>
@@ -4316,13 +4346,13 @@
         <v>52</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>248</v>
+        <v>260</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>247</v>
+        <v>259</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>3</v>
@@ -4331,27 +4361,29 @@
         <v>1</v>
       </c>
       <c r="G56" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H56" s="2">
         <v>10.0</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="J56" s="2">
-        <v>5</v>
-      </c>
-      <c r="K56" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K56" s="2">
+        <v>1</v>
+      </c>
       <c r="L56" s="2"/>
       <c r="M56" s="2">
         <v>5</v>
       </c>
       <c r="N56" s="2">
-        <v>3.17</v>
+        <v>5.8</v>
       </c>
       <c r="O56" s="2" t="s">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="P56" s="2" t="s">
         <v>0</v>
@@ -4362,19 +4394,19 @@
         <v>53</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F57" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G57" s="2">
         <v>8.0</v>
@@ -4396,10 +4428,10 @@
         <v>5</v>
       </c>
       <c r="N57" s="2">
-        <v>3.2</v>
+        <v>9911.38</v>
       </c>
       <c r="O57" s="2" t="s">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="P57" s="2" t="s">
         <v>0</v>
@@ -4410,44 +4442,44 @@
         <v>54</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>240</v>
+        <v>252</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>238</v>
+        <v>250</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F58" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G58" s="2">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
       <c r="H58" s="2">
         <v>10.0</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="J58" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K58" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L58" s="2"/>
       <c r="M58" s="2">
         <v>5</v>
       </c>
       <c r="N58" s="2">
-        <v>14.28</v>
+        <v>10012.08</v>
       </c>
       <c r="O58" s="2" t="s">
-        <v>237</v>
+        <v>249</v>
       </c>
       <c r="P58" s="2" t="s">
         <v>0</v>
@@ -4458,13 +4490,13 @@
         <v>55</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>3</v>
@@ -4473,29 +4505,27 @@
         <v>1</v>
       </c>
       <c r="G59" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H59" s="2">
         <v>10.0</v>
       </c>
       <c r="I59" s="2" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="J59" s="2">
-        <v>4</v>
-      </c>
-      <c r="K59" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K59" s="2"/>
       <c r="L59" s="2"/>
       <c r="M59" s="2">
         <v>5</v>
       </c>
       <c r="N59" s="2">
-        <v>12.48</v>
+        <v>3.17</v>
       </c>
       <c r="O59" s="2" t="s">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="P59" s="2" t="s">
         <v>0</v>
@@ -4506,13 +4536,13 @@
         <v>56</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>232</v>
+        <v>244</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>231</v>
+        <v>243</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>230</v>
+        <v>242</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>3</v>
@@ -4540,10 +4570,10 @@
         <v>5</v>
       </c>
       <c r="N60" s="2">
-        <v>4.22</v>
+        <v>3.2</v>
       </c>
       <c r="O60" s="2" t="s">
-        <v>229</v>
+        <v>241</v>
       </c>
       <c r="P60" s="2" t="s">
         <v>0</v>
@@ -4554,13 +4584,13 @@
         <v>57</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>228</v>
+        <v>240</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>227</v>
+        <v>239</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>226</v>
+        <v>238</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>3</v>
@@ -4569,29 +4599,29 @@
         <v>1</v>
       </c>
       <c r="G61" s="2">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="H61" s="2">
         <v>10.0</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="J61" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K61" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L61" s="2"/>
       <c r="M61" s="2">
         <v>5</v>
       </c>
       <c r="N61" s="2">
-        <v>8.42</v>
+        <v>14.28</v>
       </c>
       <c r="O61" s="2" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="P61" s="2" t="s">
         <v>0</v>
@@ -4602,13 +4632,13 @@
         <v>58</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>223</v>
+        <v>235</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>222</v>
+        <v>234</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>3</v>
@@ -4636,10 +4666,10 @@
         <v>5</v>
       </c>
       <c r="N62" s="2">
-        <v>7.37</v>
+        <v>12.48</v>
       </c>
       <c r="O62" s="2" t="s">
-        <v>187</v>
+        <v>233</v>
       </c>
       <c r="P62" s="2" t="s">
         <v>0</v>
@@ -4650,13 +4680,13 @@
         <v>59</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>219</v>
+        <v>230</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>3</v>
@@ -4665,27 +4695,29 @@
         <v>1</v>
       </c>
       <c r="G63" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H63" s="2">
         <v>10.0</v>
       </c>
       <c r="I63" s="2" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="J63" s="2">
-        <v>5</v>
-      </c>
-      <c r="K63" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K63" s="2">
+        <v>1</v>
+      </c>
       <c r="L63" s="2"/>
       <c r="M63" s="2">
         <v>5</v>
       </c>
       <c r="N63" s="2">
-        <v>23.67</v>
+        <v>4.22</v>
       </c>
       <c r="O63" s="2" t="s">
-        <v>218</v>
+        <v>229</v>
       </c>
       <c r="P63" s="2" t="s">
         <v>0</v>
@@ -4696,13 +4728,13 @@
         <v>60</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>216</v>
+        <v>227</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>215</v>
+        <v>226</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>3</v>
@@ -4711,29 +4743,29 @@
         <v>1</v>
       </c>
       <c r="G64" s="2">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
       <c r="H64" s="2">
         <v>10.0</v>
       </c>
       <c r="I64" s="2" t="s">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="J64" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K64" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L64" s="2"/>
       <c r="M64" s="2">
         <v>5</v>
       </c>
       <c r="N64" s="2">
-        <v>15.78</v>
+        <v>8.42</v>
       </c>
       <c r="O64" s="2" t="s">
-        <v>214</v>
+        <v>225</v>
       </c>
       <c r="P64" s="2" t="s">
         <v>0</v>
@@ -4744,13 +4776,13 @@
         <v>61</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>213</v>
+        <v>224</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>212</v>
+        <v>223</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>211</v>
+        <v>222</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>3</v>
@@ -4759,27 +4791,29 @@
         <v>1</v>
       </c>
       <c r="G65" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H65" s="2">
         <v>10.0</v>
       </c>
       <c r="I65" s="2" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="J65" s="2">
-        <v>5</v>
-      </c>
-      <c r="K65" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K65" s="2">
+        <v>1</v>
+      </c>
       <c r="L65" s="2"/>
       <c r="M65" s="2">
         <v>5</v>
       </c>
       <c r="N65" s="2">
-        <v>7.02</v>
+        <v>7.37</v>
       </c>
       <c r="O65" s="2" t="s">
-        <v>210</v>
+        <v>187</v>
       </c>
       <c r="P65" s="2" t="s">
         <v>0</v>
@@ -4790,13 +4824,13 @@
         <v>62</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>209</v>
+        <v>221</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>208</v>
+        <v>220</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>207</v>
+        <v>219</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>3</v>
@@ -4805,29 +4839,27 @@
         <v>1</v>
       </c>
       <c r="G66" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H66" s="2">
         <v>10.0</v>
       </c>
       <c r="I66" s="2" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="J66" s="2">
-        <v>4</v>
-      </c>
-      <c r="K66" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K66" s="2"/>
       <c r="L66" s="2"/>
       <c r="M66" s="2">
         <v>5</v>
       </c>
       <c r="N66" s="2">
-        <v>7.05</v>
+        <v>23.67</v>
       </c>
       <c r="O66" s="2" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="P66" s="2" t="s">
         <v>0</v>
@@ -4838,19 +4870,19 @@
         <v>63</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>205</v>
+        <v>217</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>204</v>
+        <v>216</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>203</v>
+        <v>215</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F67" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G67" s="2">
         <v>8.0</v>
@@ -4872,10 +4904,10 @@
         <v>5</v>
       </c>
       <c r="N67" s="2">
-        <v>3.77</v>
+        <v>15.78</v>
       </c>
       <c r="O67" s="2" t="s">
-        <v>202</v>
+        <v>214</v>
       </c>
       <c r="P67" s="2" t="s">
         <v>0</v>
@@ -4886,13 +4918,13 @@
         <v>64</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>201</v>
+        <v>213</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>200</v>
+        <v>212</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="E68" s="2" t="s">
         <v>3</v>
@@ -4901,29 +4933,27 @@
         <v>1</v>
       </c>
       <c r="G68" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H68" s="2">
         <v>10.0</v>
       </c>
       <c r="I68" s="2" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="J68" s="2">
-        <v>4</v>
-      </c>
-      <c r="K68" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K68" s="2"/>
       <c r="L68" s="2"/>
       <c r="M68" s="2">
         <v>5</v>
       </c>
       <c r="N68" s="2">
-        <v>11.42</v>
+        <v>7.02</v>
       </c>
       <c r="O68" s="2" t="s">
-        <v>198</v>
+        <v>210</v>
       </c>
       <c r="P68" s="2" t="s">
         <v>0</v>
@@ -4934,13 +4964,13 @@
         <v>65</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>197</v>
+        <v>209</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>196</v>
+        <v>208</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>3</v>
@@ -4949,29 +4979,29 @@
         <v>1</v>
       </c>
       <c r="G69" s="2">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="H69" s="2">
         <v>10.0</v>
       </c>
       <c r="I69" s="2" t="s">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="J69" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K69" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L69" s="2"/>
       <c r="M69" s="2">
         <v>5</v>
       </c>
       <c r="N69" s="2">
-        <v>3.57</v>
+        <v>7.05</v>
       </c>
       <c r="O69" s="2" t="s">
-        <v>194</v>
+        <v>206</v>
       </c>
       <c r="P69" s="2" t="s">
         <v>0</v>
@@ -4982,19 +5012,19 @@
         <v>66</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>193</v>
+        <v>205</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>192</v>
+        <v>204</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>191</v>
+        <v>203</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F70" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G70" s="2">
         <v>8.0</v>
@@ -5016,10 +5046,10 @@
         <v>5</v>
       </c>
       <c r="N70" s="2">
-        <v>7.5</v>
+        <v>3.77</v>
       </c>
       <c r="O70" s="2" t="s">
-        <v>179</v>
+        <v>202</v>
       </c>
       <c r="P70" s="2" t="s">
         <v>0</v>
@@ -5030,13 +5060,13 @@
         <v>67</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>190</v>
+        <v>201</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>189</v>
+        <v>200</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>188</v>
+        <v>199</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>3</v>
@@ -5064,10 +5094,10 @@
         <v>5</v>
       </c>
       <c r="N71" s="2">
-        <v>39.38</v>
+        <v>11.42</v>
       </c>
       <c r="O71" s="2" t="s">
-        <v>187</v>
+        <v>198</v>
       </c>
       <c r="P71" s="2" t="s">
         <v>0</v>
@@ -5078,13 +5108,13 @@
         <v>68</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>186</v>
+        <v>197</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>185</v>
+        <v>196</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>184</v>
+        <v>195</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>3</v>
@@ -5093,29 +5123,29 @@
         <v>1</v>
       </c>
       <c r="G72" s="2">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
       <c r="H72" s="2">
         <v>10.0</v>
       </c>
       <c r="I72" s="2" t="s">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="J72" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K72" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L72" s="2"/>
       <c r="M72" s="2">
         <v>5</v>
       </c>
       <c r="N72" s="2">
-        <v>11.68</v>
+        <v>3.57</v>
       </c>
       <c r="O72" s="2" t="s">
-        <v>183</v>
+        <v>194</v>
       </c>
       <c r="P72" s="2" t="s">
         <v>0</v>
@@ -5126,13 +5156,13 @@
         <v>69</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>182</v>
+        <v>193</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>181</v>
+        <v>192</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>180</v>
+        <v>191</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>3</v>
@@ -5160,7 +5190,7 @@
         <v>5</v>
       </c>
       <c r="N73" s="2">
-        <v>15.92</v>
+        <v>7.5</v>
       </c>
       <c r="O73" s="2" t="s">
         <v>179</v>
@@ -5174,13 +5204,13 @@
         <v>70</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>177</v>
+        <v>189</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>176</v>
+        <v>188</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>3</v>
@@ -5208,10 +5238,10 @@
         <v>5</v>
       </c>
       <c r="N74" s="2">
-        <v>6.17</v>
+        <v>39.38</v>
       </c>
       <c r="O74" s="2" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="P74" s="2" t="s">
         <v>0</v>
@@ -5222,13 +5252,13 @@
         <v>71</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>174</v>
+        <v>186</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>172</v>
+        <v>184</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>3</v>
@@ -5237,27 +5267,29 @@
         <v>1</v>
       </c>
       <c r="G75" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H75" s="2">
         <v>10.0</v>
       </c>
       <c r="I75" s="2" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="J75" s="2">
-        <v>5</v>
-      </c>
-      <c r="K75" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K75" s="2">
+        <v>1</v>
+      </c>
       <c r="L75" s="2"/>
       <c r="M75" s="2">
         <v>5</v>
       </c>
       <c r="N75" s="2">
-        <v>5.92</v>
+        <v>11.68</v>
       </c>
       <c r="O75" s="2" t="s">
-        <v>171</v>
+        <v>183</v>
       </c>
       <c r="P75" s="2" t="s">
         <v>0</v>
@@ -5268,13 +5300,13 @@
         <v>72</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="E76" s="2" t="s">
         <v>3</v>
@@ -5283,32 +5315,32 @@
         <v>1</v>
       </c>
       <c r="G76" s="2">
-        <v>4.0</v>
+        <v>8.0</v>
       </c>
       <c r="H76" s="2">
         <v>10.0</v>
       </c>
       <c r="I76" s="2" t="s">
-        <v>111</v>
+        <v>2</v>
       </c>
       <c r="J76" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K76" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L76" s="2"/>
       <c r="M76" s="2">
         <v>5</v>
       </c>
       <c r="N76" s="2">
-        <v>5.95</v>
+        <v>15.92</v>
       </c>
       <c r="O76" s="2" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="P76" s="2" t="s">
-        <v>109</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -5316,13 +5348,13 @@
         <v>73</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="E77" s="2" t="s">
         <v>3</v>
@@ -5331,27 +5363,29 @@
         <v>1</v>
       </c>
       <c r="G77" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H77" s="2">
         <v>10.0</v>
       </c>
       <c r="I77" s="2" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="J77" s="2">
-        <v>5</v>
-      </c>
-      <c r="K77" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K77" s="2">
+        <v>1</v>
+      </c>
       <c r="L77" s="2"/>
       <c r="M77" s="2">
         <v>5</v>
       </c>
       <c r="N77" s="2">
-        <v>9.08</v>
+        <v>6.17</v>
       </c>
       <c r="O77" s="2" t="s">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="P77" s="2" t="s">
         <v>0</v>
@@ -5362,13 +5396,13 @@
         <v>74</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>162</v>
+        <v>174</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="E78" s="2" t="s">
         <v>3</v>
@@ -5377,29 +5411,27 @@
         <v>1</v>
       </c>
       <c r="G78" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H78" s="2">
         <v>10.0</v>
       </c>
       <c r="I78" s="2" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="J78" s="2">
-        <v>4</v>
-      </c>
-      <c r="K78" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K78" s="2"/>
       <c r="L78" s="2"/>
       <c r="M78" s="2">
         <v>5</v>
       </c>
       <c r="N78" s="2">
-        <v>13.42</v>
+        <v>5.92</v>
       </c>
       <c r="O78" s="2" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="P78" s="2" t="s">
         <v>0</v>
@@ -5410,13 +5442,13 @@
         <v>75</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="E79" s="2" t="s">
         <v>3</v>
@@ -5425,32 +5457,32 @@
         <v>1</v>
       </c>
       <c r="G79" s="2">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
       <c r="H79" s="2">
         <v>10.0</v>
       </c>
       <c r="I79" s="2" t="s">
-        <v>16</v>
+        <v>111</v>
       </c>
       <c r="J79" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K79" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L79" s="2"/>
       <c r="M79" s="2">
         <v>5</v>
       </c>
       <c r="N79" s="2">
-        <v>2.57</v>
+        <v>5.95</v>
       </c>
       <c r="O79" s="2" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="P79" s="2" t="s">
-        <v>0</v>
+        <v>109</v>
       </c>
     </row>
     <row r="80" spans="1:16">
@@ -5458,13 +5490,13 @@
         <v>76</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="E80" s="2" t="s">
         <v>3</v>
@@ -5490,10 +5522,10 @@
         <v>5</v>
       </c>
       <c r="N80" s="2">
-        <v>1.65</v>
+        <v>9.08</v>
       </c>
       <c r="O80" s="2" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="P80" s="2" t="s">
         <v>0</v>
@@ -5504,13 +5536,13 @@
         <v>77</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>149</v>
+        <v>161</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>148</v>
+        <v>160</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>3</v>
@@ -5519,29 +5551,29 @@
         <v>1</v>
       </c>
       <c r="G81" s="2">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="H81" s="2">
         <v>10.0</v>
       </c>
       <c r="I81" s="2" t="s">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="J81" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K81" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L81" s="2"/>
       <c r="M81" s="2">
         <v>5</v>
       </c>
       <c r="N81" s="2">
-        <v>12.1</v>
+        <v>13.42</v>
       </c>
       <c r="O81" s="2" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="P81" s="2" t="s">
         <v>0</v>
@@ -5552,13 +5584,13 @@
         <v>78</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>146</v>
+        <v>158</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>145</v>
+        <v>157</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>144</v>
+        <v>156</v>
       </c>
       <c r="E82" s="2" t="s">
         <v>3</v>
@@ -5586,10 +5618,10 @@
         <v>5</v>
       </c>
       <c r="N82" s="2">
-        <v>18.58</v>
+        <v>2.57</v>
       </c>
       <c r="O82" s="2" t="s">
-        <v>143</v>
+        <v>155</v>
       </c>
       <c r="P82" s="2" t="s">
         <v>0</v>
@@ -5600,13 +5632,13 @@
         <v>79</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>142</v>
+        <v>154</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>140</v>
+        <v>152</v>
       </c>
       <c r="E83" s="2" t="s">
         <v>3</v>
@@ -5632,10 +5664,10 @@
         <v>5</v>
       </c>
       <c r="N83" s="2">
-        <v>18.03</v>
+        <v>1.65</v>
       </c>
       <c r="O83" s="2" t="s">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="P83" s="2" t="s">
         <v>0</v>
@@ -5646,13 +5678,13 @@
         <v>80</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="E84" s="2" t="s">
         <v>3</v>
@@ -5661,29 +5693,29 @@
         <v>1</v>
       </c>
       <c r="G84" s="2">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
       <c r="H84" s="2">
         <v>10.0</v>
       </c>
       <c r="I84" s="2" t="s">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="J84" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K84" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L84" s="2"/>
       <c r="M84" s="2">
         <v>5</v>
       </c>
       <c r="N84" s="2">
-        <v>9.68</v>
+        <v>12.1</v>
       </c>
       <c r="O84" s="2" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="P84" s="2" t="s">
         <v>0</v>
@@ -5694,13 +5726,13 @@
         <v>81</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="E85" s="2" t="s">
         <v>3</v>
@@ -5728,10 +5760,10 @@
         <v>5</v>
       </c>
       <c r="N85" s="2">
-        <v>14.13</v>
+        <v>18.58</v>
       </c>
       <c r="O85" s="2" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="P85" s="2" t="s">
         <v>0</v>
@@ -5742,13 +5774,13 @@
         <v>82</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>129</v>
+        <v>141</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="E86" s="2" t="s">
         <v>3</v>
@@ -5757,29 +5789,27 @@
         <v>1</v>
       </c>
       <c r="G86" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H86" s="2">
         <v>10.0</v>
       </c>
       <c r="I86" s="2" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="J86" s="2">
-        <v>4</v>
-      </c>
-      <c r="K86" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K86" s="2"/>
       <c r="L86" s="2"/>
       <c r="M86" s="2">
         <v>5</v>
       </c>
       <c r="N86" s="2">
-        <v>11.45</v>
+        <v>18.03</v>
       </c>
       <c r="O86" s="2" t="s">
-        <v>127</v>
+        <v>139</v>
       </c>
       <c r="P86" s="2" t="s">
         <v>0</v>
@@ -5790,13 +5820,13 @@
         <v>83</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="E87" s="2" t="s">
         <v>3</v>
@@ -5824,10 +5854,10 @@
         <v>5</v>
       </c>
       <c r="N87" s="2">
-        <v>12.55</v>
+        <v>9.68</v>
       </c>
       <c r="O87" s="2" t="s">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="P87" s="2" t="s">
         <v>0</v>
@@ -5838,13 +5868,13 @@
         <v>84</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="E88" s="2" t="s">
         <v>3</v>
@@ -5853,27 +5883,29 @@
         <v>1</v>
       </c>
       <c r="G88" s="2">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
       <c r="H88" s="2">
         <v>10.0</v>
       </c>
       <c r="I88" s="2" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="J88" s="2">
-        <v>5</v>
-      </c>
-      <c r="K88" s="2"/>
+        <v>3</v>
+      </c>
+      <c r="K88" s="2">
+        <v>2</v>
+      </c>
       <c r="L88" s="2"/>
       <c r="M88" s="2">
         <v>5</v>
       </c>
       <c r="N88" s="2">
-        <v>6.58</v>
+        <v>14.13</v>
       </c>
       <c r="O88" s="2" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="P88" s="2" t="s">
         <v>0</v>
@@ -5884,13 +5916,13 @@
         <v>85</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="E89" s="2" t="s">
         <v>3</v>
@@ -5918,10 +5950,10 @@
         <v>5</v>
       </c>
       <c r="N89" s="2">
-        <v>18.78</v>
+        <v>11.45</v>
       </c>
       <c r="O89" s="2" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="P89" s="2" t="s">
         <v>0</v>
@@ -5932,47 +5964,47 @@
         <v>86</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="E90" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F90" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G90" s="2">
-        <v>4.0</v>
+        <v>8.0</v>
       </c>
       <c r="H90" s="2">
         <v>10.0</v>
       </c>
       <c r="I90" s="2" t="s">
-        <v>111</v>
+        <v>2</v>
       </c>
       <c r="J90" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K90" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L90" s="2"/>
       <c r="M90" s="2">
         <v>5</v>
       </c>
       <c r="N90" s="2">
-        <v>10181.77</v>
+        <v>12.55</v>
       </c>
       <c r="O90" s="2" t="s">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="P90" s="2" t="s">
-        <v>109</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -5980,13 +6012,13 @@
         <v>87</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>108</v>
+        <v>122</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>107</v>
+        <v>121</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>106</v>
+        <v>120</v>
       </c>
       <c r="E91" s="2" t="s">
         <v>3</v>
@@ -5995,29 +6027,27 @@
         <v>1</v>
       </c>
       <c r="G91" s="2">
-        <v>6.0</v>
+        <v>10.0</v>
       </c>
       <c r="H91" s="2">
         <v>10.0</v>
       </c>
       <c r="I91" s="2" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="J91" s="2">
-        <v>3</v>
-      </c>
-      <c r="K91" s="2">
-        <v>2</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K91" s="2"/>
       <c r="L91" s="2"/>
       <c r="M91" s="2">
         <v>5</v>
       </c>
       <c r="N91" s="2">
-        <v>25.12</v>
+        <v>6.58</v>
       </c>
       <c r="O91" s="2" t="s">
-        <v>105</v>
+        <v>119</v>
       </c>
       <c r="P91" s="2" t="s">
         <v>0</v>
@@ -6028,13 +6058,13 @@
         <v>88</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>104</v>
+        <v>118</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>103</v>
+        <v>117</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>102</v>
+        <v>116</v>
       </c>
       <c r="E92" s="2" t="s">
         <v>3</v>
@@ -6043,29 +6073,29 @@
         <v>1</v>
       </c>
       <c r="G92" s="2">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="H92" s="2">
         <v>10.0</v>
       </c>
       <c r="I92" s="2" t="s">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="J92" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K92" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L92" s="2"/>
       <c r="M92" s="2">
         <v>5</v>
       </c>
       <c r="N92" s="2">
-        <v>16.98</v>
+        <v>18.78</v>
       </c>
       <c r="O92" s="2" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="P92" s="2" t="s">
         <v>0</v>
@@ -6076,45 +6106,47 @@
         <v>89</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>100</v>
+        <v>114</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>99</v>
+        <v>113</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="E93" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F93" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G93" s="2">
-        <v>10.0</v>
+        <v>4.0</v>
       </c>
       <c r="H93" s="2">
         <v>10.0</v>
       </c>
       <c r="I93" s="2" t="s">
-        <v>29</v>
+        <v>111</v>
       </c>
       <c r="J93" s="2">
-        <v>5</v>
-      </c>
-      <c r="K93" s="2"/>
+        <v>2</v>
+      </c>
+      <c r="K93" s="2">
+        <v>3</v>
+      </c>
       <c r="L93" s="2"/>
       <c r="M93" s="2">
         <v>5</v>
       </c>
       <c r="N93" s="2">
-        <v>1.45</v>
+        <v>10181.77</v>
       </c>
       <c r="O93" s="2" t="s">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="P93" s="2" t="s">
-        <v>0</v>
+        <v>109</v>
       </c>
     </row>
     <row r="94" spans="1:16">
@@ -6122,42 +6154,44 @@
         <v>90</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="E94" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F94" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G94" s="2">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
       <c r="H94" s="2">
         <v>10.0</v>
       </c>
       <c r="I94" s="2" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="J94" s="2">
-        <v>5</v>
-      </c>
-      <c r="K94" s="2"/>
+        <v>3</v>
+      </c>
+      <c r="K94" s="2">
+        <v>2</v>
+      </c>
       <c r="L94" s="2"/>
       <c r="M94" s="2">
         <v>5</v>
       </c>
       <c r="N94" s="2">
-        <v>6.18</v>
+        <v>25.12</v>
       </c>
       <c r="O94" s="2" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="P94" s="2" t="s">
         <v>0</v>
@@ -6168,13 +6202,13 @@
         <v>91</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="E95" s="2" t="s">
         <v>3</v>
@@ -6183,27 +6217,29 @@
         <v>1</v>
       </c>
       <c r="G95" s="2">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
       <c r="H95" s="2">
         <v>10.0</v>
       </c>
       <c r="I95" s="2" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="J95" s="2">
-        <v>5</v>
-      </c>
-      <c r="K95" s="2"/>
+        <v>3</v>
+      </c>
+      <c r="K95" s="2">
+        <v>2</v>
+      </c>
       <c r="L95" s="2"/>
       <c r="M95" s="2">
         <v>5</v>
       </c>
       <c r="N95" s="2">
-        <v>6.13</v>
+        <v>16.98</v>
       </c>
       <c r="O95" s="2" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="P95" s="2" t="s">
         <v>0</v>
@@ -6214,13 +6250,13 @@
         <v>92</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="E96" s="2" t="s">
         <v>3</v>
@@ -6229,29 +6265,27 @@
         <v>1</v>
       </c>
       <c r="G96" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H96" s="2">
         <v>10.0</v>
       </c>
       <c r="I96" s="2" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="J96" s="2">
-        <v>4</v>
-      </c>
-      <c r="K96" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K96" s="2"/>
       <c r="L96" s="2"/>
       <c r="M96" s="2">
         <v>5</v>
       </c>
       <c r="N96" s="2">
-        <v>2.4</v>
+        <v>1.45</v>
       </c>
       <c r="O96" s="2" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="P96" s="2" t="s">
         <v>0</v>
@@ -6262,44 +6296,42 @@
         <v>93</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="E97" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F97" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G97" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H97" s="2">
         <v>10.0</v>
       </c>
       <c r="I97" s="2" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="J97" s="2">
-        <v>4</v>
-      </c>
-      <c r="K97" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K97" s="2"/>
       <c r="L97" s="2"/>
       <c r="M97" s="2">
         <v>5</v>
       </c>
       <c r="N97" s="2">
-        <v>15.75</v>
+        <v>6.18</v>
       </c>
       <c r="O97" s="2" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="P97" s="2" t="s">
         <v>0</v>
@@ -6310,13 +6342,13 @@
         <v>94</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="E98" s="2" t="s">
         <v>3</v>
@@ -6342,10 +6374,10 @@
         <v>5</v>
       </c>
       <c r="N98" s="2">
-        <v>2.17</v>
+        <v>6.13</v>
       </c>
       <c r="O98" s="2" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="P98" s="2" t="s">
         <v>0</v>
@@ -6356,13 +6388,13 @@
         <v>95</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="E99" s="2" t="s">
         <v>3</v>
@@ -6371,29 +6403,29 @@
         <v>1</v>
       </c>
       <c r="G99" s="2">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="H99" s="2">
         <v>10.0</v>
       </c>
       <c r="I99" s="2" t="s">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="J99" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K99" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L99" s="2"/>
       <c r="M99" s="2">
         <v>5</v>
       </c>
       <c r="N99" s="2">
-        <v>9.5</v>
+        <v>2.4</v>
       </c>
       <c r="O99" s="2" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="P99" s="2" t="s">
         <v>0</v>
@@ -6404,13 +6436,13 @@
         <v>96</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="E100" s="2" t="s">
         <v>3</v>
@@ -6419,27 +6451,29 @@
         <v>1</v>
       </c>
       <c r="G100" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H100" s="2">
         <v>10.0</v>
       </c>
       <c r="I100" s="2" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="J100" s="2">
-        <v>5</v>
-      </c>
-      <c r="K100" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K100" s="2">
+        <v>1</v>
+      </c>
       <c r="L100" s="2"/>
       <c r="M100" s="2">
         <v>5</v>
       </c>
       <c r="N100" s="2">
-        <v>10.75</v>
+        <v>15.75</v>
       </c>
       <c r="O100" s="2" t="s">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="P100" s="2" t="s">
         <v>0</v>
@@ -6450,44 +6484,42 @@
         <v>97</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="E101" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F101" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G101" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H101" s="2">
         <v>10.0</v>
       </c>
       <c r="I101" s="2" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="J101" s="2">
-        <v>4</v>
-      </c>
-      <c r="K101" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K101" s="2"/>
       <c r="L101" s="2"/>
       <c r="M101" s="2">
         <v>5</v>
       </c>
       <c r="N101" s="2">
-        <v>23.17</v>
+        <v>2.17</v>
       </c>
       <c r="O101" s="2" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="P101" s="2" t="s">
         <v>0</v>
@@ -6498,42 +6530,44 @@
         <v>98</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="E102" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F102" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G102" s="2">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
       <c r="H102" s="2">
         <v>10.0</v>
       </c>
       <c r="I102" s="2" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="J102" s="2">
-        <v>5</v>
-      </c>
-      <c r="K102" s="2"/>
+        <v>3</v>
+      </c>
+      <c r="K102" s="2">
+        <v>2</v>
+      </c>
       <c r="L102" s="2"/>
       <c r="M102" s="2">
         <v>5</v>
       </c>
       <c r="N102" s="2">
-        <v>5.47</v>
+        <v>9.5</v>
       </c>
       <c r="O102" s="2" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="P102" s="2" t="s">
         <v>0</v>
@@ -6544,13 +6578,13 @@
         <v>99</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="E103" s="2" t="s">
         <v>3</v>
@@ -6559,29 +6593,27 @@
         <v>1</v>
       </c>
       <c r="G103" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H103" s="2">
         <v>10.0</v>
       </c>
       <c r="I103" s="2" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="J103" s="2">
-        <v>4</v>
-      </c>
-      <c r="K103" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K103" s="2"/>
       <c r="L103" s="2"/>
       <c r="M103" s="2">
         <v>5</v>
       </c>
       <c r="N103" s="2">
-        <v>15.8</v>
+        <v>10.75</v>
       </c>
       <c r="O103" s="2" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="P103" s="2" t="s">
         <v>0</v>
@@ -6592,42 +6624,44 @@
         <v>100</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="E104" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F104" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G104" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H104" s="2">
         <v>10.0</v>
       </c>
       <c r="I104" s="2" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="J104" s="2">
-        <v>5</v>
-      </c>
-      <c r="K104" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K104" s="2">
+        <v>1</v>
+      </c>
       <c r="L104" s="2"/>
       <c r="M104" s="2">
         <v>5</v>
       </c>
       <c r="N104" s="2">
-        <v>4.07</v>
+        <v>23.17</v>
       </c>
       <c r="O104" s="2" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="P104" s="2" t="s">
         <v>0</v>
@@ -6638,44 +6672,42 @@
         <v>101</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="E105" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F105" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G105" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H105" s="2">
         <v>10.0</v>
       </c>
       <c r="I105" s="2" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="J105" s="2">
-        <v>4</v>
-      </c>
-      <c r="K105" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K105" s="2"/>
       <c r="L105" s="2"/>
       <c r="M105" s="2">
         <v>5</v>
       </c>
       <c r="N105" s="2">
-        <v>21.8</v>
+        <v>5.47</v>
       </c>
       <c r="O105" s="2" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="P105" s="2" t="s">
         <v>0</v>
@@ -6686,13 +6718,13 @@
         <v>102</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="E106" s="2" t="s">
         <v>3</v>
@@ -6720,10 +6752,10 @@
         <v>5</v>
       </c>
       <c r="N106" s="2">
-        <v>10.12</v>
+        <v>15.8</v>
       </c>
       <c r="O106" s="2" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="P106" s="2" t="s">
         <v>0</v>
@@ -6734,13 +6766,13 @@
         <v>103</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="E107" s="2" t="s">
         <v>3</v>
@@ -6766,10 +6798,10 @@
         <v>5</v>
       </c>
       <c r="N107" s="2">
-        <v>13.48</v>
+        <v>4.07</v>
       </c>
       <c r="O107" s="2" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="P107" s="2" t="s">
         <v>0</v>
@@ -6780,13 +6812,13 @@
         <v>104</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="E108" s="2" t="s">
         <v>3</v>
@@ -6814,10 +6846,10 @@
         <v>5</v>
       </c>
       <c r="N108" s="2">
-        <v>10.6</v>
+        <v>21.8</v>
       </c>
       <c r="O108" s="2" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="P108" s="2" t="s">
         <v>0</v>
@@ -6828,13 +6860,13 @@
         <v>105</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="E109" s="2" t="s">
         <v>3</v>
@@ -6843,27 +6875,29 @@
         <v>1</v>
       </c>
       <c r="G109" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H109" s="2">
         <v>10.0</v>
       </c>
       <c r="I109" s="2" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="J109" s="2">
-        <v>5</v>
-      </c>
-      <c r="K109" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K109" s="2">
+        <v>1</v>
+      </c>
       <c r="L109" s="2"/>
       <c r="M109" s="2">
         <v>5</v>
       </c>
       <c r="N109" s="2">
-        <v>12.52</v>
+        <v>10.12</v>
       </c>
       <c r="O109" s="2" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="P109" s="2" t="s">
         <v>0</v>
@@ -6874,13 +6908,13 @@
         <v>106</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="E110" s="2" t="s">
         <v>3</v>
@@ -6906,10 +6940,10 @@
         <v>5</v>
       </c>
       <c r="N110" s="2">
-        <v>15.33</v>
+        <v>13.48</v>
       </c>
       <c r="O110" s="2" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="P110" s="2" t="s">
         <v>0</v>
@@ -6920,13 +6954,13 @@
         <v>107</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="E111" s="2" t="s">
         <v>3</v>
@@ -6954,10 +6988,10 @@
         <v>5</v>
       </c>
       <c r="N111" s="2">
-        <v>9.45</v>
+        <v>10.6</v>
       </c>
       <c r="O111" s="2" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="P111" s="2" t="s">
         <v>0</v>
@@ -6968,13 +7002,13 @@
         <v>108</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="E112" s="2" t="s">
         <v>3</v>
@@ -6983,29 +7017,27 @@
         <v>1</v>
       </c>
       <c r="G112" s="2">
-        <v>6.0</v>
+        <v>10.0</v>
       </c>
       <c r="H112" s="2">
         <v>10.0</v>
       </c>
       <c r="I112" s="2" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="J112" s="2">
-        <v>3</v>
-      </c>
-      <c r="K112" s="2">
-        <v>2</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K112" s="2"/>
       <c r="L112" s="2"/>
       <c r="M112" s="2">
         <v>5</v>
       </c>
       <c r="N112" s="2">
-        <v>3.6</v>
+        <v>12.52</v>
       </c>
       <c r="O112" s="2" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="P112" s="2" t="s">
         <v>0</v>
@@ -7016,13 +7048,13 @@
         <v>109</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="E113" s="2" t="s">
         <v>3</v>
@@ -7031,29 +7063,27 @@
         <v>1</v>
       </c>
       <c r="G113" s="2">
-        <v>6.0</v>
+        <v>10.0</v>
       </c>
       <c r="H113" s="2">
         <v>10.0</v>
       </c>
       <c r="I113" s="2" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="J113" s="2">
-        <v>3</v>
-      </c>
-      <c r="K113" s="2">
-        <v>2</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K113" s="2"/>
       <c r="L113" s="2"/>
       <c r="M113" s="2">
         <v>5</v>
       </c>
       <c r="N113" s="2">
-        <v>10.15</v>
+        <v>15.33</v>
       </c>
       <c r="O113" s="2" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="P113" s="2" t="s">
         <v>0</v>
@@ -7064,13 +7094,13 @@
         <v>110</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="E114" s="2" t="s">
         <v>3</v>
@@ -7098,10 +7128,10 @@
         <v>5</v>
       </c>
       <c r="N114" s="2">
-        <v>6.12</v>
+        <v>9.45</v>
       </c>
       <c r="O114" s="2" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="P114" s="2" t="s">
         <v>0</v>
@@ -7112,44 +7142,44 @@
         <v>111</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="E115" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F115" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G115" s="2">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
       <c r="H115" s="2">
         <v>10.0</v>
       </c>
       <c r="I115" s="2" t="s">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="J115" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K115" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L115" s="2"/>
       <c r="M115" s="2">
         <v>5</v>
       </c>
       <c r="N115" s="2">
-        <v>8.33</v>
+        <v>3.6</v>
       </c>
       <c r="O115" s="2" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="P115" s="2" t="s">
         <v>0</v>
@@ -7160,13 +7190,13 @@
         <v>112</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="E116" s="2" t="s">
         <v>3</v>
@@ -7175,31 +7205,175 @@
         <v>1</v>
       </c>
       <c r="G116" s="2">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
       <c r="H116" s="2">
         <v>10.0</v>
       </c>
       <c r="I116" s="2" t="s">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="J116" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K116" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L116" s="2"/>
       <c r="M116" s="2">
         <v>5</v>
       </c>
       <c r="N116" s="2">
+        <v>10.15</v>
+      </c>
+      <c r="O116" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="P116" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:16">
+      <c r="A117" s="2">
+        <v>113</v>
+      </c>
+      <c r="B117" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C117" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D117" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E117" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F117" s="2">
+        <v>1</v>
+      </c>
+      <c r="G117" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="H117" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I117" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J117" s="2">
+        <v>4</v>
+      </c>
+      <c r="K117" s="2">
+        <v>1</v>
+      </c>
+      <c r="L117" s="2"/>
+      <c r="M117" s="2">
+        <v>5</v>
+      </c>
+      <c r="N117" s="2">
+        <v>6.12</v>
+      </c>
+      <c r="O117" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="P117" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="1:16">
+      <c r="A118" s="2">
+        <v>114</v>
+      </c>
+      <c r="B118" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C118" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D118" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E118" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F118" s="2">
+        <v>2</v>
+      </c>
+      <c r="G118" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="H118" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I118" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J118" s="2">
+        <v>4</v>
+      </c>
+      <c r="K118" s="2">
+        <v>1</v>
+      </c>
+      <c r="L118" s="2"/>
+      <c r="M118" s="2">
+        <v>5</v>
+      </c>
+      <c r="N118" s="2">
+        <v>8.33</v>
+      </c>
+      <c r="O118" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="P118" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="1:16">
+      <c r="A119" s="2">
+        <v>115</v>
+      </c>
+      <c r="B119" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C119" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D119" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E119" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F119" s="2">
+        <v>1</v>
+      </c>
+      <c r="G119" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="H119" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I119" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J119" s="2">
+        <v>4</v>
+      </c>
+      <c r="K119" s="2">
+        <v>1</v>
+      </c>
+      <c r="L119" s="2"/>
+      <c r="M119" s="2">
+        <v>5</v>
+      </c>
+      <c r="N119" s="2">
         <v>7.77</v>
       </c>
-      <c r="O116" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="P116" s="2" t="s">
+      <c r="O119" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="P119" s="2" t="s">
         <v>0</v>
       </c>
     </row>

--- a/2lit_center.xlsx
+++ b/2lit_center.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="242">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="323">
   <si>
     <t>ناجح ✓</t>
   </si>
@@ -38,39 +38,39 @@
     <t>SHERIF MOHAMED</t>
   </si>
   <si>
-    <t>2026-03-09 18:30</t>
+    <t>2026-03-16 03:29</t>
+  </si>
+  <si>
+    <t>01125509128</t>
+  </si>
+  <si>
+    <t>marwanayman72009@gmail.com</t>
+  </si>
+  <si>
+    <t>مروان ايمن عاطف</t>
+  </si>
+  <si>
+    <t>2026-03-09 18:51</t>
+  </si>
+  <si>
+    <t>80.0%</t>
+  </si>
+  <si>
+    <t>01221970126</t>
+  </si>
+  <si>
+    <t>mareiaramez1@gmail.com</t>
+  </si>
+  <si>
+    <t>Maria ramez</t>
+  </si>
+  <si>
+    <t>2026-03-09 18:52</t>
   </si>
   <si>
     <t>100.0%</t>
   </si>
   <si>
-    <t>01125509128</t>
-  </si>
-  <si>
-    <t>marwanayman72009@gmail.com</t>
-  </si>
-  <si>
-    <t>مروان ايمن عاطف</t>
-  </si>
-  <si>
-    <t>2026-03-09 18:51</t>
-  </si>
-  <si>
-    <t>80.0%</t>
-  </si>
-  <si>
-    <t>01221970126</t>
-  </si>
-  <si>
-    <t>mareiaramez1@gmail.com</t>
-  </si>
-  <si>
-    <t>Maria ramez</t>
-  </si>
-  <si>
-    <t>2026-03-09 18:52</t>
-  </si>
-  <si>
     <t>01121973130</t>
   </si>
   <si>
@@ -284,13 +284,511 @@
     <t>منه مختار عبد القادر</t>
   </si>
   <si>
+    <t>2026-03-15 13:20</t>
+  </si>
+  <si>
+    <t>01012965454</t>
+  </si>
+  <si>
+    <t>hyawalid788@gmail.com</t>
+  </si>
+  <si>
+    <t>hya walid helal</t>
+  </si>
+  <si>
+    <t>2026-03-15 18:40</t>
+  </si>
+  <si>
+    <t>01065596920</t>
+  </si>
+  <si>
+    <t>caramella3750@gmail.com</t>
+  </si>
+  <si>
+    <t>Carma Ehab</t>
+  </si>
+  <si>
+    <t>2026-03-15 13:57</t>
+  </si>
+  <si>
+    <t>01026933947</t>
+  </si>
+  <si>
+    <t>malaksamykamel2008@gmail.com</t>
+  </si>
+  <si>
+    <t>Malak Samy</t>
+  </si>
+  <si>
+    <t>2026-03-15 15:44</t>
+  </si>
+  <si>
+    <t>01006941885</t>
+  </si>
+  <si>
+    <t>yokeahmedyahia@gmail.com</t>
+  </si>
+  <si>
+    <t>Yahia Ahmed</t>
+  </si>
+  <si>
+    <t>2026-03-15 15:50</t>
+  </si>
+  <si>
+    <t>01552477901</t>
+  </si>
+  <si>
+    <t>roayaakram0@gmail.com</t>
+  </si>
+  <si>
+    <t>رؤيا اكرم شوقي محمد</t>
+  </si>
+  <si>
+    <t>2026-03-15 16:09</t>
+  </si>
+  <si>
+    <t>01033050201</t>
+  </si>
+  <si>
+    <t>abdelfatahebrahim38@gmail.com</t>
+  </si>
+  <si>
+    <t>ابراهيم عبدالفتاح فؤاد</t>
+  </si>
+  <si>
+    <t>2026-03-15 16:22</t>
+  </si>
+  <si>
+    <t>01113765691</t>
+  </si>
+  <si>
+    <t>ahmed148mody@gmail.com</t>
+  </si>
+  <si>
+    <t>أحمد محمد أحمد سلمان</t>
+  </si>
+  <si>
+    <t>2026-03-15 16:26</t>
+  </si>
+  <si>
+    <t>01553495959</t>
+  </si>
+  <si>
+    <t>elmaghlopm@gmail.com</t>
+  </si>
+  <si>
+    <t>Mariam elmaghlop</t>
+  </si>
+  <si>
+    <t>2026-03-15 16:47</t>
+  </si>
+  <si>
+    <t>01113365191</t>
+  </si>
+  <si>
+    <t>faridamahmoud13579@gmail.com</t>
+  </si>
+  <si>
+    <t>فريدة محمود عبدالحسيب احمد</t>
+  </si>
+  <si>
+    <t>2026-03-15 16:35</t>
+  </si>
+  <si>
+    <t>01129793194</t>
+  </si>
+  <si>
+    <t>mrxyt881@gmail.com</t>
+  </si>
+  <si>
+    <t>Mahmoud ahmed salah</t>
+  </si>
+  <si>
+    <t>2026-03-15 16:53</t>
+  </si>
+  <si>
+    <t>01011317686</t>
+  </si>
+  <si>
+    <t>superman611255@gmail.com</t>
+  </si>
+  <si>
+    <t>Fares Tamer</t>
+  </si>
+  <si>
+    <t>2026-03-15 16:59</t>
+  </si>
+  <si>
+    <t>01092255761</t>
+  </si>
+  <si>
+    <t>habibagalal552004@gmail.com</t>
+  </si>
+  <si>
+    <t>moustafa galal</t>
+  </si>
+  <si>
+    <t>2026-03-15 17:17</t>
+  </si>
+  <si>
+    <t>01093571345</t>
+  </si>
+  <si>
+    <t>Mallakfathyazzam@gmail.com</t>
+  </si>
+  <si>
+    <t>Malak  fathy azzam</t>
+  </si>
+  <si>
+    <t>2026-03-15 17:21</t>
+  </si>
+  <si>
+    <t>01069526879</t>
+  </si>
+  <si>
+    <t>Safawael31@gmail.com</t>
+  </si>
+  <si>
+    <t>Safa wael fathy</t>
+  </si>
+  <si>
+    <t>2026-03-15 17:34</t>
+  </si>
+  <si>
+    <t>01100682703</t>
+  </si>
+  <si>
+    <t>Lara.eldiasti@gmail.com</t>
+  </si>
+  <si>
+    <t>لارا الحسن الديسطي</t>
+  </si>
+  <si>
+    <t>2026-03-15 17:24</t>
+  </si>
+  <si>
+    <t>01019713904</t>
+  </si>
+  <si>
+    <t>mayar.mohamed.200813@gmail.com</t>
+  </si>
+  <si>
+    <t>ميار محمد رفعت</t>
+  </si>
+  <si>
+    <t>2026-03-15 17:45</t>
+  </si>
+  <si>
+    <t>01022023062</t>
+  </si>
+  <si>
+    <t>malakmohammedalaa94@gmail.com</t>
+  </si>
+  <si>
+    <t>ملك محمد علاء الدين</t>
+  </si>
+  <si>
+    <t>2026-03-15 18:00</t>
+  </si>
+  <si>
+    <t>01127911990</t>
+  </si>
+  <si>
+    <t>fm6757434@gmail.com</t>
+  </si>
+  <si>
+    <t>Farah mohamed</t>
+  </si>
+  <si>
+    <t>2026-03-15 18:02</t>
+  </si>
+  <si>
+    <t>01007991680</t>
+  </si>
+  <si>
+    <t>nada.gamal196@gmail.com</t>
+  </si>
+  <si>
+    <t>Nada</t>
+  </si>
+  <si>
+    <t>01225460949</t>
+  </si>
+  <si>
+    <t>hm3947263@gmail.com</t>
+  </si>
+  <si>
+    <t>Rahma mohamed mostafa</t>
+  </si>
+  <si>
     <t>راسب ✗</t>
   </si>
   <si>
-    <t>2026-03-15 12:42</t>
-  </si>
-  <si>
-    <t>20.0%</t>
+    <t>2026-03-15 18:15</t>
+  </si>
+  <si>
+    <t>40.0%</t>
+  </si>
+  <si>
+    <t>01110668723</t>
+  </si>
+  <si>
+    <t>abdoeidbody2008@gmail.com</t>
+  </si>
+  <si>
+    <t>Abdullah Eid saber</t>
+  </si>
+  <si>
+    <t>2026-03-15 18:31</t>
+  </si>
+  <si>
+    <t>01010103820</t>
+  </si>
+  <si>
+    <t>somiasami88@gmail.com</t>
+  </si>
+  <si>
+    <t>salma mohamed mahmoud</t>
+  </si>
+  <si>
+    <t>2026-03-15 18:38</t>
+  </si>
+  <si>
+    <t>01121431168</t>
+  </si>
+  <si>
+    <t>ahmeddaoomy2@gmail.com</t>
+  </si>
+  <si>
+    <t>Ahmed shawky</t>
+  </si>
+  <si>
+    <t>2026-03-15 18:50</t>
+  </si>
+  <si>
+    <t>01157331074</t>
+  </si>
+  <si>
+    <t>farahgadallh@gmail.com</t>
+  </si>
+  <si>
+    <t>Farah Ahmed mohamed</t>
+  </si>
+  <si>
+    <t>2026-03-15 18:42</t>
+  </si>
+  <si>
+    <t>01012424377</t>
+  </si>
+  <si>
+    <t>janayousry@2008gmail.com</t>
+  </si>
+  <si>
+    <t>jana ahmed mohmed yousry</t>
+  </si>
+  <si>
+    <t>2026-03-15 19:09</t>
+  </si>
+  <si>
+    <t>01097794201</t>
+  </si>
+  <si>
+    <t>aytensaleh6@gmail.com</t>
+  </si>
+  <si>
+    <t>Ayten Saleh Mostafa</t>
+  </si>
+  <si>
+    <t>2026-03-15 19:08</t>
+  </si>
+  <si>
+    <t>01101097272</t>
+  </si>
+  <si>
+    <t>mohamed.almalt2009@gmail.com</t>
+  </si>
+  <si>
+    <t>محمد السيد  بهيج</t>
+  </si>
+  <si>
+    <t>2026-03-15 19:01</t>
+  </si>
+  <si>
+    <t>01065163432</t>
+  </si>
+  <si>
+    <t>Janahosein901@gmail.com</t>
+  </si>
+  <si>
+    <t>Jana hussein Fahim</t>
+  </si>
+  <si>
+    <t>01006392755</t>
+  </si>
+  <si>
+    <t>ezz44013@gmail.com</t>
+  </si>
+  <si>
+    <t>عز الدين أيمن</t>
+  </si>
+  <si>
+    <t>01023876919</t>
+  </si>
+  <si>
+    <t>yassinahmedsaid139@gmail.com</t>
+  </si>
+  <si>
+    <t>ياسين احمد سعيد</t>
+  </si>
+  <si>
+    <t>01501045643</t>
+  </si>
+  <si>
+    <t>elawadyahmed999@gmial.com</t>
+  </si>
+  <si>
+    <t>Elawady Ahmed elawady</t>
+  </si>
+  <si>
+    <t>2026-03-15 19:17</t>
+  </si>
+  <si>
+    <t>01125776411</t>
+  </si>
+  <si>
+    <t>radwanosama414@gmail.com</t>
+  </si>
+  <si>
+    <t>Radwan Osama</t>
+  </si>
+  <si>
+    <t>01124926013</t>
+  </si>
+  <si>
+    <t>marwanelnakeeb2009@gmail.com</t>
+  </si>
+  <si>
+    <t>Marwan omar</t>
+  </si>
+  <si>
+    <t>2026-03-15 19:22</t>
+  </si>
+  <si>
+    <t>01228047462</t>
+  </si>
+  <si>
+    <t>Yousefsonic22@gmail.com</t>
+  </si>
+  <si>
+    <t>Yousef hesham</t>
+  </si>
+  <si>
+    <t>2026-03-15 19:24</t>
+  </si>
+  <si>
+    <t>karimmowafak@gmail.com</t>
+  </si>
+  <si>
+    <t>Karim Mowafak</t>
+  </si>
+  <si>
+    <t>2026-03-15 19:23</t>
+  </si>
+  <si>
+    <t>01061920915</t>
+  </si>
+  <si>
+    <t>goudysherif@gmail.com</t>
+  </si>
+  <si>
+    <t>محمد شريف</t>
+  </si>
+  <si>
+    <t>2026-03-15 19:33</t>
+  </si>
+  <si>
+    <t>01121777574</t>
+  </si>
+  <si>
+    <t>zadaahmed1510@gmail.com</t>
+  </si>
+  <si>
+    <t>Zada Ahmed fathy</t>
+  </si>
+  <si>
+    <t>2026-03-15 19:55</t>
+  </si>
+  <si>
+    <t>01271532097</t>
+  </si>
+  <si>
+    <t>marlygmghobrial@gmail.com</t>
+  </si>
+  <si>
+    <t>مارلي جورج موريس</t>
+  </si>
+  <si>
+    <t>2026-03-15 22:58</t>
+  </si>
+  <si>
+    <t>01120961209</t>
+  </si>
+  <si>
+    <t>masa1412009@gmail.com</t>
+  </si>
+  <si>
+    <t>Masa mohamed mohy</t>
+  </si>
+  <si>
+    <t>2026-03-15 23:16</t>
+  </si>
+  <si>
+    <t>01123268908</t>
+  </si>
+  <si>
+    <t>habibaamrmm@icloud.com</t>
+  </si>
+  <si>
+    <t>Habiba amr eladwy</t>
+  </si>
+  <si>
+    <t>2026-03-16 00:36</t>
+  </si>
+  <si>
+    <t>01011744851</t>
+  </si>
+  <si>
+    <t>abdelrahmanbedo@gmail.com</t>
+  </si>
+  <si>
+    <t>عبدالرحمن محمد محمد</t>
+  </si>
+  <si>
+    <t>2026-03-16 02:57</t>
+  </si>
+  <si>
+    <t>01040794109</t>
+  </si>
+  <si>
+    <t>oa2743370@gmail.com</t>
+  </si>
+  <si>
+    <t>Omar Ibrahim Hegazy</t>
+  </si>
+  <si>
+    <t>2026-03-16 03:51</t>
+  </si>
+  <si>
+    <t>01016345481</t>
+  </si>
+  <si>
+    <t>ao5617814@gmail.com</t>
+  </si>
+  <si>
+    <t>Abdelrahman Ibrahim Hegazy</t>
+  </si>
+  <si>
+    <t>2026-03-16 12:57</t>
   </si>
   <si>
     <t>01018892998</t>
@@ -302,388 +800,133 @@
     <t>Gannat Abd el Nasser</t>
   </si>
   <si>
-    <t>2026-03-15 13:20</t>
-  </si>
-  <si>
-    <t>01012965454</t>
-  </si>
-  <si>
-    <t>hyawalid788@gmail.com</t>
-  </si>
-  <si>
-    <t>hya walid helal</t>
-  </si>
-  <si>
-    <t>2026-03-15 18:40</t>
-  </si>
-  <si>
-    <t>01065596920</t>
-  </si>
-  <si>
-    <t>caramella3750@gmail.com</t>
-  </si>
-  <si>
-    <t>Carma Ehab</t>
-  </si>
-  <si>
-    <t>2026-03-15 13:57</t>
-  </si>
-  <si>
-    <t>01026933947</t>
-  </si>
-  <si>
-    <t>malaksamykamel2008@gmail.com</t>
-  </si>
-  <si>
-    <t>Malak Samy</t>
-  </si>
-  <si>
-    <t>2026-03-15 15:44</t>
-  </si>
-  <si>
-    <t>01006941885</t>
-  </si>
-  <si>
-    <t>yokeahmedyahia@gmail.com</t>
-  </si>
-  <si>
-    <t>Yahia Ahmed</t>
-  </si>
-  <si>
-    <t>2026-03-15 15:50</t>
-  </si>
-  <si>
-    <t>01552477901</t>
-  </si>
-  <si>
-    <t>roayaakram0@gmail.com</t>
-  </si>
-  <si>
-    <t>رؤيا اكرم شوقي محمد</t>
-  </si>
-  <si>
-    <t>2026-03-15 16:09</t>
-  </si>
-  <si>
-    <t>01033050201</t>
-  </si>
-  <si>
-    <t>abdelfatahebrahim38@gmail.com</t>
-  </si>
-  <si>
-    <t>ابراهيم عبدالفتاح فؤاد</t>
-  </si>
-  <si>
-    <t>2026-03-15 16:22</t>
-  </si>
-  <si>
-    <t>01113765691</t>
-  </si>
-  <si>
-    <t>ahmed148mody@gmail.com</t>
-  </si>
-  <si>
-    <t>أحمد محمد أحمد سلمان</t>
-  </si>
-  <si>
-    <t>2026-03-15 16:26</t>
-  </si>
-  <si>
-    <t>01553495959</t>
-  </si>
-  <si>
-    <t>elmaghlopm@gmail.com</t>
-  </si>
-  <si>
-    <t>Mariam elmaghlop</t>
-  </si>
-  <si>
-    <t>2026-03-15 16:47</t>
-  </si>
-  <si>
-    <t>01113365191</t>
-  </si>
-  <si>
-    <t>faridamahmoud13579@gmail.com</t>
-  </si>
-  <si>
-    <t>فريدة محمود عبدالحسيب احمد</t>
-  </si>
-  <si>
-    <t>2026-03-15 16:35</t>
-  </si>
-  <si>
-    <t>01129793194</t>
-  </si>
-  <si>
-    <t>mrxyt881@gmail.com</t>
-  </si>
-  <si>
-    <t>Mahmoud ahmed salah</t>
-  </si>
-  <si>
-    <t>2026-03-15 16:53</t>
-  </si>
-  <si>
-    <t>01011317686</t>
-  </si>
-  <si>
-    <t>superman611255@gmail.com</t>
-  </si>
-  <si>
-    <t>Fares Tamer</t>
-  </si>
-  <si>
-    <t>2026-03-15 16:59</t>
-  </si>
-  <si>
-    <t>01092255761</t>
-  </si>
-  <si>
-    <t>habibagalal552004@gmail.com</t>
-  </si>
-  <si>
-    <t>moustafa galal</t>
-  </si>
-  <si>
-    <t>2026-03-15 17:17</t>
-  </si>
-  <si>
-    <t>01093571345</t>
-  </si>
-  <si>
-    <t>Mallakfathyazzam@gmail.com</t>
-  </si>
-  <si>
-    <t>Malak  fathy azzam</t>
-  </si>
-  <si>
-    <t>2026-03-15 17:21</t>
-  </si>
-  <si>
-    <t>01069526879</t>
-  </si>
-  <si>
-    <t>Safawael31@gmail.com</t>
-  </si>
-  <si>
-    <t>Safa wael fathy</t>
-  </si>
-  <si>
-    <t>2026-03-15 17:34</t>
-  </si>
-  <si>
-    <t>01100682703</t>
-  </si>
-  <si>
-    <t>Lara.eldiasti@gmail.com</t>
-  </si>
-  <si>
-    <t>لارا الحسن الديسطي</t>
-  </si>
-  <si>
-    <t>2026-03-15 17:24</t>
-  </si>
-  <si>
-    <t>01019713904</t>
-  </si>
-  <si>
-    <t>mayar.mohamed.200813@gmail.com</t>
-  </si>
-  <si>
-    <t>ميار محمد رفعت</t>
-  </si>
-  <si>
-    <t>2026-03-15 17:45</t>
-  </si>
-  <si>
-    <t>01022023062</t>
-  </si>
-  <si>
-    <t>malakmohammedalaa94@gmail.com</t>
-  </si>
-  <si>
-    <t>ملك محمد علاء الدين</t>
-  </si>
-  <si>
-    <t>2026-03-15 18:00</t>
-  </si>
-  <si>
-    <t>01127911990</t>
-  </si>
-  <si>
-    <t>fm6757434@gmail.com</t>
-  </si>
-  <si>
-    <t>Farah mohamed</t>
-  </si>
-  <si>
-    <t>2026-03-15 18:02</t>
-  </si>
-  <si>
-    <t>01007991680</t>
-  </si>
-  <si>
-    <t>nada.gamal196@gmail.com</t>
-  </si>
-  <si>
-    <t>Nada</t>
-  </si>
-  <si>
-    <t>01225460949</t>
-  </si>
-  <si>
-    <t>hm3947263@gmail.com</t>
-  </si>
-  <si>
-    <t>Rahma mohamed mostafa</t>
-  </si>
-  <si>
-    <t>2026-03-15 18:15</t>
-  </si>
-  <si>
-    <t>40.0%</t>
-  </si>
-  <si>
-    <t>01110668723</t>
-  </si>
-  <si>
-    <t>abdoeidbody2008@gmail.com</t>
-  </si>
-  <si>
-    <t>Abdullah Eid saber</t>
-  </si>
-  <si>
-    <t>2026-03-15 18:31</t>
-  </si>
-  <si>
-    <t>01010103820</t>
-  </si>
-  <si>
-    <t>somiasami88@gmail.com</t>
-  </si>
-  <si>
-    <t>salma mohamed mahmoud</t>
-  </si>
-  <si>
-    <t>2026-03-15 18:38</t>
-  </si>
-  <si>
-    <t>01121431168</t>
-  </si>
-  <si>
-    <t>ahmeddaoomy2@gmail.com</t>
-  </si>
-  <si>
-    <t>Ahmed shawky</t>
-  </si>
-  <si>
-    <t>2026-03-15 18:50</t>
-  </si>
-  <si>
-    <t>01157331074</t>
-  </si>
-  <si>
-    <t>farahgadallh@gmail.com</t>
-  </si>
-  <si>
-    <t>Farah Ahmed mohamed</t>
-  </si>
-  <si>
-    <t>2026-03-15 18:42</t>
-  </si>
-  <si>
-    <t>01012424377</t>
-  </si>
-  <si>
-    <t>janayousry@2008gmail.com</t>
-  </si>
-  <si>
-    <t>jana ahmed mohmed yousry</t>
-  </si>
-  <si>
-    <t>2026-03-15 19:09</t>
-  </si>
-  <si>
-    <t>01097794201</t>
-  </si>
-  <si>
-    <t>aytensaleh6@gmail.com</t>
-  </si>
-  <si>
-    <t>Ayten Saleh Mostafa</t>
-  </si>
-  <si>
-    <t>2026-03-15 19:08</t>
-  </si>
-  <si>
-    <t>01101097272</t>
-  </si>
-  <si>
-    <t>mohamed.almalt2009@gmail.com</t>
-  </si>
-  <si>
-    <t>محمد السيد  بهيج</t>
-  </si>
-  <si>
-    <t>2026-03-15 19:01</t>
-  </si>
-  <si>
-    <t>01065163432</t>
-  </si>
-  <si>
-    <t>Janahosein901@gmail.com</t>
-  </si>
-  <si>
-    <t>Jana hussein Fahim</t>
-  </si>
-  <si>
-    <t>01006392755</t>
-  </si>
-  <si>
-    <t>ezz44013@gmail.com</t>
-  </si>
-  <si>
-    <t>عز الدين أيمن</t>
-  </si>
-  <si>
-    <t>01023876919</t>
-  </si>
-  <si>
-    <t>yassinahmedsaid139@gmail.com</t>
-  </si>
-  <si>
-    <t>ياسين احمد سعيد</t>
-  </si>
-  <si>
-    <t>01501045643</t>
-  </si>
-  <si>
-    <t>elawadyahmed999@gmial.com</t>
-  </si>
-  <si>
-    <t>Elawady Ahmed elawady</t>
-  </si>
-  <si>
-    <t>2026-03-15 19:17</t>
-  </si>
-  <si>
-    <t>01125776411</t>
-  </si>
-  <si>
-    <t>radwanosama414@gmail.com</t>
-  </si>
-  <si>
-    <t>Radwan Osama</t>
-  </si>
-  <si>
-    <t>01124926013</t>
-  </si>
-  <si>
-    <t>marwanelnakeeb2009@gmail.com</t>
-  </si>
-  <si>
-    <t>Marwan omar</t>
+    <t>2026-03-16 15:38</t>
+  </si>
+  <si>
+    <t>+01122773746</t>
+  </si>
+  <si>
+    <t>begomego66@gmail.com</t>
+  </si>
+  <si>
+    <t>Begad Magdy Ali</t>
+  </si>
+  <si>
+    <t>2026-03-16 15:36</t>
+  </si>
+  <si>
+    <t>01062623490</t>
+  </si>
+  <si>
+    <t>omarzakaa1@gmail.com</t>
+  </si>
+  <si>
+    <t>omar zakaa</t>
+  </si>
+  <si>
+    <t>2026-03-16 16:43</t>
+  </si>
+  <si>
+    <t>01103622316</t>
+  </si>
+  <si>
+    <t>esraassaaddd30@gmail.com</t>
+  </si>
+  <si>
+    <t>Esraa saad</t>
+  </si>
+  <si>
+    <t>2026-03-16 17:23</t>
+  </si>
+  <si>
+    <t>01017803931</t>
+  </si>
+  <si>
+    <t>kokymzykm2007@gmail.com</t>
+  </si>
+  <si>
+    <t>Kenzy Mohamed</t>
+  </si>
+  <si>
+    <t>2026-03-16 17:52</t>
+  </si>
+  <si>
+    <t>01154109786</t>
+  </si>
+  <si>
+    <t>nadaaseleem@gmail.com</t>
+  </si>
+  <si>
+    <t>Nada Ahmed Seleem</t>
+  </si>
+  <si>
+    <t>2026-03-16 17:42</t>
+  </si>
+  <si>
+    <t>01017099170</t>
+  </si>
+  <si>
+    <t>joudhanynabil@gmail.com</t>
+  </si>
+  <si>
+    <t>joudy</t>
+  </si>
+  <si>
+    <t>01555066805</t>
+  </si>
+  <si>
+    <t>mohammed.el.shazly2009@gmail.com</t>
+  </si>
+  <si>
+    <t>محمد أسامة محمد الشاذلي</t>
+  </si>
+  <si>
+    <t>2026-03-16 18:48</t>
+  </si>
+  <si>
+    <t>01099284562</t>
+  </si>
+  <si>
+    <t>samehsami9@gmail.com</t>
+  </si>
+  <si>
+    <t>Mariam sameh sami</t>
+  </si>
+  <si>
+    <t>2026-03-16 19:14</t>
+  </si>
+  <si>
+    <t>01121970064</t>
+  </si>
+  <si>
+    <t>Ahmedmakg7@gmail.com</t>
+  </si>
+  <si>
+    <t>احمد محمد احمد كامل</t>
+  </si>
+  <si>
+    <t>2026-03-16 19:12</t>
+  </si>
+  <si>
+    <t>01554037795</t>
+  </si>
+  <si>
+    <t>saharrefee@gmail.com</t>
+  </si>
+  <si>
+    <t>سهر محمد ابراهيم الرفاعي</t>
+  </si>
+  <si>
+    <t>2026-03-16 19:19</t>
+  </si>
+  <si>
+    <t>01064753790</t>
+  </si>
+  <si>
+    <t>Abdullazizosama18@gmail.com</t>
+  </si>
+  <si>
+    <t>Abdullaziz</t>
   </si>
   <si>
     <t>الحالة</t>
@@ -740,7 +983,7 @@
     <t>الدرجة الكاملة: 10 | درجة النجاح: 5.00</t>
   </si>
   <si>
-    <t>تاريخ التصدير: 2026-03-15 19:17</t>
+    <t>تاريخ التصدير: 2026-03-16 19:30</t>
   </si>
 </sst>
 </file>
@@ -1128,7 +1371,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:P59"/>
+  <dimension ref="A1:P80"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="true" style="0"/>
@@ -1151,67 +1394,67 @@
   <sheetData>
     <row r="1" spans="1:16">
       <c r="A1" s="3" t="s">
-        <v>239</v>
+        <v>320</v>
       </c>
     </row>
     <row r="2" spans="1:16">
       <c r="A2" s="3" t="s">
-        <v>240</v>
+        <v>321</v>
       </c>
     </row>
     <row r="3" spans="1:16">
       <c r="A3" s="3" t="s">
-        <v>241</v>
+        <v>322</v>
       </c>
     </row>
     <row r="4" spans="1:16">
       <c r="A4" s="1" t="s">
-        <v>238</v>
+        <v>319</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>237</v>
+        <v>318</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>236</v>
+        <v>317</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>235</v>
+        <v>316</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>234</v>
+        <v>315</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>233</v>
+        <v>314</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>232</v>
+        <v>313</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>231</v>
+        <v>312</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>230</v>
+        <v>311</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>229</v>
+        <v>310</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>228</v>
+        <v>309</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>227</v>
+        <v>308</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>226</v>
+        <v>307</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>225</v>
+        <v>306</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>224</v>
+        <v>305</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>223</v>
+        <v>304</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1219,19 +1462,19 @@
         <v>1</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>222</v>
+        <v>303</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>221</v>
+        <v>302</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>220</v>
+        <v>301</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F5" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G5" s="2">
         <v>8.0</v>
@@ -1240,7 +1483,7 @@
         <v>10.0</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J5" s="2">
         <v>4</v>
@@ -1253,10 +1496,10 @@
         <v>5</v>
       </c>
       <c r="N5" s="2">
-        <v>1.67</v>
+        <v>20.53</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>216</v>
+        <v>300</v>
       </c>
       <c r="P5" s="2" t="s">
         <v>0</v>
@@ -1267,13 +1510,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>219</v>
+        <v>299</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>218</v>
+        <v>298</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>217</v>
+        <v>297</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>3</v>
@@ -1288,7 +1531,7 @@
         <v>10.0</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J6" s="2">
         <v>4</v>
@@ -1301,10 +1544,10 @@
         <v>5</v>
       </c>
       <c r="N6" s="2">
-        <v>4.2</v>
+        <v>14.28</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>216</v>
+        <v>296</v>
       </c>
       <c r="P6" s="2" t="s">
         <v>0</v>
@@ -1315,19 +1558,19 @@
         <v>3</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>215</v>
+        <v>295</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>214</v>
+        <v>294</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>213</v>
+        <v>293</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F7" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G7" s="2">
         <v>10.0</v>
@@ -1336,7 +1579,7 @@
         <v>10.0</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="J7" s="2">
         <v>5</v>
@@ -1347,10 +1590,10 @@
         <v>5</v>
       </c>
       <c r="N7" s="2">
-        <v>7.48</v>
+        <v>21.38</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>199</v>
+        <v>292</v>
       </c>
       <c r="P7" s="2" t="s">
         <v>0</v>
@@ -1361,13 +1604,13 @@
         <v>4</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>212</v>
+        <v>291</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>211</v>
+        <v>290</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>210</v>
+        <v>289</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>3</v>
@@ -1382,7 +1625,7 @@
         <v>10.0</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="J8" s="2">
         <v>5</v>
@@ -1393,10 +1636,10 @@
         <v>5</v>
       </c>
       <c r="N8" s="2">
-        <v>12.57</v>
+        <v>27.77</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>199</v>
+        <v>288</v>
       </c>
       <c r="P8" s="2" t="s">
         <v>0</v>
@@ -1407,13 +1650,13 @@
         <v>5</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>209</v>
+        <v>287</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>208</v>
+        <v>286</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>207</v>
+        <v>285</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>3</v>
@@ -1428,7 +1671,7 @@
         <v>10.0</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="J9" s="2">
         <v>5</v>
@@ -1439,10 +1682,10 @@
         <v>5</v>
       </c>
       <c r="N9" s="2">
-        <v>9.22</v>
+        <v>15.2</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>203</v>
+        <v>277</v>
       </c>
       <c r="P9" s="2" t="s">
         <v>0</v>
@@ -1453,13 +1696,13 @@
         <v>6</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>206</v>
+        <v>284</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>205</v>
+        <v>283</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>204</v>
+        <v>282</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>3</v>
@@ -1474,7 +1717,7 @@
         <v>10.0</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="J10" s="2">
         <v>5</v>
@@ -1485,10 +1728,10 @@
         <v>5</v>
       </c>
       <c r="N10" s="2">
-        <v>10.92</v>
+        <v>8.4</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>203</v>
+        <v>281</v>
       </c>
       <c r="P10" s="2" t="s">
         <v>0</v>
@@ -1499,13 +1742,13 @@
         <v>7</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>202</v>
+        <v>280</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>201</v>
+        <v>279</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>200</v>
+        <v>278</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>3</v>
@@ -1514,29 +1757,27 @@
         <v>1</v>
       </c>
       <c r="G11" s="2">
-        <v>6.0</v>
+        <v>10.0</v>
       </c>
       <c r="H11" s="2">
         <v>10.0</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="J11" s="2">
-        <v>3</v>
-      </c>
-      <c r="K11" s="2">
-        <v>2</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K11" s="2"/>
       <c r="L11" s="2"/>
       <c r="M11" s="2">
         <v>5</v>
       </c>
       <c r="N11" s="2">
-        <v>19.3</v>
+        <v>29.9</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>199</v>
+        <v>277</v>
       </c>
       <c r="P11" s="2" t="s">
         <v>0</v>
@@ -1547,13 +1788,13 @@
         <v>8</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>198</v>
+        <v>276</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>197</v>
+        <v>275</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>196</v>
+        <v>274</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>3</v>
@@ -1568,7 +1809,7 @@
         <v>10.0</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="J12" s="2">
         <v>5</v>
@@ -1579,10 +1820,10 @@
         <v>5</v>
       </c>
       <c r="N12" s="2">
-        <v>27.43</v>
+        <v>8.73</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>195</v>
+        <v>273</v>
       </c>
       <c r="P12" s="2" t="s">
         <v>0</v>
@@ -1593,13 +1834,13 @@
         <v>9</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>194</v>
+        <v>272</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>193</v>
+        <v>271</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>192</v>
+        <v>270</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>3</v>
@@ -1614,7 +1855,7 @@
         <v>10.0</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="J13" s="2">
         <v>5</v>
@@ -1625,10 +1866,10 @@
         <v>5</v>
       </c>
       <c r="N13" s="2">
-        <v>3.58</v>
+        <v>8.18</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>191</v>
+        <v>269</v>
       </c>
       <c r="P13" s="2" t="s">
         <v>0</v>
@@ -1639,13 +1880,13 @@
         <v>10</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>189</v>
+        <v>267</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>188</v>
+        <v>266</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>3</v>
@@ -1654,29 +1895,27 @@
         <v>1</v>
       </c>
       <c r="G14" s="2">
-        <v>6.0</v>
+        <v>10.0</v>
       </c>
       <c r="H14" s="2">
         <v>10.0</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="J14" s="2">
-        <v>3</v>
-      </c>
-      <c r="K14" s="2">
-        <v>2</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K14" s="2"/>
       <c r="L14" s="2"/>
       <c r="M14" s="2">
         <v>5</v>
       </c>
       <c r="N14" s="2">
-        <v>14.85</v>
+        <v>2.92</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>187</v>
+        <v>265</v>
       </c>
       <c r="P14" s="2" t="s">
         <v>0</v>
@@ -1687,13 +1926,13 @@
         <v>11</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>186</v>
+        <v>264</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>185</v>
+        <v>263</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>184</v>
+        <v>262</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>3</v>
@@ -1702,27 +1941,29 @@
         <v>1</v>
       </c>
       <c r="G15" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H15" s="2">
         <v>10.0</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J15" s="2">
-        <v>5</v>
-      </c>
-      <c r="K15" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K15" s="2">
+        <v>1</v>
+      </c>
       <c r="L15" s="2"/>
       <c r="M15" s="2">
         <v>5</v>
       </c>
       <c r="N15" s="2">
-        <v>5.42</v>
+        <v>21.08</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>183</v>
+        <v>261</v>
       </c>
       <c r="P15" s="2" t="s">
         <v>0</v>
@@ -1733,42 +1974,44 @@
         <v>12</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>182</v>
+        <v>260</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>181</v>
+        <v>259</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>180</v>
+        <v>258</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F16" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G16" s="2">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
       <c r="H16" s="2">
         <v>10.0</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J16" s="2">
-        <v>5</v>
-      </c>
-      <c r="K16" s="2"/>
+        <v>3</v>
+      </c>
+      <c r="K16" s="2">
+        <v>2</v>
+      </c>
       <c r="L16" s="2"/>
       <c r="M16" s="2">
         <v>5</v>
       </c>
       <c r="N16" s="2">
-        <v>8.33</v>
+        <v>17.15</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>179</v>
+        <v>257</v>
       </c>
       <c r="P16" s="2" t="s">
         <v>0</v>
@@ -1779,13 +2022,13 @@
         <v>13</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>178</v>
+        <v>256</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>177</v>
+        <v>255</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>176</v>
+        <v>254</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>3</v>
@@ -1794,32 +2037,30 @@
         <v>1</v>
       </c>
       <c r="G17" s="2">
-        <v>4.0</v>
+        <v>10.0</v>
       </c>
       <c r="H17" s="2">
         <v>10.0</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>175</v>
+        <v>17</v>
       </c>
       <c r="J17" s="2">
-        <v>2</v>
-      </c>
-      <c r="K17" s="2">
-        <v>3</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K17" s="2"/>
       <c r="L17" s="2"/>
       <c r="M17" s="2">
         <v>5</v>
       </c>
       <c r="N17" s="2">
-        <v>1.5</v>
+        <v>7.7</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>174</v>
+        <v>253</v>
       </c>
       <c r="P17" s="2" t="s">
-        <v>89</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -1827,13 +2068,13 @@
         <v>14</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>173</v>
+        <v>252</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>172</v>
+        <v>251</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>171</v>
+        <v>250</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>3</v>
@@ -1842,29 +2083,27 @@
         <v>1</v>
       </c>
       <c r="G18" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H18" s="2">
         <v>10.0</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="J18" s="2">
-        <v>4</v>
-      </c>
-      <c r="K18" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K18" s="2"/>
       <c r="L18" s="2"/>
       <c r="M18" s="2">
         <v>5</v>
       </c>
       <c r="N18" s="2">
-        <v>6.75</v>
+        <v>21.45</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>167</v>
+        <v>249</v>
       </c>
       <c r="P18" s="2" t="s">
         <v>0</v>
@@ -1875,13 +2114,13 @@
         <v>15</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>170</v>
+        <v>248</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>169</v>
+        <v>247</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>168</v>
+        <v>246</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>3</v>
@@ -1890,29 +2129,27 @@
         <v>1</v>
       </c>
       <c r="G19" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H19" s="2">
         <v>10.0</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="J19" s="2">
-        <v>4</v>
-      </c>
-      <c r="K19" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K19" s="2"/>
       <c r="L19" s="2"/>
       <c r="M19" s="2">
         <v>5</v>
       </c>
       <c r="N19" s="2">
-        <v>8.65</v>
+        <v>23.68</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>167</v>
+        <v>245</v>
       </c>
       <c r="P19" s="2" t="s">
         <v>0</v>
@@ -1923,13 +2160,13 @@
         <v>16</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>166</v>
+        <v>244</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>165</v>
+        <v>243</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>164</v>
+        <v>242</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>3</v>
@@ -1938,27 +2175,29 @@
         <v>1</v>
       </c>
       <c r="G20" s="2">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
       <c r="H20" s="2">
         <v>10.0</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J20" s="2">
-        <v>5</v>
-      </c>
-      <c r="K20" s="2"/>
+        <v>3</v>
+      </c>
+      <c r="K20" s="2">
+        <v>2</v>
+      </c>
       <c r="L20" s="2"/>
       <c r="M20" s="2">
         <v>5</v>
       </c>
       <c r="N20" s="2">
-        <v>10.37</v>
+        <v>7.7</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>163</v>
+        <v>241</v>
       </c>
       <c r="P20" s="2" t="s">
         <v>0</v>
@@ -1969,13 +2208,13 @@
         <v>17</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>162</v>
+        <v>240</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>161</v>
+        <v>239</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>160</v>
+        <v>238</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>3</v>
@@ -1990,7 +2229,7 @@
         <v>10.0</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="J21" s="2">
         <v>5</v>
@@ -2001,10 +2240,10 @@
         <v>5</v>
       </c>
       <c r="N21" s="2">
-        <v>7.27</v>
+        <v>18.78</v>
       </c>
       <c r="O21" s="2" t="s">
-        <v>159</v>
+        <v>237</v>
       </c>
       <c r="P21" s="2" t="s">
         <v>0</v>
@@ -2015,13 +2254,13 @@
         <v>18</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>158</v>
+        <v>236</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>157</v>
+        <v>235</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>156</v>
+        <v>234</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>3</v>
@@ -2030,27 +2269,29 @@
         <v>1</v>
       </c>
       <c r="G22" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H22" s="2">
         <v>10.0</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J22" s="2">
-        <v>5</v>
-      </c>
-      <c r="K22" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K22" s="2">
+        <v>1</v>
+      </c>
       <c r="L22" s="2"/>
       <c r="M22" s="2">
         <v>5</v>
       </c>
       <c r="N22" s="2">
-        <v>4.2</v>
+        <v>4.37</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>155</v>
+        <v>233</v>
       </c>
       <c r="P22" s="2" t="s">
         <v>0</v>
@@ -2061,44 +2302,44 @@
         <v>19</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>154</v>
+        <v>232</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>153</v>
+        <v>231</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>152</v>
+        <v>230</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F23" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G23" s="2">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
       <c r="H23" s="2">
         <v>10.0</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="J23" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K23" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L23" s="2"/>
       <c r="M23" s="2">
         <v>5</v>
       </c>
       <c r="N23" s="2">
-        <v>25.47</v>
+        <v>0.48</v>
       </c>
       <c r="O23" s="2" t="s">
-        <v>151</v>
+        <v>229</v>
       </c>
       <c r="P23" s="2" t="s">
         <v>0</v>
@@ -2109,19 +2350,19 @@
         <v>20</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>150</v>
+        <v>228</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>149</v>
+        <v>227</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>148</v>
+        <v>226</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F24" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G24" s="2">
         <v>8.0</v>
@@ -2130,7 +2371,7 @@
         <v>10.0</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J24" s="2">
         <v>4</v>
@@ -2143,10 +2384,10 @@
         <v>5</v>
       </c>
       <c r="N24" s="2">
-        <v>16.42</v>
+        <v>1.7</v>
       </c>
       <c r="O24" s="2" t="s">
-        <v>147</v>
+        <v>225</v>
       </c>
       <c r="P24" s="2" t="s">
         <v>0</v>
@@ -2157,13 +2398,13 @@
         <v>21</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>146</v>
+        <v>224</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>144</v>
+        <v>223</v>
+      </c>
+      <c r="D25" s="2">
+        <v>201118200153</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>3</v>
@@ -2172,27 +2413,29 @@
         <v>1</v>
       </c>
       <c r="G25" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H25" s="2">
         <v>10.0</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J25" s="2">
-        <v>5</v>
-      </c>
-      <c r="K25" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K25" s="2">
+        <v>1</v>
+      </c>
       <c r="L25" s="2"/>
       <c r="M25" s="2">
         <v>5</v>
       </c>
       <c r="N25" s="2">
-        <v>20.63</v>
+        <v>2.15</v>
       </c>
       <c r="O25" s="2" t="s">
-        <v>143</v>
+        <v>222</v>
       </c>
       <c r="P25" s="2" t="s">
         <v>0</v>
@@ -2203,13 +2446,13 @@
         <v>22</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>142</v>
+        <v>221</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>141</v>
+        <v>220</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>140</v>
+        <v>219</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>3</v>
@@ -2224,7 +2467,7 @@
         <v>10.0</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="J26" s="2">
         <v>5</v>
@@ -2235,10 +2478,10 @@
         <v>5</v>
       </c>
       <c r="N26" s="2">
-        <v>5.73</v>
+        <v>3.83</v>
       </c>
       <c r="O26" s="2" t="s">
-        <v>139</v>
+        <v>218</v>
       </c>
       <c r="P26" s="2" t="s">
         <v>0</v>
@@ -2249,42 +2492,44 @@
         <v>23</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>138</v>
+        <v>217</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>137</v>
+        <v>216</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>136</v>
+        <v>215</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F27" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G27" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H27" s="2">
         <v>10.0</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J27" s="2">
-        <v>5</v>
-      </c>
-      <c r="K27" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K27" s="2">
+        <v>1</v>
+      </c>
       <c r="L27" s="2"/>
       <c r="M27" s="2">
         <v>5</v>
       </c>
       <c r="N27" s="2">
-        <v>3.98</v>
+        <v>1.67</v>
       </c>
       <c r="O27" s="2" t="s">
-        <v>135</v>
+        <v>211</v>
       </c>
       <c r="P27" s="2" t="s">
         <v>0</v>
@@ -2295,13 +2540,13 @@
         <v>24</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>134</v>
+        <v>214</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>133</v>
+        <v>213</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>132</v>
+        <v>212</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>3</v>
@@ -2316,7 +2561,7 @@
         <v>10.0</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J28" s="2">
         <v>4</v>
@@ -2329,10 +2574,10 @@
         <v>5</v>
       </c>
       <c r="N28" s="2">
-        <v>7.77</v>
+        <v>4.2</v>
       </c>
       <c r="O28" s="2" t="s">
-        <v>131</v>
+        <v>211</v>
       </c>
       <c r="P28" s="2" t="s">
         <v>0</v>
@@ -2343,19 +2588,19 @@
         <v>25</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>130</v>
+        <v>210</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>129</v>
+        <v>209</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>128</v>
+        <v>208</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F29" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G29" s="2">
         <v>10.0</v>
@@ -2364,7 +2609,7 @@
         <v>10.0</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="J29" s="2">
         <v>5</v>
@@ -2375,10 +2620,10 @@
         <v>5</v>
       </c>
       <c r="N29" s="2">
-        <v>24.08</v>
+        <v>7.48</v>
       </c>
       <c r="O29" s="2" t="s">
-        <v>127</v>
+        <v>194</v>
       </c>
       <c r="P29" s="2" t="s">
         <v>0</v>
@@ -2389,13 +2634,13 @@
         <v>26</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>126</v>
+        <v>207</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>125</v>
+        <v>206</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>124</v>
+        <v>205</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>3</v>
@@ -2410,7 +2655,7 @@
         <v>10.0</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="J30" s="2">
         <v>5</v>
@@ -2421,10 +2666,10 @@
         <v>5</v>
       </c>
       <c r="N30" s="2">
-        <v>14.05</v>
+        <v>12.57</v>
       </c>
       <c r="O30" s="2" t="s">
-        <v>123</v>
+        <v>194</v>
       </c>
       <c r="P30" s="2" t="s">
         <v>0</v>
@@ -2435,13 +2680,13 @@
         <v>27</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>122</v>
+        <v>204</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>121</v>
+        <v>203</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>120</v>
+        <v>202</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>3</v>
@@ -2450,29 +2695,27 @@
         <v>1</v>
       </c>
       <c r="G31" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H31" s="2">
         <v>10.0</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="J31" s="2">
-        <v>4</v>
-      </c>
-      <c r="K31" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K31" s="2"/>
       <c r="L31" s="2"/>
       <c r="M31" s="2">
         <v>5</v>
       </c>
       <c r="N31" s="2">
-        <v>10.78</v>
+        <v>9.22</v>
       </c>
       <c r="O31" s="2" t="s">
-        <v>119</v>
+        <v>198</v>
       </c>
       <c r="P31" s="2" t="s">
         <v>0</v>
@@ -2483,13 +2726,13 @@
         <v>28</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>118</v>
+        <v>201</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>117</v>
+        <v>200</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>116</v>
+        <v>199</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>3</v>
@@ -2498,29 +2741,27 @@
         <v>1</v>
       </c>
       <c r="G32" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H32" s="2">
         <v>10.0</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="J32" s="2">
-        <v>4</v>
-      </c>
-      <c r="K32" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K32" s="2"/>
       <c r="L32" s="2"/>
       <c r="M32" s="2">
         <v>5</v>
       </c>
       <c r="N32" s="2">
-        <v>2.48</v>
+        <v>10.92</v>
       </c>
       <c r="O32" s="2" t="s">
-        <v>115</v>
+        <v>198</v>
       </c>
       <c r="P32" s="2" t="s">
         <v>0</v>
@@ -2531,13 +2772,13 @@
         <v>29</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>114</v>
+        <v>197</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>113</v>
+        <v>196</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>112</v>
+        <v>195</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>3</v>
@@ -2565,10 +2806,10 @@
         <v>5</v>
       </c>
       <c r="N33" s="2">
-        <v>8.05</v>
+        <v>19.3</v>
       </c>
       <c r="O33" s="2" t="s">
-        <v>111</v>
+        <v>194</v>
       </c>
       <c r="P33" s="2" t="s">
         <v>0</v>
@@ -2579,13 +2820,13 @@
         <v>30</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>110</v>
+        <v>193</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>109</v>
+        <v>192</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>108</v>
+        <v>191</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>3</v>
@@ -2600,7 +2841,7 @@
         <v>10.0</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="J34" s="2">
         <v>5</v>
@@ -2611,10 +2852,10 @@
         <v>5</v>
       </c>
       <c r="N34" s="2">
-        <v>32.08</v>
+        <v>27.43</v>
       </c>
       <c r="O34" s="2" t="s">
-        <v>107</v>
+        <v>190</v>
       </c>
       <c r="P34" s="2" t="s">
         <v>0</v>
@@ -2625,13 +2866,13 @@
         <v>31</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>106</v>
+        <v>189</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>105</v>
+        <v>188</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>104</v>
+        <v>187</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>3</v>
@@ -2646,7 +2887,7 @@
         <v>10.0</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="J35" s="2">
         <v>5</v>
@@ -2657,10 +2898,10 @@
         <v>5</v>
       </c>
       <c r="N35" s="2">
-        <v>2.35</v>
+        <v>3.58</v>
       </c>
       <c r="O35" s="2" t="s">
-        <v>103</v>
+        <v>186</v>
       </c>
       <c r="P35" s="2" t="s">
         <v>0</v>
@@ -2671,13 +2912,13 @@
         <v>32</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>102</v>
+        <v>185</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>101</v>
+        <v>184</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>100</v>
+        <v>183</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>3</v>
@@ -2686,27 +2927,29 @@
         <v>1</v>
       </c>
       <c r="G36" s="2">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
       <c r="H36" s="2">
         <v>10.0</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J36" s="2">
-        <v>5</v>
-      </c>
-      <c r="K36" s="2"/>
+        <v>3</v>
+      </c>
+      <c r="K36" s="2">
+        <v>2</v>
+      </c>
       <c r="L36" s="2"/>
       <c r="M36" s="2">
         <v>5</v>
       </c>
       <c r="N36" s="2">
-        <v>299.45</v>
+        <v>14.85</v>
       </c>
       <c r="O36" s="2" t="s">
-        <v>99</v>
+        <v>182</v>
       </c>
       <c r="P36" s="2" t="s">
         <v>0</v>
@@ -2717,13 +2960,13 @@
         <v>33</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>98</v>
+        <v>181</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>97</v>
+        <v>180</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>96</v>
+        <v>179</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>3</v>
@@ -2738,7 +2981,7 @@
         <v>10.0</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="J37" s="2">
         <v>5</v>
@@ -2749,10 +2992,10 @@
         <v>5</v>
       </c>
       <c r="N37" s="2">
-        <v>9.7</v>
+        <v>5.42</v>
       </c>
       <c r="O37" s="2" t="s">
-        <v>95</v>
+        <v>178</v>
       </c>
       <c r="P37" s="2" t="s">
         <v>0</v>
@@ -2763,13 +3006,13 @@
         <v>34</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>94</v>
+        <v>177</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>93</v>
+        <v>176</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>92</v>
+        <v>175</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>3</v>
@@ -2778,32 +3021,30 @@
         <v>1</v>
       </c>
       <c r="G38" s="2">
-        <v>2.0</v>
+        <v>10.0</v>
       </c>
       <c r="H38" s="2">
         <v>10.0</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>91</v>
+        <v>17</v>
       </c>
       <c r="J38" s="2">
-        <v>1</v>
-      </c>
-      <c r="K38" s="2">
-        <v>4</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K38" s="2"/>
       <c r="L38" s="2"/>
       <c r="M38" s="2">
         <v>5</v>
       </c>
       <c r="N38" s="2">
-        <v>5.52</v>
+        <v>8.33</v>
       </c>
       <c r="O38" s="2" t="s">
-        <v>90</v>
+        <v>174</v>
       </c>
       <c r="P38" s="2" t="s">
-        <v>89</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -2811,13 +3052,13 @@
         <v>35</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>88</v>
+        <v>173</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>87</v>
+        <v>172</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>86</v>
+        <v>171</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>3</v>
@@ -2826,30 +3067,32 @@
         <v>1</v>
       </c>
       <c r="G39" s="2">
-        <v>10.0</v>
+        <v>4.0</v>
       </c>
       <c r="H39" s="2">
         <v>10.0</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>8</v>
+        <v>170</v>
       </c>
       <c r="J39" s="2">
-        <v>5</v>
-      </c>
-      <c r="K39" s="2"/>
+        <v>2</v>
+      </c>
+      <c r="K39" s="2">
+        <v>3</v>
+      </c>
       <c r="L39" s="2"/>
       <c r="M39" s="2">
         <v>5</v>
       </c>
       <c r="N39" s="2">
-        <v>26.22</v>
+        <v>1.5</v>
       </c>
       <c r="O39" s="2" t="s">
-        <v>85</v>
+        <v>169</v>
       </c>
       <c r="P39" s="2" t="s">
-        <v>0</v>
+        <v>168</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -2857,13 +3100,13 @@
         <v>36</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>84</v>
+        <v>167</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>83</v>
+        <v>166</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>82</v>
+        <v>165</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>3</v>
@@ -2872,27 +3115,29 @@
         <v>1</v>
       </c>
       <c r="G40" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H40" s="2">
         <v>10.0</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J40" s="2">
-        <v>5</v>
-      </c>
-      <c r="K40" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K40" s="2">
+        <v>1</v>
+      </c>
       <c r="L40" s="2"/>
       <c r="M40" s="2">
         <v>5</v>
       </c>
       <c r="N40" s="2">
-        <v>1.18</v>
+        <v>6.75</v>
       </c>
       <c r="O40" s="2" t="s">
-        <v>81</v>
+        <v>161</v>
       </c>
       <c r="P40" s="2" t="s">
         <v>0</v>
@@ -2903,13 +3148,13 @@
         <v>37</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>80</v>
+        <v>164</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>79</v>
+        <v>163</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>78</v>
+        <v>162</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>3</v>
@@ -2918,27 +3163,29 @@
         <v>1</v>
       </c>
       <c r="G41" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H41" s="2">
         <v>10.0</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J41" s="2">
-        <v>5</v>
-      </c>
-      <c r="K41" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K41" s="2">
+        <v>1</v>
+      </c>
       <c r="L41" s="2"/>
       <c r="M41" s="2">
         <v>5</v>
       </c>
       <c r="N41" s="2">
-        <v>26.28</v>
+        <v>8.65</v>
       </c>
       <c r="O41" s="2" t="s">
-        <v>77</v>
+        <v>161</v>
       </c>
       <c r="P41" s="2" t="s">
         <v>0</v>
@@ -2949,13 +3196,13 @@
         <v>38</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>76</v>
+        <v>160</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>75</v>
+        <v>159</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>74</v>
+        <v>158</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>3</v>
@@ -2970,7 +3217,7 @@
         <v>10.0</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="J42" s="2">
         <v>5</v>
@@ -2981,10 +3228,10 @@
         <v>5</v>
       </c>
       <c r="N42" s="2">
-        <v>11.17</v>
+        <v>10.37</v>
       </c>
       <c r="O42" s="2" t="s">
-        <v>73</v>
+        <v>157</v>
       </c>
       <c r="P42" s="2" t="s">
         <v>0</v>
@@ -2995,13 +3242,13 @@
         <v>39</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>72</v>
+        <v>156</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>71</v>
+        <v>155</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>70</v>
+        <v>154</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>3</v>
@@ -3016,7 +3263,7 @@
         <v>10.0</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="J43" s="2">
         <v>5</v>
@@ -3027,10 +3274,10 @@
         <v>5</v>
       </c>
       <c r="N43" s="2">
-        <v>10.05</v>
+        <v>7.27</v>
       </c>
       <c r="O43" s="2" t="s">
-        <v>69</v>
+        <v>153</v>
       </c>
       <c r="P43" s="2" t="s">
         <v>0</v>
@@ -3041,13 +3288,13 @@
         <v>40</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>68</v>
+        <v>152</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>67</v>
+        <v>151</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>66</v>
+        <v>150</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>3</v>
@@ -3062,7 +3309,7 @@
         <v>10.0</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="J44" s="2">
         <v>5</v>
@@ -3073,10 +3320,10 @@
         <v>5</v>
       </c>
       <c r="N44" s="2">
-        <v>1507.62</v>
+        <v>4.2</v>
       </c>
       <c r="O44" s="2" t="s">
-        <v>65</v>
+        <v>149</v>
       </c>
       <c r="P44" s="2" t="s">
         <v>0</v>
@@ -3087,13 +3334,13 @@
         <v>41</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>64</v>
+        <v>148</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>63</v>
+        <v>147</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>62</v>
+        <v>146</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>3</v>
@@ -3108,7 +3355,7 @@
         <v>10.0</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J45" s="2">
         <v>4</v>
@@ -3121,10 +3368,10 @@
         <v>5</v>
       </c>
       <c r="N45" s="2">
-        <v>6.08</v>
+        <v>25.47</v>
       </c>
       <c r="O45" s="2" t="s">
-        <v>61</v>
+        <v>145</v>
       </c>
       <c r="P45" s="2" t="s">
         <v>0</v>
@@ -3135,13 +3382,13 @@
         <v>42</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>60</v>
+        <v>144</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>59</v>
+        <v>143</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>58</v>
+        <v>142</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>3</v>
@@ -3150,27 +3397,29 @@
         <v>1</v>
       </c>
       <c r="G46" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H46" s="2">
         <v>10.0</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J46" s="2">
-        <v>5</v>
-      </c>
-      <c r="K46" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K46" s="2">
+        <v>1</v>
+      </c>
       <c r="L46" s="2"/>
       <c r="M46" s="2">
         <v>5</v>
       </c>
       <c r="N46" s="2">
-        <v>1.93</v>
+        <v>16.42</v>
       </c>
       <c r="O46" s="2" t="s">
-        <v>57</v>
+        <v>141</v>
       </c>
       <c r="P46" s="2" t="s">
         <v>0</v>
@@ -3181,13 +3430,13 @@
         <v>43</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>56</v>
+        <v>140</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>55</v>
+        <v>139</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>54</v>
+        <v>138</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>3</v>
@@ -3202,7 +3451,7 @@
         <v>10.0</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="J47" s="2">
         <v>5</v>
@@ -3213,10 +3462,10 @@
         <v>5</v>
       </c>
       <c r="N47" s="2">
-        <v>11.58</v>
+        <v>20.63</v>
       </c>
       <c r="O47" s="2" t="s">
-        <v>53</v>
+        <v>137</v>
       </c>
       <c r="P47" s="2" t="s">
         <v>0</v>
@@ -3227,13 +3476,13 @@
         <v>44</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>52</v>
+        <v>136</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>51</v>
+        <v>135</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>50</v>
+        <v>134</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>3</v>
@@ -3248,7 +3497,7 @@
         <v>10.0</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="J48" s="2">
         <v>5</v>
@@ -3259,10 +3508,10 @@
         <v>5</v>
       </c>
       <c r="N48" s="2">
-        <v>25.92</v>
+        <v>5.73</v>
       </c>
       <c r="O48" s="2" t="s">
-        <v>49</v>
+        <v>133</v>
       </c>
       <c r="P48" s="2" t="s">
         <v>0</v>
@@ -3273,13 +3522,13 @@
         <v>45</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>48</v>
+        <v>132</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>47</v>
+        <v>131</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>46</v>
+        <v>130</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>3</v>
@@ -3288,29 +3537,27 @@
         <v>1</v>
       </c>
       <c r="G49" s="2">
-        <v>6.0</v>
+        <v>10.0</v>
       </c>
       <c r="H49" s="2">
         <v>10.0</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="J49" s="2">
-        <v>3</v>
-      </c>
-      <c r="K49" s="2">
-        <v>2</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K49" s="2"/>
       <c r="L49" s="2"/>
       <c r="M49" s="2">
         <v>5</v>
       </c>
       <c r="N49" s="2">
-        <v>25.67</v>
+        <v>3.98</v>
       </c>
       <c r="O49" s="2" t="s">
-        <v>45</v>
+        <v>129</v>
       </c>
       <c r="P49" s="2" t="s">
         <v>0</v>
@@ -3321,13 +3568,13 @@
         <v>46</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>44</v>
+        <v>128</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>43</v>
+        <v>127</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>42</v>
+        <v>126</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>3</v>
@@ -3342,7 +3589,7 @@
         <v>10.0</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J50" s="2">
         <v>4</v>
@@ -3355,10 +3602,10 @@
         <v>5</v>
       </c>
       <c r="N50" s="2">
-        <v>5.32</v>
+        <v>7.77</v>
       </c>
       <c r="O50" s="2" t="s">
-        <v>41</v>
+        <v>125</v>
       </c>
       <c r="P50" s="2" t="s">
         <v>0</v>
@@ -3369,13 +3616,13 @@
         <v>47</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>40</v>
+        <v>124</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>39</v>
+        <v>123</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>38</v>
+        <v>122</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>3</v>
@@ -3390,7 +3637,7 @@
         <v>10.0</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="J51" s="2">
         <v>5</v>
@@ -3401,10 +3648,10 @@
         <v>5</v>
       </c>
       <c r="N51" s="2">
-        <v>32.9</v>
+        <v>24.08</v>
       </c>
       <c r="O51" s="2" t="s">
-        <v>37</v>
+        <v>121</v>
       </c>
       <c r="P51" s="2" t="s">
         <v>0</v>
@@ -3415,13 +3662,13 @@
         <v>48</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>36</v>
+        <v>120</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>35</v>
+        <v>119</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>34</v>
+        <v>118</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>3</v>
@@ -3436,7 +3683,7 @@
         <v>10.0</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="J52" s="2">
         <v>5</v>
@@ -3447,10 +3694,10 @@
         <v>5</v>
       </c>
       <c r="N52" s="2">
-        <v>3.77</v>
+        <v>14.05</v>
       </c>
       <c r="O52" s="2" t="s">
-        <v>33</v>
+        <v>117</v>
       </c>
       <c r="P52" s="2" t="s">
         <v>0</v>
@@ -3461,42 +3708,44 @@
         <v>49</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>32</v>
+        <v>116</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>31</v>
+        <v>115</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>30</v>
+        <v>114</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F53" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G53" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H53" s="2">
         <v>10.0</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J53" s="2">
-        <v>5</v>
-      </c>
-      <c r="K53" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K53" s="2">
+        <v>1</v>
+      </c>
       <c r="L53" s="2"/>
       <c r="M53" s="2">
         <v>5</v>
       </c>
       <c r="N53" s="2">
-        <v>1.65</v>
+        <v>10.78</v>
       </c>
       <c r="O53" s="2" t="s">
-        <v>29</v>
+        <v>113</v>
       </c>
       <c r="P53" s="2" t="s">
         <v>0</v>
@@ -3507,19 +3756,19 @@
         <v>50</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>28</v>
+        <v>112</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>27</v>
+        <v>111</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>26</v>
+        <v>110</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F54" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G54" s="2">
         <v>8.0</v>
@@ -3528,7 +3777,7 @@
         <v>10.0</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J54" s="2">
         <v>4</v>
@@ -3541,10 +3790,10 @@
         <v>5</v>
       </c>
       <c r="N54" s="2">
-        <v>4.22</v>
+        <v>2.48</v>
       </c>
       <c r="O54" s="2" t="s">
-        <v>25</v>
+        <v>109</v>
       </c>
       <c r="P54" s="2" t="s">
         <v>0</v>
@@ -3555,13 +3804,13 @@
         <v>51</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>24</v>
+        <v>108</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>23</v>
+        <v>107</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>22</v>
+        <v>106</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>3</v>
@@ -3589,10 +3838,10 @@
         <v>5</v>
       </c>
       <c r="N55" s="2">
-        <v>23.22</v>
+        <v>8.05</v>
       </c>
       <c r="O55" s="2" t="s">
-        <v>21</v>
+        <v>105</v>
       </c>
       <c r="P55" s="2" t="s">
         <v>0</v>
@@ -3603,13 +3852,13 @@
         <v>52</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>20</v>
+        <v>104</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>19</v>
+        <v>103</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>18</v>
+        <v>102</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>3</v>
@@ -3624,7 +3873,7 @@
         <v>10.0</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="J56" s="2">
         <v>5</v>
@@ -3635,10 +3884,10 @@
         <v>5</v>
       </c>
       <c r="N56" s="2">
-        <v>14.3</v>
+        <v>32.08</v>
       </c>
       <c r="O56" s="2" t="s">
-        <v>17</v>
+        <v>101</v>
       </c>
       <c r="P56" s="2" t="s">
         <v>0</v>
@@ -3649,13 +3898,13 @@
         <v>53</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>16</v>
+        <v>100</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>15</v>
+        <v>99</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>14</v>
+        <v>98</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>3</v>
@@ -3664,29 +3913,27 @@
         <v>1</v>
       </c>
       <c r="G57" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H57" s="2">
         <v>10.0</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="J57" s="2">
-        <v>4</v>
-      </c>
-      <c r="K57" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K57" s="2"/>
       <c r="L57" s="2"/>
       <c r="M57" s="2">
         <v>5</v>
       </c>
       <c r="N57" s="2">
-        <v>13.45</v>
+        <v>2.35</v>
       </c>
       <c r="O57" s="2" t="s">
-        <v>12</v>
+        <v>97</v>
       </c>
       <c r="P57" s="2" t="s">
         <v>0</v>
@@ -3697,13 +3944,13 @@
         <v>54</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>11</v>
+        <v>96</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>10</v>
+        <v>95</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>9</v>
+        <v>94</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>3</v>
@@ -3718,7 +3965,7 @@
         <v>10.0</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="J58" s="2">
         <v>5</v>
@@ -3729,10 +3976,10 @@
         <v>5</v>
       </c>
       <c r="N58" s="2">
-        <v>5.65</v>
+        <v>299.45</v>
       </c>
       <c r="O58" s="2" t="s">
-        <v>7</v>
+        <v>93</v>
       </c>
       <c r="P58" s="2" t="s">
         <v>0</v>
@@ -3743,13 +3990,13 @@
         <v>55</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>6</v>
+        <v>92</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>5</v>
+        <v>91</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>4</v>
+        <v>90</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>3</v>
@@ -3758,31 +4005,1011 @@
         <v>1</v>
       </c>
       <c r="G59" s="2">
-        <v>6.0</v>
+        <v>10.0</v>
       </c>
       <c r="H59" s="2">
         <v>10.0</v>
       </c>
       <c r="I59" s="2" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="J59" s="2">
-        <v>3</v>
-      </c>
-      <c r="K59" s="2">
-        <v>2</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K59" s="2"/>
       <c r="L59" s="2"/>
       <c r="M59" s="2">
         <v>5</v>
       </c>
       <c r="N59" s="2">
+        <v>9.7</v>
+      </c>
+      <c r="O59" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="P59" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:16">
+      <c r="A60" s="2">
+        <v>56</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F60" s="2">
+        <v>1</v>
+      </c>
+      <c r="G60" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="H60" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I60" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J60" s="2">
+        <v>5</v>
+      </c>
+      <c r="K60" s="2"/>
+      <c r="L60" s="2"/>
+      <c r="M60" s="2">
+        <v>5</v>
+      </c>
+      <c r="N60" s="2">
+        <v>26.22</v>
+      </c>
+      <c r="O60" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="P60" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:16">
+      <c r="A61" s="2">
+        <v>57</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F61" s="2">
+        <v>1</v>
+      </c>
+      <c r="G61" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="H61" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I61" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J61" s="2">
+        <v>5</v>
+      </c>
+      <c r="K61" s="2"/>
+      <c r="L61" s="2"/>
+      <c r="M61" s="2">
+        <v>5</v>
+      </c>
+      <c r="N61" s="2">
+        <v>1.18</v>
+      </c>
+      <c r="O61" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="P61" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:16">
+      <c r="A62" s="2">
+        <v>58</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F62" s="2">
+        <v>1</v>
+      </c>
+      <c r="G62" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="H62" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I62" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J62" s="2">
+        <v>5</v>
+      </c>
+      <c r="K62" s="2"/>
+      <c r="L62" s="2"/>
+      <c r="M62" s="2">
+        <v>5</v>
+      </c>
+      <c r="N62" s="2">
+        <v>26.28</v>
+      </c>
+      <c r="O62" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="P62" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:16">
+      <c r="A63" s="2">
+        <v>59</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F63" s="2">
+        <v>1</v>
+      </c>
+      <c r="G63" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="H63" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I63" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J63" s="2">
+        <v>5</v>
+      </c>
+      <c r="K63" s="2"/>
+      <c r="L63" s="2"/>
+      <c r="M63" s="2">
+        <v>5</v>
+      </c>
+      <c r="N63" s="2">
+        <v>11.17</v>
+      </c>
+      <c r="O63" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="P63" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:16">
+      <c r="A64" s="2">
+        <v>60</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F64" s="2">
+        <v>1</v>
+      </c>
+      <c r="G64" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="H64" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I64" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J64" s="2">
+        <v>5</v>
+      </c>
+      <c r="K64" s="2"/>
+      <c r="L64" s="2"/>
+      <c r="M64" s="2">
+        <v>5</v>
+      </c>
+      <c r="N64" s="2">
+        <v>10.05</v>
+      </c>
+      <c r="O64" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="P64" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:16">
+      <c r="A65" s="2">
+        <v>61</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F65" s="2">
+        <v>1</v>
+      </c>
+      <c r="G65" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="H65" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I65" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J65" s="2">
+        <v>5</v>
+      </c>
+      <c r="K65" s="2"/>
+      <c r="L65" s="2"/>
+      <c r="M65" s="2">
+        <v>5</v>
+      </c>
+      <c r="N65" s="2">
+        <v>1507.62</v>
+      </c>
+      <c r="O65" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="P65" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:16">
+      <c r="A66" s="2">
+        <v>62</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F66" s="2">
+        <v>1</v>
+      </c>
+      <c r="G66" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="H66" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I66" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="J66" s="2">
+        <v>4</v>
+      </c>
+      <c r="K66" s="2">
+        <v>1</v>
+      </c>
+      <c r="L66" s="2"/>
+      <c r="M66" s="2">
+        <v>5</v>
+      </c>
+      <c r="N66" s="2">
+        <v>6.08</v>
+      </c>
+      <c r="O66" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="P66" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:16">
+      <c r="A67" s="2">
+        <v>63</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F67" s="2">
+        <v>1</v>
+      </c>
+      <c r="G67" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="H67" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I67" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J67" s="2">
+        <v>5</v>
+      </c>
+      <c r="K67" s="2"/>
+      <c r="L67" s="2"/>
+      <c r="M67" s="2">
+        <v>5</v>
+      </c>
+      <c r="N67" s="2">
+        <v>1.93</v>
+      </c>
+      <c r="O67" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="P67" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:16">
+      <c r="A68" s="2">
+        <v>64</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F68" s="2">
+        <v>1</v>
+      </c>
+      <c r="G68" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="H68" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I68" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J68" s="2">
+        <v>5</v>
+      </c>
+      <c r="K68" s="2"/>
+      <c r="L68" s="2"/>
+      <c r="M68" s="2">
+        <v>5</v>
+      </c>
+      <c r="N68" s="2">
+        <v>11.58</v>
+      </c>
+      <c r="O68" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="P68" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:16">
+      <c r="A69" s="2">
+        <v>65</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F69" s="2">
+        <v>1</v>
+      </c>
+      <c r="G69" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="H69" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I69" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J69" s="2">
+        <v>5</v>
+      </c>
+      <c r="K69" s="2"/>
+      <c r="L69" s="2"/>
+      <c r="M69" s="2">
+        <v>5</v>
+      </c>
+      <c r="N69" s="2">
+        <v>25.92</v>
+      </c>
+      <c r="O69" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="P69" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:16">
+      <c r="A70" s="2">
+        <v>66</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F70" s="2">
+        <v>1</v>
+      </c>
+      <c r="G70" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="H70" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I70" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J70" s="2">
+        <v>3</v>
+      </c>
+      <c r="K70" s="2">
+        <v>2</v>
+      </c>
+      <c r="L70" s="2"/>
+      <c r="M70" s="2">
+        <v>5</v>
+      </c>
+      <c r="N70" s="2">
+        <v>25.67</v>
+      </c>
+      <c r="O70" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="P70" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:16">
+      <c r="A71" s="2">
+        <v>67</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F71" s="2">
+        <v>1</v>
+      </c>
+      <c r="G71" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="H71" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I71" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="J71" s="2">
+        <v>4</v>
+      </c>
+      <c r="K71" s="2">
+        <v>1</v>
+      </c>
+      <c r="L71" s="2"/>
+      <c r="M71" s="2">
+        <v>5</v>
+      </c>
+      <c r="N71" s="2">
         <v>5.32</v>
       </c>
-      <c r="O59" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="P59" s="2" t="s">
+      <c r="O71" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="P71" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:16">
+      <c r="A72" s="2">
+        <v>68</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F72" s="2">
+        <v>1</v>
+      </c>
+      <c r="G72" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="H72" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I72" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J72" s="2">
+        <v>5</v>
+      </c>
+      <c r="K72" s="2"/>
+      <c r="L72" s="2"/>
+      <c r="M72" s="2">
+        <v>5</v>
+      </c>
+      <c r="N72" s="2">
+        <v>32.9</v>
+      </c>
+      <c r="O72" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="P72" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:16">
+      <c r="A73" s="2">
+        <v>69</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F73" s="2">
+        <v>1</v>
+      </c>
+      <c r="G73" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="H73" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I73" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J73" s="2">
+        <v>5</v>
+      </c>
+      <c r="K73" s="2"/>
+      <c r="L73" s="2"/>
+      <c r="M73" s="2">
+        <v>5</v>
+      </c>
+      <c r="N73" s="2">
+        <v>3.77</v>
+      </c>
+      <c r="O73" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P73" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:16">
+      <c r="A74" s="2">
+        <v>70</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F74" s="2">
+        <v>2</v>
+      </c>
+      <c r="G74" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="H74" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I74" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J74" s="2">
+        <v>5</v>
+      </c>
+      <c r="K74" s="2"/>
+      <c r="L74" s="2"/>
+      <c r="M74" s="2">
+        <v>5</v>
+      </c>
+      <c r="N74" s="2">
+        <v>1.65</v>
+      </c>
+      <c r="O74" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="P74" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:16">
+      <c r="A75" s="2">
+        <v>71</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F75" s="2">
+        <v>2</v>
+      </c>
+      <c r="G75" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="H75" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I75" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="J75" s="2">
+        <v>4</v>
+      </c>
+      <c r="K75" s="2">
+        <v>1</v>
+      </c>
+      <c r="L75" s="2"/>
+      <c r="M75" s="2">
+        <v>5</v>
+      </c>
+      <c r="N75" s="2">
+        <v>4.22</v>
+      </c>
+      <c r="O75" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P75" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:16">
+      <c r="A76" s="2">
+        <v>72</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F76" s="2">
+        <v>1</v>
+      </c>
+      <c r="G76" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="H76" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I76" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J76" s="2">
+        <v>3</v>
+      </c>
+      <c r="K76" s="2">
+        <v>2</v>
+      </c>
+      <c r="L76" s="2"/>
+      <c r="M76" s="2">
+        <v>5</v>
+      </c>
+      <c r="N76" s="2">
+        <v>23.22</v>
+      </c>
+      <c r="O76" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="P76" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:16">
+      <c r="A77" s="2">
+        <v>73</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F77" s="2">
+        <v>1</v>
+      </c>
+      <c r="G77" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="H77" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I77" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J77" s="2">
+        <v>5</v>
+      </c>
+      <c r="K77" s="2"/>
+      <c r="L77" s="2"/>
+      <c r="M77" s="2">
+        <v>5</v>
+      </c>
+      <c r="N77" s="2">
+        <v>14.3</v>
+      </c>
+      <c r="O77" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="P77" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:16">
+      <c r="A78" s="2">
+        <v>74</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E78" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F78" s="2">
+        <v>1</v>
+      </c>
+      <c r="G78" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="H78" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I78" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="J78" s="2">
+        <v>4</v>
+      </c>
+      <c r="K78" s="2">
+        <v>1</v>
+      </c>
+      <c r="L78" s="2"/>
+      <c r="M78" s="2">
+        <v>5</v>
+      </c>
+      <c r="N78" s="2">
+        <v>13.45</v>
+      </c>
+      <c r="O78" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="P78" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:16">
+      <c r="A79" s="2">
+        <v>75</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E79" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F79" s="2">
+        <v>2</v>
+      </c>
+      <c r="G79" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="H79" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I79" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J79" s="2">
+        <v>3</v>
+      </c>
+      <c r="K79" s="2">
+        <v>2</v>
+      </c>
+      <c r="L79" s="2"/>
+      <c r="M79" s="2">
+        <v>5</v>
+      </c>
+      <c r="N79" s="2">
+        <v>9179.12</v>
+      </c>
+      <c r="O79" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="P79" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:16">
+      <c r="A80" s="2">
+        <v>76</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F80" s="2">
+        <v>1</v>
+      </c>
+      <c r="G80" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="H80" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I80" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J80" s="2">
+        <v>3</v>
+      </c>
+      <c r="K80" s="2">
+        <v>2</v>
+      </c>
+      <c r="L80" s="2"/>
+      <c r="M80" s="2">
+        <v>5</v>
+      </c>
+      <c r="N80" s="2">
+        <v>5.32</v>
+      </c>
+      <c r="O80" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="P80" s="2" t="s">
         <v>0</v>
       </c>
     </row>

--- a/2lit_center.xlsx
+++ b/2lit_center.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="323">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="344">
   <si>
     <t>ناجح ✓</t>
   </si>
@@ -824,7 +824,136 @@
     <t>omar zakaa</t>
   </si>
   <si>
-    <t>2026-03-16 16:43</t>
+    <t>2026-03-16 17:23</t>
+  </si>
+  <si>
+    <t>01017803931</t>
+  </si>
+  <si>
+    <t>kokymzykm2007@gmail.com</t>
+  </si>
+  <si>
+    <t>Kenzy Mohamed</t>
+  </si>
+  <si>
+    <t>2026-03-16 17:52</t>
+  </si>
+  <si>
+    <t>01154109786</t>
+  </si>
+  <si>
+    <t>nadaaseleem@gmail.com</t>
+  </si>
+  <si>
+    <t>Nada Ahmed Seleem</t>
+  </si>
+  <si>
+    <t>2026-03-16 17:42</t>
+  </si>
+  <si>
+    <t>01017099170</t>
+  </si>
+  <si>
+    <t>joudhanynabil@gmail.com</t>
+  </si>
+  <si>
+    <t>joudy</t>
+  </si>
+  <si>
+    <t>01555066805</t>
+  </si>
+  <si>
+    <t>mohammed.el.shazly2009@gmail.com</t>
+  </si>
+  <si>
+    <t>محمد أسامة محمد الشاذلي</t>
+  </si>
+  <si>
+    <t>2026-03-16 18:48</t>
+  </si>
+  <si>
+    <t>01099284562</t>
+  </si>
+  <si>
+    <t>samehsami9@gmail.com</t>
+  </si>
+  <si>
+    <t>Mariam sameh sami</t>
+  </si>
+  <si>
+    <t>2026-03-16 19:14</t>
+  </si>
+  <si>
+    <t>01121970064</t>
+  </si>
+  <si>
+    <t>Ahmedmakg7@gmail.com</t>
+  </si>
+  <si>
+    <t>احمد محمد احمد كامل</t>
+  </si>
+  <si>
+    <t>2026-03-16 19:12</t>
+  </si>
+  <si>
+    <t>01554037795</t>
+  </si>
+  <si>
+    <t>saharrefee@gmail.com</t>
+  </si>
+  <si>
+    <t>سهر محمد ابراهيم الرفاعي</t>
+  </si>
+  <si>
+    <t>2026-03-16 19:19</t>
+  </si>
+  <si>
+    <t>01064753790</t>
+  </si>
+  <si>
+    <t>Abdullazizosama18@gmail.com</t>
+  </si>
+  <si>
+    <t>Abdullaziz</t>
+  </si>
+  <si>
+    <t>2026-03-16 19:37</t>
+  </si>
+  <si>
+    <t>01094609026</t>
+  </si>
+  <si>
+    <t>sandyalylabib560@gmail.com</t>
+  </si>
+  <si>
+    <t>Sandy aly abdelmohsen</t>
+  </si>
+  <si>
+    <t>2026-03-18 13:14</t>
+  </si>
+  <si>
+    <t>0.0%</t>
+  </si>
+  <si>
+    <t>janafrahat@icloud.com</t>
+  </si>
+  <si>
+    <t>Jana Ahmed frahat</t>
+  </si>
+  <si>
+    <t>2026-03-25 07:58</t>
+  </si>
+  <si>
+    <t>01094303365</t>
+  </si>
+  <si>
+    <t>Yomnamelhabrouk@gmail.com</t>
+  </si>
+  <si>
+    <t>Yomna</t>
+  </si>
+  <si>
+    <t>2026-03-27 03:01</t>
   </si>
   <si>
     <t>01103622316</t>
@@ -836,97 +965,31 @@
     <t>Esraa saad</t>
   </si>
   <si>
-    <t>2026-03-16 17:23</t>
-  </si>
-  <si>
-    <t>01017803931</t>
-  </si>
-  <si>
-    <t>kokymzykm2007@gmail.com</t>
-  </si>
-  <si>
-    <t>Kenzy Mohamed</t>
-  </si>
-  <si>
-    <t>2026-03-16 17:52</t>
-  </si>
-  <si>
-    <t>01154109786</t>
-  </si>
-  <si>
-    <t>nadaaseleem@gmail.com</t>
-  </si>
-  <si>
-    <t>Nada Ahmed Seleem</t>
-  </si>
-  <si>
-    <t>2026-03-16 17:42</t>
-  </si>
-  <si>
-    <t>01017099170</t>
-  </si>
-  <si>
-    <t>joudhanynabil@gmail.com</t>
-  </si>
-  <si>
-    <t>joudy</t>
-  </si>
-  <si>
-    <t>01555066805</t>
-  </si>
-  <si>
-    <t>mohammed.el.shazly2009@gmail.com</t>
-  </si>
-  <si>
-    <t>محمد أسامة محمد الشاذلي</t>
-  </si>
-  <si>
-    <t>2026-03-16 18:48</t>
-  </si>
-  <si>
-    <t>01099284562</t>
-  </si>
-  <si>
-    <t>samehsami9@gmail.com</t>
-  </si>
-  <si>
-    <t>Mariam sameh sami</t>
-  </si>
-  <si>
-    <t>2026-03-16 19:14</t>
-  </si>
-  <si>
-    <t>01121970064</t>
-  </si>
-  <si>
-    <t>Ahmedmakg7@gmail.com</t>
-  </si>
-  <si>
-    <t>احمد محمد احمد كامل</t>
-  </si>
-  <si>
-    <t>2026-03-16 19:12</t>
-  </si>
-  <si>
-    <t>01554037795</t>
-  </si>
-  <si>
-    <t>saharrefee@gmail.com</t>
-  </si>
-  <si>
-    <t>سهر محمد ابراهيم الرفاعي</t>
-  </si>
-  <si>
-    <t>2026-03-16 19:19</t>
-  </si>
-  <si>
-    <t>01064753790</t>
-  </si>
-  <si>
-    <t>Abdullazizosama18@gmail.com</t>
-  </si>
-  <si>
-    <t>Abdullaziz</t>
+    <t>2026-03-29 03:22</t>
+  </si>
+  <si>
+    <t>20.0%</t>
+  </si>
+  <si>
+    <t>01020123791</t>
+  </si>
+  <si>
+    <t>salmatareksoo17@gmail.com</t>
+  </si>
+  <si>
+    <t>Salma</t>
+  </si>
+  <si>
+    <t>2026-03-29 13:13</t>
+  </si>
+  <si>
+    <t>01501181314</t>
+  </si>
+  <si>
+    <t>bebonasser399@gamil.com</t>
+  </si>
+  <si>
+    <t>Habiba Nasser Ahmed</t>
   </si>
   <si>
     <t>الحالة</t>
@@ -983,7 +1046,7 @@
     <t>الدرجة الكاملة: 10 | درجة النجاح: 5.00</t>
   </si>
   <si>
-    <t>تاريخ التصدير: 2026-03-16 19:30</t>
+    <t>تاريخ التصدير: 2026-03-29 16:33</t>
   </si>
 </sst>
 </file>
@@ -1371,7 +1434,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:P80"/>
+  <dimension ref="A1:P85"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="true" style="0"/>
@@ -1394,67 +1457,67 @@
   <sheetData>
     <row r="1" spans="1:16">
       <c r="A1" s="3" t="s">
-        <v>320</v>
+        <v>341</v>
       </c>
     </row>
     <row r="2" spans="1:16">
       <c r="A2" s="3" t="s">
-        <v>321</v>
+        <v>342</v>
       </c>
     </row>
     <row r="3" spans="1:16">
       <c r="A3" s="3" t="s">
-        <v>322</v>
+        <v>343</v>
       </c>
     </row>
     <row r="4" spans="1:16">
       <c r="A4" s="1" t="s">
-        <v>319</v>
+        <v>340</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>318</v>
+        <v>339</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>317</v>
+        <v>338</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>316</v>
+        <v>337</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>315</v>
+        <v>336</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>314</v>
+        <v>335</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>313</v>
+        <v>334</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>312</v>
+        <v>333</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>311</v>
+        <v>332</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>310</v>
+        <v>331</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>309</v>
+        <v>330</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>308</v>
+        <v>329</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>307</v>
+        <v>328</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>306</v>
+        <v>327</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>305</v>
+        <v>326</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>304</v>
+        <v>325</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1462,13 +1525,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>303</v>
+        <v>324</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>302</v>
+        <v>323</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>301</v>
+        <v>322</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>3</v>
@@ -1477,29 +1540,27 @@
         <v>1</v>
       </c>
       <c r="G5" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H5" s="2">
         <v>10.0</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="J5" s="2">
-        <v>4</v>
-      </c>
-      <c r="K5" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K5" s="2"/>
       <c r="L5" s="2"/>
       <c r="M5" s="2">
         <v>5</v>
       </c>
       <c r="N5" s="2">
-        <v>20.53</v>
+        <v>2.95</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>300</v>
+        <v>321</v>
       </c>
       <c r="P5" s="2" t="s">
         <v>0</v>
@@ -1510,13 +1571,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>299</v>
+        <v>320</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>298</v>
+        <v>319</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>297</v>
+        <v>318</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>3</v>
@@ -1525,32 +1586,32 @@
         <v>1</v>
       </c>
       <c r="G6" s="2">
-        <v>8.0</v>
+        <v>2.0</v>
       </c>
       <c r="H6" s="2">
         <v>10.0</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>12</v>
+        <v>317</v>
       </c>
       <c r="J6" s="2">
+        <v>1</v>
+      </c>
+      <c r="K6" s="2">
         <v>4</v>
-      </c>
-      <c r="K6" s="2">
-        <v>1</v>
       </c>
       <c r="L6" s="2"/>
       <c r="M6" s="2">
         <v>5</v>
       </c>
       <c r="N6" s="2">
-        <v>14.28</v>
+        <v>0.58</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>296</v>
+        <v>316</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>0</v>
+        <v>168</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -1558,42 +1619,44 @@
         <v>3</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>295</v>
+        <v>315</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>294</v>
+        <v>314</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>293</v>
+        <v>313</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F7" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G7" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H7" s="2">
         <v>10.0</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="J7" s="2">
-        <v>5</v>
-      </c>
-      <c r="K7" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K7" s="2">
+        <v>1</v>
+      </c>
       <c r="L7" s="2"/>
       <c r="M7" s="2">
         <v>5</v>
       </c>
       <c r="N7" s="2">
-        <v>21.38</v>
+        <v>3.03</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>292</v>
+        <v>312</v>
       </c>
       <c r="P7" s="2" t="s">
         <v>0</v>
@@ -1604,13 +1667,13 @@
         <v>4</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>291</v>
+        <v>311</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>290</v>
+        <v>310</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>289</v>
+        <v>309</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>3</v>
@@ -1636,10 +1699,10 @@
         <v>5</v>
       </c>
       <c r="N8" s="2">
-        <v>27.77</v>
+        <v>10.22</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>288</v>
+        <v>308</v>
       </c>
       <c r="P8" s="2" t="s">
         <v>0</v>
@@ -1650,13 +1713,13 @@
         <v>5</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>287</v>
+        <v>307</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>285</v>
+        <v>306</v>
+      </c>
+      <c r="D9" s="2">
+        <v>1159792350</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>3</v>
@@ -1665,30 +1728,30 @@
         <v>1</v>
       </c>
       <c r="G9" s="2">
-        <v>10.0</v>
+        <v>0.0</v>
       </c>
       <c r="H9" s="2">
         <v>10.0</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J9" s="2">
-        <v>5</v>
-      </c>
-      <c r="K9" s="2"/>
+        <v>305</v>
+      </c>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2">
+        <v>5</v>
+      </c>
       <c r="L9" s="2"/>
       <c r="M9" s="2">
         <v>5</v>
       </c>
       <c r="N9" s="2">
-        <v>15.2</v>
+        <v>1.63</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>277</v>
+        <v>304</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>0</v>
+        <v>168</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -1696,13 +1759,13 @@
         <v>6</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>284</v>
+        <v>303</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>283</v>
+        <v>302</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>282</v>
+        <v>301</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>3</v>
@@ -1728,10 +1791,10 @@
         <v>5</v>
       </c>
       <c r="N10" s="2">
-        <v>8.4</v>
+        <v>1.92</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>281</v>
+        <v>300</v>
       </c>
       <c r="P10" s="2" t="s">
         <v>0</v>
@@ -1742,13 +1805,13 @@
         <v>7</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>280</v>
+        <v>299</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>279</v>
+        <v>298</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>278</v>
+        <v>297</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>3</v>
@@ -1757,27 +1820,29 @@
         <v>1</v>
       </c>
       <c r="G11" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H11" s="2">
         <v>10.0</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="J11" s="2">
-        <v>5</v>
-      </c>
-      <c r="K11" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K11" s="2">
+        <v>1</v>
+      </c>
       <c r="L11" s="2"/>
       <c r="M11" s="2">
         <v>5</v>
       </c>
       <c r="N11" s="2">
-        <v>29.9</v>
+        <v>20.53</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>277</v>
+        <v>296</v>
       </c>
       <c r="P11" s="2" t="s">
         <v>0</v>
@@ -1788,13 +1853,13 @@
         <v>8</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>276</v>
+        <v>295</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>275</v>
+        <v>294</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>274</v>
+        <v>293</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>3</v>
@@ -1803,27 +1868,29 @@
         <v>1</v>
       </c>
       <c r="G12" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H12" s="2">
         <v>10.0</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="J12" s="2">
-        <v>5</v>
-      </c>
-      <c r="K12" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K12" s="2">
+        <v>1</v>
+      </c>
       <c r="L12" s="2"/>
       <c r="M12" s="2">
         <v>5</v>
       </c>
       <c r="N12" s="2">
-        <v>8.73</v>
+        <v>14.28</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>273</v>
+        <v>292</v>
       </c>
       <c r="P12" s="2" t="s">
         <v>0</v>
@@ -1834,13 +1901,13 @@
         <v>9</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>272</v>
+        <v>291</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>271</v>
+        <v>290</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>270</v>
+        <v>289</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>3</v>
@@ -1866,10 +1933,10 @@
         <v>5</v>
       </c>
       <c r="N13" s="2">
-        <v>8.18</v>
+        <v>21.38</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>269</v>
+        <v>288</v>
       </c>
       <c r="P13" s="2" t="s">
         <v>0</v>
@@ -1880,13 +1947,13 @@
         <v>10</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>268</v>
+        <v>287</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>267</v>
+        <v>286</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>266</v>
+        <v>285</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>3</v>
@@ -1912,10 +1979,10 @@
         <v>5</v>
       </c>
       <c r="N14" s="2">
-        <v>2.92</v>
+        <v>27.77</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>265</v>
+        <v>284</v>
       </c>
       <c r="P14" s="2" t="s">
         <v>0</v>
@@ -1926,13 +1993,13 @@
         <v>11</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>264</v>
+        <v>283</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>263</v>
+        <v>282</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>262</v>
+        <v>281</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>3</v>
@@ -1941,29 +2008,27 @@
         <v>1</v>
       </c>
       <c r="G15" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H15" s="2">
         <v>10.0</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="J15" s="2">
-        <v>4</v>
-      </c>
-      <c r="K15" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K15" s="2"/>
       <c r="L15" s="2"/>
       <c r="M15" s="2">
         <v>5</v>
       </c>
       <c r="N15" s="2">
-        <v>21.08</v>
+        <v>15.2</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="P15" s="2" t="s">
         <v>0</v>
@@ -1974,44 +2039,42 @@
         <v>12</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>260</v>
+        <v>280</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>259</v>
+        <v>279</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>258</v>
+        <v>278</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F16" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G16" s="2">
-        <v>6.0</v>
+        <v>10.0</v>
       </c>
       <c r="H16" s="2">
         <v>10.0</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="J16" s="2">
-        <v>3</v>
-      </c>
-      <c r="K16" s="2">
-        <v>2</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K16" s="2"/>
       <c r="L16" s="2"/>
       <c r="M16" s="2">
         <v>5</v>
       </c>
       <c r="N16" s="2">
-        <v>17.15</v>
+        <v>8.4</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>257</v>
+        <v>277</v>
       </c>
       <c r="P16" s="2" t="s">
         <v>0</v>
@@ -2022,13 +2085,13 @@
         <v>13</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>256</v>
+        <v>276</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>255</v>
+        <v>275</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>254</v>
+        <v>274</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>3</v>
@@ -2054,10 +2117,10 @@
         <v>5</v>
       </c>
       <c r="N17" s="2">
-        <v>7.7</v>
+        <v>29.9</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>253</v>
+        <v>273</v>
       </c>
       <c r="P17" s="2" t="s">
         <v>0</v>
@@ -2068,13 +2131,13 @@
         <v>14</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>252</v>
+        <v>272</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>251</v>
+        <v>271</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>250</v>
+        <v>270</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>3</v>
@@ -2100,10 +2163,10 @@
         <v>5</v>
       </c>
       <c r="N18" s="2">
-        <v>21.45</v>
+        <v>8.73</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>249</v>
+        <v>269</v>
       </c>
       <c r="P18" s="2" t="s">
         <v>0</v>
@@ -2114,13 +2177,13 @@
         <v>15</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>248</v>
+        <v>268</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>247</v>
+        <v>267</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>246</v>
+        <v>266</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>3</v>
@@ -2146,10 +2209,10 @@
         <v>5</v>
       </c>
       <c r="N19" s="2">
-        <v>23.68</v>
+        <v>2.92</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>245</v>
+        <v>265</v>
       </c>
       <c r="P19" s="2" t="s">
         <v>0</v>
@@ -2160,13 +2223,13 @@
         <v>16</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>244</v>
+        <v>264</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>243</v>
+        <v>263</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>242</v>
+        <v>262</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>3</v>
@@ -2175,29 +2238,29 @@
         <v>1</v>
       </c>
       <c r="G20" s="2">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="H20" s="2">
         <v>10.0</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="J20" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K20" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L20" s="2"/>
       <c r="M20" s="2">
         <v>5</v>
       </c>
       <c r="N20" s="2">
-        <v>7.7</v>
+        <v>21.08</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>241</v>
+        <v>261</v>
       </c>
       <c r="P20" s="2" t="s">
         <v>0</v>
@@ -2208,42 +2271,44 @@
         <v>17</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>240</v>
+        <v>260</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>239</v>
+        <v>259</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>238</v>
+        <v>258</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F21" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G21" s="2">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
       <c r="H21" s="2">
         <v>10.0</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="J21" s="2">
-        <v>5</v>
-      </c>
-      <c r="K21" s="2"/>
+        <v>3</v>
+      </c>
+      <c r="K21" s="2">
+        <v>2</v>
+      </c>
       <c r="L21" s="2"/>
       <c r="M21" s="2">
         <v>5</v>
       </c>
       <c r="N21" s="2">
-        <v>18.78</v>
+        <v>17.15</v>
       </c>
       <c r="O21" s="2" t="s">
-        <v>237</v>
+        <v>257</v>
       </c>
       <c r="P21" s="2" t="s">
         <v>0</v>
@@ -2254,13 +2319,13 @@
         <v>18</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>236</v>
+        <v>256</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>235</v>
+        <v>255</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>234</v>
+        <v>254</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>3</v>
@@ -2269,29 +2334,27 @@
         <v>1</v>
       </c>
       <c r="G22" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H22" s="2">
         <v>10.0</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="J22" s="2">
-        <v>4</v>
-      </c>
-      <c r="K22" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K22" s="2"/>
       <c r="L22" s="2"/>
       <c r="M22" s="2">
         <v>5</v>
       </c>
       <c r="N22" s="2">
-        <v>4.37</v>
+        <v>7.7</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>233</v>
+        <v>253</v>
       </c>
       <c r="P22" s="2" t="s">
         <v>0</v>
@@ -2302,44 +2365,42 @@
         <v>19</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>232</v>
+        <v>252</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>231</v>
+        <v>251</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>230</v>
+        <v>250</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F23" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G23" s="2">
-        <v>6.0</v>
+        <v>10.0</v>
       </c>
       <c r="H23" s="2">
         <v>10.0</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="J23" s="2">
-        <v>3</v>
-      </c>
-      <c r="K23" s="2">
-        <v>2</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K23" s="2"/>
       <c r="L23" s="2"/>
       <c r="M23" s="2">
         <v>5</v>
       </c>
       <c r="N23" s="2">
-        <v>0.48</v>
+        <v>21.45</v>
       </c>
       <c r="O23" s="2" t="s">
-        <v>229</v>
+        <v>249</v>
       </c>
       <c r="P23" s="2" t="s">
         <v>0</v>
@@ -2350,44 +2411,42 @@
         <v>20</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>228</v>
+        <v>248</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>227</v>
+        <v>247</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>226</v>
+        <v>246</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F24" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G24" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H24" s="2">
         <v>10.0</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="J24" s="2">
-        <v>4</v>
-      </c>
-      <c r="K24" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K24" s="2"/>
       <c r="L24" s="2"/>
       <c r="M24" s="2">
         <v>5</v>
       </c>
       <c r="N24" s="2">
-        <v>1.7</v>
+        <v>23.68</v>
       </c>
       <c r="O24" s="2" t="s">
-        <v>225</v>
+        <v>245</v>
       </c>
       <c r="P24" s="2" t="s">
         <v>0</v>
@@ -2398,13 +2457,13 @@
         <v>21</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>224</v>
+        <v>244</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="D25" s="2">
-        <v>201118200153</v>
+        <v>243</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>242</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>3</v>
@@ -2413,29 +2472,29 @@
         <v>1</v>
       </c>
       <c r="G25" s="2">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
       <c r="H25" s="2">
         <v>10.0</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="J25" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K25" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L25" s="2"/>
       <c r="M25" s="2">
         <v>5</v>
       </c>
       <c r="N25" s="2">
-        <v>2.15</v>
+        <v>7.7</v>
       </c>
       <c r="O25" s="2" t="s">
-        <v>222</v>
+        <v>241</v>
       </c>
       <c r="P25" s="2" t="s">
         <v>0</v>
@@ -2446,13 +2505,13 @@
         <v>22</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>221</v>
+        <v>240</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>220</v>
+        <v>239</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>219</v>
+        <v>238</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>3</v>
@@ -2478,10 +2537,10 @@
         <v>5</v>
       </c>
       <c r="N26" s="2">
-        <v>3.83</v>
+        <v>18.78</v>
       </c>
       <c r="O26" s="2" t="s">
-        <v>218</v>
+        <v>237</v>
       </c>
       <c r="P26" s="2" t="s">
         <v>0</v>
@@ -2492,19 +2551,19 @@
         <v>23</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>217</v>
+        <v>236</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>216</v>
+        <v>235</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>215</v>
+        <v>234</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F27" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G27" s="2">
         <v>8.0</v>
@@ -2526,10 +2585,10 @@
         <v>5</v>
       </c>
       <c r="N27" s="2">
-        <v>1.67</v>
+        <v>4.37</v>
       </c>
       <c r="O27" s="2" t="s">
-        <v>211</v>
+        <v>233</v>
       </c>
       <c r="P27" s="2" t="s">
         <v>0</v>
@@ -2540,44 +2599,44 @@
         <v>24</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>214</v>
+        <v>232</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>213</v>
+        <v>231</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>212</v>
+        <v>230</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F28" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G28" s="2">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
       <c r="H28" s="2">
         <v>10.0</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="J28" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K28" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L28" s="2"/>
       <c r="M28" s="2">
         <v>5</v>
       </c>
       <c r="N28" s="2">
-        <v>4.2</v>
+        <v>0.48</v>
       </c>
       <c r="O28" s="2" t="s">
-        <v>211</v>
+        <v>229</v>
       </c>
       <c r="P28" s="2" t="s">
         <v>0</v>
@@ -2588,13 +2647,13 @@
         <v>25</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>210</v>
+        <v>228</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>209</v>
+        <v>227</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>208</v>
+        <v>226</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>3</v>
@@ -2603,27 +2662,29 @@
         <v>2</v>
       </c>
       <c r="G29" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H29" s="2">
         <v>10.0</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="J29" s="2">
-        <v>5</v>
-      </c>
-      <c r="K29" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K29" s="2">
+        <v>1</v>
+      </c>
       <c r="L29" s="2"/>
       <c r="M29" s="2">
         <v>5</v>
       </c>
       <c r="N29" s="2">
-        <v>7.48</v>
+        <v>1.7</v>
       </c>
       <c r="O29" s="2" t="s">
-        <v>194</v>
+        <v>225</v>
       </c>
       <c r="P29" s="2" t="s">
         <v>0</v>
@@ -2634,13 +2695,13 @@
         <v>26</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>207</v>
+        <v>224</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>205</v>
+        <v>223</v>
+      </c>
+      <c r="D30" s="2">
+        <v>201118200153</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>3</v>
@@ -2649,27 +2710,29 @@
         <v>1</v>
       </c>
       <c r="G30" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H30" s="2">
         <v>10.0</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="J30" s="2">
-        <v>5</v>
-      </c>
-      <c r="K30" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K30" s="2">
+        <v>1</v>
+      </c>
       <c r="L30" s="2"/>
       <c r="M30" s="2">
         <v>5</v>
       </c>
       <c r="N30" s="2">
-        <v>12.57</v>
+        <v>2.15</v>
       </c>
       <c r="O30" s="2" t="s">
-        <v>194</v>
+        <v>222</v>
       </c>
       <c r="P30" s="2" t="s">
         <v>0</v>
@@ -2680,13 +2743,13 @@
         <v>27</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>204</v>
+        <v>221</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>203</v>
+        <v>220</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>202</v>
+        <v>219</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>3</v>
@@ -2712,10 +2775,10 @@
         <v>5</v>
       </c>
       <c r="N31" s="2">
-        <v>9.22</v>
+        <v>3.83</v>
       </c>
       <c r="O31" s="2" t="s">
-        <v>198</v>
+        <v>218</v>
       </c>
       <c r="P31" s="2" t="s">
         <v>0</v>
@@ -2726,42 +2789,44 @@
         <v>28</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>201</v>
+        <v>217</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>200</v>
+        <v>216</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>199</v>
+        <v>215</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F32" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G32" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H32" s="2">
         <v>10.0</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="J32" s="2">
-        <v>5</v>
-      </c>
-      <c r="K32" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K32" s="2">
+        <v>1</v>
+      </c>
       <c r="L32" s="2"/>
       <c r="M32" s="2">
         <v>5</v>
       </c>
       <c r="N32" s="2">
-        <v>10.92</v>
+        <v>1.67</v>
       </c>
       <c r="O32" s="2" t="s">
-        <v>198</v>
+        <v>211</v>
       </c>
       <c r="P32" s="2" t="s">
         <v>0</v>
@@ -2772,13 +2837,13 @@
         <v>29</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>197</v>
+        <v>214</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>196</v>
+        <v>213</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>195</v>
+        <v>212</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>3</v>
@@ -2787,29 +2852,29 @@
         <v>1</v>
       </c>
       <c r="G33" s="2">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="H33" s="2">
         <v>10.0</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="J33" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K33" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L33" s="2"/>
       <c r="M33" s="2">
         <v>5</v>
       </c>
       <c r="N33" s="2">
-        <v>19.3</v>
+        <v>4.2</v>
       </c>
       <c r="O33" s="2" t="s">
-        <v>194</v>
+        <v>211</v>
       </c>
       <c r="P33" s="2" t="s">
         <v>0</v>
@@ -2820,19 +2885,19 @@
         <v>30</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>193</v>
+        <v>210</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>192</v>
+        <v>209</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>191</v>
+        <v>208</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F34" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G34" s="2">
         <v>10.0</v>
@@ -2852,10 +2917,10 @@
         <v>5</v>
       </c>
       <c r="N34" s="2">
-        <v>27.43</v>
+        <v>7.48</v>
       </c>
       <c r="O34" s="2" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="P34" s="2" t="s">
         <v>0</v>
@@ -2866,13 +2931,13 @@
         <v>31</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>189</v>
+        <v>207</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>188</v>
+        <v>206</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>187</v>
+        <v>205</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>3</v>
@@ -2898,10 +2963,10 @@
         <v>5</v>
       </c>
       <c r="N35" s="2">
-        <v>3.58</v>
+        <v>12.57</v>
       </c>
       <c r="O35" s="2" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="P35" s="2" t="s">
         <v>0</v>
@@ -2912,13 +2977,13 @@
         <v>32</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>185</v>
+        <v>204</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>184</v>
+        <v>203</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>183</v>
+        <v>202</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>3</v>
@@ -2927,29 +2992,27 @@
         <v>1</v>
       </c>
       <c r="G36" s="2">
-        <v>6.0</v>
+        <v>10.0</v>
       </c>
       <c r="H36" s="2">
         <v>10.0</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="J36" s="2">
-        <v>3</v>
-      </c>
-      <c r="K36" s="2">
-        <v>2</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K36" s="2"/>
       <c r="L36" s="2"/>
       <c r="M36" s="2">
         <v>5</v>
       </c>
       <c r="N36" s="2">
-        <v>14.85</v>
+        <v>9.22</v>
       </c>
       <c r="O36" s="2" t="s">
-        <v>182</v>
+        <v>198</v>
       </c>
       <c r="P36" s="2" t="s">
         <v>0</v>
@@ -2960,13 +3023,13 @@
         <v>33</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>181</v>
+        <v>201</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>179</v>
+        <v>199</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>3</v>
@@ -2992,10 +3055,10 @@
         <v>5</v>
       </c>
       <c r="N37" s="2">
-        <v>5.42</v>
+        <v>10.92</v>
       </c>
       <c r="O37" s="2" t="s">
-        <v>178</v>
+        <v>198</v>
       </c>
       <c r="P37" s="2" t="s">
         <v>0</v>
@@ -3006,13 +3069,13 @@
         <v>34</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>177</v>
+        <v>197</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>176</v>
+        <v>196</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>175</v>
+        <v>195</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>3</v>
@@ -3021,27 +3084,29 @@
         <v>1</v>
       </c>
       <c r="G38" s="2">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
       <c r="H38" s="2">
         <v>10.0</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="J38" s="2">
-        <v>5</v>
-      </c>
-      <c r="K38" s="2"/>
+        <v>3</v>
+      </c>
+      <c r="K38" s="2">
+        <v>2</v>
+      </c>
       <c r="L38" s="2"/>
       <c r="M38" s="2">
         <v>5</v>
       </c>
       <c r="N38" s="2">
-        <v>8.33</v>
+        <v>19.3</v>
       </c>
       <c r="O38" s="2" t="s">
-        <v>174</v>
+        <v>194</v>
       </c>
       <c r="P38" s="2" t="s">
         <v>0</v>
@@ -3052,13 +3117,13 @@
         <v>35</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>173</v>
+        <v>193</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>172</v>
+        <v>192</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>171</v>
+        <v>191</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>3</v>
@@ -3067,32 +3132,30 @@
         <v>1</v>
       </c>
       <c r="G39" s="2">
-        <v>4.0</v>
+        <v>10.0</v>
       </c>
       <c r="H39" s="2">
         <v>10.0</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>170</v>
+        <v>17</v>
       </c>
       <c r="J39" s="2">
-        <v>2</v>
-      </c>
-      <c r="K39" s="2">
-        <v>3</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K39" s="2"/>
       <c r="L39" s="2"/>
       <c r="M39" s="2">
         <v>5</v>
       </c>
       <c r="N39" s="2">
-        <v>1.5</v>
+        <v>27.43</v>
       </c>
       <c r="O39" s="2" t="s">
-        <v>169</v>
+        <v>190</v>
       </c>
       <c r="P39" s="2" t="s">
-        <v>168</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3100,13 +3163,13 @@
         <v>36</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>167</v>
+        <v>189</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>166</v>
+        <v>188</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>165</v>
+        <v>187</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>3</v>
@@ -3115,29 +3178,27 @@
         <v>1</v>
       </c>
       <c r="G40" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H40" s="2">
         <v>10.0</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="J40" s="2">
-        <v>4</v>
-      </c>
-      <c r="K40" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K40" s="2"/>
       <c r="L40" s="2"/>
       <c r="M40" s="2">
         <v>5</v>
       </c>
       <c r="N40" s="2">
-        <v>6.75</v>
+        <v>3.58</v>
       </c>
       <c r="O40" s="2" t="s">
-        <v>161</v>
+        <v>186</v>
       </c>
       <c r="P40" s="2" t="s">
         <v>0</v>
@@ -3148,13 +3209,13 @@
         <v>37</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>164</v>
+        <v>185</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>163</v>
+        <v>184</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>162</v>
+        <v>183</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>3</v>
@@ -3163,29 +3224,29 @@
         <v>1</v>
       </c>
       <c r="G41" s="2">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
       <c r="H41" s="2">
         <v>10.0</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="J41" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K41" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L41" s="2"/>
       <c r="M41" s="2">
         <v>5</v>
       </c>
       <c r="N41" s="2">
-        <v>8.65</v>
+        <v>14.85</v>
       </c>
       <c r="O41" s="2" t="s">
-        <v>161</v>
+        <v>182</v>
       </c>
       <c r="P41" s="2" t="s">
         <v>0</v>
@@ -3196,13 +3257,13 @@
         <v>38</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>160</v>
+        <v>181</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>159</v>
+        <v>180</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>158</v>
+        <v>179</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>3</v>
@@ -3228,10 +3289,10 @@
         <v>5</v>
       </c>
       <c r="N42" s="2">
-        <v>10.37</v>
+        <v>5.42</v>
       </c>
       <c r="O42" s="2" t="s">
-        <v>157</v>
+        <v>178</v>
       </c>
       <c r="P42" s="2" t="s">
         <v>0</v>
@@ -3242,13 +3303,13 @@
         <v>39</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>156</v>
+        <v>177</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>155</v>
+        <v>176</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>154</v>
+        <v>175</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>3</v>
@@ -3274,10 +3335,10 @@
         <v>5</v>
       </c>
       <c r="N43" s="2">
-        <v>7.27</v>
+        <v>8.33</v>
       </c>
       <c r="O43" s="2" t="s">
-        <v>153</v>
+        <v>174</v>
       </c>
       <c r="P43" s="2" t="s">
         <v>0</v>
@@ -3288,13 +3349,13 @@
         <v>40</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>152</v>
+        <v>173</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>151</v>
+        <v>172</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>150</v>
+        <v>171</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>3</v>
@@ -3303,30 +3364,32 @@
         <v>1</v>
       </c>
       <c r="G44" s="2">
-        <v>10.0</v>
+        <v>4.0</v>
       </c>
       <c r="H44" s="2">
         <v>10.0</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>17</v>
+        <v>170</v>
       </c>
       <c r="J44" s="2">
-        <v>5</v>
-      </c>
-      <c r="K44" s="2"/>
+        <v>2</v>
+      </c>
+      <c r="K44" s="2">
+        <v>3</v>
+      </c>
       <c r="L44" s="2"/>
       <c r="M44" s="2">
         <v>5</v>
       </c>
       <c r="N44" s="2">
-        <v>4.2</v>
+        <v>1.5</v>
       </c>
       <c r="O44" s="2" t="s">
-        <v>149</v>
+        <v>169</v>
       </c>
       <c r="P44" s="2" t="s">
-        <v>0</v>
+        <v>168</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -3334,13 +3397,13 @@
         <v>41</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>148</v>
+        <v>167</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>147</v>
+        <v>166</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>146</v>
+        <v>165</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>3</v>
@@ -3368,10 +3431,10 @@
         <v>5</v>
       </c>
       <c r="N45" s="2">
-        <v>25.47</v>
+        <v>6.75</v>
       </c>
       <c r="O45" s="2" t="s">
-        <v>145</v>
+        <v>161</v>
       </c>
       <c r="P45" s="2" t="s">
         <v>0</v>
@@ -3382,13 +3445,13 @@
         <v>42</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>144</v>
+        <v>164</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>143</v>
+        <v>163</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>142</v>
+        <v>162</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>3</v>
@@ -3416,10 +3479,10 @@
         <v>5</v>
       </c>
       <c r="N46" s="2">
-        <v>16.42</v>
+        <v>8.65</v>
       </c>
       <c r="O46" s="2" t="s">
-        <v>141</v>
+        <v>161</v>
       </c>
       <c r="P46" s="2" t="s">
         <v>0</v>
@@ -3430,13 +3493,13 @@
         <v>43</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>139</v>
+        <v>159</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>138</v>
+        <v>158</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>3</v>
@@ -3462,10 +3525,10 @@
         <v>5</v>
       </c>
       <c r="N47" s="2">
-        <v>20.63</v>
+        <v>10.37</v>
       </c>
       <c r="O47" s="2" t="s">
-        <v>137</v>
+        <v>157</v>
       </c>
       <c r="P47" s="2" t="s">
         <v>0</v>
@@ -3476,13 +3539,13 @@
         <v>44</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>136</v>
+        <v>156</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>135</v>
+        <v>155</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>134</v>
+        <v>154</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>3</v>
@@ -3508,10 +3571,10 @@
         <v>5</v>
       </c>
       <c r="N48" s="2">
-        <v>5.73</v>
+        <v>7.27</v>
       </c>
       <c r="O48" s="2" t="s">
-        <v>133</v>
+        <v>153</v>
       </c>
       <c r="P48" s="2" t="s">
         <v>0</v>
@@ -3522,13 +3585,13 @@
         <v>45</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>132</v>
+        <v>152</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>131</v>
+        <v>151</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>3</v>
@@ -3554,10 +3617,10 @@
         <v>5</v>
       </c>
       <c r="N49" s="2">
-        <v>3.98</v>
+        <v>4.2</v>
       </c>
       <c r="O49" s="2" t="s">
-        <v>129</v>
+        <v>149</v>
       </c>
       <c r="P49" s="2" t="s">
         <v>0</v>
@@ -3568,13 +3631,13 @@
         <v>46</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>128</v>
+        <v>148</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>127</v>
+        <v>147</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>126</v>
+        <v>146</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>3</v>
@@ -3602,10 +3665,10 @@
         <v>5</v>
       </c>
       <c r="N50" s="2">
-        <v>7.77</v>
+        <v>25.47</v>
       </c>
       <c r="O50" s="2" t="s">
-        <v>125</v>
+        <v>145</v>
       </c>
       <c r="P50" s="2" t="s">
         <v>0</v>
@@ -3616,13 +3679,13 @@
         <v>47</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>124</v>
+        <v>144</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>123</v>
+        <v>143</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>122</v>
+        <v>142</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>3</v>
@@ -3631,27 +3694,29 @@
         <v>1</v>
       </c>
       <c r="G51" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H51" s="2">
         <v>10.0</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="J51" s="2">
-        <v>5</v>
-      </c>
-      <c r="K51" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K51" s="2">
+        <v>1</v>
+      </c>
       <c r="L51" s="2"/>
       <c r="M51" s="2">
         <v>5</v>
       </c>
       <c r="N51" s="2">
-        <v>24.08</v>
+        <v>16.42</v>
       </c>
       <c r="O51" s="2" t="s">
-        <v>121</v>
+        <v>141</v>
       </c>
       <c r="P51" s="2" t="s">
         <v>0</v>
@@ -3662,13 +3727,13 @@
         <v>48</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>119</v>
+        <v>139</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>118</v>
+        <v>138</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>3</v>
@@ -3694,10 +3759,10 @@
         <v>5</v>
       </c>
       <c r="N52" s="2">
-        <v>14.05</v>
+        <v>20.63</v>
       </c>
       <c r="O52" s="2" t="s">
-        <v>117</v>
+        <v>137</v>
       </c>
       <c r="P52" s="2" t="s">
         <v>0</v>
@@ -3708,13 +3773,13 @@
         <v>49</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>115</v>
+        <v>135</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>114</v>
+        <v>134</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>3</v>
@@ -3723,29 +3788,27 @@
         <v>1</v>
       </c>
       <c r="G53" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H53" s="2">
         <v>10.0</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="J53" s="2">
-        <v>4</v>
-      </c>
-      <c r="K53" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K53" s="2"/>
       <c r="L53" s="2"/>
       <c r="M53" s="2">
         <v>5</v>
       </c>
       <c r="N53" s="2">
-        <v>10.78</v>
+        <v>5.73</v>
       </c>
       <c r="O53" s="2" t="s">
-        <v>113</v>
+        <v>133</v>
       </c>
       <c r="P53" s="2" t="s">
         <v>0</v>
@@ -3756,13 +3819,13 @@
         <v>50</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>112</v>
+        <v>132</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>111</v>
+        <v>131</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>3</v>
@@ -3771,29 +3834,27 @@
         <v>1</v>
       </c>
       <c r="G54" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H54" s="2">
         <v>10.0</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="J54" s="2">
-        <v>4</v>
-      </c>
-      <c r="K54" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K54" s="2"/>
       <c r="L54" s="2"/>
       <c r="M54" s="2">
         <v>5</v>
       </c>
       <c r="N54" s="2">
-        <v>2.48</v>
+        <v>3.98</v>
       </c>
       <c r="O54" s="2" t="s">
-        <v>109</v>
+        <v>129</v>
       </c>
       <c r="P54" s="2" t="s">
         <v>0</v>
@@ -3804,13 +3865,13 @@
         <v>51</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>108</v>
+        <v>128</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>107</v>
+        <v>127</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>106</v>
+        <v>126</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>3</v>
@@ -3819,29 +3880,29 @@
         <v>1</v>
       </c>
       <c r="G55" s="2">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="H55" s="2">
         <v>10.0</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="J55" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K55" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L55" s="2"/>
       <c r="M55" s="2">
         <v>5</v>
       </c>
       <c r="N55" s="2">
-        <v>8.05</v>
+        <v>7.77</v>
       </c>
       <c r="O55" s="2" t="s">
-        <v>105</v>
+        <v>125</v>
       </c>
       <c r="P55" s="2" t="s">
         <v>0</v>
@@ -3852,13 +3913,13 @@
         <v>52</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>104</v>
+        <v>124</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>103</v>
+        <v>123</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>102</v>
+        <v>122</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>3</v>
@@ -3884,10 +3945,10 @@
         <v>5</v>
       </c>
       <c r="N56" s="2">
-        <v>32.08</v>
+        <v>24.08</v>
       </c>
       <c r="O56" s="2" t="s">
-        <v>101</v>
+        <v>121</v>
       </c>
       <c r="P56" s="2" t="s">
         <v>0</v>
@@ -3898,13 +3959,13 @@
         <v>53</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>99</v>
+        <v>119</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>98</v>
+        <v>118</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>3</v>
@@ -3930,10 +3991,10 @@
         <v>5</v>
       </c>
       <c r="N57" s="2">
-        <v>2.35</v>
+        <v>14.05</v>
       </c>
       <c r="O57" s="2" t="s">
-        <v>97</v>
+        <v>117</v>
       </c>
       <c r="P57" s="2" t="s">
         <v>0</v>
@@ -3944,13 +4005,13 @@
         <v>54</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>95</v>
+        <v>115</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>94</v>
+        <v>114</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>3</v>
@@ -3959,27 +4020,29 @@
         <v>1</v>
       </c>
       <c r="G58" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H58" s="2">
         <v>10.0</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="J58" s="2">
-        <v>5</v>
-      </c>
-      <c r="K58" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K58" s="2">
+        <v>1</v>
+      </c>
       <c r="L58" s="2"/>
       <c r="M58" s="2">
         <v>5</v>
       </c>
       <c r="N58" s="2">
-        <v>299.45</v>
+        <v>10.78</v>
       </c>
       <c r="O58" s="2" t="s">
-        <v>93</v>
+        <v>113</v>
       </c>
       <c r="P58" s="2" t="s">
         <v>0</v>
@@ -3990,13 +4053,13 @@
         <v>55</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>92</v>
+        <v>112</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>91</v>
+        <v>111</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>3</v>
@@ -4005,27 +4068,29 @@
         <v>1</v>
       </c>
       <c r="G59" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H59" s="2">
         <v>10.0</v>
       </c>
       <c r="I59" s="2" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="J59" s="2">
-        <v>5</v>
-      </c>
-      <c r="K59" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K59" s="2">
+        <v>1</v>
+      </c>
       <c r="L59" s="2"/>
       <c r="M59" s="2">
         <v>5</v>
       </c>
       <c r="N59" s="2">
-        <v>9.7</v>
+        <v>2.48</v>
       </c>
       <c r="O59" s="2" t="s">
-        <v>89</v>
+        <v>109</v>
       </c>
       <c r="P59" s="2" t="s">
         <v>0</v>
@@ -4036,13 +4101,13 @@
         <v>56</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>88</v>
+        <v>108</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>87</v>
+        <v>107</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>3</v>
@@ -4051,27 +4116,29 @@
         <v>1</v>
       </c>
       <c r="G60" s="2">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
       <c r="H60" s="2">
         <v>10.0</v>
       </c>
       <c r="I60" s="2" t="s">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="J60" s="2">
-        <v>5</v>
-      </c>
-      <c r="K60" s="2"/>
+        <v>3</v>
+      </c>
+      <c r="K60" s="2">
+        <v>2</v>
+      </c>
       <c r="L60" s="2"/>
       <c r="M60" s="2">
         <v>5</v>
       </c>
       <c r="N60" s="2">
-        <v>26.22</v>
+        <v>8.05</v>
       </c>
       <c r="O60" s="2" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="P60" s="2" t="s">
         <v>0</v>
@@ -4082,13 +4149,13 @@
         <v>57</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>83</v>
+        <v>103</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>3</v>
@@ -4114,10 +4181,10 @@
         <v>5</v>
       </c>
       <c r="N61" s="2">
-        <v>1.18</v>
+        <v>32.08</v>
       </c>
       <c r="O61" s="2" t="s">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="P61" s="2" t="s">
         <v>0</v>
@@ -4128,13 +4195,13 @@
         <v>58</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>78</v>
+        <v>98</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>3</v>
@@ -4160,10 +4227,10 @@
         <v>5</v>
       </c>
       <c r="N62" s="2">
-        <v>26.28</v>
+        <v>2.35</v>
       </c>
       <c r="O62" s="2" t="s">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="P62" s="2" t="s">
         <v>0</v>
@@ -4174,13 +4241,13 @@
         <v>59</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>74</v>
+        <v>94</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>3</v>
@@ -4206,10 +4273,10 @@
         <v>5</v>
       </c>
       <c r="N63" s="2">
-        <v>11.17</v>
+        <v>299.45</v>
       </c>
       <c r="O63" s="2" t="s">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="P63" s="2" t="s">
         <v>0</v>
@@ -4220,13 +4287,13 @@
         <v>60</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>71</v>
+        <v>91</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>3</v>
@@ -4252,10 +4319,10 @@
         <v>5</v>
       </c>
       <c r="N64" s="2">
-        <v>10.05</v>
+        <v>9.7</v>
       </c>
       <c r="O64" s="2" t="s">
-        <v>69</v>
+        <v>89</v>
       </c>
       <c r="P64" s="2" t="s">
         <v>0</v>
@@ -4266,13 +4333,13 @@
         <v>61</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>68</v>
+        <v>88</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>67</v>
+        <v>87</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>66</v>
+        <v>86</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>3</v>
@@ -4298,10 +4365,10 @@
         <v>5</v>
       </c>
       <c r="N65" s="2">
-        <v>1507.62</v>
+        <v>26.22</v>
       </c>
       <c r="O65" s="2" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="P65" s="2" t="s">
         <v>0</v>
@@ -4312,13 +4379,13 @@
         <v>62</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>64</v>
+        <v>84</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>63</v>
+        <v>83</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>3</v>
@@ -4327,29 +4394,27 @@
         <v>1</v>
       </c>
       <c r="G66" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H66" s="2">
         <v>10.0</v>
       </c>
       <c r="I66" s="2" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="J66" s="2">
-        <v>4</v>
-      </c>
-      <c r="K66" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K66" s="2"/>
       <c r="L66" s="2"/>
       <c r="M66" s="2">
         <v>5</v>
       </c>
       <c r="N66" s="2">
-        <v>6.08</v>
+        <v>1.18</v>
       </c>
       <c r="O66" s="2" t="s">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="P66" s="2" t="s">
         <v>0</v>
@@ -4360,13 +4425,13 @@
         <v>63</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>59</v>
+        <v>79</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>58</v>
+        <v>78</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>3</v>
@@ -4392,10 +4457,10 @@
         <v>5</v>
       </c>
       <c r="N67" s="2">
-        <v>1.93</v>
+        <v>26.28</v>
       </c>
       <c r="O67" s="2" t="s">
-        <v>57</v>
+        <v>77</v>
       </c>
       <c r="P67" s="2" t="s">
         <v>0</v>
@@ -4406,13 +4471,13 @@
         <v>64</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>54</v>
+        <v>74</v>
       </c>
       <c r="E68" s="2" t="s">
         <v>3</v>
@@ -4438,10 +4503,10 @@
         <v>5</v>
       </c>
       <c r="N68" s="2">
-        <v>11.58</v>
+        <v>11.17</v>
       </c>
       <c r="O68" s="2" t="s">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="P68" s="2" t="s">
         <v>0</v>
@@ -4452,13 +4517,13 @@
         <v>65</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>3</v>
@@ -4484,10 +4549,10 @@
         <v>5</v>
       </c>
       <c r="N69" s="2">
-        <v>25.92</v>
+        <v>10.05</v>
       </c>
       <c r="O69" s="2" t="s">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="P69" s="2" t="s">
         <v>0</v>
@@ -4498,13 +4563,13 @@
         <v>66</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>48</v>
+        <v>68</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>3</v>
@@ -4513,29 +4578,27 @@
         <v>1</v>
       </c>
       <c r="G70" s="2">
-        <v>6.0</v>
+        <v>10.0</v>
       </c>
       <c r="H70" s="2">
         <v>10.0</v>
       </c>
       <c r="I70" s="2" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="J70" s="2">
-        <v>3</v>
-      </c>
-      <c r="K70" s="2">
-        <v>2</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K70" s="2"/>
       <c r="L70" s="2"/>
       <c r="M70" s="2">
         <v>5</v>
       </c>
       <c r="N70" s="2">
-        <v>25.67</v>
+        <v>1507.62</v>
       </c>
       <c r="O70" s="2" t="s">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="P70" s="2" t="s">
         <v>0</v>
@@ -4546,13 +4609,13 @@
         <v>67</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>3</v>
@@ -4580,10 +4643,10 @@
         <v>5</v>
       </c>
       <c r="N71" s="2">
-        <v>5.32</v>
+        <v>6.08</v>
       </c>
       <c r="O71" s="2" t="s">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="P71" s="2" t="s">
         <v>0</v>
@@ -4594,13 +4657,13 @@
         <v>68</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>3</v>
@@ -4626,10 +4689,10 @@
         <v>5</v>
       </c>
       <c r="N72" s="2">
-        <v>32.9</v>
+        <v>1.93</v>
       </c>
       <c r="O72" s="2" t="s">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="P72" s="2" t="s">
         <v>0</v>
@@ -4640,13 +4703,13 @@
         <v>69</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>3</v>
@@ -4672,10 +4735,10 @@
         <v>5</v>
       </c>
       <c r="N73" s="2">
-        <v>3.77</v>
+        <v>11.58</v>
       </c>
       <c r="O73" s="2" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="P73" s="2" t="s">
         <v>0</v>
@@ -4686,19 +4749,19 @@
         <v>70</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F74" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G74" s="2">
         <v>10.0</v>
@@ -4718,10 +4781,10 @@
         <v>5</v>
       </c>
       <c r="N74" s="2">
-        <v>1.65</v>
+        <v>25.92</v>
       </c>
       <c r="O74" s="2" t="s">
-        <v>29</v>
+        <v>49</v>
       </c>
       <c r="P74" s="2" t="s">
         <v>0</v>
@@ -4732,44 +4795,44 @@
         <v>71</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F75" s="2">
+        <v>1</v>
+      </c>
+      <c r="G75" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="H75" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I75" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="G75" s="2">
-        <v>8.0</v>
-      </c>
-      <c r="H75" s="2">
-        <v>10.0</v>
-      </c>
-      <c r="I75" s="2" t="s">
-        <v>12</v>
-      </c>
       <c r="J75" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K75" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L75" s="2"/>
       <c r="M75" s="2">
         <v>5</v>
       </c>
       <c r="N75" s="2">
-        <v>4.22</v>
+        <v>25.67</v>
       </c>
       <c r="O75" s="2" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="P75" s="2" t="s">
         <v>0</v>
@@ -4780,13 +4843,13 @@
         <v>72</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="E76" s="2" t="s">
         <v>3</v>
@@ -4795,29 +4858,29 @@
         <v>1</v>
       </c>
       <c r="G76" s="2">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="H76" s="2">
         <v>10.0</v>
       </c>
       <c r="I76" s="2" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="J76" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K76" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L76" s="2"/>
       <c r="M76" s="2">
         <v>5</v>
       </c>
       <c r="N76" s="2">
-        <v>23.22</v>
+        <v>5.32</v>
       </c>
       <c r="O76" s="2" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="P76" s="2" t="s">
         <v>0</v>
@@ -4828,13 +4891,13 @@
         <v>73</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="E77" s="2" t="s">
         <v>3</v>
@@ -4860,10 +4923,10 @@
         <v>5</v>
       </c>
       <c r="N77" s="2">
-        <v>14.3</v>
+        <v>32.9</v>
       </c>
       <c r="O77" s="2" t="s">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="P77" s="2" t="s">
         <v>0</v>
@@ -4874,13 +4937,13 @@
         <v>74</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="E78" s="2" t="s">
         <v>3</v>
@@ -4889,29 +4952,27 @@
         <v>1</v>
       </c>
       <c r="G78" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H78" s="2">
         <v>10.0</v>
       </c>
       <c r="I78" s="2" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="J78" s="2">
-        <v>4</v>
-      </c>
-      <c r="K78" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K78" s="2"/>
       <c r="L78" s="2"/>
       <c r="M78" s="2">
         <v>5</v>
       </c>
       <c r="N78" s="2">
-        <v>13.45</v>
+        <v>3.77</v>
       </c>
       <c r="O78" s="2" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="P78" s="2" t="s">
         <v>0</v>
@@ -4922,13 +4983,13 @@
         <v>75</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="E79" s="2" t="s">
         <v>3</v>
@@ -4937,29 +4998,27 @@
         <v>2</v>
       </c>
       <c r="G79" s="2">
-        <v>6.0</v>
+        <v>10.0</v>
       </c>
       <c r="H79" s="2">
         <v>10.0</v>
       </c>
       <c r="I79" s="2" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="J79" s="2">
-        <v>3</v>
-      </c>
-      <c r="K79" s="2">
-        <v>2</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K79" s="2"/>
       <c r="L79" s="2"/>
       <c r="M79" s="2">
         <v>5</v>
       </c>
       <c r="N79" s="2">
-        <v>9179.12</v>
+        <v>1.65</v>
       </c>
       <c r="O79" s="2" t="s">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="P79" s="2" t="s">
         <v>0</v>
@@ -4970,46 +5029,284 @@
         <v>76</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="D80" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F80" s="2">
+        <v>2</v>
+      </c>
+      <c r="G80" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="H80" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I80" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="J80" s="2">
         <v>4</v>
       </c>
-      <c r="E80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F80" s="2">
-        <v>1</v>
-      </c>
-      <c r="G80" s="2">
-        <v>6.0</v>
-      </c>
-      <c r="H80" s="2">
-        <v>10.0</v>
-      </c>
-      <c r="I80" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="J80" s="2">
-        <v>3</v>
-      </c>
       <c r="K80" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L80" s="2"/>
       <c r="M80" s="2">
         <v>5</v>
       </c>
       <c r="N80" s="2">
+        <v>4.22</v>
+      </c>
+      <c r="O80" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P80" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:16">
+      <c r="A81" s="2">
+        <v>77</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E81" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F81" s="2">
+        <v>1</v>
+      </c>
+      <c r="G81" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="H81" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I81" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J81" s="2">
+        <v>3</v>
+      </c>
+      <c r="K81" s="2">
+        <v>2</v>
+      </c>
+      <c r="L81" s="2"/>
+      <c r="M81" s="2">
+        <v>5</v>
+      </c>
+      <c r="N81" s="2">
+        <v>23.22</v>
+      </c>
+      <c r="O81" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="P81" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:16">
+      <c r="A82" s="2">
+        <v>78</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F82" s="2">
+        <v>1</v>
+      </c>
+      <c r="G82" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="H82" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I82" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J82" s="2">
+        <v>5</v>
+      </c>
+      <c r="K82" s="2"/>
+      <c r="L82" s="2"/>
+      <c r="M82" s="2">
+        <v>5</v>
+      </c>
+      <c r="N82" s="2">
+        <v>14.3</v>
+      </c>
+      <c r="O82" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="P82" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:16">
+      <c r="A83" s="2">
+        <v>79</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F83" s="2">
+        <v>1</v>
+      </c>
+      <c r="G83" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="H83" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I83" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="J83" s="2">
+        <v>4</v>
+      </c>
+      <c r="K83" s="2">
+        <v>1</v>
+      </c>
+      <c r="L83" s="2"/>
+      <c r="M83" s="2">
+        <v>5</v>
+      </c>
+      <c r="N83" s="2">
+        <v>13.45</v>
+      </c>
+      <c r="O83" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="P83" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:16">
+      <c r="A84" s="2">
+        <v>80</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F84" s="2">
+        <v>2</v>
+      </c>
+      <c r="G84" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="H84" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I84" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J84" s="2">
+        <v>3</v>
+      </c>
+      <c r="K84" s="2">
+        <v>2</v>
+      </c>
+      <c r="L84" s="2"/>
+      <c r="M84" s="2">
+        <v>5</v>
+      </c>
+      <c r="N84" s="2">
+        <v>9179.12</v>
+      </c>
+      <c r="O84" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="P84" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:16">
+      <c r="A85" s="2">
+        <v>81</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F85" s="2">
+        <v>1</v>
+      </c>
+      <c r="G85" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="H85" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I85" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J85" s="2">
+        <v>3</v>
+      </c>
+      <c r="K85" s="2">
+        <v>2</v>
+      </c>
+      <c r="L85" s="2"/>
+      <c r="M85" s="2">
+        <v>5</v>
+      </c>
+      <c r="N85" s="2">
         <v>5.32</v>
       </c>
-      <c r="O80" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="P80" s="2" t="s">
+      <c r="O85" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="P85" s="2" t="s">
         <v>0</v>
       </c>
     </row>

--- a/2lit_center.xlsx
+++ b/2lit_center.xlsx
@@ -881,7 +881,106 @@
     <t>Mariam sameh sami</t>
   </si>
   <si>
-    <t>2026-03-16 19:14</t>
+    <t>2026-03-16 19:12</t>
+  </si>
+  <si>
+    <t>01554037795</t>
+  </si>
+  <si>
+    <t>saharrefee@gmail.com</t>
+  </si>
+  <si>
+    <t>سهر محمد ابراهيم الرفاعي</t>
+  </si>
+  <si>
+    <t>2026-03-16 19:19</t>
+  </si>
+  <si>
+    <t>01064753790</t>
+  </si>
+  <si>
+    <t>Abdullazizosama18@gmail.com</t>
+  </si>
+  <si>
+    <t>Abdullaziz</t>
+  </si>
+  <si>
+    <t>2026-03-16 19:37</t>
+  </si>
+  <si>
+    <t>01094609026</t>
+  </si>
+  <si>
+    <t>sandyalylabib560@gmail.com</t>
+  </si>
+  <si>
+    <t>Sandy aly abdelmohsen</t>
+  </si>
+  <si>
+    <t>2026-03-18 13:14</t>
+  </si>
+  <si>
+    <t>0.0%</t>
+  </si>
+  <si>
+    <t>janafrahat@icloud.com</t>
+  </si>
+  <si>
+    <t>Jana Ahmed frahat</t>
+  </si>
+  <si>
+    <t>2026-03-25 07:58</t>
+  </si>
+  <si>
+    <t>01094303365</t>
+  </si>
+  <si>
+    <t>Yomnamelhabrouk@gmail.com</t>
+  </si>
+  <si>
+    <t>Yomna</t>
+  </si>
+  <si>
+    <t>2026-03-27 03:01</t>
+  </si>
+  <si>
+    <t>01103622316</t>
+  </si>
+  <si>
+    <t>esraassaaddd30@gmail.com</t>
+  </si>
+  <si>
+    <t>Esraa saad</t>
+  </si>
+  <si>
+    <t>2026-03-29 03:22</t>
+  </si>
+  <si>
+    <t>20.0%</t>
+  </si>
+  <si>
+    <t>01020123791</t>
+  </si>
+  <si>
+    <t>salmatareksoo17@gmail.com</t>
+  </si>
+  <si>
+    <t>Salma</t>
+  </si>
+  <si>
+    <t>2026-03-29 13:13</t>
+  </si>
+  <si>
+    <t>01501181314</t>
+  </si>
+  <si>
+    <t>bebonasser399@gamil.com</t>
+  </si>
+  <si>
+    <t>Habiba Nasser Ahmed</t>
+  </si>
+  <si>
+    <t>2026-03-30 15:59</t>
   </si>
   <si>
     <t>01121970064</t>
@@ -893,105 +992,6 @@
     <t>احمد محمد احمد كامل</t>
   </si>
   <si>
-    <t>2026-03-16 19:12</t>
-  </si>
-  <si>
-    <t>01554037795</t>
-  </si>
-  <si>
-    <t>saharrefee@gmail.com</t>
-  </si>
-  <si>
-    <t>سهر محمد ابراهيم الرفاعي</t>
-  </si>
-  <si>
-    <t>2026-03-16 19:19</t>
-  </si>
-  <si>
-    <t>01064753790</t>
-  </si>
-  <si>
-    <t>Abdullazizosama18@gmail.com</t>
-  </si>
-  <si>
-    <t>Abdullaziz</t>
-  </si>
-  <si>
-    <t>2026-03-16 19:37</t>
-  </si>
-  <si>
-    <t>01094609026</t>
-  </si>
-  <si>
-    <t>sandyalylabib560@gmail.com</t>
-  </si>
-  <si>
-    <t>Sandy aly abdelmohsen</t>
-  </si>
-  <si>
-    <t>2026-03-18 13:14</t>
-  </si>
-  <si>
-    <t>0.0%</t>
-  </si>
-  <si>
-    <t>janafrahat@icloud.com</t>
-  </si>
-  <si>
-    <t>Jana Ahmed frahat</t>
-  </si>
-  <si>
-    <t>2026-03-25 07:58</t>
-  </si>
-  <si>
-    <t>01094303365</t>
-  </si>
-  <si>
-    <t>Yomnamelhabrouk@gmail.com</t>
-  </si>
-  <si>
-    <t>Yomna</t>
-  </si>
-  <si>
-    <t>2026-03-27 03:01</t>
-  </si>
-  <si>
-    <t>01103622316</t>
-  </si>
-  <si>
-    <t>esraassaaddd30@gmail.com</t>
-  </si>
-  <si>
-    <t>Esraa saad</t>
-  </si>
-  <si>
-    <t>2026-03-29 03:22</t>
-  </si>
-  <si>
-    <t>20.0%</t>
-  </si>
-  <si>
-    <t>01020123791</t>
-  </si>
-  <si>
-    <t>salmatareksoo17@gmail.com</t>
-  </si>
-  <si>
-    <t>Salma</t>
-  </si>
-  <si>
-    <t>2026-03-29 13:13</t>
-  </si>
-  <si>
-    <t>01501181314</t>
-  </si>
-  <si>
-    <t>bebonasser399@gamil.com</t>
-  </si>
-  <si>
-    <t>Habiba Nasser Ahmed</t>
-  </si>
-  <si>
     <t>الحالة</t>
   </si>
   <si>
@@ -1046,7 +1046,7 @@
     <t>الدرجة الكاملة: 10 | درجة النجاح: 5.00</t>
   </si>
   <si>
-    <t>تاريخ التصدير: 2026-03-29 16:33</t>
+    <t>تاريخ التصدير: 2026-03-30 16:27</t>
   </si>
 </sst>
 </file>
@@ -1537,7 +1537,7 @@
         <v>3</v>
       </c>
       <c r="F5" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G5" s="2">
         <v>10.0</v>
@@ -1557,7 +1557,7 @@
         <v>5</v>
       </c>
       <c r="N5" s="2">
-        <v>2.95</v>
+        <v>1135.68</v>
       </c>
       <c r="O5" s="2" t="s">
         <v>321</v>
@@ -1586,32 +1586,30 @@
         <v>1</v>
       </c>
       <c r="G6" s="2">
-        <v>2.0</v>
+        <v>10.0</v>
       </c>
       <c r="H6" s="2">
         <v>10.0</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>317</v>
+        <v>17</v>
       </c>
       <c r="J6" s="2">
-        <v>1</v>
-      </c>
-      <c r="K6" s="2">
-        <v>4</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K6" s="2"/>
       <c r="L6" s="2"/>
       <c r="M6" s="2">
         <v>5</v>
       </c>
       <c r="N6" s="2">
-        <v>0.58</v>
+        <v>2.95</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>168</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -1619,47 +1617,47 @@
         <v>3</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>315</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
         <v>314</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="E7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F7" s="2">
+        <v>1</v>
+      </c>
+      <c r="G7" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="H7" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I7" s="2" t="s">
         <v>313</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F7" s="2">
-        <v>2</v>
-      </c>
-      <c r="G7" s="2">
-        <v>8.0</v>
-      </c>
-      <c r="H7" s="2">
-        <v>10.0</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>12</v>
-      </c>
       <c r="J7" s="2">
+        <v>1</v>
+      </c>
+      <c r="K7" s="2">
         <v>4</v>
-      </c>
-      <c r="K7" s="2">
-        <v>1</v>
       </c>
       <c r="L7" s="2"/>
       <c r="M7" s="2">
         <v>5</v>
       </c>
       <c r="N7" s="2">
-        <v>3.03</v>
+        <v>0.58</v>
       </c>
       <c r="O7" s="2" t="s">
         <v>312</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>0</v>
+        <v>168</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -1679,27 +1677,29 @@
         <v>3</v>
       </c>
       <c r="F8" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G8" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H8" s="2">
         <v>10.0</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="J8" s="2">
-        <v>5</v>
-      </c>
-      <c r="K8" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K8" s="2">
+        <v>1</v>
+      </c>
       <c r="L8" s="2"/>
       <c r="M8" s="2">
         <v>5</v>
       </c>
       <c r="N8" s="2">
-        <v>10.22</v>
+        <v>3.03</v>
       </c>
       <c r="O8" s="2" t="s">
         <v>308</v>
@@ -1718,8 +1718,8 @@
       <c r="C9" s="2" t="s">
         <v>306</v>
       </c>
-      <c r="D9" s="2">
-        <v>1159792350</v>
+      <c r="D9" s="2" t="s">
+        <v>305</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>3</v>
@@ -1728,30 +1728,30 @@
         <v>1</v>
       </c>
       <c r="G9" s="2">
-        <v>0.0</v>
+        <v>10.0</v>
       </c>
       <c r="H9" s="2">
         <v>10.0</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="J9" s="2"/>
-      <c r="K9" s="2">
-        <v>5</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="J9" s="2">
+        <v>5</v>
+      </c>
+      <c r="K9" s="2"/>
       <c r="L9" s="2"/>
       <c r="M9" s="2">
         <v>5</v>
       </c>
       <c r="N9" s="2">
-        <v>1.63</v>
+        <v>10.22</v>
       </c>
       <c r="O9" s="2" t="s">
         <v>304</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>168</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -1764,40 +1764,40 @@
       <c r="C10" s="2" t="s">
         <v>302</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D10" s="2">
+        <v>1159792350</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F10" s="2">
+        <v>1</v>
+      </c>
+      <c r="G10" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="H10" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I10" s="2" t="s">
         <v>301</v>
       </c>
-      <c r="E10" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F10" s="2">
-        <v>1</v>
-      </c>
-      <c r="G10" s="2">
-        <v>10.0</v>
-      </c>
-      <c r="H10" s="2">
-        <v>10.0</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J10" s="2">
-        <v>5</v>
-      </c>
-      <c r="K10" s="2"/>
+      <c r="J10" s="2"/>
+      <c r="K10" s="2">
+        <v>5</v>
+      </c>
       <c r="L10" s="2"/>
       <c r="M10" s="2">
         <v>5</v>
       </c>
       <c r="N10" s="2">
-        <v>1.92</v>
+        <v>1.63</v>
       </c>
       <c r="O10" s="2" t="s">
         <v>300</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>0</v>
+        <v>168</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -1820,26 +1820,24 @@
         <v>1</v>
       </c>
       <c r="G11" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H11" s="2">
         <v>10.0</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="J11" s="2">
-        <v>4</v>
-      </c>
-      <c r="K11" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K11" s="2"/>
       <c r="L11" s="2"/>
       <c r="M11" s="2">
         <v>5</v>
       </c>
       <c r="N11" s="2">
-        <v>20.53</v>
+        <v>1.92</v>
       </c>
       <c r="O11" s="2" t="s">
         <v>296</v>
@@ -1887,7 +1885,7 @@
         <v>5</v>
       </c>
       <c r="N12" s="2">
-        <v>14.28</v>
+        <v>20.53</v>
       </c>
       <c r="O12" s="2" t="s">
         <v>292</v>
@@ -1916,24 +1914,26 @@
         <v>1</v>
       </c>
       <c r="G13" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H13" s="2">
         <v>10.0</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="J13" s="2">
-        <v>5</v>
-      </c>
-      <c r="K13" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K13" s="2">
+        <v>1</v>
+      </c>
       <c r="L13" s="2"/>
       <c r="M13" s="2">
         <v>5</v>
       </c>
       <c r="N13" s="2">
-        <v>21.38</v>
+        <v>14.28</v>
       </c>
       <c r="O13" s="2" t="s">
         <v>288</v>

--- a/2lit_center.xlsx
+++ b/2lit_center.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="344">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="356">
   <si>
     <t>ناجح ✓</t>
   </si>
@@ -260,7 +260,763 @@
     <t>ياسمين محمود محمد خلاف</t>
   </si>
   <si>
-    <t>2026-03-15 04:52</t>
+    <t>2026-03-15 07:16</t>
+  </si>
+  <si>
+    <t>01100422373</t>
+  </si>
+  <si>
+    <t>menna262menna@gmail.com</t>
+  </si>
+  <si>
+    <t>منه مختار عبد القادر</t>
+  </si>
+  <si>
+    <t>2026-03-15 13:20</t>
+  </si>
+  <si>
+    <t>01012965454</t>
+  </si>
+  <si>
+    <t>hyawalid788@gmail.com</t>
+  </si>
+  <si>
+    <t>hya walid helal</t>
+  </si>
+  <si>
+    <t>2026-03-15 18:40</t>
+  </si>
+  <si>
+    <t>01065596920</t>
+  </si>
+  <si>
+    <t>caramella3750@gmail.com</t>
+  </si>
+  <si>
+    <t>Carma Ehab</t>
+  </si>
+  <si>
+    <t>2026-03-15 13:57</t>
+  </si>
+  <si>
+    <t>01026933947</t>
+  </si>
+  <si>
+    <t>malaksamykamel2008@gmail.com</t>
+  </si>
+  <si>
+    <t>Malak Samy</t>
+  </si>
+  <si>
+    <t>2026-03-15 15:44</t>
+  </si>
+  <si>
+    <t>01006941885</t>
+  </si>
+  <si>
+    <t>yokeahmedyahia@gmail.com</t>
+  </si>
+  <si>
+    <t>Yahia Ahmed</t>
+  </si>
+  <si>
+    <t>2026-03-15 15:50</t>
+  </si>
+  <si>
+    <t>01552477901</t>
+  </si>
+  <si>
+    <t>roayaakram0@gmail.com</t>
+  </si>
+  <si>
+    <t>رؤيا اكرم شوقي محمد</t>
+  </si>
+  <si>
+    <t>2026-03-15 16:09</t>
+  </si>
+  <si>
+    <t>01033050201</t>
+  </si>
+  <si>
+    <t>abdelfatahebrahim38@gmail.com</t>
+  </si>
+  <si>
+    <t>ابراهيم عبدالفتاح فؤاد</t>
+  </si>
+  <si>
+    <t>2026-03-15 16:22</t>
+  </si>
+  <si>
+    <t>01113765691</t>
+  </si>
+  <si>
+    <t>ahmed148mody@gmail.com</t>
+  </si>
+  <si>
+    <t>أحمد محمد أحمد سلمان</t>
+  </si>
+  <si>
+    <t>2026-03-15 16:26</t>
+  </si>
+  <si>
+    <t>01553495959</t>
+  </si>
+  <si>
+    <t>elmaghlopm@gmail.com</t>
+  </si>
+  <si>
+    <t>Mariam elmaghlop</t>
+  </si>
+  <si>
+    <t>2026-03-15 16:47</t>
+  </si>
+  <si>
+    <t>01113365191</t>
+  </si>
+  <si>
+    <t>faridamahmoud13579@gmail.com</t>
+  </si>
+  <si>
+    <t>فريدة محمود عبدالحسيب احمد</t>
+  </si>
+  <si>
+    <t>2026-03-15 16:35</t>
+  </si>
+  <si>
+    <t>01129793194</t>
+  </si>
+  <si>
+    <t>mrxyt881@gmail.com</t>
+  </si>
+  <si>
+    <t>Mahmoud ahmed salah</t>
+  </si>
+  <si>
+    <t>2026-03-15 16:53</t>
+  </si>
+  <si>
+    <t>01011317686</t>
+  </si>
+  <si>
+    <t>superman611255@gmail.com</t>
+  </si>
+  <si>
+    <t>Fares Tamer</t>
+  </si>
+  <si>
+    <t>2026-03-15 16:59</t>
+  </si>
+  <si>
+    <t>01092255761</t>
+  </si>
+  <si>
+    <t>habibagalal552004@gmail.com</t>
+  </si>
+  <si>
+    <t>moustafa galal</t>
+  </si>
+  <si>
+    <t>2026-03-15 17:17</t>
+  </si>
+  <si>
+    <t>01093571345</t>
+  </si>
+  <si>
+    <t>Mallakfathyazzam@gmail.com</t>
+  </si>
+  <si>
+    <t>Malak  fathy azzam</t>
+  </si>
+  <si>
+    <t>2026-03-15 17:21</t>
+  </si>
+  <si>
+    <t>01069526879</t>
+  </si>
+  <si>
+    <t>Safawael31@gmail.com</t>
+  </si>
+  <si>
+    <t>Safa wael fathy</t>
+  </si>
+  <si>
+    <t>2026-03-15 17:34</t>
+  </si>
+  <si>
+    <t>01100682703</t>
+  </si>
+  <si>
+    <t>Lara.eldiasti@gmail.com</t>
+  </si>
+  <si>
+    <t>لارا الحسن الديسطي</t>
+  </si>
+  <si>
+    <t>2026-03-15 17:24</t>
+  </si>
+  <si>
+    <t>01019713904</t>
+  </si>
+  <si>
+    <t>mayar.mohamed.200813@gmail.com</t>
+  </si>
+  <si>
+    <t>ميار محمد رفعت</t>
+  </si>
+  <si>
+    <t>2026-03-15 17:45</t>
+  </si>
+  <si>
+    <t>01022023062</t>
+  </si>
+  <si>
+    <t>malakmohammedalaa94@gmail.com</t>
+  </si>
+  <si>
+    <t>ملك محمد علاء الدين</t>
+  </si>
+  <si>
+    <t>2026-03-15 18:00</t>
+  </si>
+  <si>
+    <t>01127911990</t>
+  </si>
+  <si>
+    <t>fm6757434@gmail.com</t>
+  </si>
+  <si>
+    <t>Farah mohamed</t>
+  </si>
+  <si>
+    <t>2026-03-15 18:02</t>
+  </si>
+  <si>
+    <t>01007991680</t>
+  </si>
+  <si>
+    <t>nada.gamal196@gmail.com</t>
+  </si>
+  <si>
+    <t>Nada</t>
+  </si>
+  <si>
+    <t>01225460949</t>
+  </si>
+  <si>
+    <t>hm3947263@gmail.com</t>
+  </si>
+  <si>
+    <t>Rahma mohamed mostafa</t>
+  </si>
+  <si>
+    <t>راسب ✗</t>
+  </si>
+  <si>
+    <t>2026-03-15 18:15</t>
+  </si>
+  <si>
+    <t>40.0%</t>
+  </si>
+  <si>
+    <t>01110668723</t>
+  </si>
+  <si>
+    <t>abdoeidbody2008@gmail.com</t>
+  </si>
+  <si>
+    <t>Abdullah Eid saber</t>
+  </si>
+  <si>
+    <t>2026-03-15 18:31</t>
+  </si>
+  <si>
+    <t>01010103820</t>
+  </si>
+  <si>
+    <t>somiasami88@gmail.com</t>
+  </si>
+  <si>
+    <t>salma mohamed mahmoud</t>
+  </si>
+  <si>
+    <t>2026-03-15 18:38</t>
+  </si>
+  <si>
+    <t>01121431168</t>
+  </si>
+  <si>
+    <t>ahmeddaoomy2@gmail.com</t>
+  </si>
+  <si>
+    <t>Ahmed shawky</t>
+  </si>
+  <si>
+    <t>2026-03-15 18:50</t>
+  </si>
+  <si>
+    <t>01157331074</t>
+  </si>
+  <si>
+    <t>farahgadallh@gmail.com</t>
+  </si>
+  <si>
+    <t>Farah Ahmed mohamed</t>
+  </si>
+  <si>
+    <t>2026-03-15 18:42</t>
+  </si>
+  <si>
+    <t>01012424377</t>
+  </si>
+  <si>
+    <t>janayousry@2008gmail.com</t>
+  </si>
+  <si>
+    <t>jana ahmed mohmed yousry</t>
+  </si>
+  <si>
+    <t>2026-03-15 19:09</t>
+  </si>
+  <si>
+    <t>01097794201</t>
+  </si>
+  <si>
+    <t>aytensaleh6@gmail.com</t>
+  </si>
+  <si>
+    <t>Ayten Saleh Mostafa</t>
+  </si>
+  <si>
+    <t>2026-03-15 19:08</t>
+  </si>
+  <si>
+    <t>01101097272</t>
+  </si>
+  <si>
+    <t>mohamed.almalt2009@gmail.com</t>
+  </si>
+  <si>
+    <t>محمد السيد  بهيج</t>
+  </si>
+  <si>
+    <t>2026-03-15 19:01</t>
+  </si>
+  <si>
+    <t>01065163432</t>
+  </si>
+  <si>
+    <t>Janahosein901@gmail.com</t>
+  </si>
+  <si>
+    <t>Jana hussein Fahim</t>
+  </si>
+  <si>
+    <t>01006392755</t>
+  </si>
+  <si>
+    <t>ezz44013@gmail.com</t>
+  </si>
+  <si>
+    <t>عز الدين أيمن</t>
+  </si>
+  <si>
+    <t>01023876919</t>
+  </si>
+  <si>
+    <t>yassinahmedsaid139@gmail.com</t>
+  </si>
+  <si>
+    <t>ياسين احمد سعيد</t>
+  </si>
+  <si>
+    <t>01501045643</t>
+  </si>
+  <si>
+    <t>elawadyahmed999@gmial.com</t>
+  </si>
+  <si>
+    <t>Elawady Ahmed elawady</t>
+  </si>
+  <si>
+    <t>2026-03-15 19:17</t>
+  </si>
+  <si>
+    <t>01125776411</t>
+  </si>
+  <si>
+    <t>radwanosama414@gmail.com</t>
+  </si>
+  <si>
+    <t>Radwan Osama</t>
+  </si>
+  <si>
+    <t>01124926013</t>
+  </si>
+  <si>
+    <t>marwanelnakeeb2009@gmail.com</t>
+  </si>
+  <si>
+    <t>Marwan omar</t>
+  </si>
+  <si>
+    <t>2026-03-15 19:22</t>
+  </si>
+  <si>
+    <t>01228047462</t>
+  </si>
+  <si>
+    <t>Yousefsonic22@gmail.com</t>
+  </si>
+  <si>
+    <t>Yousef hesham</t>
+  </si>
+  <si>
+    <t>2026-03-15 19:24</t>
+  </si>
+  <si>
+    <t>karimmowafak@gmail.com</t>
+  </si>
+  <si>
+    <t>Karim Mowafak</t>
+  </si>
+  <si>
+    <t>2026-03-15 19:23</t>
+  </si>
+  <si>
+    <t>01061920915</t>
+  </si>
+  <si>
+    <t>goudysherif@gmail.com</t>
+  </si>
+  <si>
+    <t>محمد شريف</t>
+  </si>
+  <si>
+    <t>2026-03-15 19:33</t>
+  </si>
+  <si>
+    <t>01121777574</t>
+  </si>
+  <si>
+    <t>zadaahmed1510@gmail.com</t>
+  </si>
+  <si>
+    <t>Zada Ahmed fathy</t>
+  </si>
+  <si>
+    <t>2026-03-15 19:55</t>
+  </si>
+  <si>
+    <t>01271532097</t>
+  </si>
+  <si>
+    <t>marlygmghobrial@gmail.com</t>
+  </si>
+  <si>
+    <t>مارلي جورج موريس</t>
+  </si>
+  <si>
+    <t>2026-03-15 22:58</t>
+  </si>
+  <si>
+    <t>01120961209</t>
+  </si>
+  <si>
+    <t>masa1412009@gmail.com</t>
+  </si>
+  <si>
+    <t>Masa mohamed mohy</t>
+  </si>
+  <si>
+    <t>2026-03-15 23:16</t>
+  </si>
+  <si>
+    <t>01123268908</t>
+  </si>
+  <si>
+    <t>habibaamrmm@icloud.com</t>
+  </si>
+  <si>
+    <t>Habiba amr eladwy</t>
+  </si>
+  <si>
+    <t>2026-03-16 00:36</t>
+  </si>
+  <si>
+    <t>01011744851</t>
+  </si>
+  <si>
+    <t>abdelrahmanbedo@gmail.com</t>
+  </si>
+  <si>
+    <t>عبدالرحمن محمد محمد</t>
+  </si>
+  <si>
+    <t>2026-03-16 02:57</t>
+  </si>
+  <si>
+    <t>01040794109</t>
+  </si>
+  <si>
+    <t>oa2743370@gmail.com</t>
+  </si>
+  <si>
+    <t>Omar Ibrahim Hegazy</t>
+  </si>
+  <si>
+    <t>2026-03-16 03:51</t>
+  </si>
+  <si>
+    <t>01016345481</t>
+  </si>
+  <si>
+    <t>ao5617814@gmail.com</t>
+  </si>
+  <si>
+    <t>Abdelrahman Ibrahim Hegazy</t>
+  </si>
+  <si>
+    <t>2026-03-16 12:57</t>
+  </si>
+  <si>
+    <t>01018892998</t>
+  </si>
+  <si>
+    <t>gannatnasser8@gmail.com</t>
+  </si>
+  <si>
+    <t>Gannat Abd el Nasser</t>
+  </si>
+  <si>
+    <t>2026-03-16 15:38</t>
+  </si>
+  <si>
+    <t>+01122773746</t>
+  </si>
+  <si>
+    <t>begomego66@gmail.com</t>
+  </si>
+  <si>
+    <t>Begad Magdy Ali</t>
+  </si>
+  <si>
+    <t>2026-03-16 15:36</t>
+  </si>
+  <si>
+    <t>01062623490</t>
+  </si>
+  <si>
+    <t>omarzakaa1@gmail.com</t>
+  </si>
+  <si>
+    <t>omar zakaa</t>
+  </si>
+  <si>
+    <t>2026-03-16 17:23</t>
+  </si>
+  <si>
+    <t>01017803931</t>
+  </si>
+  <si>
+    <t>kokymzykm2007@gmail.com</t>
+  </si>
+  <si>
+    <t>Kenzy Mohamed</t>
+  </si>
+  <si>
+    <t>2026-03-16 17:52</t>
+  </si>
+  <si>
+    <t>01154109786</t>
+  </si>
+  <si>
+    <t>nadaaseleem@gmail.com</t>
+  </si>
+  <si>
+    <t>Nada Ahmed Seleem</t>
+  </si>
+  <si>
+    <t>2026-03-16 17:42</t>
+  </si>
+  <si>
+    <t>01017099170</t>
+  </si>
+  <si>
+    <t>joudhanynabil@gmail.com</t>
+  </si>
+  <si>
+    <t>joudy</t>
+  </si>
+  <si>
+    <t>01555066805</t>
+  </si>
+  <si>
+    <t>mohammed.el.shazly2009@gmail.com</t>
+  </si>
+  <si>
+    <t>محمد أسامة محمد الشاذلي</t>
+  </si>
+  <si>
+    <t>2026-03-16 18:48</t>
+  </si>
+  <si>
+    <t>01099284562</t>
+  </si>
+  <si>
+    <t>samehsami9@gmail.com</t>
+  </si>
+  <si>
+    <t>Mariam sameh sami</t>
+  </si>
+  <si>
+    <t>2026-03-16 19:12</t>
+  </si>
+  <si>
+    <t>01554037795</t>
+  </si>
+  <si>
+    <t>saharrefee@gmail.com</t>
+  </si>
+  <si>
+    <t>سهر محمد ابراهيم الرفاعي</t>
+  </si>
+  <si>
+    <t>2026-04-03 17:18</t>
+  </si>
+  <si>
+    <t>01094609026</t>
+  </si>
+  <si>
+    <t>sandyalylabib560@gmail.com</t>
+  </si>
+  <si>
+    <t>Sandy aly abdelmohsen</t>
+  </si>
+  <si>
+    <t>2026-03-18 13:14</t>
+  </si>
+  <si>
+    <t>0.0%</t>
+  </si>
+  <si>
+    <t>janafrahat@icloud.com</t>
+  </si>
+  <si>
+    <t>Jana Ahmed frahat</t>
+  </si>
+  <si>
+    <t>2026-03-25 07:58</t>
+  </si>
+  <si>
+    <t>01094303365</t>
+  </si>
+  <si>
+    <t>Yomnamelhabrouk@gmail.com</t>
+  </si>
+  <si>
+    <t>Yomna</t>
+  </si>
+  <si>
+    <t>2026-03-27 03:01</t>
+  </si>
+  <si>
+    <t>01103622316</t>
+  </si>
+  <si>
+    <t>esraassaaddd30@gmail.com</t>
+  </si>
+  <si>
+    <t>Esraa saad</t>
+  </si>
+  <si>
+    <t>2026-03-29 03:22</t>
+  </si>
+  <si>
+    <t>20.0%</t>
+  </si>
+  <si>
+    <t>01020123791</t>
+  </si>
+  <si>
+    <t>salmatareksoo17@gmail.com</t>
+  </si>
+  <si>
+    <t>Salma</t>
+  </si>
+  <si>
+    <t>2026-03-29 13:13</t>
+  </si>
+  <si>
+    <t>01501181314</t>
+  </si>
+  <si>
+    <t>bebonasser399@gamil.com</t>
+  </si>
+  <si>
+    <t>Habiba Nasser Ahmed</t>
+  </si>
+  <si>
+    <t>2026-03-30 15:59</t>
+  </si>
+  <si>
+    <t>01121970064</t>
+  </si>
+  <si>
+    <t>Ahmedmakg7@gmail.com</t>
+  </si>
+  <si>
+    <t>احمد محمد احمد كامل</t>
+  </si>
+  <si>
+    <t>2026-03-30 16:53</t>
+  </si>
+  <si>
+    <t>01064753790</t>
+  </si>
+  <si>
+    <t>Abdullazizosama18@gmail.com</t>
+  </si>
+  <si>
+    <t>Abdullaziz</t>
+  </si>
+  <si>
+    <t>2026-04-02 17:03</t>
+  </si>
+  <si>
+    <t>01030133382</t>
+  </si>
+  <si>
+    <t>hamza2210mg@gmail.com</t>
+  </si>
+  <si>
+    <t>Hamza</t>
+  </si>
+  <si>
+    <t>2026-04-03 16:50</t>
+  </si>
+  <si>
+    <t>01222221223</t>
+  </si>
+  <si>
+    <t>elbadryjojo@gmail.com</t>
+  </si>
+  <si>
+    <t>لوجين</t>
+  </si>
+  <si>
+    <t>2026-04-03 20:06</t>
+  </si>
+  <si>
+    <t>01001269403</t>
+  </si>
+  <si>
+    <t>ahmed.tarek3729@gmail.com</t>
+  </si>
+  <si>
+    <t>احمد طارق فتحي</t>
+  </si>
+  <si>
+    <t>2026-04-05 14:32</t>
   </si>
   <si>
     <t>01011452702</t>
@@ -272,726 +1028,6 @@
     <t>Ahmed Mohamed</t>
   </si>
   <si>
-    <t>2026-03-15 07:16</t>
-  </si>
-  <si>
-    <t>01100422373</t>
-  </si>
-  <si>
-    <t>menna262menna@gmail.com</t>
-  </si>
-  <si>
-    <t>منه مختار عبد القادر</t>
-  </si>
-  <si>
-    <t>2026-03-15 13:20</t>
-  </si>
-  <si>
-    <t>01012965454</t>
-  </si>
-  <si>
-    <t>hyawalid788@gmail.com</t>
-  </si>
-  <si>
-    <t>hya walid helal</t>
-  </si>
-  <si>
-    <t>2026-03-15 18:40</t>
-  </si>
-  <si>
-    <t>01065596920</t>
-  </si>
-  <si>
-    <t>caramella3750@gmail.com</t>
-  </si>
-  <si>
-    <t>Carma Ehab</t>
-  </si>
-  <si>
-    <t>2026-03-15 13:57</t>
-  </si>
-  <si>
-    <t>01026933947</t>
-  </si>
-  <si>
-    <t>malaksamykamel2008@gmail.com</t>
-  </si>
-  <si>
-    <t>Malak Samy</t>
-  </si>
-  <si>
-    <t>2026-03-15 15:44</t>
-  </si>
-  <si>
-    <t>01006941885</t>
-  </si>
-  <si>
-    <t>yokeahmedyahia@gmail.com</t>
-  </si>
-  <si>
-    <t>Yahia Ahmed</t>
-  </si>
-  <si>
-    <t>2026-03-15 15:50</t>
-  </si>
-  <si>
-    <t>01552477901</t>
-  </si>
-  <si>
-    <t>roayaakram0@gmail.com</t>
-  </si>
-  <si>
-    <t>رؤيا اكرم شوقي محمد</t>
-  </si>
-  <si>
-    <t>2026-03-15 16:09</t>
-  </si>
-  <si>
-    <t>01033050201</t>
-  </si>
-  <si>
-    <t>abdelfatahebrahim38@gmail.com</t>
-  </si>
-  <si>
-    <t>ابراهيم عبدالفتاح فؤاد</t>
-  </si>
-  <si>
-    <t>2026-03-15 16:22</t>
-  </si>
-  <si>
-    <t>01113765691</t>
-  </si>
-  <si>
-    <t>ahmed148mody@gmail.com</t>
-  </si>
-  <si>
-    <t>أحمد محمد أحمد سلمان</t>
-  </si>
-  <si>
-    <t>2026-03-15 16:26</t>
-  </si>
-  <si>
-    <t>01553495959</t>
-  </si>
-  <si>
-    <t>elmaghlopm@gmail.com</t>
-  </si>
-  <si>
-    <t>Mariam elmaghlop</t>
-  </si>
-  <si>
-    <t>2026-03-15 16:47</t>
-  </si>
-  <si>
-    <t>01113365191</t>
-  </si>
-  <si>
-    <t>faridamahmoud13579@gmail.com</t>
-  </si>
-  <si>
-    <t>فريدة محمود عبدالحسيب احمد</t>
-  </si>
-  <si>
-    <t>2026-03-15 16:35</t>
-  </si>
-  <si>
-    <t>01129793194</t>
-  </si>
-  <si>
-    <t>mrxyt881@gmail.com</t>
-  </si>
-  <si>
-    <t>Mahmoud ahmed salah</t>
-  </si>
-  <si>
-    <t>2026-03-15 16:53</t>
-  </si>
-  <si>
-    <t>01011317686</t>
-  </si>
-  <si>
-    <t>superman611255@gmail.com</t>
-  </si>
-  <si>
-    <t>Fares Tamer</t>
-  </si>
-  <si>
-    <t>2026-03-15 16:59</t>
-  </si>
-  <si>
-    <t>01092255761</t>
-  </si>
-  <si>
-    <t>habibagalal552004@gmail.com</t>
-  </si>
-  <si>
-    <t>moustafa galal</t>
-  </si>
-  <si>
-    <t>2026-03-15 17:17</t>
-  </si>
-  <si>
-    <t>01093571345</t>
-  </si>
-  <si>
-    <t>Mallakfathyazzam@gmail.com</t>
-  </si>
-  <si>
-    <t>Malak  fathy azzam</t>
-  </si>
-  <si>
-    <t>2026-03-15 17:21</t>
-  </si>
-  <si>
-    <t>01069526879</t>
-  </si>
-  <si>
-    <t>Safawael31@gmail.com</t>
-  </si>
-  <si>
-    <t>Safa wael fathy</t>
-  </si>
-  <si>
-    <t>2026-03-15 17:34</t>
-  </si>
-  <si>
-    <t>01100682703</t>
-  </si>
-  <si>
-    <t>Lara.eldiasti@gmail.com</t>
-  </si>
-  <si>
-    <t>لارا الحسن الديسطي</t>
-  </si>
-  <si>
-    <t>2026-03-15 17:24</t>
-  </si>
-  <si>
-    <t>01019713904</t>
-  </si>
-  <si>
-    <t>mayar.mohamed.200813@gmail.com</t>
-  </si>
-  <si>
-    <t>ميار محمد رفعت</t>
-  </si>
-  <si>
-    <t>2026-03-15 17:45</t>
-  </si>
-  <si>
-    <t>01022023062</t>
-  </si>
-  <si>
-    <t>malakmohammedalaa94@gmail.com</t>
-  </si>
-  <si>
-    <t>ملك محمد علاء الدين</t>
-  </si>
-  <si>
-    <t>2026-03-15 18:00</t>
-  </si>
-  <si>
-    <t>01127911990</t>
-  </si>
-  <si>
-    <t>fm6757434@gmail.com</t>
-  </si>
-  <si>
-    <t>Farah mohamed</t>
-  </si>
-  <si>
-    <t>2026-03-15 18:02</t>
-  </si>
-  <si>
-    <t>01007991680</t>
-  </si>
-  <si>
-    <t>nada.gamal196@gmail.com</t>
-  </si>
-  <si>
-    <t>Nada</t>
-  </si>
-  <si>
-    <t>01225460949</t>
-  </si>
-  <si>
-    <t>hm3947263@gmail.com</t>
-  </si>
-  <si>
-    <t>Rahma mohamed mostafa</t>
-  </si>
-  <si>
-    <t>راسب ✗</t>
-  </si>
-  <si>
-    <t>2026-03-15 18:15</t>
-  </si>
-  <si>
-    <t>40.0%</t>
-  </si>
-  <si>
-    <t>01110668723</t>
-  </si>
-  <si>
-    <t>abdoeidbody2008@gmail.com</t>
-  </si>
-  <si>
-    <t>Abdullah Eid saber</t>
-  </si>
-  <si>
-    <t>2026-03-15 18:31</t>
-  </si>
-  <si>
-    <t>01010103820</t>
-  </si>
-  <si>
-    <t>somiasami88@gmail.com</t>
-  </si>
-  <si>
-    <t>salma mohamed mahmoud</t>
-  </si>
-  <si>
-    <t>2026-03-15 18:38</t>
-  </si>
-  <si>
-    <t>01121431168</t>
-  </si>
-  <si>
-    <t>ahmeddaoomy2@gmail.com</t>
-  </si>
-  <si>
-    <t>Ahmed shawky</t>
-  </si>
-  <si>
-    <t>2026-03-15 18:50</t>
-  </si>
-  <si>
-    <t>01157331074</t>
-  </si>
-  <si>
-    <t>farahgadallh@gmail.com</t>
-  </si>
-  <si>
-    <t>Farah Ahmed mohamed</t>
-  </si>
-  <si>
-    <t>2026-03-15 18:42</t>
-  </si>
-  <si>
-    <t>01012424377</t>
-  </si>
-  <si>
-    <t>janayousry@2008gmail.com</t>
-  </si>
-  <si>
-    <t>jana ahmed mohmed yousry</t>
-  </si>
-  <si>
-    <t>2026-03-15 19:09</t>
-  </si>
-  <si>
-    <t>01097794201</t>
-  </si>
-  <si>
-    <t>aytensaleh6@gmail.com</t>
-  </si>
-  <si>
-    <t>Ayten Saleh Mostafa</t>
-  </si>
-  <si>
-    <t>2026-03-15 19:08</t>
-  </si>
-  <si>
-    <t>01101097272</t>
-  </si>
-  <si>
-    <t>mohamed.almalt2009@gmail.com</t>
-  </si>
-  <si>
-    <t>محمد السيد  بهيج</t>
-  </si>
-  <si>
-    <t>2026-03-15 19:01</t>
-  </si>
-  <si>
-    <t>01065163432</t>
-  </si>
-  <si>
-    <t>Janahosein901@gmail.com</t>
-  </si>
-  <si>
-    <t>Jana hussein Fahim</t>
-  </si>
-  <si>
-    <t>01006392755</t>
-  </si>
-  <si>
-    <t>ezz44013@gmail.com</t>
-  </si>
-  <si>
-    <t>عز الدين أيمن</t>
-  </si>
-  <si>
-    <t>01023876919</t>
-  </si>
-  <si>
-    <t>yassinahmedsaid139@gmail.com</t>
-  </si>
-  <si>
-    <t>ياسين احمد سعيد</t>
-  </si>
-  <si>
-    <t>01501045643</t>
-  </si>
-  <si>
-    <t>elawadyahmed999@gmial.com</t>
-  </si>
-  <si>
-    <t>Elawady Ahmed elawady</t>
-  </si>
-  <si>
-    <t>2026-03-15 19:17</t>
-  </si>
-  <si>
-    <t>01125776411</t>
-  </si>
-  <si>
-    <t>radwanosama414@gmail.com</t>
-  </si>
-  <si>
-    <t>Radwan Osama</t>
-  </si>
-  <si>
-    <t>01124926013</t>
-  </si>
-  <si>
-    <t>marwanelnakeeb2009@gmail.com</t>
-  </si>
-  <si>
-    <t>Marwan omar</t>
-  </si>
-  <si>
-    <t>2026-03-15 19:22</t>
-  </si>
-  <si>
-    <t>01228047462</t>
-  </si>
-  <si>
-    <t>Yousefsonic22@gmail.com</t>
-  </si>
-  <si>
-    <t>Yousef hesham</t>
-  </si>
-  <si>
-    <t>2026-03-15 19:24</t>
-  </si>
-  <si>
-    <t>karimmowafak@gmail.com</t>
-  </si>
-  <si>
-    <t>Karim Mowafak</t>
-  </si>
-  <si>
-    <t>2026-03-15 19:23</t>
-  </si>
-  <si>
-    <t>01061920915</t>
-  </si>
-  <si>
-    <t>goudysherif@gmail.com</t>
-  </si>
-  <si>
-    <t>محمد شريف</t>
-  </si>
-  <si>
-    <t>2026-03-15 19:33</t>
-  </si>
-  <si>
-    <t>01121777574</t>
-  </si>
-  <si>
-    <t>zadaahmed1510@gmail.com</t>
-  </si>
-  <si>
-    <t>Zada Ahmed fathy</t>
-  </si>
-  <si>
-    <t>2026-03-15 19:55</t>
-  </si>
-  <si>
-    <t>01271532097</t>
-  </si>
-  <si>
-    <t>marlygmghobrial@gmail.com</t>
-  </si>
-  <si>
-    <t>مارلي جورج موريس</t>
-  </si>
-  <si>
-    <t>2026-03-15 22:58</t>
-  </si>
-  <si>
-    <t>01120961209</t>
-  </si>
-  <si>
-    <t>masa1412009@gmail.com</t>
-  </si>
-  <si>
-    <t>Masa mohamed mohy</t>
-  </si>
-  <si>
-    <t>2026-03-15 23:16</t>
-  </si>
-  <si>
-    <t>01123268908</t>
-  </si>
-  <si>
-    <t>habibaamrmm@icloud.com</t>
-  </si>
-  <si>
-    <t>Habiba amr eladwy</t>
-  </si>
-  <si>
-    <t>2026-03-16 00:36</t>
-  </si>
-  <si>
-    <t>01011744851</t>
-  </si>
-  <si>
-    <t>abdelrahmanbedo@gmail.com</t>
-  </si>
-  <si>
-    <t>عبدالرحمن محمد محمد</t>
-  </si>
-  <si>
-    <t>2026-03-16 02:57</t>
-  </si>
-  <si>
-    <t>01040794109</t>
-  </si>
-  <si>
-    <t>oa2743370@gmail.com</t>
-  </si>
-  <si>
-    <t>Omar Ibrahim Hegazy</t>
-  </si>
-  <si>
-    <t>2026-03-16 03:51</t>
-  </si>
-  <si>
-    <t>01016345481</t>
-  </si>
-  <si>
-    <t>ao5617814@gmail.com</t>
-  </si>
-  <si>
-    <t>Abdelrahman Ibrahim Hegazy</t>
-  </si>
-  <si>
-    <t>2026-03-16 12:57</t>
-  </si>
-  <si>
-    <t>01018892998</t>
-  </si>
-  <si>
-    <t>gannatnasser8@gmail.com</t>
-  </si>
-  <si>
-    <t>Gannat Abd el Nasser</t>
-  </si>
-  <si>
-    <t>2026-03-16 15:38</t>
-  </si>
-  <si>
-    <t>+01122773746</t>
-  </si>
-  <si>
-    <t>begomego66@gmail.com</t>
-  </si>
-  <si>
-    <t>Begad Magdy Ali</t>
-  </si>
-  <si>
-    <t>2026-03-16 15:36</t>
-  </si>
-  <si>
-    <t>01062623490</t>
-  </si>
-  <si>
-    <t>omarzakaa1@gmail.com</t>
-  </si>
-  <si>
-    <t>omar zakaa</t>
-  </si>
-  <si>
-    <t>2026-03-16 17:23</t>
-  </si>
-  <si>
-    <t>01017803931</t>
-  </si>
-  <si>
-    <t>kokymzykm2007@gmail.com</t>
-  </si>
-  <si>
-    <t>Kenzy Mohamed</t>
-  </si>
-  <si>
-    <t>2026-03-16 17:52</t>
-  </si>
-  <si>
-    <t>01154109786</t>
-  </si>
-  <si>
-    <t>nadaaseleem@gmail.com</t>
-  </si>
-  <si>
-    <t>Nada Ahmed Seleem</t>
-  </si>
-  <si>
-    <t>2026-03-16 17:42</t>
-  </si>
-  <si>
-    <t>01017099170</t>
-  </si>
-  <si>
-    <t>joudhanynabil@gmail.com</t>
-  </si>
-  <si>
-    <t>joudy</t>
-  </si>
-  <si>
-    <t>01555066805</t>
-  </si>
-  <si>
-    <t>mohammed.el.shazly2009@gmail.com</t>
-  </si>
-  <si>
-    <t>محمد أسامة محمد الشاذلي</t>
-  </si>
-  <si>
-    <t>2026-03-16 18:48</t>
-  </si>
-  <si>
-    <t>01099284562</t>
-  </si>
-  <si>
-    <t>samehsami9@gmail.com</t>
-  </si>
-  <si>
-    <t>Mariam sameh sami</t>
-  </si>
-  <si>
-    <t>2026-03-16 19:12</t>
-  </si>
-  <si>
-    <t>01554037795</t>
-  </si>
-  <si>
-    <t>saharrefee@gmail.com</t>
-  </si>
-  <si>
-    <t>سهر محمد ابراهيم الرفاعي</t>
-  </si>
-  <si>
-    <t>2026-03-16 19:19</t>
-  </si>
-  <si>
-    <t>01064753790</t>
-  </si>
-  <si>
-    <t>Abdullazizosama18@gmail.com</t>
-  </si>
-  <si>
-    <t>Abdullaziz</t>
-  </si>
-  <si>
-    <t>2026-03-16 19:37</t>
-  </si>
-  <si>
-    <t>01094609026</t>
-  </si>
-  <si>
-    <t>sandyalylabib560@gmail.com</t>
-  </si>
-  <si>
-    <t>Sandy aly abdelmohsen</t>
-  </si>
-  <si>
-    <t>2026-03-18 13:14</t>
-  </si>
-  <si>
-    <t>0.0%</t>
-  </si>
-  <si>
-    <t>janafrahat@icloud.com</t>
-  </si>
-  <si>
-    <t>Jana Ahmed frahat</t>
-  </si>
-  <si>
-    <t>2026-03-25 07:58</t>
-  </si>
-  <si>
-    <t>01094303365</t>
-  </si>
-  <si>
-    <t>Yomnamelhabrouk@gmail.com</t>
-  </si>
-  <si>
-    <t>Yomna</t>
-  </si>
-  <si>
-    <t>2026-03-27 03:01</t>
-  </si>
-  <si>
-    <t>01103622316</t>
-  </si>
-  <si>
-    <t>esraassaaddd30@gmail.com</t>
-  </si>
-  <si>
-    <t>Esraa saad</t>
-  </si>
-  <si>
-    <t>2026-03-29 03:22</t>
-  </si>
-  <si>
-    <t>20.0%</t>
-  </si>
-  <si>
-    <t>01020123791</t>
-  </si>
-  <si>
-    <t>salmatareksoo17@gmail.com</t>
-  </si>
-  <si>
-    <t>Salma</t>
-  </si>
-  <si>
-    <t>2026-03-29 13:13</t>
-  </si>
-  <si>
-    <t>01501181314</t>
-  </si>
-  <si>
-    <t>bebonasser399@gamil.com</t>
-  </si>
-  <si>
-    <t>Habiba Nasser Ahmed</t>
-  </si>
-  <si>
-    <t>2026-03-30 15:59</t>
-  </si>
-  <si>
-    <t>01121970064</t>
-  </si>
-  <si>
-    <t>Ahmedmakg7@gmail.com</t>
-  </si>
-  <si>
-    <t>احمد محمد احمد كامل</t>
-  </si>
-  <si>
     <t>الحالة</t>
   </si>
   <si>
@@ -1046,7 +1082,7 @@
     <t>الدرجة الكاملة: 10 | درجة النجاح: 5.00</t>
   </si>
   <si>
-    <t>تاريخ التصدير: 2026-03-30 16:27</t>
+    <t>تاريخ التصدير: 2026-04-05 16:57</t>
   </si>
 </sst>
 </file>
@@ -1434,7 +1470,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:P85"/>
+  <dimension ref="A1:P88"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="true" style="0"/>
@@ -1457,67 +1493,67 @@
   <sheetData>
     <row r="1" spans="1:16">
       <c r="A1" s="3" t="s">
-        <v>341</v>
+        <v>353</v>
       </c>
     </row>
     <row r="2" spans="1:16">
       <c r="A2" s="3" t="s">
-        <v>342</v>
+        <v>354</v>
       </c>
     </row>
     <row r="3" spans="1:16">
       <c r="A3" s="3" t="s">
-        <v>343</v>
+        <v>355</v>
       </c>
     </row>
     <row r="4" spans="1:16">
       <c r="A4" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="M4" s="1" t="s">
         <v>340</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="N4" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="O4" s="1" t="s">
         <v>338</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="P4" s="1" t="s">
         <v>337</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>336</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>335</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>334</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>333</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>332</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>331</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>330</v>
-      </c>
-      <c r="L4" s="1" t="s">
-        <v>329</v>
-      </c>
-      <c r="M4" s="1" t="s">
-        <v>328</v>
-      </c>
-      <c r="N4" s="1" t="s">
-        <v>327</v>
-      </c>
-      <c r="O4" s="1" t="s">
-        <v>326</v>
-      </c>
-      <c r="P4" s="1" t="s">
-        <v>325</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1525,13 +1561,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>324</v>
+        <v>336</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>322</v>
+        <v>334</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>3</v>
@@ -1557,10 +1593,10 @@
         <v>5</v>
       </c>
       <c r="N5" s="2">
-        <v>1135.68</v>
+        <v>1.43</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="P5" s="2" t="s">
         <v>0</v>
@@ -1571,42 +1607,44 @@
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>320</v>
+        <v>332</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>319</v>
+        <v>331</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>318</v>
+        <v>330</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F6" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G6" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H6" s="2">
         <v>10.0</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="J6" s="2">
-        <v>5</v>
-      </c>
-      <c r="K6" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K6" s="2">
+        <v>1</v>
+      </c>
       <c r="L6" s="2"/>
       <c r="M6" s="2">
         <v>5</v>
       </c>
       <c r="N6" s="2">
-        <v>2.95</v>
+        <v>22.02</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>317</v>
+        <v>329</v>
       </c>
       <c r="P6" s="2" t="s">
         <v>0</v>
@@ -1617,13 +1655,13 @@
         <v>3</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>316</v>
+        <v>328</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>315</v>
+        <v>327</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>314</v>
+        <v>326</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>3</v>
@@ -1632,32 +1670,30 @@
         <v>1</v>
       </c>
       <c r="G7" s="2">
-        <v>2.0</v>
+        <v>10.0</v>
       </c>
       <c r="H7" s="2">
         <v>10.0</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>313</v>
+        <v>17</v>
       </c>
       <c r="J7" s="2">
-        <v>1</v>
-      </c>
-      <c r="K7" s="2">
-        <v>4</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K7" s="2"/>
       <c r="L7" s="2"/>
       <c r="M7" s="2">
         <v>5</v>
       </c>
       <c r="N7" s="2">
-        <v>0.58</v>
+        <v>16.1</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>312</v>
+        <v>325</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>168</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -1665,44 +1701,42 @@
         <v>4</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>311</v>
+        <v>324</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>310</v>
+        <v>323</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>309</v>
+        <v>322</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F8" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G8" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H8" s="2">
         <v>10.0</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="J8" s="2">
-        <v>4</v>
-      </c>
-      <c r="K8" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K8" s="2"/>
       <c r="L8" s="2"/>
       <c r="M8" s="2">
         <v>5</v>
       </c>
       <c r="N8" s="2">
-        <v>3.03</v>
+        <v>10.8</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>308</v>
+        <v>321</v>
       </c>
       <c r="P8" s="2" t="s">
         <v>0</v>
@@ -1713,42 +1747,44 @@
         <v>5</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>307</v>
+        <v>320</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>306</v>
+        <v>319</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>305</v>
+        <v>318</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F9" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G9" s="2">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
       <c r="H9" s="2">
         <v>10.0</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="J9" s="2">
-        <v>5</v>
-      </c>
-      <c r="K9" s="2"/>
+        <v>3</v>
+      </c>
+      <c r="K9" s="2">
+        <v>2</v>
+      </c>
       <c r="L9" s="2"/>
       <c r="M9" s="2">
         <v>5</v>
       </c>
       <c r="N9" s="2">
-        <v>10.22</v>
+        <v>9.78</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>304</v>
+        <v>317</v>
       </c>
       <c r="P9" s="2" t="s">
         <v>0</v>
@@ -1759,45 +1795,45 @@
         <v>6</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>303</v>
+        <v>316</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="D10" s="2">
-        <v>1159792350</v>
+        <v>315</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>314</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F10" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G10" s="2">
-        <v>0.0</v>
+        <v>10.0</v>
       </c>
       <c r="H10" s="2">
         <v>10.0</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="J10" s="2"/>
-      <c r="K10" s="2">
-        <v>5</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="J10" s="2">
+        <v>5</v>
+      </c>
+      <c r="K10" s="2"/>
       <c r="L10" s="2"/>
       <c r="M10" s="2">
         <v>5</v>
       </c>
       <c r="N10" s="2">
-        <v>1.63</v>
+        <v>1135.68</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>300</v>
+        <v>313</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>168</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -1805,13 +1841,13 @@
         <v>7</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>299</v>
+        <v>312</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>297</v>
+        <v>310</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>3</v>
@@ -1837,10 +1873,10 @@
         <v>5</v>
       </c>
       <c r="N11" s="2">
-        <v>1.92</v>
+        <v>2.95</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>296</v>
+        <v>309</v>
       </c>
       <c r="P11" s="2" t="s">
         <v>0</v>
@@ -1851,13 +1887,13 @@
         <v>8</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>295</v>
+        <v>308</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>294</v>
+        <v>307</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>293</v>
+        <v>306</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>3</v>
@@ -1866,32 +1902,32 @@
         <v>1</v>
       </c>
       <c r="G12" s="2">
-        <v>8.0</v>
+        <v>2.0</v>
       </c>
       <c r="H12" s="2">
         <v>10.0</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>12</v>
+        <v>305</v>
       </c>
       <c r="J12" s="2">
+        <v>1</v>
+      </c>
+      <c r="K12" s="2">
         <v>4</v>
-      </c>
-      <c r="K12" s="2">
-        <v>1</v>
       </c>
       <c r="L12" s="2"/>
       <c r="M12" s="2">
         <v>5</v>
       </c>
       <c r="N12" s="2">
-        <v>20.53</v>
+        <v>0.58</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>292</v>
+        <v>304</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>0</v>
+        <v>164</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -1899,19 +1935,19 @@
         <v>9</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>291</v>
+        <v>303</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>290</v>
+        <v>302</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>289</v>
+        <v>301</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F13" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G13" s="2">
         <v>8.0</v>
@@ -1933,10 +1969,10 @@
         <v>5</v>
       </c>
       <c r="N13" s="2">
-        <v>14.28</v>
+        <v>3.03</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>288</v>
+        <v>300</v>
       </c>
       <c r="P13" s="2" t="s">
         <v>0</v>
@@ -1947,13 +1983,13 @@
         <v>10</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>287</v>
+        <v>299</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>286</v>
+        <v>298</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>285</v>
+        <v>297</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>3</v>
@@ -1979,10 +2015,10 @@
         <v>5</v>
       </c>
       <c r="N14" s="2">
-        <v>27.77</v>
+        <v>10.22</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>284</v>
+        <v>296</v>
       </c>
       <c r="P14" s="2" t="s">
         <v>0</v>
@@ -1993,13 +2029,13 @@
         <v>11</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>283</v>
+        <v>295</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>281</v>
+        <v>294</v>
+      </c>
+      <c r="D15" s="2">
+        <v>1159792350</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>3</v>
@@ -2008,30 +2044,30 @@
         <v>1</v>
       </c>
       <c r="G15" s="2">
-        <v>10.0</v>
+        <v>0.0</v>
       </c>
       <c r="H15" s="2">
         <v>10.0</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J15" s="2">
-        <v>5</v>
-      </c>
-      <c r="K15" s="2"/>
+        <v>293</v>
+      </c>
+      <c r="J15" s="2"/>
+      <c r="K15" s="2">
+        <v>5</v>
+      </c>
       <c r="L15" s="2"/>
       <c r="M15" s="2">
         <v>5</v>
       </c>
       <c r="N15" s="2">
-        <v>15.2</v>
+        <v>1.63</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>273</v>
+        <v>292</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>0</v>
+        <v>164</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -2039,42 +2075,44 @@
         <v>12</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>280</v>
+        <v>291</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>279</v>
+        <v>290</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>278</v>
+        <v>289</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F16" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G16" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H16" s="2">
         <v>10.0</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="J16" s="2">
-        <v>5</v>
-      </c>
-      <c r="K16" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K16" s="2">
+        <v>1</v>
+      </c>
       <c r="L16" s="2"/>
       <c r="M16" s="2">
         <v>5</v>
       </c>
       <c r="N16" s="2">
-        <v>8.4</v>
+        <v>25734.55</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>277</v>
+        <v>288</v>
       </c>
       <c r="P16" s="2" t="s">
         <v>0</v>
@@ -2085,13 +2123,13 @@
         <v>13</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>276</v>
+        <v>287</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>275</v>
+        <v>286</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>274</v>
+        <v>285</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>3</v>
@@ -2100,27 +2138,29 @@
         <v>1</v>
       </c>
       <c r="G17" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H17" s="2">
         <v>10.0</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="J17" s="2">
-        <v>5</v>
-      </c>
-      <c r="K17" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K17" s="2">
+        <v>1</v>
+      </c>
       <c r="L17" s="2"/>
       <c r="M17" s="2">
         <v>5</v>
       </c>
       <c r="N17" s="2">
-        <v>29.9</v>
+        <v>14.28</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>273</v>
+        <v>284</v>
       </c>
       <c r="P17" s="2" t="s">
         <v>0</v>
@@ -2131,13 +2171,13 @@
         <v>14</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>272</v>
+        <v>283</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>271</v>
+        <v>282</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>270</v>
+        <v>281</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>3</v>
@@ -2163,10 +2203,10 @@
         <v>5</v>
       </c>
       <c r="N18" s="2">
-        <v>8.73</v>
+        <v>27.77</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>269</v>
+        <v>280</v>
       </c>
       <c r="P18" s="2" t="s">
         <v>0</v>
@@ -2177,13 +2217,13 @@
         <v>15</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>268</v>
+        <v>279</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>267</v>
+        <v>278</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>266</v>
+        <v>277</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>3</v>
@@ -2209,10 +2249,10 @@
         <v>5</v>
       </c>
       <c r="N19" s="2">
-        <v>2.92</v>
+        <v>15.2</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="P19" s="2" t="s">
         <v>0</v>
@@ -2223,13 +2263,13 @@
         <v>16</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>264</v>
+        <v>276</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>262</v>
+        <v>274</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>3</v>
@@ -2238,29 +2278,27 @@
         <v>1</v>
       </c>
       <c r="G20" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H20" s="2">
         <v>10.0</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="J20" s="2">
-        <v>4</v>
-      </c>
-      <c r="K20" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K20" s="2"/>
       <c r="L20" s="2"/>
       <c r="M20" s="2">
         <v>5</v>
       </c>
       <c r="N20" s="2">
-        <v>21.08</v>
+        <v>8.4</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="P20" s="2" t="s">
         <v>0</v>
@@ -2271,44 +2309,42 @@
         <v>17</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>260</v>
+        <v>272</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>258</v>
+        <v>270</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F21" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G21" s="2">
-        <v>6.0</v>
+        <v>10.0</v>
       </c>
       <c r="H21" s="2">
         <v>10.0</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="J21" s="2">
-        <v>3</v>
-      </c>
-      <c r="K21" s="2">
-        <v>2</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K21" s="2"/>
       <c r="L21" s="2"/>
       <c r="M21" s="2">
         <v>5</v>
       </c>
       <c r="N21" s="2">
-        <v>17.15</v>
+        <v>29.9</v>
       </c>
       <c r="O21" s="2" t="s">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="P21" s="2" t="s">
         <v>0</v>
@@ -2319,13 +2355,13 @@
         <v>18</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>256</v>
+        <v>268</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>255</v>
+        <v>267</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>254</v>
+        <v>266</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>3</v>
@@ -2351,10 +2387,10 @@
         <v>5</v>
       </c>
       <c r="N22" s="2">
-        <v>7.7</v>
+        <v>8.73</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>253</v>
+        <v>265</v>
       </c>
       <c r="P22" s="2" t="s">
         <v>0</v>
@@ -2365,13 +2401,13 @@
         <v>19</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>3</v>
@@ -2397,10 +2433,10 @@
         <v>5</v>
       </c>
       <c r="N23" s="2">
-        <v>21.45</v>
+        <v>2.92</v>
       </c>
       <c r="O23" s="2" t="s">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="P23" s="2" t="s">
         <v>0</v>
@@ -2411,13 +2447,13 @@
         <v>20</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>248</v>
+        <v>260</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>247</v>
+        <v>259</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>3</v>
@@ -2426,27 +2462,29 @@
         <v>1</v>
       </c>
       <c r="G24" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H24" s="2">
         <v>10.0</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="J24" s="2">
-        <v>5</v>
-      </c>
-      <c r="K24" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K24" s="2">
+        <v>1</v>
+      </c>
       <c r="L24" s="2"/>
       <c r="M24" s="2">
         <v>5</v>
       </c>
       <c r="N24" s="2">
-        <v>23.68</v>
+        <v>21.08</v>
       </c>
       <c r="O24" s="2" t="s">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="P24" s="2" t="s">
         <v>0</v>
@@ -2457,19 +2495,19 @@
         <v>21</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F25" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G25" s="2">
         <v>6.0</v>
@@ -2491,10 +2529,10 @@
         <v>5</v>
       </c>
       <c r="N25" s="2">
-        <v>7.7</v>
+        <v>17.15</v>
       </c>
       <c r="O25" s="2" t="s">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="P25" s="2" t="s">
         <v>0</v>
@@ -2505,13 +2543,13 @@
         <v>22</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>240</v>
+        <v>252</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>238</v>
+        <v>250</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>3</v>
@@ -2537,10 +2575,10 @@
         <v>5</v>
       </c>
       <c r="N26" s="2">
-        <v>18.78</v>
+        <v>7.7</v>
       </c>
       <c r="O26" s="2" t="s">
-        <v>237</v>
+        <v>249</v>
       </c>
       <c r="P26" s="2" t="s">
         <v>0</v>
@@ -2551,13 +2589,13 @@
         <v>23</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>3</v>
@@ -2566,29 +2604,27 @@
         <v>1</v>
       </c>
       <c r="G27" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H27" s="2">
         <v>10.0</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="J27" s="2">
-        <v>4</v>
-      </c>
-      <c r="K27" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K27" s="2"/>
       <c r="L27" s="2"/>
       <c r="M27" s="2">
         <v>5</v>
       </c>
       <c r="N27" s="2">
-        <v>4.37</v>
+        <v>21.45</v>
       </c>
       <c r="O27" s="2" t="s">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="P27" s="2" t="s">
         <v>0</v>
@@ -2599,44 +2635,42 @@
         <v>24</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>232</v>
+        <v>244</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>231</v>
+        <v>243</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>230</v>
+        <v>242</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F28" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G28" s="2">
-        <v>6.0</v>
+        <v>10.0</v>
       </c>
       <c r="H28" s="2">
         <v>10.0</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="J28" s="2">
-        <v>3</v>
-      </c>
-      <c r="K28" s="2">
-        <v>2</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K28" s="2"/>
       <c r="L28" s="2"/>
       <c r="M28" s="2">
         <v>5</v>
       </c>
       <c r="N28" s="2">
-        <v>0.48</v>
+        <v>23.68</v>
       </c>
       <c r="O28" s="2" t="s">
-        <v>229</v>
+        <v>241</v>
       </c>
       <c r="P28" s="2" t="s">
         <v>0</v>
@@ -2647,44 +2681,44 @@
         <v>25</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>228</v>
+        <v>240</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>227</v>
+        <v>239</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>226</v>
+        <v>238</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F29" s="2">
+        <v>1</v>
+      </c>
+      <c r="G29" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="H29" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I29" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="G29" s="2">
-        <v>8.0</v>
-      </c>
-      <c r="H29" s="2">
-        <v>10.0</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>12</v>
-      </c>
       <c r="J29" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K29" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L29" s="2"/>
       <c r="M29" s="2">
         <v>5</v>
       </c>
       <c r="N29" s="2">
-        <v>1.7</v>
+        <v>7.7</v>
       </c>
       <c r="O29" s="2" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="P29" s="2" t="s">
         <v>0</v>
@@ -2695,13 +2729,13 @@
         <v>26</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="D30" s="2">
-        <v>201118200153</v>
+        <v>235</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>234</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>3</v>
@@ -2710,29 +2744,27 @@
         <v>1</v>
       </c>
       <c r="G30" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H30" s="2">
         <v>10.0</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="J30" s="2">
-        <v>4</v>
-      </c>
-      <c r="K30" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K30" s="2"/>
       <c r="L30" s="2"/>
       <c r="M30" s="2">
         <v>5</v>
       </c>
       <c r="N30" s="2">
-        <v>2.15</v>
+        <v>18.78</v>
       </c>
       <c r="O30" s="2" t="s">
-        <v>222</v>
+        <v>233</v>
       </c>
       <c r="P30" s="2" t="s">
         <v>0</v>
@@ -2743,13 +2775,13 @@
         <v>27</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>219</v>
+        <v>230</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>3</v>
@@ -2758,27 +2790,29 @@
         <v>1</v>
       </c>
       <c r="G31" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H31" s="2">
         <v>10.0</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="J31" s="2">
-        <v>5</v>
-      </c>
-      <c r="K31" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K31" s="2">
+        <v>1</v>
+      </c>
       <c r="L31" s="2"/>
       <c r="M31" s="2">
         <v>5</v>
       </c>
       <c r="N31" s="2">
-        <v>3.83</v>
+        <v>4.37</v>
       </c>
       <c r="O31" s="2" t="s">
-        <v>218</v>
+        <v>229</v>
       </c>
       <c r="P31" s="2" t="s">
         <v>0</v>
@@ -2789,13 +2823,13 @@
         <v>28</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>216</v>
+        <v>227</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>215</v>
+        <v>226</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>3</v>
@@ -2804,29 +2838,29 @@
         <v>2</v>
       </c>
       <c r="G32" s="2">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
       <c r="H32" s="2">
         <v>10.0</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="J32" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K32" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L32" s="2"/>
       <c r="M32" s="2">
         <v>5</v>
       </c>
       <c r="N32" s="2">
-        <v>1.67</v>
+        <v>0.48</v>
       </c>
       <c r="O32" s="2" t="s">
-        <v>211</v>
+        <v>225</v>
       </c>
       <c r="P32" s="2" t="s">
         <v>0</v>
@@ -2837,19 +2871,19 @@
         <v>29</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>214</v>
+        <v>224</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>212</v>
+        <v>222</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F33" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G33" s="2">
         <v>8.0</v>
@@ -2871,10 +2905,10 @@
         <v>5</v>
       </c>
       <c r="N33" s="2">
-        <v>4.2</v>
+        <v>1.7</v>
       </c>
       <c r="O33" s="2" t="s">
-        <v>211</v>
+        <v>221</v>
       </c>
       <c r="P33" s="2" t="s">
         <v>0</v>
@@ -2885,42 +2919,44 @@
         <v>30</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>208</v>
+        <v>219</v>
+      </c>
+      <c r="D34" s="2">
+        <v>201118200153</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F34" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G34" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H34" s="2">
         <v>10.0</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="J34" s="2">
-        <v>5</v>
-      </c>
-      <c r="K34" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K34" s="2">
+        <v>1</v>
+      </c>
       <c r="L34" s="2"/>
       <c r="M34" s="2">
         <v>5</v>
       </c>
       <c r="N34" s="2">
-        <v>7.48</v>
+        <v>2.15</v>
       </c>
       <c r="O34" s="2" t="s">
-        <v>194</v>
+        <v>218</v>
       </c>
       <c r="P34" s="2" t="s">
         <v>0</v>
@@ -2931,13 +2967,13 @@
         <v>31</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>207</v>
+        <v>217</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>206</v>
+        <v>216</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>205</v>
+        <v>215</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>3</v>
@@ -2963,10 +2999,10 @@
         <v>5</v>
       </c>
       <c r="N35" s="2">
-        <v>12.57</v>
+        <v>3.83</v>
       </c>
       <c r="O35" s="2" t="s">
-        <v>194</v>
+        <v>214</v>
       </c>
       <c r="P35" s="2" t="s">
         <v>0</v>
@@ -2977,42 +3013,44 @@
         <v>32</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F36" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G36" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H36" s="2">
         <v>10.0</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="J36" s="2">
-        <v>5</v>
-      </c>
-      <c r="K36" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K36" s="2">
+        <v>1</v>
+      </c>
       <c r="L36" s="2"/>
       <c r="M36" s="2">
         <v>5</v>
       </c>
       <c r="N36" s="2">
-        <v>9.22</v>
+        <v>1.67</v>
       </c>
       <c r="O36" s="2" t="s">
-        <v>198</v>
+        <v>207</v>
       </c>
       <c r="P36" s="2" t="s">
         <v>0</v>
@@ -3023,13 +3061,13 @@
         <v>33</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>3</v>
@@ -3038,27 +3076,29 @@
         <v>1</v>
       </c>
       <c r="G37" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H37" s="2">
         <v>10.0</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="J37" s="2">
-        <v>5</v>
-      </c>
-      <c r="K37" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K37" s="2">
+        <v>1</v>
+      </c>
       <c r="L37" s="2"/>
       <c r="M37" s="2">
         <v>5</v>
       </c>
       <c r="N37" s="2">
-        <v>10.92</v>
+        <v>4.2</v>
       </c>
       <c r="O37" s="2" t="s">
-        <v>198</v>
+        <v>207</v>
       </c>
       <c r="P37" s="2" t="s">
         <v>0</v>
@@ -3069,44 +3109,42 @@
         <v>34</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F38" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G38" s="2">
-        <v>6.0</v>
+        <v>10.0</v>
       </c>
       <c r="H38" s="2">
         <v>10.0</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="J38" s="2">
-        <v>3</v>
-      </c>
-      <c r="K38" s="2">
-        <v>2</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K38" s="2"/>
       <c r="L38" s="2"/>
       <c r="M38" s="2">
         <v>5</v>
       </c>
       <c r="N38" s="2">
-        <v>19.3</v>
+        <v>7.48</v>
       </c>
       <c r="O38" s="2" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="P38" s="2" t="s">
         <v>0</v>
@@ -3117,13 +3155,13 @@
         <v>35</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>192</v>
+        <v>202</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>3</v>
@@ -3149,7 +3187,7 @@
         <v>5</v>
       </c>
       <c r="N39" s="2">
-        <v>27.43</v>
+        <v>12.57</v>
       </c>
       <c r="O39" s="2" t="s">
         <v>190</v>
@@ -3163,13 +3201,13 @@
         <v>36</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>189</v>
+        <v>200</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>188</v>
+        <v>199</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>187</v>
+        <v>198</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>3</v>
@@ -3195,10 +3233,10 @@
         <v>5</v>
       </c>
       <c r="N40" s="2">
-        <v>3.58</v>
+        <v>9.22</v>
       </c>
       <c r="O40" s="2" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="P40" s="2" t="s">
         <v>0</v>
@@ -3209,13 +3247,13 @@
         <v>37</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>3</v>
@@ -3224,29 +3262,27 @@
         <v>1</v>
       </c>
       <c r="G41" s="2">
-        <v>6.0</v>
+        <v>10.0</v>
       </c>
       <c r="H41" s="2">
         <v>10.0</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="J41" s="2">
-        <v>3</v>
-      </c>
-      <c r="K41" s="2">
-        <v>2</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K41" s="2"/>
       <c r="L41" s="2"/>
       <c r="M41" s="2">
         <v>5</v>
       </c>
       <c r="N41" s="2">
-        <v>14.85</v>
+        <v>10.92</v>
       </c>
       <c r="O41" s="2" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="P41" s="2" t="s">
         <v>0</v>
@@ -3257,13 +3293,13 @@
         <v>38</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>3</v>
@@ -3272,27 +3308,29 @@
         <v>1</v>
       </c>
       <c r="G42" s="2">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
       <c r="H42" s="2">
         <v>10.0</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="J42" s="2">
-        <v>5</v>
-      </c>
-      <c r="K42" s="2"/>
+        <v>3</v>
+      </c>
+      <c r="K42" s="2">
+        <v>2</v>
+      </c>
       <c r="L42" s="2"/>
       <c r="M42" s="2">
         <v>5</v>
       </c>
       <c r="N42" s="2">
-        <v>5.42</v>
+        <v>19.3</v>
       </c>
       <c r="O42" s="2" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="P42" s="2" t="s">
         <v>0</v>
@@ -3303,13 +3341,13 @@
         <v>39</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>177</v>
+        <v>189</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>176</v>
+        <v>188</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>3</v>
@@ -3335,10 +3373,10 @@
         <v>5</v>
       </c>
       <c r="N43" s="2">
-        <v>8.33</v>
+        <v>27.43</v>
       </c>
       <c r="O43" s="2" t="s">
-        <v>174</v>
+        <v>186</v>
       </c>
       <c r="P43" s="2" t="s">
         <v>0</v>
@@ -3349,13 +3387,13 @@
         <v>40</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>172</v>
+        <v>184</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>171</v>
+        <v>183</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>3</v>
@@ -3364,32 +3402,30 @@
         <v>1</v>
       </c>
       <c r="G44" s="2">
-        <v>4.0</v>
+        <v>10.0</v>
       </c>
       <c r="H44" s="2">
         <v>10.0</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>170</v>
+        <v>17</v>
       </c>
       <c r="J44" s="2">
-        <v>2</v>
-      </c>
-      <c r="K44" s="2">
-        <v>3</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K44" s="2"/>
       <c r="L44" s="2"/>
       <c r="M44" s="2">
         <v>5</v>
       </c>
       <c r="N44" s="2">
-        <v>1.5</v>
+        <v>3.58</v>
       </c>
       <c r="O44" s="2" t="s">
-        <v>169</v>
+        <v>182</v>
       </c>
       <c r="P44" s="2" t="s">
-        <v>168</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -3397,13 +3433,13 @@
         <v>41</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>167</v>
+        <v>181</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>166</v>
+        <v>180</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>165</v>
+        <v>179</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>3</v>
@@ -3412,29 +3448,29 @@
         <v>1</v>
       </c>
       <c r="G45" s="2">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
       <c r="H45" s="2">
         <v>10.0</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="J45" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K45" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L45" s="2"/>
       <c r="M45" s="2">
         <v>5</v>
       </c>
       <c r="N45" s="2">
-        <v>6.75</v>
+        <v>14.85</v>
       </c>
       <c r="O45" s="2" t="s">
-        <v>161</v>
+        <v>178</v>
       </c>
       <c r="P45" s="2" t="s">
         <v>0</v>
@@ -3445,13 +3481,13 @@
         <v>42</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>164</v>
+        <v>177</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>163</v>
+        <v>176</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>162</v>
+        <v>175</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>3</v>
@@ -3460,29 +3496,27 @@
         <v>1</v>
       </c>
       <c r="G46" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H46" s="2">
         <v>10.0</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="J46" s="2">
-        <v>4</v>
-      </c>
-      <c r="K46" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K46" s="2"/>
       <c r="L46" s="2"/>
       <c r="M46" s="2">
         <v>5</v>
       </c>
       <c r="N46" s="2">
-        <v>8.65</v>
+        <v>5.42</v>
       </c>
       <c r="O46" s="2" t="s">
-        <v>161</v>
+        <v>174</v>
       </c>
       <c r="P46" s="2" t="s">
         <v>0</v>
@@ -3493,13 +3527,13 @@
         <v>43</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>160</v>
+        <v>173</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>159</v>
+        <v>172</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>158</v>
+        <v>171</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>3</v>
@@ -3525,10 +3559,10 @@
         <v>5</v>
       </c>
       <c r="N47" s="2">
-        <v>10.37</v>
+        <v>8.33</v>
       </c>
       <c r="O47" s="2" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
       <c r="P47" s="2" t="s">
         <v>0</v>
@@ -3539,13 +3573,13 @@
         <v>44</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>154</v>
+        <v>167</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>3</v>
@@ -3554,30 +3588,32 @@
         <v>1</v>
       </c>
       <c r="G48" s="2">
-        <v>10.0</v>
+        <v>4.0</v>
       </c>
       <c r="H48" s="2">
         <v>10.0</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>17</v>
+        <v>166</v>
       </c>
       <c r="J48" s="2">
-        <v>5</v>
-      </c>
-      <c r="K48" s="2"/>
+        <v>2</v>
+      </c>
+      <c r="K48" s="2">
+        <v>3</v>
+      </c>
       <c r="L48" s="2"/>
       <c r="M48" s="2">
         <v>5</v>
       </c>
       <c r="N48" s="2">
-        <v>7.27</v>
+        <v>1.5</v>
       </c>
       <c r="O48" s="2" t="s">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="P48" s="2" t="s">
-        <v>0</v>
+        <v>164</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -3585,13 +3621,13 @@
         <v>45</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>152</v>
+        <v>163</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>151</v>
+        <v>162</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>3</v>
@@ -3600,27 +3636,29 @@
         <v>1</v>
       </c>
       <c r="G49" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H49" s="2">
         <v>10.0</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="J49" s="2">
-        <v>5</v>
-      </c>
-      <c r="K49" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K49" s="2">
+        <v>1</v>
+      </c>
       <c r="L49" s="2"/>
       <c r="M49" s="2">
         <v>5</v>
       </c>
       <c r="N49" s="2">
-        <v>4.2</v>
+        <v>6.75</v>
       </c>
       <c r="O49" s="2" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="P49" s="2" t="s">
         <v>0</v>
@@ -3631,13 +3669,13 @@
         <v>46</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>148</v>
+        <v>160</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>146</v>
+        <v>158</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>3</v>
@@ -3665,10 +3703,10 @@
         <v>5</v>
       </c>
       <c r="N50" s="2">
-        <v>25.47</v>
+        <v>8.65</v>
       </c>
       <c r="O50" s="2" t="s">
-        <v>145</v>
+        <v>157</v>
       </c>
       <c r="P50" s="2" t="s">
         <v>0</v>
@@ -3679,13 +3717,13 @@
         <v>47</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>144</v>
+        <v>156</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>143</v>
+        <v>155</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>142</v>
+        <v>154</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>3</v>
@@ -3694,29 +3732,27 @@
         <v>1</v>
       </c>
       <c r="G51" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H51" s="2">
         <v>10.0</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="J51" s="2">
-        <v>4</v>
-      </c>
-      <c r="K51" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K51" s="2"/>
       <c r="L51" s="2"/>
       <c r="M51" s="2">
         <v>5</v>
       </c>
       <c r="N51" s="2">
-        <v>16.42</v>
+        <v>10.37</v>
       </c>
       <c r="O51" s="2" t="s">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="P51" s="2" t="s">
         <v>0</v>
@@ -3727,13 +3763,13 @@
         <v>48</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>140</v>
+        <v>152</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>3</v>
@@ -3759,10 +3795,10 @@
         <v>5</v>
       </c>
       <c r="N52" s="2">
-        <v>20.63</v>
+        <v>7.27</v>
       </c>
       <c r="O52" s="2" t="s">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="P52" s="2" t="s">
         <v>0</v>
@@ -3773,13 +3809,13 @@
         <v>49</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>3</v>
@@ -3805,10 +3841,10 @@
         <v>5</v>
       </c>
       <c r="N53" s="2">
-        <v>5.73</v>
+        <v>4.2</v>
       </c>
       <c r="O53" s="2" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="P53" s="2" t="s">
         <v>0</v>
@@ -3819,13 +3855,13 @@
         <v>50</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>3</v>
@@ -3834,27 +3870,29 @@
         <v>1</v>
       </c>
       <c r="G54" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H54" s="2">
         <v>10.0</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="J54" s="2">
-        <v>5</v>
-      </c>
-      <c r="K54" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K54" s="2">
+        <v>1</v>
+      </c>
       <c r="L54" s="2"/>
       <c r="M54" s="2">
         <v>5</v>
       </c>
       <c r="N54" s="2">
-        <v>3.98</v>
+        <v>25.47</v>
       </c>
       <c r="O54" s="2" t="s">
-        <v>129</v>
+        <v>141</v>
       </c>
       <c r="P54" s="2" t="s">
         <v>0</v>
@@ -3865,13 +3903,13 @@
         <v>51</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>127</v>
+        <v>139</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>3</v>
@@ -3899,10 +3937,10 @@
         <v>5</v>
       </c>
       <c r="N55" s="2">
-        <v>7.77</v>
+        <v>16.42</v>
       </c>
       <c r="O55" s="2" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="P55" s="2" t="s">
         <v>0</v>
@@ -3913,13 +3951,13 @@
         <v>52</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>3</v>
@@ -3945,10 +3983,10 @@
         <v>5</v>
       </c>
       <c r="N56" s="2">
-        <v>24.08</v>
+        <v>20.63</v>
       </c>
       <c r="O56" s="2" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="P56" s="2" t="s">
         <v>0</v>
@@ -3959,13 +3997,13 @@
         <v>53</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>3</v>
@@ -3991,10 +4029,10 @@
         <v>5</v>
       </c>
       <c r="N57" s="2">
-        <v>14.05</v>
+        <v>5.73</v>
       </c>
       <c r="O57" s="2" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="P57" s="2" t="s">
         <v>0</v>
@@ -4005,13 +4043,13 @@
         <v>54</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>3</v>
@@ -4020,29 +4058,27 @@
         <v>1</v>
       </c>
       <c r="G58" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H58" s="2">
         <v>10.0</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="J58" s="2">
-        <v>4</v>
-      </c>
-      <c r="K58" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K58" s="2"/>
       <c r="L58" s="2"/>
       <c r="M58" s="2">
         <v>5</v>
       </c>
       <c r="N58" s="2">
-        <v>10.78</v>
+        <v>3.98</v>
       </c>
       <c r="O58" s="2" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="P58" s="2" t="s">
         <v>0</v>
@@ -4053,13 +4089,13 @@
         <v>55</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>3</v>
@@ -4087,10 +4123,10 @@
         <v>5</v>
       </c>
       <c r="N59" s="2">
-        <v>2.48</v>
+        <v>7.77</v>
       </c>
       <c r="O59" s="2" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="P59" s="2" t="s">
         <v>0</v>
@@ -4101,13 +4137,13 @@
         <v>56</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>3</v>
@@ -4116,29 +4152,27 @@
         <v>1</v>
       </c>
       <c r="G60" s="2">
-        <v>6.0</v>
+        <v>10.0</v>
       </c>
       <c r="H60" s="2">
         <v>10.0</v>
       </c>
       <c r="I60" s="2" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="J60" s="2">
-        <v>3</v>
-      </c>
-      <c r="K60" s="2">
-        <v>2</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K60" s="2"/>
       <c r="L60" s="2"/>
       <c r="M60" s="2">
         <v>5</v>
       </c>
       <c r="N60" s="2">
-        <v>8.05</v>
+        <v>24.08</v>
       </c>
       <c r="O60" s="2" t="s">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="P60" s="2" t="s">
         <v>0</v>
@@ -4149,13 +4183,13 @@
         <v>57</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>3</v>
@@ -4181,10 +4215,10 @@
         <v>5</v>
       </c>
       <c r="N61" s="2">
-        <v>32.08</v>
+        <v>14.05</v>
       </c>
       <c r="O61" s="2" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="P61" s="2" t="s">
         <v>0</v>
@@ -4195,13 +4229,13 @@
         <v>58</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>3</v>
@@ -4210,27 +4244,29 @@
         <v>1</v>
       </c>
       <c r="G62" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H62" s="2">
         <v>10.0</v>
       </c>
       <c r="I62" s="2" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="J62" s="2">
-        <v>5</v>
-      </c>
-      <c r="K62" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K62" s="2">
+        <v>1</v>
+      </c>
       <c r="L62" s="2"/>
       <c r="M62" s="2">
         <v>5</v>
       </c>
       <c r="N62" s="2">
-        <v>2.35</v>
+        <v>10.78</v>
       </c>
       <c r="O62" s="2" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="P62" s="2" t="s">
         <v>0</v>
@@ -4241,13 +4277,13 @@
         <v>59</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>3</v>
@@ -4256,27 +4292,29 @@
         <v>1</v>
       </c>
       <c r="G63" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H63" s="2">
         <v>10.0</v>
       </c>
       <c r="I63" s="2" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="J63" s="2">
-        <v>5</v>
-      </c>
-      <c r="K63" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K63" s="2">
+        <v>1</v>
+      </c>
       <c r="L63" s="2"/>
       <c r="M63" s="2">
         <v>5</v>
       </c>
       <c r="N63" s="2">
-        <v>299.45</v>
+        <v>2.48</v>
       </c>
       <c r="O63" s="2" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="P63" s="2" t="s">
         <v>0</v>
@@ -4287,13 +4325,13 @@
         <v>60</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>3</v>
@@ -4302,27 +4340,29 @@
         <v>1</v>
       </c>
       <c r="G64" s="2">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
       <c r="H64" s="2">
         <v>10.0</v>
       </c>
       <c r="I64" s="2" t="s">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="J64" s="2">
-        <v>5</v>
-      </c>
-      <c r="K64" s="2"/>
+        <v>3</v>
+      </c>
+      <c r="K64" s="2">
+        <v>2</v>
+      </c>
       <c r="L64" s="2"/>
       <c r="M64" s="2">
         <v>5</v>
       </c>
       <c r="N64" s="2">
-        <v>9.7</v>
+        <v>8.05</v>
       </c>
       <c r="O64" s="2" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="P64" s="2" t="s">
         <v>0</v>
@@ -4333,13 +4373,13 @@
         <v>61</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>3</v>
@@ -4365,10 +4405,10 @@
         <v>5</v>
       </c>
       <c r="N65" s="2">
-        <v>26.22</v>
+        <v>32.08</v>
       </c>
       <c r="O65" s="2" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="P65" s="2" t="s">
         <v>0</v>
@@ -4379,13 +4419,13 @@
         <v>62</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>3</v>
@@ -4411,10 +4451,10 @@
         <v>5</v>
       </c>
       <c r="N66" s="2">
-        <v>1.18</v>
+        <v>2.35</v>
       </c>
       <c r="O66" s="2" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="P66" s="2" t="s">
         <v>0</v>
@@ -4425,13 +4465,13 @@
         <v>63</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>3</v>
@@ -4457,10 +4497,10 @@
         <v>5</v>
       </c>
       <c r="N67" s="2">
-        <v>26.28</v>
+        <v>299.45</v>
       </c>
       <c r="O67" s="2" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="P67" s="2" t="s">
         <v>0</v>
@@ -4471,13 +4511,13 @@
         <v>64</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="E68" s="2" t="s">
         <v>3</v>
@@ -4503,10 +4543,10 @@
         <v>5</v>
       </c>
       <c r="N68" s="2">
-        <v>11.17</v>
+        <v>9.7</v>
       </c>
       <c r="O68" s="2" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="P68" s="2" t="s">
         <v>0</v>
@@ -4517,13 +4557,13 @@
         <v>65</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>3</v>
@@ -4549,10 +4589,10 @@
         <v>5</v>
       </c>
       <c r="N69" s="2">
-        <v>10.05</v>
+        <v>26.22</v>
       </c>
       <c r="O69" s="2" t="s">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="P69" s="2" t="s">
         <v>0</v>
@@ -4563,13 +4603,13 @@
         <v>66</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>3</v>
@@ -4595,10 +4635,10 @@
         <v>5</v>
       </c>
       <c r="N70" s="2">
-        <v>1507.62</v>
+        <v>26.28</v>
       </c>
       <c r="O70" s="2" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="P70" s="2" t="s">
         <v>0</v>
@@ -4609,13 +4649,13 @@
         <v>67</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>3</v>
@@ -4624,29 +4664,27 @@
         <v>1</v>
       </c>
       <c r="G71" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H71" s="2">
         <v>10.0</v>
       </c>
       <c r="I71" s="2" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="J71" s="2">
-        <v>4</v>
-      </c>
-      <c r="K71" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K71" s="2"/>
       <c r="L71" s="2"/>
       <c r="M71" s="2">
         <v>5</v>
       </c>
       <c r="N71" s="2">
-        <v>6.08</v>
+        <v>11.17</v>
       </c>
       <c r="O71" s="2" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="P71" s="2" t="s">
         <v>0</v>
@@ -4657,13 +4695,13 @@
         <v>68</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>3</v>
@@ -4689,10 +4727,10 @@
         <v>5</v>
       </c>
       <c r="N72" s="2">
-        <v>1.93</v>
+        <v>10.05</v>
       </c>
       <c r="O72" s="2" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="P72" s="2" t="s">
         <v>0</v>
@@ -4703,13 +4741,13 @@
         <v>69</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>3</v>
@@ -4735,10 +4773,10 @@
         <v>5</v>
       </c>
       <c r="N73" s="2">
-        <v>11.58</v>
+        <v>1507.62</v>
       </c>
       <c r="O73" s="2" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="P73" s="2" t="s">
         <v>0</v>
@@ -4749,13 +4787,13 @@
         <v>70</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>3</v>
@@ -4764,27 +4802,29 @@
         <v>1</v>
       </c>
       <c r="G74" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H74" s="2">
         <v>10.0</v>
       </c>
       <c r="I74" s="2" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="J74" s="2">
-        <v>5</v>
-      </c>
-      <c r="K74" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K74" s="2">
+        <v>1</v>
+      </c>
       <c r="L74" s="2"/>
       <c r="M74" s="2">
         <v>5</v>
       </c>
       <c r="N74" s="2">
-        <v>25.92</v>
+        <v>6.08</v>
       </c>
       <c r="O74" s="2" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="P74" s="2" t="s">
         <v>0</v>
@@ -4795,13 +4835,13 @@
         <v>71</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>3</v>
@@ -4810,29 +4850,27 @@
         <v>1</v>
       </c>
       <c r="G75" s="2">
-        <v>6.0</v>
+        <v>10.0</v>
       </c>
       <c r="H75" s="2">
         <v>10.0</v>
       </c>
       <c r="I75" s="2" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="J75" s="2">
-        <v>3</v>
-      </c>
-      <c r="K75" s="2">
-        <v>2</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K75" s="2"/>
       <c r="L75" s="2"/>
       <c r="M75" s="2">
         <v>5</v>
       </c>
       <c r="N75" s="2">
-        <v>25.67</v>
+        <v>1.93</v>
       </c>
       <c r="O75" s="2" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="P75" s="2" t="s">
         <v>0</v>
@@ -4843,13 +4881,13 @@
         <v>72</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="E76" s="2" t="s">
         <v>3</v>
@@ -4858,29 +4896,27 @@
         <v>1</v>
       </c>
       <c r="G76" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H76" s="2">
         <v>10.0</v>
       </c>
       <c r="I76" s="2" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="J76" s="2">
-        <v>4</v>
-      </c>
-      <c r="K76" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K76" s="2"/>
       <c r="L76" s="2"/>
       <c r="M76" s="2">
         <v>5</v>
       </c>
       <c r="N76" s="2">
-        <v>5.32</v>
+        <v>11.58</v>
       </c>
       <c r="O76" s="2" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="P76" s="2" t="s">
         <v>0</v>
@@ -4891,13 +4927,13 @@
         <v>73</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="E77" s="2" t="s">
         <v>3</v>
@@ -4923,10 +4959,10 @@
         <v>5</v>
       </c>
       <c r="N77" s="2">
-        <v>32.9</v>
+        <v>25.92</v>
       </c>
       <c r="O77" s="2" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="P77" s="2" t="s">
         <v>0</v>
@@ -4937,13 +4973,13 @@
         <v>74</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="E78" s="2" t="s">
         <v>3</v>
@@ -4952,27 +4988,29 @@
         <v>1</v>
       </c>
       <c r="G78" s="2">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
       <c r="H78" s="2">
         <v>10.0</v>
       </c>
       <c r="I78" s="2" t="s">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="J78" s="2">
-        <v>5</v>
-      </c>
-      <c r="K78" s="2"/>
+        <v>3</v>
+      </c>
+      <c r="K78" s="2">
+        <v>2</v>
+      </c>
       <c r="L78" s="2"/>
       <c r="M78" s="2">
         <v>5</v>
       </c>
       <c r="N78" s="2">
-        <v>3.77</v>
+        <v>25.67</v>
       </c>
       <c r="O78" s="2" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="P78" s="2" t="s">
         <v>0</v>
@@ -4983,42 +5021,44 @@
         <v>75</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="E79" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F79" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G79" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H79" s="2">
         <v>10.0</v>
       </c>
       <c r="I79" s="2" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="J79" s="2">
-        <v>5</v>
-      </c>
-      <c r="K79" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K79" s="2">
+        <v>1</v>
+      </c>
       <c r="L79" s="2"/>
       <c r="M79" s="2">
         <v>5</v>
       </c>
       <c r="N79" s="2">
-        <v>1.65</v>
+        <v>5.32</v>
       </c>
       <c r="O79" s="2" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="P79" s="2" t="s">
         <v>0</v>
@@ -5029,44 +5069,42 @@
         <v>76</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="E80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F80" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G80" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H80" s="2">
         <v>10.0</v>
       </c>
       <c r="I80" s="2" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="J80" s="2">
-        <v>4</v>
-      </c>
-      <c r="K80" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K80" s="2"/>
       <c r="L80" s="2"/>
       <c r="M80" s="2">
         <v>5</v>
       </c>
       <c r="N80" s="2">
-        <v>4.22</v>
+        <v>32.9</v>
       </c>
       <c r="O80" s="2" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="P80" s="2" t="s">
         <v>0</v>
@@ -5077,13 +5115,13 @@
         <v>77</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>3</v>
@@ -5092,29 +5130,27 @@
         <v>1</v>
       </c>
       <c r="G81" s="2">
-        <v>6.0</v>
+        <v>10.0</v>
       </c>
       <c r="H81" s="2">
         <v>10.0</v>
       </c>
       <c r="I81" s="2" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="J81" s="2">
-        <v>3</v>
-      </c>
-      <c r="K81" s="2">
-        <v>2</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K81" s="2"/>
       <c r="L81" s="2"/>
       <c r="M81" s="2">
         <v>5</v>
       </c>
       <c r="N81" s="2">
-        <v>23.22</v>
+        <v>3.77</v>
       </c>
       <c r="O81" s="2" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="P81" s="2" t="s">
         <v>0</v>
@@ -5125,19 +5161,19 @@
         <v>78</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="E82" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F82" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G82" s="2">
         <v>10.0</v>
@@ -5157,10 +5193,10 @@
         <v>5</v>
       </c>
       <c r="N82" s="2">
-        <v>14.3</v>
+        <v>1.65</v>
       </c>
       <c r="O82" s="2" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="P82" s="2" t="s">
         <v>0</v>
@@ -5171,19 +5207,19 @@
         <v>79</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="E83" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F83" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G83" s="2">
         <v>8.0</v>
@@ -5205,10 +5241,10 @@
         <v>5</v>
       </c>
       <c r="N83" s="2">
-        <v>13.45</v>
+        <v>4.22</v>
       </c>
       <c r="O83" s="2" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="P83" s="2" t="s">
         <v>0</v>
@@ -5219,19 +5255,19 @@
         <v>80</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="E84" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F84" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G84" s="2">
         <v>6.0</v>
@@ -5253,10 +5289,10 @@
         <v>5</v>
       </c>
       <c r="N84" s="2">
-        <v>9179.12</v>
+        <v>23.22</v>
       </c>
       <c r="O84" s="2" t="s">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="P84" s="2" t="s">
         <v>0</v>
@@ -5267,13 +5303,13 @@
         <v>81</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="E85" s="2" t="s">
         <v>3</v>
@@ -5282,31 +5318,173 @@
         <v>1</v>
       </c>
       <c r="G85" s="2">
-        <v>6.0</v>
+        <v>10.0</v>
       </c>
       <c r="H85" s="2">
         <v>10.0</v>
       </c>
       <c r="I85" s="2" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="J85" s="2">
-        <v>3</v>
-      </c>
-      <c r="K85" s="2">
-        <v>2</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K85" s="2"/>
       <c r="L85" s="2"/>
       <c r="M85" s="2">
         <v>5</v>
       </c>
       <c r="N85" s="2">
+        <v>14.3</v>
+      </c>
+      <c r="O85" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="P85" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:16">
+      <c r="A86" s="2">
+        <v>82</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E86" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F86" s="2">
+        <v>1</v>
+      </c>
+      <c r="G86" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="H86" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I86" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="J86" s="2">
+        <v>4</v>
+      </c>
+      <c r="K86" s="2">
+        <v>1</v>
+      </c>
+      <c r="L86" s="2"/>
+      <c r="M86" s="2">
+        <v>5</v>
+      </c>
+      <c r="N86" s="2">
+        <v>13.45</v>
+      </c>
+      <c r="O86" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="P86" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:16">
+      <c r="A87" s="2">
+        <v>83</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E87" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F87" s="2">
+        <v>2</v>
+      </c>
+      <c r="G87" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="H87" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I87" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J87" s="2">
+        <v>3</v>
+      </c>
+      <c r="K87" s="2">
+        <v>2</v>
+      </c>
+      <c r="L87" s="2"/>
+      <c r="M87" s="2">
+        <v>5</v>
+      </c>
+      <c r="N87" s="2">
+        <v>9179.12</v>
+      </c>
+      <c r="O87" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="P87" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:16">
+      <c r="A88" s="2">
+        <v>84</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E88" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F88" s="2">
+        <v>1</v>
+      </c>
+      <c r="G88" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="H88" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I88" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J88" s="2">
+        <v>3</v>
+      </c>
+      <c r="K88" s="2">
+        <v>2</v>
+      </c>
+      <c r="L88" s="2"/>
+      <c r="M88" s="2">
+        <v>5</v>
+      </c>
+      <c r="N88" s="2">
         <v>5.32</v>
       </c>
-      <c r="O85" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="P85" s="2" t="s">
+      <c r="O88" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="P88" s="2" t="s">
         <v>0</v>
       </c>
     </row>

--- a/2lit_center.xlsx
+++ b/2lit_center.xlsx
@@ -1082,7 +1082,7 @@
     <t>الدرجة الكاملة: 10 | درجة النجاح: 5.00</t>
   </si>
   <si>
-    <t>تاريخ التصدير: 2026-04-05 16:57</t>
+    <t>تاريخ التصدير: 2026-04-05 17:08</t>
   </si>
 </sst>
 </file>

--- a/2lit_center.xlsx
+++ b/2lit_center.xlsx
@@ -1082,7 +1082,7 @@
     <t>الدرجة الكاملة: 10 | درجة النجاح: 5.00</t>
   </si>
   <si>
-    <t>تاريخ التصدير: 2026-04-05 17:08</t>
+    <t>تاريخ التصدير: 2026-04-05 17:45</t>
   </si>
 </sst>
 </file>

--- a/2lit_center.xlsx
+++ b/2lit_center.xlsx
@@ -1082,7 +1082,7 @@
     <t>الدرجة الكاملة: 10 | درجة النجاح: 5.00</t>
   </si>
   <si>
-    <t>تاريخ التصدير: 2026-04-05 17:45</t>
+    <t>تاريخ التصدير: 2026-04-06 16:50</t>
   </si>
 </sst>
 </file>
